--- a/source/bin/excel/mall.xlsx
+++ b/source/bin/excel/mall.xlsx
@@ -1,24 +1,24 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="28925"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29231"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\liqi-excel\data\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Work\Git\liqi-excel\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A0A4E5C3-DC4D-4C7C-BA22-B2D97AFC22E2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C60EB59E-FF90-4E15-9819-D73FF874A83D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="28110" windowHeight="16440" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="export" sheetId="2" r:id="rId1"/>
     <sheet name="month_ticket" sheetId="9" r:id="rId2"/>
     <sheet name="month_ticket_info" sheetId="11" r:id="rId3"/>
     <sheet name="goods" sheetId="1" r:id="rId4"/>
-    <sheet name="zone_params" sheetId="7" r:id="rId5"/>
-    <sheet name="product" sheetId="3" r:id="rId6"/>
+    <sheet name="product" sheetId="3" r:id="rId5"/>
+    <sheet name="zone_params" sheetId="7" r:id="rId6"/>
     <sheet name="goods_shelves" sheetId="6" r:id="rId7"/>
     <sheet name="channel_config" sheetId="10" r:id="rId8"/>
     <sheet name="支付平台" sheetId="5" r:id="rId9"/>
@@ -26,7 +26,7 @@
     <sheet name="区域参数说明" sheetId="8" r:id="rId11"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">product!$B$1:$B$665</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">product!$B$1:$B$665</definedName>
   </definedNames>
   <calcPr calcId="181029"/>
 </workbook>
@@ -60,7 +60,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4569" uniqueCount="1729">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4602" uniqueCount="1737">
   <si>
     <t>sheet</t>
   </si>
@@ -9034,16 +9034,47 @@
     <t>2025-08-20 08:00+08</t>
     <phoneticPr fontId="27" type="noConversion"/>
   </si>
+  <si>
+    <t>₩1,500</t>
+    <phoneticPr fontId="27" type="noConversion"/>
+  </si>
+  <si>
+    <t>₩7,500</t>
+    <phoneticPr fontId="27" type="noConversion"/>
+  </si>
+  <si>
+    <t>₩12,000</t>
+    <phoneticPr fontId="27" type="noConversion"/>
+  </si>
+  <si>
+    <t>₩23,000</t>
+    <phoneticPr fontId="27" type="noConversion"/>
+  </si>
+  <si>
+    <t>₩30,000</t>
+    <phoneticPr fontId="27" type="noConversion"/>
+  </si>
+  <si>
+    <t>₩45,000</t>
+    <phoneticPr fontId="27" type="noConversion"/>
+  </si>
+  <si>
+    <t>₩60,000</t>
+    <phoneticPr fontId="27" type="noConversion"/>
+  </si>
+  <si>
+    <t>₩119,000</t>
+    <phoneticPr fontId="27" type="noConversion"/>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="4">
+  <numFmts count="3">
     <numFmt numFmtId="44" formatCode="_ &quot;¥&quot;* #,##0.00_ ;_ &quot;¥&quot;* \-#,##0.00_ ;_ &quot;¥&quot;* &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="176" formatCode="0;[Red]0"/>
     <numFmt numFmtId="177" formatCode="\¥#,##0;[Red]\¥\-#,##0"/>
-    <numFmt numFmtId="178" formatCode="[$₩-412]#,##0;[Red][$₩-412]#,##0"/>
   </numFmts>
   <fonts count="42">
     <font>
@@ -9602,9 +9633,6 @@
     </xf>
     <xf numFmtId="177" fontId="28" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="178" fontId="37" fillId="3" borderId="3" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" readingOrder="1"/>
-    </xf>
     <xf numFmtId="0" fontId="28" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
@@ -9687,6 +9715,9 @@
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="13" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="49" fontId="37" fillId="3" borderId="3" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" readingOrder="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="4">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -10987,7 +11018,7 @@
       <c r="Z6" s="28" t="s">
         <v>84</v>
       </c>
-      <c r="AA6" s="78" t="s">
+      <c r="AA6" s="77" t="s">
         <v>1672</v>
       </c>
     </row>
@@ -11041,7 +11072,7 @@
       <c r="U7" s="28" t="s">
         <v>1677</v>
       </c>
-      <c r="V7" s="78" t="s">
+      <c r="V7" s="77" t="s">
         <v>1678</v>
       </c>
       <c r="W7" t="s">
@@ -11056,7 +11087,7 @@
       <c r="Z7" s="28" t="s">
         <v>1677</v>
       </c>
-      <c r="AA7" s="78" t="s">
+      <c r="AA7" s="77" t="s">
         <v>1678</v>
       </c>
     </row>
@@ -16426,8 +16457,8 @@
       <c r="R68">
         <v>12</v>
       </c>
-      <c r="S68" s="54">
-        <v>1500</v>
+      <c r="S68" s="92" t="s">
+        <v>1729</v>
       </c>
       <c r="T68" t="s">
         <v>1511</v>
@@ -16510,8 +16541,8 @@
       <c r="R69">
         <v>30</v>
       </c>
-      <c r="S69" s="54">
-        <v>7500</v>
+      <c r="S69" s="92" t="s">
+        <v>1730</v>
       </c>
       <c r="T69" t="s">
         <v>1521</v>
@@ -16608,8 +16639,8 @@
       <c r="R70">
         <v>60</v>
       </c>
-      <c r="S70" s="54">
-        <v>12000</v>
+      <c r="S70" s="92" t="s">
+        <v>1731</v>
       </c>
       <c r="T70" t="s">
         <v>1534</v>
@@ -16706,8 +16737,8 @@
       <c r="R71">
         <v>98</v>
       </c>
-      <c r="S71" s="54">
-        <v>23000</v>
+      <c r="S71" s="92" t="s">
+        <v>1732</v>
       </c>
       <c r="T71" t="s">
         <v>1547</v>
@@ -16804,8 +16835,8 @@
       <c r="R72">
         <v>128</v>
       </c>
-      <c r="S72" s="54">
-        <v>30000</v>
+      <c r="S72" s="92" t="s">
+        <v>1733</v>
       </c>
       <c r="T72" t="s">
         <v>1560</v>
@@ -16902,8 +16933,8 @@
       <c r="R73">
         <v>198</v>
       </c>
-      <c r="S73" s="54">
-        <v>45000</v>
+      <c r="S73" s="92" t="s">
+        <v>1734</v>
       </c>
       <c r="T73" t="s">
         <v>1573</v>
@@ -17000,8 +17031,8 @@
       <c r="R74">
         <v>328</v>
       </c>
-      <c r="S74" s="54">
-        <v>60000</v>
+      <c r="S74" s="92" t="s">
+        <v>1735</v>
       </c>
       <c r="T74" t="s">
         <v>1586</v>
@@ -17098,8 +17129,8 @@
       <c r="R75">
         <v>648</v>
       </c>
-      <c r="S75" s="54">
-        <v>119000</v>
+      <c r="S75" s="92" t="s">
+        <v>1736</v>
       </c>
       <c r="T75" t="s">
         <v>1599</v>
@@ -17193,8 +17224,8 @@
       <c r="Q76">
         <v>7</v>
       </c>
-      <c r="S76" s="54">
-        <v>1500</v>
+      <c r="S76" s="92" t="s">
+        <v>1729</v>
       </c>
       <c r="X76" s="23"/>
       <c r="AD76" s="23"/>
@@ -17254,8 +17285,8 @@
       <c r="Q77">
         <v>35</v>
       </c>
-      <c r="S77" s="54">
-        <v>7500</v>
+      <c r="S77" s="92" t="s">
+        <v>1730</v>
       </c>
       <c r="X77" s="23"/>
       <c r="AD77" s="23"/>
@@ -17315,8 +17346,8 @@
       <c r="Q78">
         <v>56</v>
       </c>
-      <c r="S78" s="54">
-        <v>12000</v>
+      <c r="S78" s="92" t="s">
+        <v>1731</v>
       </c>
       <c r="X78" s="23"/>
       <c r="AD78" s="23"/>
@@ -17376,8 +17407,8 @@
       <c r="Q79">
         <v>110</v>
       </c>
-      <c r="S79" s="54">
-        <v>23000</v>
+      <c r="S79" s="92" t="s">
+        <v>1732</v>
       </c>
       <c r="X79" s="23"/>
       <c r="AD79" s="23"/>
@@ -17437,8 +17468,8 @@
       <c r="Q80">
         <v>145</v>
       </c>
-      <c r="S80" s="54">
-        <v>30000</v>
+      <c r="S80" s="92" t="s">
+        <v>1733</v>
       </c>
       <c r="X80" s="23"/>
       <c r="AD80" s="23"/>
@@ -17498,8 +17529,8 @@
       <c r="Q81">
         <v>220</v>
       </c>
-      <c r="S81" s="54">
-        <v>45000</v>
+      <c r="S81" s="92" t="s">
+        <v>1734</v>
       </c>
       <c r="X81" s="23"/>
       <c r="AD81" s="23"/>
@@ -17559,8 +17590,8 @@
       <c r="Q82">
         <v>293</v>
       </c>
-      <c r="S82" s="54">
-        <v>60000</v>
+      <c r="S82" s="92" t="s">
+        <v>1735</v>
       </c>
       <c r="X82" s="23"/>
       <c r="AD82" s="23"/>
@@ -17620,8 +17651,8 @@
       <c r="Q83">
         <v>580</v>
       </c>
-      <c r="S83" s="54">
-        <v>119000</v>
+      <c r="S83" s="92" t="s">
+        <v>1736</v>
       </c>
       <c r="X83" s="23"/>
       <c r="AD83" s="23"/>
@@ -17629,3678 +17660,3676 @@
         <v>2</v>
       </c>
     </row>
-    <row r="84" spans="1:32">
+    <row r="84" spans="1:32" ht="16.5">
       <c r="G84" s="27"/>
       <c r="M84" s="27"/>
     </row>
-    <row r="85" spans="1:32">
+    <row r="85" spans="1:32" ht="16.5">
       <c r="G85" s="27"/>
       <c r="M85" s="27"/>
     </row>
-    <row r="86" spans="1:32">
+    <row r="86" spans="1:32" ht="16.5">
       <c r="G86" s="27"/>
       <c r="M86" s="27"/>
     </row>
-    <row r="87" spans="1:32">
+    <row r="87" spans="1:32" ht="16.5">
       <c r="G87" s="27"/>
       <c r="M87" s="27"/>
     </row>
-    <row r="88" spans="1:32">
+    <row r="88" spans="1:32" ht="16.5">
       <c r="G88" s="27"/>
       <c r="M88" s="27"/>
     </row>
-    <row r="89" spans="1:32">
+    <row r="89" spans="1:32" ht="16.5">
       <c r="G89" s="27"/>
       <c r="M89" s="27"/>
     </row>
-    <row r="90" spans="1:32">
+    <row r="90" spans="1:32" ht="16.5">
       <c r="G90" s="27"/>
       <c r="M90" s="27"/>
     </row>
-    <row r="91" spans="1:32">
+    <row r="91" spans="1:32" ht="16.5">
       <c r="G91" s="27"/>
       <c r="M91" s="27"/>
-      <c r="S91" s="33"/>
       <c r="T91" s="33"/>
       <c r="U91" s="33"/>
     </row>
-    <row r="92" spans="1:32">
+    <row r="92" spans="1:32" ht="16.5">
       <c r="G92" s="27"/>
       <c r="M92" s="27"/>
     </row>
-    <row r="93" spans="1:32">
+    <row r="93" spans="1:32" ht="16.5">
       <c r="G93" s="27"/>
       <c r="M93" s="27"/>
     </row>
-    <row r="94" spans="1:32">
+    <row r="94" spans="1:32" ht="16.5">
       <c r="G94" s="27"/>
       <c r="M94" s="27"/>
     </row>
-    <row r="95" spans="1:32">
+    <row r="95" spans="1:32" ht="16.5">
       <c r="G95" s="27"/>
       <c r="M95" s="27"/>
     </row>
-    <row r="96" spans="1:32">
+    <row r="96" spans="1:32" ht="16.5">
       <c r="G96" s="27"/>
       <c r="M96" s="27"/>
     </row>
-    <row r="97" spans="7:23">
+    <row r="97" spans="7:23" ht="16.5">
       <c r="G97" s="27"/>
       <c r="M97" s="27"/>
     </row>
-    <row r="98" spans="7:23">
+    <row r="98" spans="7:23" ht="16.5">
       <c r="G98" s="27"/>
       <c r="M98" s="27"/>
     </row>
-    <row r="99" spans="7:23">
+    <row r="99" spans="7:23" ht="16.5">
       <c r="G99" s="27"/>
       <c r="M99" s="27"/>
     </row>
-    <row r="100" spans="7:23">
+    <row r="100" spans="7:23" ht="16.5">
       <c r="G100" s="27"/>
       <c r="M100" s="27"/>
     </row>
-    <row r="101" spans="7:23">
+    <row r="101" spans="7:23" ht="16.5">
       <c r="G101" s="27"/>
       <c r="M101" s="27"/>
-      <c r="S101" s="33"/>
       <c r="T101" s="33"/>
       <c r="U101" s="33"/>
     </row>
-    <row r="102" spans="7:23">
+    <row r="102" spans="7:23" ht="16.5">
       <c r="G102" s="27"/>
       <c r="M102" s="27"/>
     </row>
-    <row r="103" spans="7:23">
+    <row r="103" spans="7:23" ht="16.5">
       <c r="G103" s="27"/>
       <c r="M103" s="27"/>
     </row>
-    <row r="104" spans="7:23">
+    <row r="104" spans="7:23" ht="16.5">
       <c r="G104" s="27"/>
       <c r="M104" s="27"/>
     </row>
-    <row r="105" spans="7:23">
+    <row r="105" spans="7:23" ht="16.5">
       <c r="G105" s="27"/>
       <c r="M105" s="27"/>
       <c r="W105" s="33"/>
     </row>
-    <row r="106" spans="7:23">
+    <row r="106" spans="7:23" ht="16.5">
       <c r="G106" s="27"/>
       <c r="M106" s="27"/>
     </row>
-    <row r="107" spans="7:23">
+    <row r="107" spans="7:23" ht="16.5">
       <c r="G107" s="27"/>
       <c r="M107" s="27"/>
     </row>
-    <row r="108" spans="7:23">
+    <row r="108" spans="7:23" ht="16.5">
       <c r="G108" s="27"/>
       <c r="M108" s="27"/>
     </row>
-    <row r="109" spans="7:23">
+    <row r="109" spans="7:23" ht="16.5">
       <c r="G109" s="27"/>
       <c r="M109" s="27"/>
     </row>
-    <row r="110" spans="7:23">
+    <row r="110" spans="7:23" ht="16.5">
       <c r="G110" s="27"/>
       <c r="M110" s="27"/>
     </row>
-    <row r="111" spans="7:23">
+    <row r="111" spans="7:23" ht="16.5">
       <c r="G111" s="27"/>
       <c r="M111" s="27"/>
     </row>
-    <row r="112" spans="7:23">
+    <row r="112" spans="7:23" ht="16.5">
       <c r="G112" s="27"/>
       <c r="M112" s="27"/>
     </row>
-    <row r="113" spans="7:13">
+    <row r="113" spans="7:13" ht="16.5">
       <c r="G113" s="27"/>
       <c r="M113" s="27"/>
     </row>
-    <row r="114" spans="7:13">
+    <row r="114" spans="7:13" ht="16.5">
       <c r="G114" s="27"/>
       <c r="M114" s="27"/>
     </row>
-    <row r="115" spans="7:13">
+    <row r="115" spans="7:13" ht="16.5">
       <c r="G115" s="27"/>
       <c r="M115" s="27"/>
     </row>
-    <row r="116" spans="7:13">
+    <row r="116" spans="7:13" ht="16.5">
       <c r="G116" s="27"/>
       <c r="M116" s="27"/>
     </row>
-    <row r="117" spans="7:13">
+    <row r="117" spans="7:13" ht="16.5">
       <c r="G117" s="27"/>
       <c r="M117" s="27"/>
     </row>
-    <row r="118" spans="7:13">
+    <row r="118" spans="7:13" ht="16.5">
       <c r="G118" s="27"/>
       <c r="M118" s="27"/>
     </row>
-    <row r="119" spans="7:13">
+    <row r="119" spans="7:13" ht="16.5">
       <c r="G119" s="27"/>
       <c r="M119" s="27"/>
     </row>
-    <row r="120" spans="7:13">
+    <row r="120" spans="7:13" ht="16.5">
       <c r="G120" s="27"/>
       <c r="M120" s="27"/>
     </row>
-    <row r="121" spans="7:13">
+    <row r="121" spans="7:13" ht="16.5">
       <c r="G121" s="27"/>
       <c r="M121" s="27"/>
     </row>
-    <row r="122" spans="7:13">
+    <row r="122" spans="7:13" ht="16.5">
       <c r="G122" s="27"/>
       <c r="M122" s="27"/>
     </row>
-    <row r="123" spans="7:13">
+    <row r="123" spans="7:13" ht="16.5">
       <c r="G123" s="27"/>
       <c r="M123" s="27"/>
     </row>
-    <row r="124" spans="7:13">
+    <row r="124" spans="7:13" ht="16.5">
       <c r="G124" s="27"/>
       <c r="M124" s="27"/>
     </row>
-    <row r="125" spans="7:13">
+    <row r="125" spans="7:13" ht="16.5">
       <c r="G125" s="27"/>
       <c r="M125" s="27"/>
     </row>
-    <row r="126" spans="7:13">
+    <row r="126" spans="7:13" ht="16.5">
       <c r="G126" s="27"/>
       <c r="M126" s="27"/>
     </row>
-    <row r="127" spans="7:13">
+    <row r="127" spans="7:13" ht="16.5">
       <c r="G127" s="27"/>
       <c r="M127" s="27"/>
     </row>
-    <row r="128" spans="7:13">
+    <row r="128" spans="7:13" ht="16.5">
       <c r="G128" s="27"/>
       <c r="M128" s="27"/>
     </row>
-    <row r="129" spans="7:13">
+    <row r="129" spans="7:13" ht="16.5">
       <c r="G129" s="27"/>
       <c r="M129" s="27"/>
     </row>
-    <row r="130" spans="7:13">
+    <row r="130" spans="7:13" ht="16.5">
       <c r="G130" s="27"/>
       <c r="M130" s="27"/>
     </row>
-    <row r="131" spans="7:13">
+    <row r="131" spans="7:13" ht="16.5">
       <c r="G131" s="27"/>
       <c r="M131" s="27"/>
     </row>
-    <row r="132" spans="7:13">
+    <row r="132" spans="7:13" ht="16.5">
       <c r="G132" s="27"/>
       <c r="M132" s="27"/>
     </row>
-    <row r="133" spans="7:13">
+    <row r="133" spans="7:13" ht="16.5">
       <c r="G133" s="27"/>
       <c r="M133" s="27"/>
     </row>
-    <row r="134" spans="7:13">
+    <row r="134" spans="7:13" ht="16.5">
       <c r="G134" s="27"/>
       <c r="M134" s="27"/>
     </row>
-    <row r="135" spans="7:13">
+    <row r="135" spans="7:13" ht="16.5">
       <c r="G135" s="27"/>
       <c r="M135" s="27"/>
     </row>
-    <row r="136" spans="7:13">
+    <row r="136" spans="7:13" ht="16.5">
       <c r="G136" s="27"/>
       <c r="M136" s="27"/>
     </row>
-    <row r="137" spans="7:13">
+    <row r="137" spans="7:13" ht="16.5">
       <c r="G137" s="27"/>
       <c r="M137" s="27"/>
     </row>
-    <row r="138" spans="7:13">
+    <row r="138" spans="7:13" ht="16.5">
       <c r="G138" s="27"/>
       <c r="M138" s="27"/>
     </row>
-    <row r="139" spans="7:13">
+    <row r="139" spans="7:13" ht="16.5">
       <c r="G139" s="27"/>
       <c r="M139" s="27"/>
     </row>
-    <row r="140" spans="7:13">
+    <row r="140" spans="7:13" ht="16.5">
       <c r="G140" s="27"/>
       <c r="M140" s="27"/>
     </row>
-    <row r="141" spans="7:13">
+    <row r="141" spans="7:13" ht="16.5">
       <c r="G141" s="27"/>
       <c r="M141" s="27"/>
     </row>
-    <row r="142" spans="7:13">
+    <row r="142" spans="7:13" ht="16.5">
       <c r="G142" s="27"/>
       <c r="M142" s="27"/>
     </row>
-    <row r="143" spans="7:13">
+    <row r="143" spans="7:13" ht="16.5">
       <c r="G143" s="27"/>
       <c r="M143" s="27"/>
     </row>
-    <row r="144" spans="7:13">
+    <row r="144" spans="7:13" ht="16.5">
       <c r="G144" s="27"/>
       <c r="M144" s="27"/>
     </row>
-    <row r="145" spans="7:13">
+    <row r="145" spans="7:13" ht="16.5">
       <c r="G145" s="27"/>
       <c r="M145" s="27"/>
     </row>
-    <row r="146" spans="7:13">
+    <row r="146" spans="7:13" ht="16.5">
       <c r="G146" s="27"/>
       <c r="M146" s="27"/>
     </row>
-    <row r="147" spans="7:13">
+    <row r="147" spans="7:13" ht="16.5">
       <c r="G147" s="27"/>
       <c r="M147" s="27"/>
     </row>
-    <row r="148" spans="7:13">
+    <row r="148" spans="7:13" ht="16.5">
       <c r="G148" s="27"/>
       <c r="M148" s="27"/>
     </row>
-    <row r="149" spans="7:13">
+    <row r="149" spans="7:13" ht="16.5">
       <c r="G149" s="27"/>
       <c r="M149" s="27"/>
     </row>
-    <row r="150" spans="7:13">
+    <row r="150" spans="7:13" ht="16.5">
       <c r="G150" s="27"/>
       <c r="M150" s="27"/>
     </row>
-    <row r="151" spans="7:13">
+    <row r="151" spans="7:13" ht="16.5">
       <c r="G151" s="27"/>
       <c r="M151" s="27"/>
     </row>
-    <row r="152" spans="7:13">
+    <row r="152" spans="7:13" ht="16.5">
       <c r="G152" s="27"/>
       <c r="M152" s="27"/>
     </row>
-    <row r="153" spans="7:13">
+    <row r="153" spans="7:13" ht="16.5">
       <c r="G153" s="27"/>
       <c r="M153" s="27"/>
     </row>
-    <row r="154" spans="7:13">
+    <row r="154" spans="7:13" ht="16.5">
       <c r="G154" s="27"/>
       <c r="M154" s="27"/>
     </row>
-    <row r="155" spans="7:13">
+    <row r="155" spans="7:13" ht="16.5">
       <c r="G155" s="27"/>
       <c r="M155" s="27"/>
     </row>
-    <row r="156" spans="7:13">
+    <row r="156" spans="7:13" ht="16.5">
       <c r="G156" s="27"/>
       <c r="M156" s="27"/>
     </row>
-    <row r="157" spans="7:13">
+    <row r="157" spans="7:13" ht="16.5">
       <c r="G157" s="27"/>
       <c r="M157" s="27"/>
     </row>
-    <row r="158" spans="7:13">
+    <row r="158" spans="7:13" ht="16.5">
       <c r="G158" s="27"/>
       <c r="M158" s="27"/>
     </row>
-    <row r="159" spans="7:13">
+    <row r="159" spans="7:13" ht="16.5">
       <c r="G159" s="27"/>
       <c r="M159" s="27"/>
     </row>
-    <row r="160" spans="7:13">
+    <row r="160" spans="7:13" ht="16.5">
       <c r="G160" s="27"/>
       <c r="M160" s="27"/>
     </row>
-    <row r="161" spans="7:13">
+    <row r="161" spans="7:13" ht="16.5">
       <c r="G161" s="27"/>
       <c r="M161" s="27"/>
     </row>
-    <row r="162" spans="7:13">
+    <row r="162" spans="7:13" ht="16.5">
       <c r="G162" s="27"/>
       <c r="M162" s="27"/>
     </row>
-    <row r="163" spans="7:13">
+    <row r="163" spans="7:13" ht="16.5">
       <c r="G163" s="27"/>
       <c r="M163" s="27"/>
     </row>
-    <row r="164" spans="7:13">
+    <row r="164" spans="7:13" ht="16.5">
       <c r="G164" s="27"/>
       <c r="M164" s="27"/>
     </row>
-    <row r="165" spans="7:13">
+    <row r="165" spans="7:13" ht="16.5">
       <c r="G165" s="27"/>
       <c r="M165" s="27"/>
     </row>
-    <row r="166" spans="7:13">
+    <row r="166" spans="7:13" ht="16.5">
       <c r="G166" s="27"/>
       <c r="M166" s="27"/>
     </row>
-    <row r="167" spans="7:13">
+    <row r="167" spans="7:13" ht="16.5">
       <c r="G167" s="27"/>
       <c r="M167" s="27"/>
     </row>
-    <row r="168" spans="7:13">
+    <row r="168" spans="7:13" ht="16.5">
       <c r="G168" s="27"/>
       <c r="M168" s="27"/>
     </row>
-    <row r="169" spans="7:13">
+    <row r="169" spans="7:13" ht="16.5">
       <c r="G169" s="27"/>
       <c r="M169" s="27"/>
     </row>
-    <row r="170" spans="7:13">
+    <row r="170" spans="7:13" ht="16.5">
       <c r="G170" s="27"/>
       <c r="M170" s="27"/>
     </row>
-    <row r="171" spans="7:13">
+    <row r="171" spans="7:13" ht="16.5">
       <c r="G171" s="27"/>
       <c r="M171" s="27"/>
     </row>
-    <row r="172" spans="7:13">
+    <row r="172" spans="7:13" ht="16.5">
       <c r="G172" s="27"/>
       <c r="M172" s="27"/>
     </row>
-    <row r="173" spans="7:13">
+    <row r="173" spans="7:13" ht="16.5">
       <c r="G173" s="27"/>
       <c r="M173" s="27"/>
     </row>
-    <row r="174" spans="7:13">
+    <row r="174" spans="7:13" ht="16.5">
       <c r="G174" s="27"/>
       <c r="M174" s="27"/>
     </row>
-    <row r="175" spans="7:13">
+    <row r="175" spans="7:13" ht="16.5">
       <c r="G175" s="27"/>
       <c r="M175" s="27"/>
     </row>
-    <row r="176" spans="7:13">
+    <row r="176" spans="7:13" ht="16.5">
       <c r="G176" s="27"/>
       <c r="M176" s="27"/>
     </row>
-    <row r="177" spans="7:13">
+    <row r="177" spans="7:13" ht="16.5">
       <c r="G177" s="27"/>
       <c r="M177" s="27"/>
     </row>
-    <row r="178" spans="7:13">
+    <row r="178" spans="7:13" ht="16.5">
       <c r="G178" s="27"/>
       <c r="M178" s="27"/>
     </row>
-    <row r="179" spans="7:13">
+    <row r="179" spans="7:13" ht="16.5">
       <c r="G179" s="27"/>
       <c r="M179" s="27"/>
     </row>
-    <row r="180" spans="7:13">
+    <row r="180" spans="7:13" ht="16.5">
       <c r="G180" s="27"/>
       <c r="M180" s="27"/>
     </row>
-    <row r="181" spans="7:13">
+    <row r="181" spans="7:13" ht="16.5">
       <c r="G181" s="27"/>
       <c r="M181" s="27"/>
     </row>
-    <row r="182" spans="7:13">
+    <row r="182" spans="7:13" ht="16.5">
       <c r="G182" s="27"/>
       <c r="M182" s="27"/>
     </row>
-    <row r="183" spans="7:13">
+    <row r="183" spans="7:13" ht="16.5">
       <c r="G183" s="27"/>
       <c r="M183" s="27"/>
     </row>
-    <row r="184" spans="7:13">
+    <row r="184" spans="7:13" ht="16.5">
       <c r="G184" s="27"/>
       <c r="M184" s="27"/>
     </row>
-    <row r="185" spans="7:13">
+    <row r="185" spans="7:13" ht="16.5">
       <c r="G185" s="27"/>
       <c r="M185" s="27"/>
     </row>
-    <row r="186" spans="7:13">
+    <row r="186" spans="7:13" ht="16.5">
       <c r="G186" s="27"/>
       <c r="M186" s="27"/>
     </row>
-    <row r="187" spans="7:13">
+    <row r="187" spans="7:13" ht="16.5">
       <c r="G187" s="27"/>
       <c r="M187" s="27"/>
     </row>
-    <row r="188" spans="7:13">
+    <row r="188" spans="7:13" ht="16.5">
       <c r="G188" s="27"/>
       <c r="M188" s="27"/>
     </row>
-    <row r="189" spans="7:13">
+    <row r="189" spans="7:13" ht="16.5">
       <c r="G189" s="27"/>
       <c r="M189" s="27"/>
     </row>
-    <row r="190" spans="7:13">
+    <row r="190" spans="7:13" ht="16.5">
       <c r="G190" s="27"/>
       <c r="M190" s="27"/>
     </row>
-    <row r="191" spans="7:13">
+    <row r="191" spans="7:13" ht="16.5">
       <c r="G191" s="27"/>
       <c r="M191" s="27"/>
     </row>
-    <row r="192" spans="7:13">
+    <row r="192" spans="7:13" ht="16.5">
       <c r="G192" s="27"/>
       <c r="M192" s="27"/>
     </row>
-    <row r="193" spans="7:13">
+    <row r="193" spans="7:13" ht="16.5">
       <c r="G193" s="27"/>
       <c r="M193" s="27"/>
     </row>
-    <row r="194" spans="7:13">
+    <row r="194" spans="7:13" ht="16.5">
       <c r="G194" s="27"/>
       <c r="M194" s="27"/>
     </row>
-    <row r="195" spans="7:13">
+    <row r="195" spans="7:13" ht="16.5">
       <c r="G195" s="27"/>
       <c r="M195" s="27"/>
     </row>
-    <row r="196" spans="7:13">
+    <row r="196" spans="7:13" ht="16.5">
       <c r="G196" s="27"/>
       <c r="M196" s="27"/>
     </row>
-    <row r="197" spans="7:13">
+    <row r="197" spans="7:13" ht="16.5">
       <c r="G197" s="27"/>
       <c r="M197" s="27"/>
     </row>
-    <row r="198" spans="7:13">
+    <row r="198" spans="7:13" ht="16.5">
       <c r="G198" s="27"/>
       <c r="M198" s="27"/>
     </row>
-    <row r="199" spans="7:13">
+    <row r="199" spans="7:13" ht="16.5">
       <c r="G199" s="27"/>
       <c r="M199" s="27"/>
     </row>
-    <row r="200" spans="7:13">
+    <row r="200" spans="7:13" ht="16.5">
       <c r="G200" s="27"/>
       <c r="M200" s="27"/>
     </row>
-    <row r="201" spans="7:13">
+    <row r="201" spans="7:13" ht="16.5">
       <c r="G201" s="27"/>
       <c r="M201" s="27"/>
     </row>
-    <row r="202" spans="7:13">
+    <row r="202" spans="7:13" ht="16.5">
       <c r="G202" s="27"/>
       <c r="M202" s="27"/>
     </row>
-    <row r="203" spans="7:13">
+    <row r="203" spans="7:13" ht="16.5">
       <c r="G203" s="27"/>
       <c r="M203" s="27"/>
     </row>
-    <row r="204" spans="7:13">
+    <row r="204" spans="7:13" ht="16.5">
       <c r="G204" s="27"/>
       <c r="M204" s="27"/>
     </row>
-    <row r="205" spans="7:13">
+    <row r="205" spans="7:13" ht="16.5">
       <c r="G205" s="27"/>
       <c r="M205" s="27"/>
     </row>
-    <row r="206" spans="7:13">
+    <row r="206" spans="7:13" ht="16.5">
       <c r="G206" s="27"/>
       <c r="M206" s="27"/>
     </row>
-    <row r="207" spans="7:13">
+    <row r="207" spans="7:13" ht="16.5">
       <c r="G207" s="27"/>
       <c r="M207" s="27"/>
     </row>
-    <row r="208" spans="7:13">
+    <row r="208" spans="7:13" ht="16.5">
       <c r="G208" s="27"/>
       <c r="M208" s="27"/>
     </row>
-    <row r="209" spans="7:13">
+    <row r="209" spans="7:13" ht="16.5">
       <c r="G209" s="27"/>
       <c r="M209" s="27"/>
     </row>
-    <row r="210" spans="7:13">
+    <row r="210" spans="7:13" ht="16.5">
       <c r="G210" s="27"/>
       <c r="M210" s="27"/>
     </row>
-    <row r="211" spans="7:13">
+    <row r="211" spans="7:13" ht="16.5">
       <c r="G211" s="27"/>
       <c r="M211" s="27"/>
     </row>
-    <row r="212" spans="7:13">
+    <row r="212" spans="7:13" ht="16.5">
       <c r="G212" s="27"/>
       <c r="M212" s="27"/>
     </row>
-    <row r="213" spans="7:13">
+    <row r="213" spans="7:13" ht="16.5">
       <c r="G213" s="27"/>
       <c r="M213" s="27"/>
     </row>
-    <row r="214" spans="7:13">
+    <row r="214" spans="7:13" ht="16.5">
       <c r="G214" s="27"/>
       <c r="M214" s="27"/>
     </row>
-    <row r="215" spans="7:13">
+    <row r="215" spans="7:13" ht="16.5">
       <c r="G215" s="27"/>
       <c r="M215" s="27"/>
     </row>
-    <row r="216" spans="7:13">
+    <row r="216" spans="7:13" ht="16.5">
       <c r="G216" s="27"/>
       <c r="M216" s="27"/>
     </row>
-    <row r="217" spans="7:13">
+    <row r="217" spans="7:13" ht="16.5">
       <c r="G217" s="27"/>
       <c r="M217" s="27"/>
     </row>
-    <row r="218" spans="7:13">
+    <row r="218" spans="7:13" ht="16.5">
       <c r="G218" s="27"/>
       <c r="M218" s="27"/>
     </row>
-    <row r="219" spans="7:13">
+    <row r="219" spans="7:13" ht="16.5">
       <c r="G219" s="27"/>
       <c r="M219" s="27"/>
     </row>
-    <row r="220" spans="7:13">
+    <row r="220" spans="7:13" ht="16.5">
       <c r="G220" s="27"/>
       <c r="M220" s="27"/>
     </row>
-    <row r="221" spans="7:13">
+    <row r="221" spans="7:13" ht="16.5">
       <c r="G221" s="27"/>
       <c r="M221" s="27"/>
     </row>
-    <row r="222" spans="7:13">
+    <row r="222" spans="7:13" ht="16.5">
       <c r="G222" s="27"/>
       <c r="M222" s="27"/>
     </row>
-    <row r="223" spans="7:13">
+    <row r="223" spans="7:13" ht="16.5">
       <c r="G223" s="27"/>
       <c r="M223" s="27"/>
     </row>
-    <row r="224" spans="7:13">
+    <row r="224" spans="7:13" ht="16.5">
       <c r="G224" s="27"/>
       <c r="M224" s="27"/>
     </row>
-    <row r="225" spans="7:13">
+    <row r="225" spans="7:13" ht="16.5">
       <c r="G225" s="27"/>
       <c r="M225" s="27"/>
     </row>
-    <row r="226" spans="7:13">
+    <row r="226" spans="7:13" ht="16.5">
       <c r="G226" s="27"/>
       <c r="M226" s="27"/>
     </row>
-    <row r="227" spans="7:13">
+    <row r="227" spans="7:13" ht="16.5">
       <c r="G227" s="27"/>
       <c r="M227" s="27"/>
     </row>
-    <row r="228" spans="7:13">
+    <row r="228" spans="7:13" ht="16.5">
       <c r="G228" s="27"/>
       <c r="M228" s="27"/>
     </row>
-    <row r="229" spans="7:13">
+    <row r="229" spans="7:13" ht="16.5">
       <c r="G229" s="27"/>
       <c r="M229" s="27"/>
     </row>
-    <row r="230" spans="7:13">
+    <row r="230" spans="7:13" ht="16.5">
       <c r="G230" s="27"/>
       <c r="M230" s="27"/>
     </row>
-    <row r="231" spans="7:13">
+    <row r="231" spans="7:13" ht="16.5">
       <c r="G231" s="27"/>
       <c r="M231" s="27"/>
     </row>
-    <row r="232" spans="7:13">
+    <row r="232" spans="7:13" ht="16.5">
       <c r="G232" s="27"/>
       <c r="M232" s="27"/>
     </row>
-    <row r="233" spans="7:13">
+    <row r="233" spans="7:13" ht="16.5">
       <c r="G233" s="27"/>
       <c r="M233" s="27"/>
     </row>
-    <row r="234" spans="7:13">
+    <row r="234" spans="7:13" ht="16.5">
       <c r="G234" s="27"/>
       <c r="M234" s="27"/>
     </row>
-    <row r="235" spans="7:13">
+    <row r="235" spans="7:13" ht="16.5">
       <c r="G235" s="27"/>
       <c r="M235" s="27"/>
     </row>
-    <row r="236" spans="7:13">
+    <row r="236" spans="7:13" ht="16.5">
       <c r="G236" s="27"/>
       <c r="M236" s="27"/>
     </row>
-    <row r="237" spans="7:13">
+    <row r="237" spans="7:13" ht="16.5">
       <c r="G237" s="27"/>
       <c r="M237" s="27"/>
     </row>
-    <row r="238" spans="7:13">
+    <row r="238" spans="7:13" ht="16.5">
       <c r="G238" s="27"/>
       <c r="M238" s="27"/>
     </row>
-    <row r="239" spans="7:13">
+    <row r="239" spans="7:13" ht="16.5">
       <c r="G239" s="27"/>
       <c r="M239" s="27"/>
     </row>
-    <row r="240" spans="7:13">
+    <row r="240" spans="7:13" ht="16.5">
       <c r="G240" s="27"/>
       <c r="M240" s="27"/>
     </row>
-    <row r="241" spans="7:13">
+    <row r="241" spans="7:13" ht="16.5">
       <c r="G241" s="27"/>
       <c r="M241" s="27"/>
     </row>
-    <row r="242" spans="7:13">
+    <row r="242" spans="7:13" ht="16.5">
       <c r="G242" s="27"/>
       <c r="M242" s="27"/>
     </row>
-    <row r="243" spans="7:13">
+    <row r="243" spans="7:13" ht="16.5">
       <c r="G243" s="27"/>
       <c r="M243" s="27"/>
     </row>
-    <row r="244" spans="7:13">
+    <row r="244" spans="7:13" ht="16.5">
       <c r="G244" s="27"/>
       <c r="M244" s="27"/>
     </row>
-    <row r="245" spans="7:13">
+    <row r="245" spans="7:13" ht="16.5">
       <c r="G245" s="27"/>
       <c r="M245" s="27"/>
     </row>
-    <row r="246" spans="7:13">
+    <row r="246" spans="7:13" ht="16.5">
       <c r="G246" s="27"/>
       <c r="M246" s="27"/>
     </row>
-    <row r="247" spans="7:13">
+    <row r="247" spans="7:13" ht="16.5">
       <c r="G247" s="27"/>
       <c r="M247" s="27"/>
     </row>
-    <row r="248" spans="7:13">
+    <row r="248" spans="7:13" ht="16.5">
       <c r="G248" s="27"/>
       <c r="M248" s="27"/>
     </row>
-    <row r="249" spans="7:13">
+    <row r="249" spans="7:13" ht="16.5">
       <c r="G249" s="27"/>
       <c r="M249" s="27"/>
     </row>
-    <row r="250" spans="7:13">
+    <row r="250" spans="7:13" ht="16.5">
       <c r="G250" s="27"/>
       <c r="M250" s="27"/>
     </row>
-    <row r="251" spans="7:13">
+    <row r="251" spans="7:13" ht="16.5">
       <c r="G251" s="27"/>
       <c r="M251" s="27"/>
     </row>
-    <row r="252" spans="7:13">
+    <row r="252" spans="7:13" ht="16.5">
       <c r="G252" s="27"/>
       <c r="M252" s="27"/>
     </row>
-    <row r="253" spans="7:13">
+    <row r="253" spans="7:13" ht="16.5">
       <c r="G253" s="27"/>
       <c r="M253" s="27"/>
     </row>
-    <row r="254" spans="7:13">
+    <row r="254" spans="7:13" ht="16.5">
       <c r="G254" s="27"/>
       <c r="M254" s="27"/>
     </row>
-    <row r="255" spans="7:13">
+    <row r="255" spans="7:13" ht="16.5">
       <c r="G255" s="27"/>
       <c r="M255" s="27"/>
     </row>
-    <row r="256" spans="7:13">
+    <row r="256" spans="7:13" ht="16.5">
       <c r="G256" s="27"/>
       <c r="M256" s="27"/>
     </row>
-    <row r="257" spans="7:13">
+    <row r="257" spans="7:13" ht="16.5">
       <c r="G257" s="27"/>
       <c r="M257" s="27"/>
     </row>
-    <row r="258" spans="7:13">
+    <row r="258" spans="7:13" ht="16.5">
       <c r="G258" s="27"/>
       <c r="M258" s="27"/>
     </row>
-    <row r="259" spans="7:13">
+    <row r="259" spans="7:13" ht="16.5">
       <c r="G259" s="27"/>
       <c r="M259" s="27"/>
     </row>
-    <row r="260" spans="7:13">
+    <row r="260" spans="7:13" ht="16.5">
       <c r="G260" s="27"/>
       <c r="M260" s="27"/>
     </row>
-    <row r="261" spans="7:13">
+    <row r="261" spans="7:13" ht="16.5">
       <c r="G261" s="27"/>
       <c r="M261" s="27"/>
     </row>
-    <row r="262" spans="7:13">
+    <row r="262" spans="7:13" ht="16.5">
       <c r="G262" s="27"/>
       <c r="M262" s="27"/>
     </row>
-    <row r="263" spans="7:13">
+    <row r="263" spans="7:13" ht="16.5">
       <c r="G263" s="27"/>
       <c r="M263" s="27"/>
     </row>
-    <row r="264" spans="7:13">
+    <row r="264" spans="7:13" ht="16.5">
       <c r="G264" s="27"/>
       <c r="M264" s="27"/>
     </row>
-    <row r="265" spans="7:13">
+    <row r="265" spans="7:13" ht="16.5">
       <c r="G265" s="27"/>
       <c r="M265" s="27"/>
     </row>
-    <row r="266" spans="7:13">
+    <row r="266" spans="7:13" ht="16.5">
       <c r="G266" s="27"/>
       <c r="M266" s="27"/>
     </row>
-    <row r="267" spans="7:13">
+    <row r="267" spans="7:13" ht="16.5">
       <c r="G267" s="27"/>
       <c r="M267" s="27"/>
     </row>
-    <row r="268" spans="7:13">
+    <row r="268" spans="7:13" ht="16.5">
       <c r="G268" s="27"/>
       <c r="M268" s="27"/>
     </row>
-    <row r="269" spans="7:13">
+    <row r="269" spans="7:13" ht="16.5">
       <c r="G269" s="27"/>
       <c r="M269" s="27"/>
     </row>
-    <row r="270" spans="7:13">
+    <row r="270" spans="7:13" ht="16.5">
       <c r="G270" s="27"/>
       <c r="M270" s="27"/>
     </row>
-    <row r="271" spans="7:13">
+    <row r="271" spans="7:13" ht="16.5">
       <c r="G271" s="27"/>
       <c r="M271" s="27"/>
     </row>
-    <row r="272" spans="7:13">
+    <row r="272" spans="7:13" ht="16.5">
       <c r="G272" s="27"/>
       <c r="M272" s="27"/>
     </row>
-    <row r="273" spans="7:13">
+    <row r="273" spans="7:13" ht="16.5">
       <c r="G273" s="27"/>
       <c r="M273" s="27"/>
     </row>
-    <row r="274" spans="7:13">
+    <row r="274" spans="7:13" ht="16.5">
       <c r="G274" s="27"/>
       <c r="M274" s="27"/>
     </row>
-    <row r="275" spans="7:13">
+    <row r="275" spans="7:13" ht="16.5">
       <c r="G275" s="27"/>
       <c r="M275" s="27"/>
     </row>
-    <row r="276" spans="7:13">
+    <row r="276" spans="7:13" ht="16.5">
       <c r="G276" s="27"/>
       <c r="M276" s="27"/>
     </row>
-    <row r="277" spans="7:13">
+    <row r="277" spans="7:13" ht="16.5">
       <c r="G277" s="27"/>
       <c r="M277" s="27"/>
     </row>
-    <row r="278" spans="7:13">
+    <row r="278" spans="7:13" ht="16.5">
       <c r="G278" s="27"/>
       <c r="M278" s="27"/>
     </row>
-    <row r="279" spans="7:13">
+    <row r="279" spans="7:13" ht="16.5">
       <c r="G279" s="27"/>
       <c r="M279" s="27"/>
     </row>
-    <row r="280" spans="7:13">
+    <row r="280" spans="7:13" ht="16.5">
       <c r="G280" s="27"/>
       <c r="M280" s="27"/>
     </row>
-    <row r="281" spans="7:13">
+    <row r="281" spans="7:13" ht="16.5">
       <c r="G281" s="27"/>
       <c r="M281" s="27"/>
     </row>
-    <row r="282" spans="7:13">
+    <row r="282" spans="7:13" ht="16.5">
       <c r="G282" s="27"/>
       <c r="M282" s="27"/>
     </row>
-    <row r="283" spans="7:13">
+    <row r="283" spans="7:13" ht="16.5">
       <c r="G283" s="27"/>
       <c r="M283" s="27"/>
     </row>
-    <row r="284" spans="7:13">
+    <row r="284" spans="7:13" ht="16.5">
       <c r="G284" s="27"/>
       <c r="M284" s="27"/>
     </row>
-    <row r="285" spans="7:13">
+    <row r="285" spans="7:13" ht="16.5">
       <c r="G285" s="27"/>
       <c r="M285" s="27"/>
     </row>
-    <row r="286" spans="7:13">
+    <row r="286" spans="7:13" ht="16.5">
       <c r="G286" s="27"/>
       <c r="M286" s="27"/>
     </row>
-    <row r="287" spans="7:13">
+    <row r="287" spans="7:13" ht="16.5">
       <c r="G287" s="27"/>
       <c r="M287" s="27"/>
     </row>
-    <row r="288" spans="7:13">
+    <row r="288" spans="7:13" ht="16.5">
       <c r="G288" s="27"/>
       <c r="M288" s="27"/>
     </row>
-    <row r="289" spans="7:13">
+    <row r="289" spans="7:13" ht="16.5">
       <c r="G289" s="27"/>
       <c r="M289" s="27"/>
     </row>
-    <row r="290" spans="7:13">
+    <row r="290" spans="7:13" ht="16.5">
       <c r="G290" s="27"/>
       <c r="M290" s="27"/>
     </row>
-    <row r="291" spans="7:13">
+    <row r="291" spans="7:13" ht="16.5">
       <c r="G291" s="27"/>
       <c r="M291" s="27"/>
     </row>
-    <row r="292" spans="7:13">
+    <row r="292" spans="7:13" ht="16.5">
       <c r="G292" s="27"/>
       <c r="M292" s="27"/>
     </row>
-    <row r="293" spans="7:13">
+    <row r="293" spans="7:13" ht="16.5">
       <c r="G293" s="27"/>
       <c r="M293" s="27"/>
     </row>
-    <row r="294" spans="7:13">
+    <row r="294" spans="7:13" ht="16.5">
       <c r="G294" s="27"/>
       <c r="M294" s="27"/>
     </row>
-    <row r="295" spans="7:13">
+    <row r="295" spans="7:13" ht="16.5">
       <c r="G295" s="27"/>
       <c r="M295" s="27"/>
     </row>
-    <row r="296" spans="7:13">
+    <row r="296" spans="7:13" ht="16.5">
       <c r="G296" s="27"/>
       <c r="M296" s="27"/>
     </row>
-    <row r="297" spans="7:13">
+    <row r="297" spans="7:13" ht="16.5">
       <c r="G297" s="27"/>
       <c r="M297" s="27"/>
     </row>
-    <row r="298" spans="7:13">
+    <row r="298" spans="7:13" ht="16.5">
       <c r="G298" s="27"/>
       <c r="M298" s="27"/>
     </row>
-    <row r="299" spans="7:13">
+    <row r="299" spans="7:13" ht="16.5">
       <c r="G299" s="27"/>
       <c r="M299" s="27"/>
     </row>
-    <row r="300" spans="7:13">
+    <row r="300" spans="7:13" ht="16.5">
       <c r="G300" s="27"/>
       <c r="M300" s="27"/>
     </row>
-    <row r="301" spans="7:13">
+    <row r="301" spans="7:13" ht="16.5">
       <c r="G301" s="27"/>
       <c r="M301" s="27"/>
     </row>
-    <row r="302" spans="7:13">
+    <row r="302" spans="7:13" ht="16.5">
       <c r="G302" s="27"/>
       <c r="M302" s="27"/>
     </row>
-    <row r="303" spans="7:13">
+    <row r="303" spans="7:13" ht="16.5">
       <c r="G303" s="27"/>
       <c r="M303" s="27"/>
     </row>
-    <row r="304" spans="7:13">
+    <row r="304" spans="7:13" ht="16.5">
       <c r="G304" s="27"/>
       <c r="M304" s="27"/>
     </row>
-    <row r="305" spans="7:13">
+    <row r="305" spans="7:13" ht="16.5">
       <c r="G305" s="27"/>
       <c r="M305" s="27"/>
     </row>
-    <row r="306" spans="7:13">
+    <row r="306" spans="7:13" ht="16.5">
       <c r="G306" s="27"/>
       <c r="M306" s="27"/>
     </row>
-    <row r="307" spans="7:13">
+    <row r="307" spans="7:13" ht="16.5">
       <c r="G307" s="27"/>
       <c r="M307" s="27"/>
     </row>
-    <row r="308" spans="7:13">
+    <row r="308" spans="7:13" ht="16.5">
       <c r="G308" s="27"/>
       <c r="M308" s="27"/>
     </row>
-    <row r="309" spans="7:13">
+    <row r="309" spans="7:13" ht="16.5">
       <c r="G309" s="27"/>
       <c r="M309" s="27"/>
     </row>
-    <row r="310" spans="7:13">
+    <row r="310" spans="7:13" ht="16.5">
       <c r="G310" s="27"/>
       <c r="M310" s="27"/>
     </row>
-    <row r="311" spans="7:13">
+    <row r="311" spans="7:13" ht="16.5">
       <c r="G311" s="27"/>
       <c r="M311" s="27"/>
     </row>
-    <row r="312" spans="7:13">
+    <row r="312" spans="7:13" ht="16.5">
       <c r="G312" s="27"/>
       <c r="M312" s="27"/>
     </row>
-    <row r="313" spans="7:13">
+    <row r="313" spans="7:13" ht="16.5">
       <c r="G313" s="27"/>
       <c r="M313" s="27"/>
     </row>
-    <row r="314" spans="7:13">
+    <row r="314" spans="7:13" ht="16.5">
       <c r="G314" s="27"/>
       <c r="M314" s="27"/>
     </row>
-    <row r="315" spans="7:13">
+    <row r="315" spans="7:13" ht="16.5">
       <c r="G315" s="27"/>
       <c r="M315" s="27"/>
     </row>
-    <row r="316" spans="7:13">
+    <row r="316" spans="7:13" ht="16.5">
       <c r="G316" s="27"/>
       <c r="M316" s="27"/>
     </row>
-    <row r="317" spans="7:13">
+    <row r="317" spans="7:13" ht="16.5">
       <c r="G317" s="27"/>
       <c r="M317" s="27"/>
     </row>
-    <row r="318" spans="7:13">
+    <row r="318" spans="7:13" ht="16.5">
       <c r="G318" s="27"/>
       <c r="M318" s="27"/>
     </row>
-    <row r="319" spans="7:13">
+    <row r="319" spans="7:13" ht="16.5">
       <c r="G319" s="27"/>
       <c r="M319" s="27"/>
     </row>
-    <row r="320" spans="7:13">
+    <row r="320" spans="7:13" ht="16.5">
       <c r="G320" s="27"/>
       <c r="M320" s="27"/>
     </row>
-    <row r="321" spans="7:13">
+    <row r="321" spans="7:13" ht="16.5">
       <c r="G321" s="27"/>
       <c r="M321" s="27"/>
     </row>
-    <row r="322" spans="7:13">
+    <row r="322" spans="7:13" ht="16.5">
       <c r="G322" s="27"/>
       <c r="M322" s="27"/>
     </row>
-    <row r="323" spans="7:13">
+    <row r="323" spans="7:13" ht="16.5">
       <c r="G323" s="27"/>
       <c r="M323" s="27"/>
     </row>
-    <row r="324" spans="7:13">
+    <row r="324" spans="7:13" ht="16.5">
       <c r="G324" s="27"/>
       <c r="M324" s="27"/>
     </row>
-    <row r="325" spans="7:13">
+    <row r="325" spans="7:13" ht="16.5">
       <c r="G325" s="27"/>
       <c r="M325" s="27"/>
     </row>
-    <row r="326" spans="7:13">
+    <row r="326" spans="7:13" ht="16.5">
       <c r="G326" s="27"/>
       <c r="M326" s="27"/>
     </row>
-    <row r="327" spans="7:13">
+    <row r="327" spans="7:13" ht="16.5">
       <c r="G327" s="27"/>
       <c r="M327" s="27"/>
     </row>
-    <row r="328" spans="7:13">
+    <row r="328" spans="7:13" ht="16.5">
       <c r="G328" s="27"/>
       <c r="M328" s="27"/>
     </row>
-    <row r="329" spans="7:13">
+    <row r="329" spans="7:13" ht="16.5">
       <c r="G329" s="27"/>
       <c r="M329" s="27"/>
     </row>
-    <row r="330" spans="7:13">
+    <row r="330" spans="7:13" ht="16.5">
       <c r="G330" s="27"/>
       <c r="M330" s="27"/>
     </row>
-    <row r="331" spans="7:13">
+    <row r="331" spans="7:13" ht="16.5">
       <c r="G331" s="27"/>
       <c r="M331" s="27"/>
     </row>
-    <row r="332" spans="7:13">
+    <row r="332" spans="7:13" ht="16.5">
       <c r="G332" s="27"/>
       <c r="M332" s="27"/>
     </row>
-    <row r="333" spans="7:13">
+    <row r="333" spans="7:13" ht="16.5">
       <c r="G333" s="27"/>
       <c r="M333" s="27"/>
     </row>
-    <row r="334" spans="7:13">
+    <row r="334" spans="7:13" ht="16.5">
       <c r="G334" s="27"/>
       <c r="M334" s="27"/>
     </row>
-    <row r="335" spans="7:13">
+    <row r="335" spans="7:13" ht="16.5">
       <c r="G335" s="27"/>
       <c r="M335" s="27"/>
     </row>
-    <row r="336" spans="7:13">
+    <row r="336" spans="7:13" ht="16.5">
       <c r="G336" s="27"/>
       <c r="M336" s="27"/>
     </row>
-    <row r="337" spans="7:13">
+    <row r="337" spans="7:13" ht="16.5">
       <c r="G337" s="27"/>
       <c r="M337" s="27"/>
     </row>
-    <row r="338" spans="7:13">
+    <row r="338" spans="7:13" ht="16.5">
       <c r="G338" s="27"/>
       <c r="M338" s="27"/>
     </row>
-    <row r="339" spans="7:13">
+    <row r="339" spans="7:13" ht="16.5">
       <c r="G339" s="27"/>
       <c r="M339" s="27"/>
     </row>
-    <row r="340" spans="7:13">
+    <row r="340" spans="7:13" ht="16.5">
       <c r="G340" s="27"/>
       <c r="M340" s="27"/>
     </row>
-    <row r="341" spans="7:13">
+    <row r="341" spans="7:13" ht="16.5">
       <c r="G341" s="27"/>
       <c r="M341" s="27"/>
     </row>
-    <row r="342" spans="7:13">
+    <row r="342" spans="7:13" ht="16.5">
       <c r="G342" s="27"/>
       <c r="M342" s="27"/>
     </row>
-    <row r="343" spans="7:13">
+    <row r="343" spans="7:13" ht="16.5">
       <c r="G343" s="27"/>
       <c r="M343" s="27"/>
     </row>
-    <row r="344" spans="7:13">
+    <row r="344" spans="7:13" ht="16.5">
       <c r="G344" s="27"/>
       <c r="M344" s="27"/>
     </row>
-    <row r="345" spans="7:13">
+    <row r="345" spans="7:13" ht="16.5">
       <c r="G345" s="27"/>
       <c r="M345" s="27"/>
     </row>
-    <row r="346" spans="7:13">
+    <row r="346" spans="7:13" ht="16.5">
       <c r="G346" s="27"/>
       <c r="M346" s="27"/>
     </row>
-    <row r="347" spans="7:13">
+    <row r="347" spans="7:13" ht="16.5">
       <c r="G347" s="27"/>
       <c r="M347" s="27"/>
     </row>
-    <row r="348" spans="7:13">
+    <row r="348" spans="7:13" ht="16.5">
       <c r="G348" s="27"/>
       <c r="M348" s="27"/>
     </row>
-    <row r="349" spans="7:13">
+    <row r="349" spans="7:13" ht="16.5">
       <c r="G349" s="27"/>
       <c r="M349" s="27"/>
     </row>
-    <row r="350" spans="7:13">
+    <row r="350" spans="7:13" ht="16.5">
       <c r="G350" s="27"/>
       <c r="M350" s="27"/>
     </row>
-    <row r="351" spans="7:13">
+    <row r="351" spans="7:13" ht="16.5">
       <c r="G351" s="27"/>
       <c r="M351" s="27"/>
     </row>
-    <row r="352" spans="7:13">
+    <row r="352" spans="7:13" ht="16.5">
       <c r="G352" s="27"/>
       <c r="M352" s="27"/>
     </row>
-    <row r="353" spans="7:13">
+    <row r="353" spans="7:13" ht="16.5">
       <c r="G353" s="27"/>
       <c r="M353" s="27"/>
     </row>
-    <row r="354" spans="7:13">
+    <row r="354" spans="7:13" ht="16.5">
       <c r="G354" s="27"/>
       <c r="M354" s="27"/>
     </row>
-    <row r="355" spans="7:13">
+    <row r="355" spans="7:13" ht="16.5">
       <c r="G355" s="27"/>
       <c r="M355" s="27"/>
     </row>
-    <row r="356" spans="7:13">
+    <row r="356" spans="7:13" ht="16.5">
       <c r="G356" s="27"/>
       <c r="M356" s="27"/>
     </row>
-    <row r="357" spans="7:13">
+    <row r="357" spans="7:13" ht="16.5">
       <c r="G357" s="27"/>
       <c r="M357" s="27"/>
     </row>
-    <row r="358" spans="7:13">
+    <row r="358" spans="7:13" ht="16.5">
       <c r="G358" s="27"/>
       <c r="M358" s="27"/>
     </row>
-    <row r="359" spans="7:13">
+    <row r="359" spans="7:13" ht="16.5">
       <c r="G359" s="27"/>
       <c r="M359" s="27"/>
     </row>
-    <row r="360" spans="7:13">
+    <row r="360" spans="7:13" ht="16.5">
       <c r="G360" s="27"/>
       <c r="M360" s="27"/>
     </row>
-    <row r="361" spans="7:13">
+    <row r="361" spans="7:13" ht="16.5">
       <c r="G361" s="27"/>
       <c r="M361" s="27"/>
     </row>
-    <row r="362" spans="7:13">
+    <row r="362" spans="7:13" ht="16.5">
       <c r="G362" s="27"/>
       <c r="M362" s="27"/>
     </row>
-    <row r="363" spans="7:13">
+    <row r="363" spans="7:13" ht="16.5">
       <c r="G363" s="27"/>
       <c r="M363" s="27"/>
     </row>
-    <row r="364" spans="7:13">
+    <row r="364" spans="7:13" ht="16.5">
       <c r="G364" s="27"/>
       <c r="M364" s="27"/>
     </row>
-    <row r="365" spans="7:13">
+    <row r="365" spans="7:13" ht="16.5">
       <c r="G365" s="27"/>
       <c r="M365" s="27"/>
     </row>
-    <row r="366" spans="7:13">
+    <row r="366" spans="7:13" ht="16.5">
       <c r="G366" s="27"/>
       <c r="M366" s="27"/>
     </row>
-    <row r="367" spans="7:13">
+    <row r="367" spans="7:13" ht="16.5">
       <c r="G367" s="27"/>
       <c r="M367" s="27"/>
     </row>
-    <row r="368" spans="7:13">
+    <row r="368" spans="7:13" ht="16.5">
       <c r="G368" s="27"/>
       <c r="M368" s="27"/>
     </row>
-    <row r="369" spans="7:13">
+    <row r="369" spans="7:13" ht="16.5">
       <c r="G369" s="27"/>
       <c r="M369" s="27"/>
     </row>
-    <row r="370" spans="7:13">
+    <row r="370" spans="7:13" ht="16.5">
       <c r="G370" s="27"/>
       <c r="M370" s="27"/>
     </row>
-    <row r="371" spans="7:13">
+    <row r="371" spans="7:13" ht="16.5">
       <c r="G371" s="27"/>
       <c r="M371" s="27"/>
     </row>
-    <row r="372" spans="7:13">
+    <row r="372" spans="7:13" ht="16.5">
       <c r="G372" s="27"/>
       <c r="M372" s="27"/>
     </row>
-    <row r="373" spans="7:13">
+    <row r="373" spans="7:13" ht="16.5">
       <c r="G373" s="27"/>
       <c r="M373" s="27"/>
     </row>
-    <row r="374" spans="7:13">
+    <row r="374" spans="7:13" ht="16.5">
       <c r="G374" s="27"/>
       <c r="M374" s="27"/>
     </row>
-    <row r="375" spans="7:13">
+    <row r="375" spans="7:13" ht="16.5">
       <c r="G375" s="27"/>
       <c r="M375" s="27"/>
     </row>
-    <row r="376" spans="7:13">
+    <row r="376" spans="7:13" ht="16.5">
       <c r="G376" s="27"/>
       <c r="M376" s="27"/>
     </row>
-    <row r="377" spans="7:13">
+    <row r="377" spans="7:13" ht="16.5">
       <c r="G377" s="27"/>
       <c r="M377" s="27"/>
     </row>
-    <row r="378" spans="7:13">
+    <row r="378" spans="7:13" ht="16.5">
       <c r="G378" s="27"/>
       <c r="M378" s="27"/>
     </row>
-    <row r="379" spans="7:13">
+    <row r="379" spans="7:13" ht="16.5">
       <c r="G379" s="27"/>
       <c r="M379" s="27"/>
     </row>
-    <row r="380" spans="7:13">
+    <row r="380" spans="7:13" ht="16.5">
       <c r="G380" s="27"/>
       <c r="M380" s="27"/>
     </row>
-    <row r="381" spans="7:13">
+    <row r="381" spans="7:13" ht="16.5">
       <c r="G381" s="27"/>
       <c r="M381" s="27"/>
     </row>
-    <row r="382" spans="7:13">
+    <row r="382" spans="7:13" ht="16.5">
       <c r="G382" s="27"/>
       <c r="M382" s="27"/>
     </row>
-    <row r="383" spans="7:13">
+    <row r="383" spans="7:13" ht="16.5">
       <c r="G383" s="27"/>
       <c r="M383" s="27"/>
     </row>
-    <row r="384" spans="7:13">
+    <row r="384" spans="7:13" ht="16.5">
       <c r="G384" s="27"/>
       <c r="M384" s="27"/>
     </row>
-    <row r="385" spans="7:13">
+    <row r="385" spans="7:13" ht="16.5">
       <c r="G385" s="27"/>
       <c r="M385" s="27"/>
     </row>
-    <row r="386" spans="7:13">
+    <row r="386" spans="7:13" ht="16.5">
       <c r="G386" s="27"/>
       <c r="M386" s="27"/>
     </row>
-    <row r="387" spans="7:13">
+    <row r="387" spans="7:13" ht="16.5">
       <c r="G387" s="27"/>
       <c r="M387" s="27"/>
     </row>
-    <row r="388" spans="7:13">
+    <row r="388" spans="7:13" ht="16.5">
       <c r="G388" s="27"/>
       <c r="M388" s="27"/>
     </row>
-    <row r="389" spans="7:13">
+    <row r="389" spans="7:13" ht="16.5">
       <c r="G389" s="27"/>
       <c r="M389" s="27"/>
     </row>
-    <row r="390" spans="7:13">
+    <row r="390" spans="7:13" ht="16.5">
       <c r="G390" s="27"/>
       <c r="M390" s="27"/>
     </row>
-    <row r="391" spans="7:13">
+    <row r="391" spans="7:13" ht="16.5">
       <c r="G391" s="27"/>
       <c r="M391" s="27"/>
     </row>
-    <row r="392" spans="7:13">
+    <row r="392" spans="7:13" ht="16.5">
       <c r="G392" s="27"/>
       <c r="M392" s="27"/>
     </row>
-    <row r="393" spans="7:13">
+    <row r="393" spans="7:13" ht="16.5">
       <c r="G393" s="27"/>
       <c r="M393" s="27"/>
     </row>
-    <row r="394" spans="7:13">
+    <row r="394" spans="7:13" ht="16.5">
       <c r="G394" s="27"/>
       <c r="M394" s="27"/>
     </row>
-    <row r="395" spans="7:13">
+    <row r="395" spans="7:13" ht="16.5">
       <c r="G395" s="27"/>
       <c r="M395" s="27"/>
     </row>
-    <row r="396" spans="7:13">
+    <row r="396" spans="7:13" ht="16.5">
       <c r="G396" s="27"/>
       <c r="M396" s="27"/>
     </row>
-    <row r="397" spans="7:13">
+    <row r="397" spans="7:13" ht="16.5">
       <c r="G397" s="27"/>
       <c r="M397" s="27"/>
     </row>
-    <row r="398" spans="7:13">
+    <row r="398" spans="7:13" ht="16.5">
       <c r="G398" s="27"/>
       <c r="M398" s="27"/>
     </row>
-    <row r="399" spans="7:13">
+    <row r="399" spans="7:13" ht="16.5">
       <c r="G399" s="27"/>
       <c r="M399" s="27"/>
     </row>
-    <row r="400" spans="7:13">
+    <row r="400" spans="7:13" ht="16.5">
       <c r="G400" s="27"/>
       <c r="M400" s="27"/>
     </row>
-    <row r="401" spans="7:13">
+    <row r="401" spans="7:13" ht="16.5">
       <c r="G401" s="27"/>
       <c r="M401" s="27"/>
     </row>
-    <row r="402" spans="7:13">
+    <row r="402" spans="7:13" ht="16.5">
       <c r="G402" s="27"/>
       <c r="M402" s="27"/>
     </row>
-    <row r="403" spans="7:13">
+    <row r="403" spans="7:13" ht="16.5">
       <c r="G403" s="27"/>
       <c r="M403" s="27"/>
     </row>
-    <row r="404" spans="7:13">
+    <row r="404" spans="7:13" ht="16.5">
       <c r="G404" s="27"/>
       <c r="M404" s="27"/>
     </row>
-    <row r="405" spans="7:13">
+    <row r="405" spans="7:13" ht="16.5">
       <c r="G405" s="27"/>
       <c r="M405" s="27"/>
     </row>
-    <row r="406" spans="7:13">
+    <row r="406" spans="7:13" ht="16.5">
       <c r="G406" s="27"/>
       <c r="M406" s="27"/>
     </row>
-    <row r="407" spans="7:13">
+    <row r="407" spans="7:13" ht="16.5">
       <c r="G407" s="27"/>
       <c r="M407" s="27"/>
     </row>
-    <row r="408" spans="7:13">
+    <row r="408" spans="7:13" ht="16.5">
       <c r="G408" s="27"/>
       <c r="M408" s="27"/>
     </row>
-    <row r="409" spans="7:13">
+    <row r="409" spans="7:13" ht="16.5">
       <c r="G409" s="27"/>
       <c r="M409" s="27"/>
     </row>
-    <row r="410" spans="7:13">
+    <row r="410" spans="7:13" ht="16.5">
       <c r="G410" s="27"/>
       <c r="M410" s="27"/>
     </row>
-    <row r="411" spans="7:13">
+    <row r="411" spans="7:13" ht="16.5">
       <c r="G411" s="27"/>
       <c r="M411" s="27"/>
     </row>
-    <row r="412" spans="7:13">
+    <row r="412" spans="7:13" ht="16.5">
       <c r="G412" s="27"/>
       <c r="M412" s="27"/>
     </row>
-    <row r="413" spans="7:13">
+    <row r="413" spans="7:13" ht="16.5">
       <c r="G413" s="27"/>
       <c r="M413" s="27"/>
     </row>
-    <row r="414" spans="7:13">
+    <row r="414" spans="7:13" ht="16.5">
       <c r="G414" s="27"/>
       <c r="M414" s="27"/>
     </row>
-    <row r="415" spans="7:13">
+    <row r="415" spans="7:13" ht="16.5">
       <c r="G415" s="27"/>
       <c r="M415" s="27"/>
     </row>
-    <row r="416" spans="7:13">
+    <row r="416" spans="7:13" ht="16.5">
       <c r="G416" s="27"/>
       <c r="M416" s="27"/>
     </row>
-    <row r="417" spans="7:13">
+    <row r="417" spans="7:13" ht="16.5">
       <c r="G417" s="27"/>
       <c r="M417" s="27"/>
     </row>
-    <row r="418" spans="7:13">
+    <row r="418" spans="7:13" ht="16.5">
       <c r="G418" s="27"/>
       <c r="M418" s="27"/>
     </row>
-    <row r="419" spans="7:13">
+    <row r="419" spans="7:13" ht="16.5">
       <c r="G419" s="27"/>
       <c r="M419" s="27"/>
     </row>
-    <row r="420" spans="7:13">
+    <row r="420" spans="7:13" ht="16.5">
       <c r="G420" s="27"/>
       <c r="M420" s="27"/>
     </row>
-    <row r="421" spans="7:13">
+    <row r="421" spans="7:13" ht="16.5">
       <c r="G421" s="27"/>
       <c r="M421" s="27"/>
     </row>
-    <row r="422" spans="7:13">
+    <row r="422" spans="7:13" ht="16.5">
       <c r="G422" s="27"/>
       <c r="M422" s="27"/>
     </row>
-    <row r="423" spans="7:13">
+    <row r="423" spans="7:13" ht="16.5">
       <c r="G423" s="27"/>
       <c r="M423" s="27"/>
     </row>
-    <row r="424" spans="7:13">
+    <row r="424" spans="7:13" ht="16.5">
       <c r="G424" s="27"/>
       <c r="M424" s="27"/>
     </row>
-    <row r="425" spans="7:13">
+    <row r="425" spans="7:13" ht="16.5">
       <c r="G425" s="27"/>
       <c r="M425" s="27"/>
     </row>
-    <row r="426" spans="7:13">
+    <row r="426" spans="7:13" ht="16.5">
       <c r="G426" s="27"/>
       <c r="M426" s="27"/>
     </row>
-    <row r="427" spans="7:13">
+    <row r="427" spans="7:13" ht="16.5">
       <c r="G427" s="27"/>
       <c r="M427" s="27"/>
     </row>
-    <row r="428" spans="7:13">
+    <row r="428" spans="7:13" ht="16.5">
       <c r="G428" s="27"/>
       <c r="M428" s="27"/>
     </row>
-    <row r="429" spans="7:13">
+    <row r="429" spans="7:13" ht="16.5">
       <c r="G429" s="27"/>
       <c r="M429" s="27"/>
     </row>
-    <row r="430" spans="7:13">
+    <row r="430" spans="7:13" ht="16.5">
       <c r="G430" s="27"/>
       <c r="M430" s="27"/>
     </row>
-    <row r="431" spans="7:13">
+    <row r="431" spans="7:13" ht="16.5">
       <c r="G431" s="27"/>
       <c r="M431" s="27"/>
     </row>
-    <row r="432" spans="7:13">
+    <row r="432" spans="7:13" ht="16.5">
       <c r="G432" s="27"/>
       <c r="M432" s="27"/>
     </row>
-    <row r="433" spans="7:13">
+    <row r="433" spans="7:13" ht="16.5">
       <c r="G433" s="27"/>
       <c r="M433" s="27"/>
     </row>
-    <row r="434" spans="7:13">
+    <row r="434" spans="7:13" ht="16.5">
       <c r="G434" s="27"/>
       <c r="M434" s="27"/>
     </row>
-    <row r="435" spans="7:13">
+    <row r="435" spans="7:13" ht="16.5">
       <c r="G435" s="27"/>
       <c r="M435" s="27"/>
     </row>
-    <row r="436" spans="7:13">
+    <row r="436" spans="7:13" ht="16.5">
       <c r="G436" s="27"/>
       <c r="M436" s="27"/>
     </row>
-    <row r="437" spans="7:13">
+    <row r="437" spans="7:13" ht="16.5">
       <c r="G437" s="27"/>
       <c r="M437" s="27"/>
     </row>
-    <row r="438" spans="7:13">
+    <row r="438" spans="7:13" ht="16.5">
       <c r="G438" s="27"/>
       <c r="M438" s="27"/>
     </row>
-    <row r="439" spans="7:13">
+    <row r="439" spans="7:13" ht="16.5">
       <c r="G439" s="27"/>
       <c r="M439" s="27"/>
     </row>
-    <row r="440" spans="7:13">
+    <row r="440" spans="7:13" ht="16.5">
       <c r="G440" s="27"/>
       <c r="M440" s="27"/>
     </row>
-    <row r="441" spans="7:13">
+    <row r="441" spans="7:13" ht="16.5">
       <c r="G441" s="27"/>
       <c r="M441" s="27"/>
     </row>
-    <row r="442" spans="7:13">
+    <row r="442" spans="7:13" ht="16.5">
       <c r="G442" s="27"/>
       <c r="M442" s="27"/>
     </row>
-    <row r="443" spans="7:13">
+    <row r="443" spans="7:13" ht="16.5">
       <c r="G443" s="27"/>
       <c r="M443" s="27"/>
     </row>
-    <row r="444" spans="7:13">
+    <row r="444" spans="7:13" ht="16.5">
       <c r="G444" s="27"/>
       <c r="M444" s="27"/>
     </row>
-    <row r="445" spans="7:13">
+    <row r="445" spans="7:13" ht="16.5">
       <c r="G445" s="27"/>
       <c r="M445" s="27"/>
     </row>
-    <row r="446" spans="7:13">
+    <row r="446" spans="7:13" ht="16.5">
       <c r="G446" s="27"/>
       <c r="M446" s="27"/>
     </row>
-    <row r="447" spans="7:13">
+    <row r="447" spans="7:13" ht="16.5">
       <c r="G447" s="27"/>
       <c r="M447" s="27"/>
     </row>
-    <row r="448" spans="7:13">
+    <row r="448" spans="7:13" ht="16.5">
       <c r="G448" s="27"/>
       <c r="M448" s="27"/>
     </row>
-    <row r="449" spans="7:13">
+    <row r="449" spans="7:13" ht="16.5">
       <c r="G449" s="27"/>
       <c r="M449" s="27"/>
     </row>
-    <row r="450" spans="7:13">
+    <row r="450" spans="7:13" ht="16.5">
       <c r="G450" s="27"/>
       <c r="M450" s="27"/>
     </row>
-    <row r="451" spans="7:13">
+    <row r="451" spans="7:13" ht="16.5">
       <c r="G451" s="27"/>
       <c r="M451" s="27"/>
     </row>
-    <row r="452" spans="7:13">
+    <row r="452" spans="7:13" ht="16.5">
       <c r="G452" s="27"/>
       <c r="M452" s="27"/>
     </row>
-    <row r="453" spans="7:13">
+    <row r="453" spans="7:13" ht="16.5">
       <c r="G453" s="27"/>
       <c r="M453" s="27"/>
     </row>
-    <row r="454" spans="7:13">
+    <row r="454" spans="7:13" ht="16.5">
       <c r="G454" s="27"/>
       <c r="M454" s="27"/>
     </row>
-    <row r="455" spans="7:13">
+    <row r="455" spans="7:13" ht="16.5">
       <c r="G455" s="27"/>
       <c r="M455" s="27"/>
     </row>
-    <row r="456" spans="7:13">
+    <row r="456" spans="7:13" ht="16.5">
       <c r="G456" s="27"/>
       <c r="M456" s="27"/>
     </row>
-    <row r="457" spans="7:13">
+    <row r="457" spans="7:13" ht="16.5">
       <c r="G457" s="27"/>
       <c r="M457" s="27"/>
     </row>
-    <row r="458" spans="7:13">
+    <row r="458" spans="7:13" ht="16.5">
       <c r="G458" s="27"/>
       <c r="M458" s="27"/>
     </row>
-    <row r="459" spans="7:13">
+    <row r="459" spans="7:13" ht="16.5">
       <c r="G459" s="27"/>
       <c r="M459" s="27"/>
     </row>
-    <row r="460" spans="7:13">
+    <row r="460" spans="7:13" ht="16.5">
       <c r="G460" s="27"/>
       <c r="M460" s="27"/>
     </row>
-    <row r="461" spans="7:13">
+    <row r="461" spans="7:13" ht="16.5">
       <c r="G461" s="27"/>
       <c r="M461" s="27"/>
     </row>
-    <row r="462" spans="7:13">
+    <row r="462" spans="7:13" ht="16.5">
       <c r="G462" s="27"/>
       <c r="M462" s="27"/>
     </row>
-    <row r="463" spans="7:13">
+    <row r="463" spans="7:13" ht="16.5">
       <c r="G463" s="27"/>
       <c r="M463" s="27"/>
     </row>
-    <row r="464" spans="7:13">
+    <row r="464" spans="7:13" ht="16.5">
       <c r="G464" s="27"/>
       <c r="M464" s="27"/>
     </row>
-    <row r="465" spans="7:13">
+    <row r="465" spans="7:13" ht="16.5">
       <c r="G465" s="27"/>
       <c r="M465" s="27"/>
     </row>
-    <row r="466" spans="7:13">
+    <row r="466" spans="7:13" ht="16.5">
       <c r="G466" s="27"/>
       <c r="M466" s="27"/>
     </row>
-    <row r="467" spans="7:13">
+    <row r="467" spans="7:13" ht="16.5">
       <c r="G467" s="27"/>
       <c r="M467" s="27"/>
     </row>
-    <row r="468" spans="7:13">
+    <row r="468" spans="7:13" ht="16.5">
       <c r="G468" s="27"/>
       <c r="M468" s="27"/>
     </row>
-    <row r="469" spans="7:13">
+    <row r="469" spans="7:13" ht="16.5">
       <c r="G469" s="27"/>
       <c r="M469" s="27"/>
     </row>
-    <row r="470" spans="7:13">
+    <row r="470" spans="7:13" ht="16.5">
       <c r="G470" s="27"/>
       <c r="M470" s="27"/>
     </row>
-    <row r="471" spans="7:13">
+    <row r="471" spans="7:13" ht="16.5">
       <c r="G471" s="27"/>
       <c r="M471" s="27"/>
     </row>
-    <row r="472" spans="7:13">
+    <row r="472" spans="7:13" ht="16.5">
       <c r="G472" s="27"/>
       <c r="M472" s="27"/>
     </row>
-    <row r="473" spans="7:13">
+    <row r="473" spans="7:13" ht="16.5">
       <c r="G473" s="27"/>
       <c r="M473" s="27"/>
     </row>
-    <row r="474" spans="7:13">
+    <row r="474" spans="7:13" ht="16.5">
       <c r="G474" s="27"/>
       <c r="M474" s="27"/>
     </row>
-    <row r="475" spans="7:13">
+    <row r="475" spans="7:13" ht="16.5">
       <c r="G475" s="27"/>
       <c r="M475" s="27"/>
     </row>
-    <row r="476" spans="7:13">
+    <row r="476" spans="7:13" ht="16.5">
       <c r="G476" s="27"/>
       <c r="M476" s="27"/>
     </row>
-    <row r="477" spans="7:13">
+    <row r="477" spans="7:13" ht="16.5">
       <c r="G477" s="27"/>
       <c r="M477" s="27"/>
     </row>
-    <row r="478" spans="7:13">
+    <row r="478" spans="7:13" ht="16.5">
       <c r="G478" s="27"/>
       <c r="M478" s="27"/>
     </row>
-    <row r="479" spans="7:13">
+    <row r="479" spans="7:13" ht="16.5">
       <c r="G479" s="27"/>
       <c r="M479" s="27"/>
     </row>
-    <row r="480" spans="7:13">
+    <row r="480" spans="7:13" ht="16.5">
       <c r="G480" s="27"/>
       <c r="M480" s="27"/>
     </row>
-    <row r="481" spans="7:13">
+    <row r="481" spans="7:13" ht="16.5">
       <c r="G481" s="27"/>
       <c r="M481" s="27"/>
     </row>
-    <row r="482" spans="7:13">
+    <row r="482" spans="7:13" ht="16.5">
       <c r="G482" s="27"/>
       <c r="M482" s="27"/>
     </row>
-    <row r="483" spans="7:13">
+    <row r="483" spans="7:13" ht="16.5">
       <c r="G483" s="27"/>
       <c r="M483" s="27"/>
     </row>
-    <row r="484" spans="7:13">
+    <row r="484" spans="7:13" ht="16.5">
       <c r="G484" s="27"/>
       <c r="M484" s="27"/>
     </row>
-    <row r="485" spans="7:13">
+    <row r="485" spans="7:13" ht="16.5">
       <c r="G485" s="27"/>
       <c r="M485" s="27"/>
     </row>
-    <row r="486" spans="7:13">
+    <row r="486" spans="7:13" ht="16.5">
       <c r="G486" s="27"/>
       <c r="M486" s="27"/>
     </row>
-    <row r="487" spans="7:13">
+    <row r="487" spans="7:13" ht="16.5">
       <c r="G487" s="27"/>
       <c r="M487" s="27"/>
     </row>
-    <row r="488" spans="7:13">
+    <row r="488" spans="7:13" ht="16.5">
       <c r="G488" s="27"/>
       <c r="M488" s="27"/>
     </row>
-    <row r="489" spans="7:13">
+    <row r="489" spans="7:13" ht="16.5">
       <c r="G489" s="27"/>
       <c r="M489" s="27"/>
     </row>
-    <row r="490" spans="7:13">
+    <row r="490" spans="7:13" ht="16.5">
       <c r="G490" s="27"/>
       <c r="M490" s="27"/>
     </row>
-    <row r="491" spans="7:13">
+    <row r="491" spans="7:13" ht="16.5">
       <c r="G491" s="27"/>
       <c r="M491" s="27"/>
     </row>
-    <row r="492" spans="7:13">
+    <row r="492" spans="7:13" ht="16.5">
       <c r="G492" s="27"/>
       <c r="M492" s="27"/>
     </row>
-    <row r="493" spans="7:13">
+    <row r="493" spans="7:13" ht="16.5">
       <c r="G493" s="27"/>
       <c r="M493" s="27"/>
     </row>
-    <row r="494" spans="7:13">
+    <row r="494" spans="7:13" ht="16.5">
       <c r="G494" s="27"/>
       <c r="M494" s="27"/>
     </row>
-    <row r="495" spans="7:13">
+    <row r="495" spans="7:13" ht="16.5">
       <c r="G495" s="27"/>
       <c r="M495" s="27"/>
     </row>
-    <row r="496" spans="7:13">
+    <row r="496" spans="7:13" ht="16.5">
       <c r="G496" s="27"/>
       <c r="M496" s="27"/>
     </row>
-    <row r="497" spans="7:13">
+    <row r="497" spans="7:13" ht="16.5">
       <c r="G497" s="27"/>
       <c r="M497" s="27"/>
     </row>
-    <row r="498" spans="7:13">
+    <row r="498" spans="7:13" ht="16.5">
       <c r="G498" s="27"/>
       <c r="M498" s="27"/>
     </row>
-    <row r="499" spans="7:13">
+    <row r="499" spans="7:13" ht="16.5">
       <c r="G499" s="27"/>
       <c r="M499" s="27"/>
     </row>
-    <row r="500" spans="7:13">
+    <row r="500" spans="7:13" ht="16.5">
       <c r="G500" s="27"/>
       <c r="M500" s="27"/>
     </row>
-    <row r="501" spans="7:13">
+    <row r="501" spans="7:13" ht="16.5">
       <c r="G501" s="27"/>
       <c r="M501" s="27"/>
     </row>
-    <row r="502" spans="7:13">
+    <row r="502" spans="7:13" ht="16.5">
       <c r="G502" s="27"/>
       <c r="M502" s="27"/>
     </row>
-    <row r="503" spans="7:13">
+    <row r="503" spans="7:13" ht="16.5">
       <c r="G503" s="27"/>
       <c r="M503" s="27"/>
     </row>
-    <row r="504" spans="7:13">
+    <row r="504" spans="7:13" ht="16.5">
       <c r="G504" s="27"/>
       <c r="M504" s="27"/>
     </row>
-    <row r="505" spans="7:13">
+    <row r="505" spans="7:13" ht="16.5">
       <c r="G505" s="27"/>
       <c r="M505" s="27"/>
     </row>
-    <row r="506" spans="7:13">
+    <row r="506" spans="7:13" ht="16.5">
       <c r="G506" s="27"/>
       <c r="M506" s="27"/>
     </row>
-    <row r="507" spans="7:13">
+    <row r="507" spans="7:13" ht="16.5">
       <c r="G507" s="27"/>
       <c r="M507" s="27"/>
     </row>
-    <row r="508" spans="7:13">
+    <row r="508" spans="7:13" ht="16.5">
       <c r="G508" s="27"/>
       <c r="M508" s="27"/>
     </row>
-    <row r="509" spans="7:13">
+    <row r="509" spans="7:13" ht="16.5">
       <c r="G509" s="27"/>
       <c r="M509" s="27"/>
     </row>
-    <row r="510" spans="7:13">
+    <row r="510" spans="7:13" ht="16.5">
       <c r="G510" s="27"/>
       <c r="M510" s="27"/>
     </row>
-    <row r="511" spans="7:13">
+    <row r="511" spans="7:13" ht="16.5">
       <c r="G511" s="27"/>
       <c r="M511" s="27"/>
     </row>
-    <row r="512" spans="7:13">
+    <row r="512" spans="7:13" ht="16.5">
       <c r="G512" s="27"/>
       <c r="M512" s="27"/>
     </row>
-    <row r="513" spans="7:13">
+    <row r="513" spans="7:13" ht="16.5">
       <c r="G513" s="27"/>
       <c r="M513" s="27"/>
     </row>
-    <row r="514" spans="7:13">
+    <row r="514" spans="7:13" ht="16.5">
       <c r="G514" s="27"/>
       <c r="M514" s="27"/>
     </row>
-    <row r="515" spans="7:13">
+    <row r="515" spans="7:13" ht="16.5">
       <c r="G515" s="27"/>
       <c r="M515" s="27"/>
     </row>
-    <row r="516" spans="7:13">
+    <row r="516" spans="7:13" ht="16.5">
       <c r="G516" s="27"/>
       <c r="M516" s="27"/>
     </row>
-    <row r="517" spans="7:13">
+    <row r="517" spans="7:13" ht="16.5">
       <c r="G517" s="27"/>
       <c r="M517" s="27"/>
     </row>
-    <row r="518" spans="7:13">
+    <row r="518" spans="7:13" ht="16.5">
       <c r="G518" s="27"/>
       <c r="M518" s="27"/>
     </row>
-    <row r="519" spans="7:13">
+    <row r="519" spans="7:13" ht="16.5">
       <c r="G519" s="27"/>
       <c r="M519" s="27"/>
     </row>
-    <row r="520" spans="7:13">
+    <row r="520" spans="7:13" ht="16.5">
       <c r="G520" s="27"/>
       <c r="M520" s="27"/>
     </row>
-    <row r="521" spans="7:13">
+    <row r="521" spans="7:13" ht="16.5">
       <c r="G521" s="27"/>
       <c r="M521" s="27"/>
     </row>
-    <row r="522" spans="7:13">
+    <row r="522" spans="7:13" ht="16.5">
       <c r="G522" s="27"/>
       <c r="M522" s="27"/>
     </row>
-    <row r="523" spans="7:13">
+    <row r="523" spans="7:13" ht="16.5">
       <c r="G523" s="27"/>
       <c r="M523" s="27"/>
     </row>
-    <row r="524" spans="7:13">
+    <row r="524" spans="7:13" ht="16.5">
       <c r="G524" s="27"/>
       <c r="M524" s="27"/>
     </row>
-    <row r="525" spans="7:13">
+    <row r="525" spans="7:13" ht="16.5">
       <c r="G525" s="27"/>
       <c r="M525" s="27"/>
     </row>
-    <row r="526" spans="7:13">
+    <row r="526" spans="7:13" ht="16.5">
       <c r="G526" s="27"/>
       <c r="M526" s="27"/>
     </row>
-    <row r="527" spans="7:13">
+    <row r="527" spans="7:13" ht="16.5">
       <c r="G527" s="27"/>
       <c r="M527" s="27"/>
     </row>
-    <row r="528" spans="7:13">
+    <row r="528" spans="7:13" ht="16.5">
       <c r="G528" s="27"/>
       <c r="M528" s="27"/>
     </row>
-    <row r="529" spans="7:13">
+    <row r="529" spans="7:13" ht="16.5">
       <c r="G529" s="27"/>
       <c r="M529" s="27"/>
     </row>
-    <row r="530" spans="7:13">
+    <row r="530" spans="7:13" ht="16.5">
       <c r="G530" s="27"/>
       <c r="M530" s="27"/>
     </row>
-    <row r="531" spans="7:13">
+    <row r="531" spans="7:13" ht="16.5">
       <c r="G531" s="27"/>
       <c r="M531" s="27"/>
     </row>
-    <row r="532" spans="7:13">
+    <row r="532" spans="7:13" ht="16.5">
       <c r="G532" s="27"/>
       <c r="M532" s="27"/>
     </row>
-    <row r="533" spans="7:13">
+    <row r="533" spans="7:13" ht="16.5">
       <c r="G533" s="27"/>
       <c r="M533" s="27"/>
     </row>
-    <row r="534" spans="7:13">
+    <row r="534" spans="7:13" ht="16.5">
       <c r="G534" s="27"/>
       <c r="M534" s="27"/>
     </row>
-    <row r="535" spans="7:13">
+    <row r="535" spans="7:13" ht="16.5">
       <c r="G535" s="27"/>
       <c r="M535" s="27"/>
     </row>
-    <row r="536" spans="7:13">
+    <row r="536" spans="7:13" ht="16.5">
       <c r="G536" s="27"/>
       <c r="M536" s="27"/>
     </row>
-    <row r="537" spans="7:13">
+    <row r="537" spans="7:13" ht="16.5">
       <c r="G537" s="27"/>
       <c r="M537" s="27"/>
     </row>
-    <row r="538" spans="7:13">
+    <row r="538" spans="7:13" ht="16.5">
       <c r="G538" s="27"/>
       <c r="M538" s="27"/>
     </row>
-    <row r="539" spans="7:13">
+    <row r="539" spans="7:13" ht="16.5">
       <c r="G539" s="27"/>
       <c r="M539" s="27"/>
     </row>
-    <row r="540" spans="7:13">
+    <row r="540" spans="7:13" ht="16.5">
       <c r="G540" s="27"/>
       <c r="M540" s="27"/>
     </row>
-    <row r="541" spans="7:13">
+    <row r="541" spans="7:13" ht="16.5">
       <c r="G541" s="27"/>
       <c r="M541" s="27"/>
     </row>
-    <row r="542" spans="7:13">
+    <row r="542" spans="7:13" ht="16.5">
       <c r="G542" s="27"/>
       <c r="M542" s="27"/>
     </row>
-    <row r="543" spans="7:13">
+    <row r="543" spans="7:13" ht="16.5">
       <c r="G543" s="27"/>
       <c r="M543" s="27"/>
     </row>
-    <row r="544" spans="7:13">
+    <row r="544" spans="7:13" ht="16.5">
       <c r="G544" s="27"/>
       <c r="M544" s="27"/>
     </row>
-    <row r="545" spans="7:13">
+    <row r="545" spans="7:13" ht="16.5">
       <c r="G545" s="27"/>
       <c r="M545" s="27"/>
     </row>
-    <row r="546" spans="7:13">
+    <row r="546" spans="7:13" ht="16.5">
       <c r="G546" s="27"/>
       <c r="M546" s="27"/>
     </row>
-    <row r="547" spans="7:13">
+    <row r="547" spans="7:13" ht="16.5">
       <c r="G547" s="27"/>
       <c r="M547" s="27"/>
     </row>
-    <row r="548" spans="7:13">
+    <row r="548" spans="7:13" ht="16.5">
       <c r="G548" s="27"/>
       <c r="M548" s="27"/>
     </row>
-    <row r="549" spans="7:13">
+    <row r="549" spans="7:13" ht="16.5">
       <c r="G549" s="27"/>
       <c r="M549" s="27"/>
     </row>
-    <row r="550" spans="7:13">
+    <row r="550" spans="7:13" ht="16.5">
       <c r="G550" s="27"/>
       <c r="M550" s="27"/>
     </row>
-    <row r="551" spans="7:13">
+    <row r="551" spans="7:13" ht="16.5">
       <c r="G551" s="27"/>
       <c r="M551" s="27"/>
     </row>
-    <row r="552" spans="7:13">
+    <row r="552" spans="7:13" ht="16.5">
       <c r="G552" s="27"/>
       <c r="M552" s="27"/>
     </row>
-    <row r="553" spans="7:13">
+    <row r="553" spans="7:13" ht="16.5">
       <c r="G553" s="27"/>
       <c r="M553" s="27"/>
     </row>
-    <row r="554" spans="7:13">
+    <row r="554" spans="7:13" ht="16.5">
       <c r="G554" s="27"/>
       <c r="M554" s="27"/>
     </row>
-    <row r="555" spans="7:13">
+    <row r="555" spans="7:13" ht="16.5">
       <c r="G555" s="27"/>
       <c r="M555" s="27"/>
     </row>
-    <row r="556" spans="7:13">
+    <row r="556" spans="7:13" ht="16.5">
       <c r="G556" s="27"/>
       <c r="M556" s="27"/>
     </row>
-    <row r="557" spans="7:13">
+    <row r="557" spans="7:13" ht="16.5">
       <c r="G557" s="27"/>
       <c r="M557" s="27"/>
     </row>
-    <row r="558" spans="7:13">
+    <row r="558" spans="7:13" ht="16.5">
       <c r="G558" s="27"/>
       <c r="M558" s="27"/>
     </row>
-    <row r="559" spans="7:13">
+    <row r="559" spans="7:13" ht="16.5">
       <c r="G559" s="27"/>
       <c r="M559" s="27"/>
     </row>
-    <row r="560" spans="7:13">
+    <row r="560" spans="7:13" ht="16.5">
       <c r="G560" s="27"/>
       <c r="M560" s="27"/>
     </row>
-    <row r="561" spans="7:13">
+    <row r="561" spans="7:13" ht="16.5">
       <c r="G561" s="27"/>
       <c r="M561" s="27"/>
     </row>
-    <row r="562" spans="7:13">
+    <row r="562" spans="7:13" ht="16.5">
       <c r="G562" s="27"/>
       <c r="M562" s="27"/>
     </row>
-    <row r="563" spans="7:13">
+    <row r="563" spans="7:13" ht="16.5">
       <c r="G563" s="27"/>
       <c r="M563" s="27"/>
     </row>
-    <row r="564" spans="7:13">
+    <row r="564" spans="7:13" ht="16.5">
       <c r="G564" s="27"/>
       <c r="M564" s="27"/>
     </row>
-    <row r="565" spans="7:13">
+    <row r="565" spans="7:13" ht="16.5">
       <c r="G565" s="27"/>
       <c r="M565" s="27"/>
     </row>
-    <row r="566" spans="7:13">
+    <row r="566" spans="7:13" ht="16.5">
       <c r="G566" s="27"/>
       <c r="M566" s="27"/>
     </row>
-    <row r="567" spans="7:13">
+    <row r="567" spans="7:13" ht="16.5">
       <c r="G567" s="27"/>
       <c r="M567" s="27"/>
     </row>
-    <row r="568" spans="7:13">
+    <row r="568" spans="7:13" ht="16.5">
       <c r="G568" s="27"/>
       <c r="M568" s="27"/>
     </row>
-    <row r="569" spans="7:13">
+    <row r="569" spans="7:13" ht="16.5">
       <c r="G569" s="27"/>
       <c r="M569" s="27"/>
     </row>
-    <row r="570" spans="7:13">
+    <row r="570" spans="7:13" ht="16.5">
       <c r="G570" s="27"/>
       <c r="M570" s="27"/>
     </row>
-    <row r="571" spans="7:13">
+    <row r="571" spans="7:13" ht="16.5">
       <c r="G571" s="27"/>
       <c r="M571" s="27"/>
     </row>
-    <row r="572" spans="7:13">
+    <row r="572" spans="7:13" ht="16.5">
       <c r="G572" s="27"/>
       <c r="M572" s="27"/>
     </row>
-    <row r="573" spans="7:13">
+    <row r="573" spans="7:13" ht="16.5">
       <c r="G573" s="27"/>
       <c r="M573" s="27"/>
     </row>
-    <row r="574" spans="7:13">
+    <row r="574" spans="7:13" ht="16.5">
       <c r="G574" s="27"/>
       <c r="M574" s="27"/>
     </row>
-    <row r="575" spans="7:13">
+    <row r="575" spans="7:13" ht="16.5">
       <c r="G575" s="27"/>
       <c r="M575" s="27"/>
     </row>
-    <row r="576" spans="7:13">
+    <row r="576" spans="7:13" ht="16.5">
       <c r="G576" s="27"/>
       <c r="M576" s="27"/>
     </row>
-    <row r="577" spans="7:13">
+    <row r="577" spans="7:13" ht="16.5">
       <c r="G577" s="27"/>
       <c r="M577" s="27"/>
     </row>
-    <row r="578" spans="7:13">
+    <row r="578" spans="7:13" ht="16.5">
       <c r="G578" s="27"/>
       <c r="M578" s="27"/>
     </row>
-    <row r="579" spans="7:13">
+    <row r="579" spans="7:13" ht="16.5">
       <c r="G579" s="27"/>
       <c r="M579" s="27"/>
     </row>
-    <row r="580" spans="7:13">
+    <row r="580" spans="7:13" ht="16.5">
       <c r="G580" s="27"/>
       <c r="M580" s="27"/>
     </row>
-    <row r="581" spans="7:13">
+    <row r="581" spans="7:13" ht="16.5">
       <c r="G581" s="27"/>
       <c r="M581" s="27"/>
     </row>
-    <row r="582" spans="7:13">
+    <row r="582" spans="7:13" ht="16.5">
       <c r="G582" s="27"/>
       <c r="M582" s="27"/>
     </row>
-    <row r="583" spans="7:13">
+    <row r="583" spans="7:13" ht="16.5">
       <c r="G583" s="27"/>
       <c r="M583" s="27"/>
     </row>
-    <row r="584" spans="7:13">
+    <row r="584" spans="7:13" ht="16.5">
       <c r="G584" s="27"/>
       <c r="M584" s="27"/>
     </row>
-    <row r="585" spans="7:13">
+    <row r="585" spans="7:13" ht="16.5">
       <c r="G585" s="27"/>
       <c r="M585" s="27"/>
     </row>
-    <row r="586" spans="7:13">
+    <row r="586" spans="7:13" ht="16.5">
       <c r="G586" s="27"/>
       <c r="M586" s="27"/>
     </row>
-    <row r="587" spans="7:13">
+    <row r="587" spans="7:13" ht="16.5">
       <c r="G587" s="27"/>
       <c r="M587" s="27"/>
     </row>
-    <row r="588" spans="7:13">
+    <row r="588" spans="7:13" ht="16.5">
       <c r="G588" s="27"/>
       <c r="M588" s="27"/>
     </row>
-    <row r="589" spans="7:13">
+    <row r="589" spans="7:13" ht="16.5">
       <c r="G589" s="27"/>
       <c r="M589" s="27"/>
     </row>
-    <row r="590" spans="7:13">
+    <row r="590" spans="7:13" ht="16.5">
       <c r="G590" s="27"/>
       <c r="M590" s="27"/>
     </row>
-    <row r="591" spans="7:13">
+    <row r="591" spans="7:13" ht="16.5">
       <c r="G591" s="27"/>
       <c r="M591" s="27"/>
     </row>
-    <row r="592" spans="7:13">
+    <row r="592" spans="7:13" ht="16.5">
       <c r="G592" s="27"/>
       <c r="M592" s="27"/>
     </row>
-    <row r="593" spans="7:13">
+    <row r="593" spans="7:13" ht="16.5">
       <c r="G593" s="27"/>
       <c r="M593" s="27"/>
     </row>
-    <row r="594" spans="7:13">
+    <row r="594" spans="7:13" ht="16.5">
       <c r="G594" s="27"/>
       <c r="M594" s="27"/>
     </row>
-    <row r="595" spans="7:13">
+    <row r="595" spans="7:13" ht="16.5">
       <c r="G595" s="27"/>
       <c r="M595" s="27"/>
     </row>
-    <row r="596" spans="7:13">
+    <row r="596" spans="7:13" ht="16.5">
       <c r="G596" s="27"/>
       <c r="M596" s="27"/>
     </row>
-    <row r="597" spans="7:13">
+    <row r="597" spans="7:13" ht="16.5">
       <c r="G597" s="27"/>
       <c r="M597" s="27"/>
     </row>
-    <row r="598" spans="7:13">
+    <row r="598" spans="7:13" ht="16.5">
       <c r="G598" s="27"/>
       <c r="M598" s="27"/>
     </row>
-    <row r="599" spans="7:13">
+    <row r="599" spans="7:13" ht="16.5">
       <c r="G599" s="27"/>
       <c r="M599" s="27"/>
     </row>
-    <row r="600" spans="7:13">
+    <row r="600" spans="7:13" ht="16.5">
       <c r="G600" s="27"/>
       <c r="M600" s="27"/>
     </row>
-    <row r="601" spans="7:13">
+    <row r="601" spans="7:13" ht="16.5">
       <c r="G601" s="27"/>
       <c r="M601" s="27"/>
     </row>
-    <row r="602" spans="7:13">
+    <row r="602" spans="7:13" ht="16.5">
       <c r="G602" s="27"/>
       <c r="M602" s="27"/>
     </row>
-    <row r="603" spans="7:13">
+    <row r="603" spans="7:13" ht="16.5">
       <c r="G603" s="27"/>
       <c r="M603" s="27"/>
     </row>
-    <row r="604" spans="7:13">
+    <row r="604" spans="7:13" ht="16.5">
       <c r="G604" s="27"/>
       <c r="M604" s="27"/>
     </row>
-    <row r="605" spans="7:13">
+    <row r="605" spans="7:13" ht="16.5">
       <c r="G605" s="27"/>
       <c r="M605" s="27"/>
     </row>
-    <row r="606" spans="7:13">
+    <row r="606" spans="7:13" ht="16.5">
       <c r="G606" s="27"/>
       <c r="M606" s="27"/>
     </row>
-    <row r="607" spans="7:13">
+    <row r="607" spans="7:13" ht="16.5">
       <c r="G607" s="27"/>
       <c r="M607" s="27"/>
     </row>
-    <row r="608" spans="7:13">
+    <row r="608" spans="7:13" ht="16.5">
       <c r="G608" s="27"/>
       <c r="M608" s="27"/>
     </row>
-    <row r="609" spans="7:13">
+    <row r="609" spans="7:13" ht="16.5">
       <c r="G609" s="27"/>
       <c r="M609" s="27"/>
     </row>
-    <row r="610" spans="7:13">
+    <row r="610" spans="7:13" ht="16.5">
       <c r="G610" s="27"/>
       <c r="M610" s="27"/>
     </row>
-    <row r="611" spans="7:13">
+    <row r="611" spans="7:13" ht="16.5">
       <c r="G611" s="27"/>
       <c r="M611" s="27"/>
     </row>
-    <row r="612" spans="7:13">
+    <row r="612" spans="7:13" ht="16.5">
       <c r="G612" s="27"/>
       <c r="M612" s="27"/>
     </row>
-    <row r="613" spans="7:13">
+    <row r="613" spans="7:13" ht="16.5">
       <c r="G613" s="27"/>
       <c r="M613" s="27"/>
     </row>
-    <row r="614" spans="7:13">
+    <row r="614" spans="7:13" ht="16.5">
       <c r="G614" s="27"/>
       <c r="M614" s="27"/>
     </row>
-    <row r="615" spans="7:13">
+    <row r="615" spans="7:13" ht="16.5">
       <c r="G615" s="27"/>
       <c r="M615" s="27"/>
     </row>
-    <row r="616" spans="7:13">
+    <row r="616" spans="7:13" ht="16.5">
       <c r="G616" s="27"/>
       <c r="M616" s="27"/>
     </row>
-    <row r="617" spans="7:13">
+    <row r="617" spans="7:13" ht="16.5">
       <c r="G617" s="27"/>
       <c r="M617" s="27"/>
     </row>
-    <row r="618" spans="7:13">
+    <row r="618" spans="7:13" ht="16.5">
       <c r="G618" s="27"/>
       <c r="M618" s="27"/>
     </row>
-    <row r="619" spans="7:13">
+    <row r="619" spans="7:13" ht="16.5">
       <c r="G619" s="27"/>
       <c r="M619" s="27"/>
     </row>
-    <row r="620" spans="7:13">
+    <row r="620" spans="7:13" ht="16.5">
       <c r="G620" s="27"/>
       <c r="M620" s="27"/>
     </row>
-    <row r="621" spans="7:13">
+    <row r="621" spans="7:13" ht="16.5">
       <c r="G621" s="27"/>
       <c r="M621" s="27"/>
     </row>
-    <row r="622" spans="7:13">
+    <row r="622" spans="7:13" ht="16.5">
       <c r="G622" s="27"/>
       <c r="M622" s="27"/>
     </row>
-    <row r="623" spans="7:13">
+    <row r="623" spans="7:13" ht="16.5">
       <c r="G623" s="27"/>
       <c r="M623" s="27"/>
     </row>
-    <row r="624" spans="7:13">
+    <row r="624" spans="7:13" ht="16.5">
       <c r="G624" s="27"/>
       <c r="M624" s="27"/>
     </row>
-    <row r="625" spans="7:13">
+    <row r="625" spans="7:13" ht="16.5">
       <c r="G625" s="27"/>
       <c r="M625" s="27"/>
     </row>
-    <row r="626" spans="7:13">
+    <row r="626" spans="7:13" ht="16.5">
       <c r="G626" s="27"/>
       <c r="M626" s="27"/>
     </row>
-    <row r="627" spans="7:13">
+    <row r="627" spans="7:13" ht="16.5">
       <c r="G627" s="27"/>
       <c r="M627" s="27"/>
     </row>
-    <row r="628" spans="7:13">
+    <row r="628" spans="7:13" ht="16.5">
       <c r="G628" s="27"/>
       <c r="M628" s="27"/>
     </row>
-    <row r="629" spans="7:13">
+    <row r="629" spans="7:13" ht="16.5">
       <c r="G629" s="27"/>
       <c r="M629" s="27"/>
     </row>
-    <row r="630" spans="7:13">
+    <row r="630" spans="7:13" ht="16.5">
       <c r="G630" s="27"/>
       <c r="M630" s="27"/>
     </row>
-    <row r="631" spans="7:13">
+    <row r="631" spans="7:13" ht="16.5">
       <c r="G631" s="27"/>
       <c r="M631" s="27"/>
     </row>
-    <row r="632" spans="7:13">
+    <row r="632" spans="7:13" ht="16.5">
       <c r="G632" s="27"/>
       <c r="M632" s="27"/>
     </row>
-    <row r="633" spans="7:13">
+    <row r="633" spans="7:13" ht="16.5">
       <c r="G633" s="27"/>
       <c r="M633" s="27"/>
     </row>
-    <row r="634" spans="7:13">
+    <row r="634" spans="7:13" ht="16.5">
       <c r="G634" s="27"/>
       <c r="M634" s="27"/>
     </row>
-    <row r="635" spans="7:13">
+    <row r="635" spans="7:13" ht="16.5">
       <c r="G635" s="27"/>
       <c r="M635" s="27"/>
     </row>
-    <row r="636" spans="7:13">
+    <row r="636" spans="7:13" ht="16.5">
       <c r="G636" s="27"/>
       <c r="M636" s="27"/>
     </row>
-    <row r="637" spans="7:13">
+    <row r="637" spans="7:13" ht="16.5">
       <c r="G637" s="27"/>
       <c r="M637" s="27"/>
     </row>
-    <row r="638" spans="7:13">
+    <row r="638" spans="7:13" ht="16.5">
       <c r="G638" s="27"/>
       <c r="M638" s="27"/>
     </row>
-    <row r="639" spans="7:13">
+    <row r="639" spans="7:13" ht="16.5">
       <c r="G639" s="27"/>
       <c r="M639" s="27"/>
     </row>
-    <row r="640" spans="7:13">
+    <row r="640" spans="7:13" ht="16.5">
       <c r="G640" s="27"/>
       <c r="M640" s="27"/>
     </row>
-    <row r="641" spans="7:13">
+    <row r="641" spans="7:13" ht="16.5">
       <c r="G641" s="27"/>
       <c r="M641" s="27"/>
     </row>
-    <row r="642" spans="7:13">
+    <row r="642" spans="7:13" ht="16.5">
       <c r="G642" s="27"/>
       <c r="M642" s="27"/>
     </row>
-    <row r="643" spans="7:13">
+    <row r="643" spans="7:13" ht="16.5">
       <c r="G643" s="27"/>
       <c r="M643" s="27"/>
     </row>
-    <row r="644" spans="7:13">
+    <row r="644" spans="7:13" ht="16.5">
       <c r="G644" s="27"/>
       <c r="M644" s="27"/>
     </row>
-    <row r="645" spans="7:13">
+    <row r="645" spans="7:13" ht="16.5">
       <c r="G645" s="27"/>
       <c r="M645" s="27"/>
     </row>
-    <row r="646" spans="7:13">
+    <row r="646" spans="7:13" ht="16.5">
       <c r="G646" s="27"/>
       <c r="M646" s="27"/>
     </row>
-    <row r="647" spans="7:13">
+    <row r="647" spans="7:13" ht="16.5">
       <c r="G647" s="27"/>
       <c r="M647" s="27"/>
     </row>
-    <row r="648" spans="7:13">
+    <row r="648" spans="7:13" ht="16.5">
       <c r="G648" s="27"/>
       <c r="M648" s="27"/>
     </row>
-    <row r="649" spans="7:13">
+    <row r="649" spans="7:13" ht="16.5">
       <c r="G649" s="27"/>
       <c r="M649" s="27"/>
     </row>
-    <row r="650" spans="7:13">
+    <row r="650" spans="7:13" ht="16.5">
       <c r="G650" s="27"/>
       <c r="M650" s="27"/>
     </row>
-    <row r="651" spans="7:13">
+    <row r="651" spans="7:13" ht="16.5">
       <c r="G651" s="27"/>
       <c r="M651" s="27"/>
     </row>
-    <row r="652" spans="7:13">
+    <row r="652" spans="7:13" ht="16.5">
       <c r="G652" s="27"/>
       <c r="M652" s="27"/>
     </row>
-    <row r="653" spans="7:13">
+    <row r="653" spans="7:13" ht="16.5">
       <c r="G653" s="27"/>
       <c r="M653" s="27"/>
     </row>
-    <row r="654" spans="7:13">
+    <row r="654" spans="7:13" ht="16.5">
       <c r="G654" s="27"/>
       <c r="M654" s="27"/>
     </row>
-    <row r="655" spans="7:13">
+    <row r="655" spans="7:13" ht="16.5">
       <c r="G655" s="27"/>
       <c r="M655" s="27"/>
     </row>
-    <row r="656" spans="7:13">
+    <row r="656" spans="7:13" ht="16.5">
       <c r="G656" s="27"/>
       <c r="M656" s="27"/>
     </row>
-    <row r="657" spans="7:13">
+    <row r="657" spans="7:13" ht="16.5">
       <c r="G657" s="27"/>
       <c r="M657" s="27"/>
     </row>
-    <row r="658" spans="7:13">
+    <row r="658" spans="7:13" ht="16.5">
       <c r="G658" s="27"/>
       <c r="M658" s="27"/>
     </row>
-    <row r="659" spans="7:13">
+    <row r="659" spans="7:13" ht="16.5">
       <c r="G659" s="27"/>
       <c r="M659" s="27"/>
     </row>
-    <row r="660" spans="7:13">
+    <row r="660" spans="7:13" ht="16.5">
       <c r="G660" s="27"/>
       <c r="M660" s="27"/>
     </row>
-    <row r="661" spans="7:13">
+    <row r="661" spans="7:13" ht="16.5">
       <c r="G661" s="27"/>
       <c r="M661" s="27"/>
     </row>
-    <row r="662" spans="7:13">
+    <row r="662" spans="7:13" ht="16.5">
       <c r="G662" s="27"/>
       <c r="M662" s="27"/>
     </row>
-    <row r="663" spans="7:13">
+    <row r="663" spans="7:13" ht="16.5">
       <c r="G663" s="27"/>
       <c r="M663" s="27"/>
     </row>
-    <row r="664" spans="7:13">
+    <row r="664" spans="7:13" ht="16.5">
       <c r="G664" s="27"/>
       <c r="M664" s="27"/>
     </row>
-    <row r="665" spans="7:13">
+    <row r="665" spans="7:13" ht="16.5">
       <c r="G665" s="27"/>
       <c r="M665" s="27"/>
     </row>
-    <row r="666" spans="7:13">
+    <row r="666" spans="7:13" ht="16.5">
       <c r="G666" s="27"/>
       <c r="M666" s="27"/>
     </row>
-    <row r="667" spans="7:13">
+    <row r="667" spans="7:13" ht="16.5">
       <c r="G667" s="27"/>
       <c r="M667" s="27"/>
     </row>
-    <row r="668" spans="7:13">
+    <row r="668" spans="7:13" ht="16.5">
       <c r="G668" s="27"/>
       <c r="M668" s="27"/>
     </row>
-    <row r="669" spans="7:13">
+    <row r="669" spans="7:13" ht="16.5">
       <c r="G669" s="27"/>
       <c r="M669" s="27"/>
     </row>
-    <row r="670" spans="7:13">
+    <row r="670" spans="7:13" ht="16.5">
       <c r="G670" s="27"/>
       <c r="M670" s="27"/>
     </row>
-    <row r="671" spans="7:13">
+    <row r="671" spans="7:13" ht="16.5">
       <c r="G671" s="27"/>
       <c r="M671" s="27"/>
     </row>
-    <row r="672" spans="7:13">
+    <row r="672" spans="7:13" ht="16.5">
       <c r="G672" s="27"/>
       <c r="M672" s="27"/>
     </row>
-    <row r="673" spans="7:13">
+    <row r="673" spans="7:13" ht="16.5">
       <c r="G673" s="27"/>
       <c r="M673" s="27"/>
     </row>
-    <row r="674" spans="7:13">
+    <row r="674" spans="7:13" ht="16.5">
       <c r="G674" s="27"/>
       <c r="M674" s="27"/>
     </row>
-    <row r="675" spans="7:13">
+    <row r="675" spans="7:13" ht="16.5">
       <c r="G675" s="27"/>
       <c r="M675" s="27"/>
     </row>
-    <row r="676" spans="7:13">
+    <row r="676" spans="7:13" ht="16.5">
       <c r="G676" s="27"/>
       <c r="M676" s="27"/>
     </row>
-    <row r="677" spans="7:13">
+    <row r="677" spans="7:13" ht="16.5">
       <c r="G677" s="27"/>
       <c r="M677" s="27"/>
     </row>
-    <row r="678" spans="7:13">
+    <row r="678" spans="7:13" ht="16.5">
       <c r="G678" s="27"/>
       <c r="M678" s="27"/>
     </row>
-    <row r="679" spans="7:13">
+    <row r="679" spans="7:13" ht="16.5">
       <c r="G679" s="27"/>
       <c r="M679" s="27"/>
     </row>
-    <row r="680" spans="7:13">
+    <row r="680" spans="7:13" ht="16.5">
       <c r="G680" s="27"/>
       <c r="M680" s="27"/>
     </row>
-    <row r="681" spans="7:13">
+    <row r="681" spans="7:13" ht="16.5">
       <c r="G681" s="27"/>
       <c r="M681" s="27"/>
     </row>
-    <row r="682" spans="7:13">
+    <row r="682" spans="7:13" ht="16.5">
       <c r="G682" s="27"/>
       <c r="M682" s="27"/>
     </row>
-    <row r="683" spans="7:13">
+    <row r="683" spans="7:13" ht="16.5">
       <c r="G683" s="27"/>
       <c r="M683" s="27"/>
     </row>
-    <row r="684" spans="7:13">
+    <row r="684" spans="7:13" ht="16.5">
       <c r="G684" s="27"/>
       <c r="M684" s="27"/>
     </row>
-    <row r="685" spans="7:13">
+    <row r="685" spans="7:13" ht="16.5">
       <c r="G685" s="27"/>
       <c r="M685" s="27"/>
     </row>
-    <row r="686" spans="7:13">
+    <row r="686" spans="7:13" ht="16.5">
       <c r="G686" s="27"/>
       <c r="M686" s="27"/>
     </row>
-    <row r="687" spans="7:13">
+    <row r="687" spans="7:13" ht="16.5">
       <c r="G687" s="27"/>
       <c r="M687" s="27"/>
     </row>
-    <row r="688" spans="7:13">
+    <row r="688" spans="7:13" ht="16.5">
       <c r="G688" s="27"/>
       <c r="M688" s="27"/>
     </row>
-    <row r="689" spans="7:13">
+    <row r="689" spans="7:13" ht="16.5">
       <c r="G689" s="27"/>
       <c r="M689" s="27"/>
     </row>
-    <row r="690" spans="7:13">
+    <row r="690" spans="7:13" ht="16.5">
       <c r="G690" s="27"/>
       <c r="M690" s="27"/>
     </row>
-    <row r="691" spans="7:13">
+    <row r="691" spans="7:13" ht="16.5">
       <c r="G691" s="27"/>
       <c r="M691" s="27"/>
     </row>
-    <row r="692" spans="7:13">
+    <row r="692" spans="7:13" ht="16.5">
       <c r="G692" s="27"/>
       <c r="M692" s="27"/>
     </row>
-    <row r="693" spans="7:13">
+    <row r="693" spans="7:13" ht="16.5">
       <c r="G693" s="27"/>
       <c r="M693" s="27"/>
     </row>
-    <row r="694" spans="7:13">
+    <row r="694" spans="7:13" ht="16.5">
       <c r="G694" s="27"/>
       <c r="M694" s="27"/>
     </row>
-    <row r="695" spans="7:13">
+    <row r="695" spans="7:13" ht="16.5">
       <c r="G695" s="27"/>
       <c r="M695" s="27"/>
     </row>
-    <row r="696" spans="7:13">
+    <row r="696" spans="7:13" ht="16.5">
       <c r="G696" s="27"/>
       <c r="M696" s="27"/>
     </row>
-    <row r="697" spans="7:13">
+    <row r="697" spans="7:13" ht="16.5">
       <c r="G697" s="27"/>
       <c r="M697" s="27"/>
     </row>
-    <row r="698" spans="7:13">
+    <row r="698" spans="7:13" ht="16.5">
       <c r="G698" s="27"/>
       <c r="M698" s="27"/>
     </row>
-    <row r="699" spans="7:13">
+    <row r="699" spans="7:13" ht="16.5">
       <c r="G699" s="27"/>
       <c r="M699" s="27"/>
     </row>
-    <row r="700" spans="7:13">
+    <row r="700" spans="7:13" ht="16.5">
       <c r="G700" s="27"/>
       <c r="M700" s="27"/>
     </row>
-    <row r="701" spans="7:13">
+    <row r="701" spans="7:13" ht="16.5">
       <c r="G701" s="27"/>
       <c r="M701" s="27"/>
     </row>
-    <row r="702" spans="7:13">
+    <row r="702" spans="7:13" ht="16.5">
       <c r="G702" s="27"/>
       <c r="M702" s="27"/>
     </row>
-    <row r="703" spans="7:13">
+    <row r="703" spans="7:13" ht="16.5">
       <c r="G703" s="27"/>
       <c r="M703" s="27"/>
     </row>
-    <row r="704" spans="7:13">
+    <row r="704" spans="7:13" ht="16.5">
       <c r="G704" s="27"/>
       <c r="M704" s="27"/>
     </row>
-    <row r="705" spans="7:13">
+    <row r="705" spans="7:13" ht="16.5">
       <c r="G705" s="27"/>
       <c r="M705" s="27"/>
     </row>
-    <row r="706" spans="7:13">
+    <row r="706" spans="7:13" ht="16.5">
       <c r="G706" s="27"/>
       <c r="M706" s="27"/>
     </row>
-    <row r="707" spans="7:13">
+    <row r="707" spans="7:13" ht="16.5">
       <c r="G707" s="27"/>
       <c r="M707" s="27"/>
     </row>
-    <row r="708" spans="7:13">
+    <row r="708" spans="7:13" ht="16.5">
       <c r="G708" s="27"/>
       <c r="M708" s="27"/>
     </row>
-    <row r="709" spans="7:13">
+    <row r="709" spans="7:13" ht="16.5">
       <c r="G709" s="27"/>
       <c r="M709" s="27"/>
     </row>
-    <row r="710" spans="7:13">
+    <row r="710" spans="7:13" ht="16.5">
       <c r="G710" s="27"/>
       <c r="M710" s="27"/>
     </row>
-    <row r="711" spans="7:13">
+    <row r="711" spans="7:13" ht="16.5">
       <c r="G711" s="27"/>
       <c r="M711" s="27"/>
     </row>
-    <row r="712" spans="7:13">
+    <row r="712" spans="7:13" ht="16.5">
       <c r="G712" s="27"/>
       <c r="M712" s="27"/>
     </row>
-    <row r="713" spans="7:13">
+    <row r="713" spans="7:13" ht="16.5">
       <c r="G713" s="27"/>
       <c r="M713" s="27"/>
     </row>
-    <row r="714" spans="7:13">
+    <row r="714" spans="7:13" ht="16.5">
       <c r="G714" s="27"/>
       <c r="M714" s="27"/>
     </row>
-    <row r="715" spans="7:13">
+    <row r="715" spans="7:13" ht="16.5">
       <c r="G715" s="27"/>
       <c r="M715" s="27"/>
     </row>
-    <row r="716" spans="7:13">
+    <row r="716" spans="7:13" ht="16.5">
       <c r="G716" s="27"/>
       <c r="M716" s="27"/>
     </row>
-    <row r="717" spans="7:13">
+    <row r="717" spans="7:13" ht="16.5">
       <c r="G717" s="27"/>
       <c r="M717" s="27"/>
     </row>
-    <row r="718" spans="7:13">
+    <row r="718" spans="7:13" ht="16.5">
       <c r="G718" s="27"/>
       <c r="M718" s="27"/>
     </row>
-    <row r="719" spans="7:13">
+    <row r="719" spans="7:13" ht="16.5">
       <c r="G719" s="27"/>
       <c r="M719" s="27"/>
     </row>
-    <row r="720" spans="7:13">
+    <row r="720" spans="7:13" ht="16.5">
       <c r="G720" s="27"/>
       <c r="M720" s="27"/>
     </row>
-    <row r="721" spans="7:13">
+    <row r="721" spans="7:13" ht="16.5">
       <c r="G721" s="27"/>
       <c r="M721" s="27"/>
     </row>
-    <row r="722" spans="7:13">
+    <row r="722" spans="7:13" ht="16.5">
       <c r="G722" s="27"/>
       <c r="M722" s="27"/>
     </row>
-    <row r="723" spans="7:13">
+    <row r="723" spans="7:13" ht="16.5">
       <c r="G723" s="27"/>
       <c r="M723" s="27"/>
     </row>
-    <row r="724" spans="7:13">
+    <row r="724" spans="7:13" ht="16.5">
       <c r="G724" s="27"/>
       <c r="M724" s="27"/>
     </row>
-    <row r="725" spans="7:13">
+    <row r="725" spans="7:13" ht="16.5">
       <c r="G725" s="27"/>
       <c r="M725" s="27"/>
     </row>
-    <row r="726" spans="7:13">
+    <row r="726" spans="7:13" ht="16.5">
       <c r="G726" s="27"/>
       <c r="M726" s="27"/>
     </row>
-    <row r="727" spans="7:13">
+    <row r="727" spans="7:13" ht="16.5">
       <c r="G727" s="27"/>
       <c r="M727" s="27"/>
     </row>
-    <row r="728" spans="7:13">
+    <row r="728" spans="7:13" ht="16.5">
       <c r="G728" s="27"/>
       <c r="M728" s="27"/>
     </row>
-    <row r="729" spans="7:13">
+    <row r="729" spans="7:13" ht="16.5">
       <c r="G729" s="27"/>
       <c r="M729" s="27"/>
     </row>
-    <row r="730" spans="7:13">
+    <row r="730" spans="7:13" ht="16.5">
       <c r="G730" s="27"/>
       <c r="M730" s="27"/>
     </row>
-    <row r="731" spans="7:13">
+    <row r="731" spans="7:13" ht="16.5">
       <c r="G731" s="27"/>
       <c r="M731" s="27"/>
     </row>
-    <row r="732" spans="7:13">
+    <row r="732" spans="7:13" ht="16.5">
       <c r="G732" s="27"/>
       <c r="M732" s="27"/>
     </row>
-    <row r="733" spans="7:13">
+    <row r="733" spans="7:13" ht="16.5">
       <c r="G733" s="27"/>
       <c r="M733" s="27"/>
     </row>
-    <row r="734" spans="7:13">
+    <row r="734" spans="7:13" ht="16.5">
       <c r="G734" s="27"/>
       <c r="M734" s="27"/>
     </row>
-    <row r="735" spans="7:13">
+    <row r="735" spans="7:13" ht="16.5">
       <c r="G735" s="27"/>
       <c r="M735" s="27"/>
     </row>
-    <row r="736" spans="7:13">
+    <row r="736" spans="7:13" ht="16.5">
       <c r="G736" s="27"/>
       <c r="M736" s="27"/>
     </row>
-    <row r="737" spans="7:13">
+    <row r="737" spans="7:13" ht="16.5">
       <c r="G737" s="27"/>
       <c r="M737" s="27"/>
     </row>
-    <row r="738" spans="7:13">
+    <row r="738" spans="7:13" ht="16.5">
       <c r="G738" s="27"/>
       <c r="M738" s="27"/>
     </row>
-    <row r="739" spans="7:13">
+    <row r="739" spans="7:13" ht="16.5">
       <c r="G739" s="27"/>
       <c r="M739" s="27"/>
     </row>
-    <row r="740" spans="7:13">
+    <row r="740" spans="7:13" ht="16.5">
       <c r="G740" s="27"/>
       <c r="M740" s="27"/>
     </row>
-    <row r="741" spans="7:13">
+    <row r="741" spans="7:13" ht="16.5">
       <c r="G741" s="27"/>
       <c r="M741" s="27"/>
     </row>
-    <row r="742" spans="7:13">
+    <row r="742" spans="7:13" ht="16.5">
       <c r="G742" s="27"/>
       <c r="M742" s="27"/>
     </row>
-    <row r="743" spans="7:13">
+    <row r="743" spans="7:13" ht="16.5">
       <c r="G743" s="27"/>
       <c r="M743" s="27"/>
     </row>
-    <row r="744" spans="7:13">
+    <row r="744" spans="7:13" ht="16.5">
       <c r="G744" s="27"/>
       <c r="M744" s="27"/>
     </row>
-    <row r="745" spans="7:13">
+    <row r="745" spans="7:13" ht="16.5">
       <c r="G745" s="27"/>
       <c r="M745" s="27"/>
     </row>
-    <row r="746" spans="7:13">
+    <row r="746" spans="7:13" ht="16.5">
       <c r="G746" s="27"/>
       <c r="M746" s="27"/>
     </row>
-    <row r="747" spans="7:13">
+    <row r="747" spans="7:13" ht="16.5">
       <c r="G747" s="27"/>
       <c r="M747" s="27"/>
     </row>
-    <row r="748" spans="7:13">
+    <row r="748" spans="7:13" ht="16.5">
       <c r="G748" s="27"/>
       <c r="M748" s="27"/>
     </row>
-    <row r="749" spans="7:13">
+    <row r="749" spans="7:13" ht="16.5">
       <c r="G749" s="27"/>
       <c r="M749" s="27"/>
     </row>
-    <row r="750" spans="7:13">
+    <row r="750" spans="7:13" ht="16.5">
       <c r="G750" s="27"/>
       <c r="M750" s="27"/>
     </row>
-    <row r="751" spans="7:13">
+    <row r="751" spans="7:13" ht="16.5">
       <c r="G751" s="27"/>
       <c r="M751" s="27"/>
     </row>
-    <row r="752" spans="7:13">
+    <row r="752" spans="7:13" ht="16.5">
       <c r="G752" s="27"/>
       <c r="M752" s="27"/>
     </row>
-    <row r="753" spans="7:13">
+    <row r="753" spans="7:13" ht="16.5">
       <c r="G753" s="27"/>
       <c r="M753" s="27"/>
     </row>
-    <row r="754" spans="7:13">
+    <row r="754" spans="7:13" ht="16.5">
       <c r="G754" s="27"/>
       <c r="M754" s="27"/>
     </row>
-    <row r="755" spans="7:13">
+    <row r="755" spans="7:13" ht="16.5">
       <c r="G755" s="27"/>
       <c r="M755" s="27"/>
     </row>
-    <row r="756" spans="7:13">
+    <row r="756" spans="7:13" ht="16.5">
       <c r="G756" s="27"/>
       <c r="M756" s="27"/>
     </row>
-    <row r="757" spans="7:13">
+    <row r="757" spans="7:13" ht="16.5">
       <c r="G757" s="27"/>
       <c r="M757" s="27"/>
     </row>
-    <row r="758" spans="7:13">
+    <row r="758" spans="7:13" ht="16.5">
       <c r="G758" s="27"/>
       <c r="M758" s="27"/>
     </row>
-    <row r="759" spans="7:13">
+    <row r="759" spans="7:13" ht="16.5">
       <c r="G759" s="27"/>
       <c r="M759" s="27"/>
     </row>
-    <row r="760" spans="7:13">
+    <row r="760" spans="7:13" ht="16.5">
       <c r="G760" s="27"/>
       <c r="M760" s="27"/>
     </row>
-    <row r="761" spans="7:13">
+    <row r="761" spans="7:13" ht="16.5">
       <c r="G761" s="27"/>
       <c r="M761" s="27"/>
     </row>
-    <row r="762" spans="7:13">
+    <row r="762" spans="7:13" ht="16.5">
       <c r="G762" s="27"/>
       <c r="M762" s="27"/>
     </row>
-    <row r="763" spans="7:13">
+    <row r="763" spans="7:13" ht="16.5">
       <c r="G763" s="27"/>
       <c r="M763" s="27"/>
     </row>
-    <row r="764" spans="7:13">
+    <row r="764" spans="7:13" ht="16.5">
       <c r="G764" s="27"/>
       <c r="M764" s="27"/>
     </row>
-    <row r="765" spans="7:13">
+    <row r="765" spans="7:13" ht="16.5">
       <c r="G765" s="27"/>
       <c r="M765" s="27"/>
     </row>
-    <row r="766" spans="7:13">
+    <row r="766" spans="7:13" ht="16.5">
       <c r="G766" s="27"/>
       <c r="M766" s="27"/>
     </row>
-    <row r="767" spans="7:13">
+    <row r="767" spans="7:13" ht="16.5">
       <c r="G767" s="27"/>
       <c r="M767" s="27"/>
     </row>
-    <row r="768" spans="7:13">
+    <row r="768" spans="7:13" ht="16.5">
       <c r="G768" s="27"/>
       <c r="M768" s="27"/>
     </row>
-    <row r="769" spans="7:13">
+    <row r="769" spans="7:13" ht="16.5">
       <c r="G769" s="27"/>
       <c r="M769" s="27"/>
     </row>
-    <row r="770" spans="7:13">
+    <row r="770" spans="7:13" ht="16.5">
       <c r="G770" s="27"/>
       <c r="M770" s="27"/>
     </row>
-    <row r="771" spans="7:13">
+    <row r="771" spans="7:13" ht="16.5">
       <c r="G771" s="27"/>
       <c r="M771" s="27"/>
     </row>
-    <row r="772" spans="7:13">
+    <row r="772" spans="7:13" ht="16.5">
       <c r="G772" s="27"/>
       <c r="M772" s="27"/>
     </row>
-    <row r="773" spans="7:13">
+    <row r="773" spans="7:13" ht="16.5">
       <c r="G773" s="27"/>
       <c r="M773" s="27"/>
     </row>
-    <row r="774" spans="7:13">
+    <row r="774" spans="7:13" ht="16.5">
       <c r="G774" s="27"/>
       <c r="M774" s="27"/>
     </row>
-    <row r="775" spans="7:13">
+    <row r="775" spans="7:13" ht="16.5">
       <c r="G775" s="27"/>
       <c r="M775" s="27"/>
     </row>
-    <row r="776" spans="7:13">
+    <row r="776" spans="7:13" ht="16.5">
       <c r="G776" s="27"/>
       <c r="M776" s="27"/>
     </row>
-    <row r="777" spans="7:13">
+    <row r="777" spans="7:13" ht="16.5">
       <c r="G777" s="27"/>
       <c r="M777" s="27"/>
     </row>
-    <row r="778" spans="7:13">
+    <row r="778" spans="7:13" ht="16.5">
       <c r="G778" s="27"/>
       <c r="M778" s="27"/>
     </row>
-    <row r="779" spans="7:13">
+    <row r="779" spans="7:13" ht="16.5">
       <c r="G779" s="27"/>
       <c r="M779" s="27"/>
     </row>
-    <row r="780" spans="7:13">
+    <row r="780" spans="7:13" ht="16.5">
       <c r="G780" s="27"/>
       <c r="M780" s="27"/>
     </row>
-    <row r="781" spans="7:13">
+    <row r="781" spans="7:13" ht="16.5">
       <c r="G781" s="27"/>
       <c r="M781" s="27"/>
     </row>
-    <row r="782" spans="7:13">
+    <row r="782" spans="7:13" ht="16.5">
       <c r="G782" s="27"/>
       <c r="M782" s="27"/>
     </row>
-    <row r="783" spans="7:13">
+    <row r="783" spans="7:13" ht="16.5">
       <c r="G783" s="27"/>
       <c r="M783" s="27"/>
     </row>
-    <row r="784" spans="7:13">
+    <row r="784" spans="7:13" ht="16.5">
       <c r="G784" s="27"/>
       <c r="M784" s="27"/>
     </row>
-    <row r="785" spans="7:13">
+    <row r="785" spans="7:13" ht="16.5">
       <c r="G785" s="27"/>
       <c r="M785" s="27"/>
     </row>
-    <row r="786" spans="7:13">
+    <row r="786" spans="7:13" ht="16.5">
       <c r="G786" s="27"/>
       <c r="M786" s="27"/>
     </row>
-    <row r="787" spans="7:13">
+    <row r="787" spans="7:13" ht="16.5">
       <c r="G787" s="27"/>
       <c r="M787" s="27"/>
     </row>
-    <row r="788" spans="7:13">
+    <row r="788" spans="7:13" ht="16.5">
       <c r="G788" s="27"/>
       <c r="M788" s="27"/>
     </row>
-    <row r="789" spans="7:13">
+    <row r="789" spans="7:13" ht="16.5">
       <c r="G789" s="27"/>
       <c r="M789" s="27"/>
     </row>
-    <row r="790" spans="7:13">
+    <row r="790" spans="7:13" ht="16.5">
       <c r="G790" s="27"/>
       <c r="M790" s="27"/>
     </row>
-    <row r="791" spans="7:13">
+    <row r="791" spans="7:13" ht="16.5">
       <c r="G791" s="27"/>
       <c r="M791" s="27"/>
     </row>
-    <row r="792" spans="7:13">
+    <row r="792" spans="7:13" ht="16.5">
       <c r="G792" s="27"/>
       <c r="M792" s="27"/>
     </row>
-    <row r="793" spans="7:13">
+    <row r="793" spans="7:13" ht="16.5">
       <c r="G793" s="27"/>
       <c r="M793" s="27"/>
     </row>
-    <row r="794" spans="7:13">
+    <row r="794" spans="7:13" ht="16.5">
       <c r="G794" s="27"/>
       <c r="M794" s="27"/>
     </row>
-    <row r="795" spans="7:13">
+    <row r="795" spans="7:13" ht="16.5">
       <c r="G795" s="27"/>
       <c r="M795" s="27"/>
     </row>
-    <row r="796" spans="7:13">
+    <row r="796" spans="7:13" ht="16.5">
       <c r="G796" s="27"/>
       <c r="M796" s="27"/>
     </row>
-    <row r="797" spans="7:13">
+    <row r="797" spans="7:13" ht="16.5">
       <c r="G797" s="27"/>
       <c r="M797" s="27"/>
     </row>
-    <row r="798" spans="7:13">
+    <row r="798" spans="7:13" ht="16.5">
       <c r="G798" s="27"/>
       <c r="M798" s="27"/>
     </row>
-    <row r="799" spans="7:13">
+    <row r="799" spans="7:13" ht="16.5">
       <c r="G799" s="27"/>
       <c r="M799" s="27"/>
     </row>
-    <row r="800" spans="7:13">
+    <row r="800" spans="7:13" ht="16.5">
       <c r="G800" s="27"/>
       <c r="M800" s="27"/>
     </row>
-    <row r="801" spans="7:13">
+    <row r="801" spans="7:13" ht="16.5">
       <c r="G801" s="27"/>
       <c r="M801" s="27"/>
     </row>
-    <row r="802" spans="7:13">
+    <row r="802" spans="7:13" ht="16.5">
       <c r="G802" s="27"/>
       <c r="M802" s="27"/>
     </row>
-    <row r="803" spans="7:13">
+    <row r="803" spans="7:13" ht="16.5">
       <c r="G803" s="27"/>
       <c r="M803" s="27"/>
     </row>
-    <row r="804" spans="7:13">
+    <row r="804" spans="7:13" ht="16.5">
       <c r="G804" s="27"/>
       <c r="M804" s="27"/>
     </row>
-    <row r="805" spans="7:13">
+    <row r="805" spans="7:13" ht="16.5">
       <c r="G805" s="27"/>
       <c r="M805" s="27"/>
     </row>
-    <row r="806" spans="7:13">
+    <row r="806" spans="7:13" ht="16.5">
       <c r="G806" s="27"/>
       <c r="M806" s="27"/>
     </row>
-    <row r="807" spans="7:13">
+    <row r="807" spans="7:13" ht="16.5">
       <c r="G807" s="27"/>
       <c r="M807" s="27"/>
     </row>
-    <row r="808" spans="7:13">
+    <row r="808" spans="7:13" ht="16.5">
       <c r="G808" s="27"/>
       <c r="M808" s="27"/>
     </row>
-    <row r="809" spans="7:13">
+    <row r="809" spans="7:13" ht="16.5">
       <c r="G809" s="27"/>
       <c r="M809" s="27"/>
     </row>
-    <row r="810" spans="7:13">
+    <row r="810" spans="7:13" ht="16.5">
       <c r="G810" s="27"/>
       <c r="M810" s="27"/>
     </row>
-    <row r="811" spans="7:13">
+    <row r="811" spans="7:13" ht="16.5">
       <c r="G811" s="27"/>
       <c r="M811" s="27"/>
     </row>
-    <row r="812" spans="7:13">
+    <row r="812" spans="7:13" ht="16.5">
       <c r="G812" s="27"/>
       <c r="M812" s="27"/>
     </row>
-    <row r="813" spans="7:13">
+    <row r="813" spans="7:13" ht="16.5">
       <c r="G813" s="27"/>
       <c r="M813" s="27"/>
     </row>
-    <row r="814" spans="7:13">
+    <row r="814" spans="7:13" ht="16.5">
       <c r="G814" s="27"/>
       <c r="M814" s="27"/>
     </row>
-    <row r="815" spans="7:13">
+    <row r="815" spans="7:13" ht="16.5">
       <c r="G815" s="27"/>
       <c r="M815" s="27"/>
     </row>
-    <row r="816" spans="7:13">
+    <row r="816" spans="7:13" ht="16.5">
       <c r="G816" s="27"/>
       <c r="M816" s="27"/>
     </row>
-    <row r="817" spans="7:13">
+    <row r="817" spans="7:13" ht="16.5">
       <c r="G817" s="27"/>
       <c r="M817" s="27"/>
     </row>
-    <row r="818" spans="7:13">
+    <row r="818" spans="7:13" ht="16.5">
       <c r="G818" s="27"/>
       <c r="M818" s="27"/>
     </row>
-    <row r="819" spans="7:13">
+    <row r="819" spans="7:13" ht="16.5">
       <c r="G819" s="27"/>
       <c r="M819" s="27"/>
     </row>
-    <row r="820" spans="7:13">
+    <row r="820" spans="7:13" ht="16.5">
       <c r="G820" s="27"/>
       <c r="M820" s="27"/>
     </row>
-    <row r="821" spans="7:13">
+    <row r="821" spans="7:13" ht="16.5">
       <c r="G821" s="27"/>
       <c r="M821" s="27"/>
     </row>
-    <row r="822" spans="7:13">
+    <row r="822" spans="7:13" ht="16.5">
       <c r="G822" s="27"/>
       <c r="M822" s="27"/>
     </row>
-    <row r="823" spans="7:13">
+    <row r="823" spans="7:13" ht="16.5">
       <c r="G823" s="27"/>
       <c r="M823" s="27"/>
     </row>
-    <row r="824" spans="7:13">
+    <row r="824" spans="7:13" ht="16.5">
       <c r="G824" s="27"/>
       <c r="M824" s="27"/>
     </row>
-    <row r="825" spans="7:13">
+    <row r="825" spans="7:13" ht="16.5">
       <c r="G825" s="27"/>
       <c r="M825" s="27"/>
     </row>
-    <row r="826" spans="7:13">
+    <row r="826" spans="7:13" ht="16.5">
       <c r="G826" s="27"/>
       <c r="M826" s="27"/>
     </row>
-    <row r="827" spans="7:13">
+    <row r="827" spans="7:13" ht="16.5">
       <c r="G827" s="27"/>
       <c r="M827" s="27"/>
     </row>
-    <row r="828" spans="7:13">
+    <row r="828" spans="7:13" ht="16.5">
       <c r="G828" s="27"/>
       <c r="M828" s="27"/>
     </row>
-    <row r="829" spans="7:13">
+    <row r="829" spans="7:13" ht="16.5">
       <c r="G829" s="27"/>
       <c r="M829" s="27"/>
     </row>
-    <row r="830" spans="7:13">
+    <row r="830" spans="7:13" ht="16.5">
       <c r="G830" s="27"/>
       <c r="M830" s="27"/>
     </row>
-    <row r="831" spans="7:13">
+    <row r="831" spans="7:13" ht="16.5">
       <c r="G831" s="27"/>
       <c r="M831" s="27"/>
     </row>
-    <row r="832" spans="7:13">
+    <row r="832" spans="7:13" ht="16.5">
       <c r="G832" s="27"/>
       <c r="M832" s="27"/>
     </row>
-    <row r="833" spans="7:13">
+    <row r="833" spans="7:13" ht="16.5">
       <c r="G833" s="27"/>
       <c r="M833" s="27"/>
     </row>
-    <row r="834" spans="7:13">
+    <row r="834" spans="7:13" ht="16.5">
       <c r="G834" s="27"/>
       <c r="M834" s="27"/>
     </row>
-    <row r="835" spans="7:13">
+    <row r="835" spans="7:13" ht="16.5">
       <c r="G835" s="27"/>
       <c r="M835" s="27"/>
     </row>
-    <row r="836" spans="7:13">
+    <row r="836" spans="7:13" ht="16.5">
       <c r="G836" s="27"/>
       <c r="M836" s="27"/>
     </row>
-    <row r="837" spans="7:13">
+    <row r="837" spans="7:13" ht="16.5">
       <c r="G837" s="27"/>
       <c r="M837" s="27"/>
     </row>
-    <row r="838" spans="7:13">
+    <row r="838" spans="7:13" ht="16.5">
       <c r="G838" s="27"/>
       <c r="M838" s="27"/>
     </row>
-    <row r="839" spans="7:13">
+    <row r="839" spans="7:13" ht="16.5">
       <c r="G839" s="27"/>
       <c r="M839" s="27"/>
     </row>
-    <row r="840" spans="7:13">
+    <row r="840" spans="7:13" ht="16.5">
       <c r="G840" s="27"/>
       <c r="M840" s="27"/>
     </row>
-    <row r="841" spans="7:13">
+    <row r="841" spans="7:13" ht="16.5">
       <c r="G841" s="27"/>
       <c r="M841" s="27"/>
     </row>
-    <row r="842" spans="7:13">
+    <row r="842" spans="7:13" ht="16.5">
       <c r="G842" s="27"/>
       <c r="M842" s="27"/>
     </row>
-    <row r="843" spans="7:13">
+    <row r="843" spans="7:13" ht="16.5">
       <c r="G843" s="27"/>
       <c r="M843" s="27"/>
     </row>
-    <row r="844" spans="7:13">
+    <row r="844" spans="7:13" ht="16.5">
       <c r="G844" s="27"/>
       <c r="M844" s="27"/>
     </row>
-    <row r="845" spans="7:13">
+    <row r="845" spans="7:13" ht="16.5">
       <c r="G845" s="27"/>
       <c r="M845" s="27"/>
     </row>
-    <row r="846" spans="7:13">
+    <row r="846" spans="7:13" ht="16.5">
       <c r="G846" s="27"/>
       <c r="M846" s="27"/>
     </row>
-    <row r="847" spans="7:13">
+    <row r="847" spans="7:13" ht="16.5">
       <c r="G847" s="27"/>
       <c r="M847" s="27"/>
     </row>
-    <row r="848" spans="7:13">
+    <row r="848" spans="7:13" ht="16.5">
       <c r="G848" s="27"/>
       <c r="M848" s="27"/>
     </row>
-    <row r="849" spans="7:13">
+    <row r="849" spans="7:13" ht="16.5">
       <c r="G849" s="27"/>
       <c r="M849" s="27"/>
     </row>
-    <row r="850" spans="7:13">
+    <row r="850" spans="7:13" ht="16.5">
       <c r="G850" s="27"/>
       <c r="M850" s="27"/>
     </row>
-    <row r="851" spans="7:13">
+    <row r="851" spans="7:13" ht="16.5">
       <c r="G851" s="27"/>
       <c r="M851" s="27"/>
     </row>
-    <row r="852" spans="7:13">
+    <row r="852" spans="7:13" ht="16.5">
       <c r="G852" s="27"/>
       <c r="M852" s="27"/>
     </row>
-    <row r="853" spans="7:13">
+    <row r="853" spans="7:13" ht="16.5">
       <c r="G853" s="27"/>
       <c r="M853" s="27"/>
     </row>
-    <row r="854" spans="7:13">
+    <row r="854" spans="7:13" ht="16.5">
       <c r="G854" s="27"/>
       <c r="M854" s="27"/>
     </row>
-    <row r="855" spans="7:13">
+    <row r="855" spans="7:13" ht="16.5">
       <c r="G855" s="27"/>
       <c r="M855" s="27"/>
     </row>
-    <row r="856" spans="7:13">
+    <row r="856" spans="7:13" ht="16.5">
       <c r="G856" s="27"/>
       <c r="M856" s="27"/>
     </row>
-    <row r="857" spans="7:13">
+    <row r="857" spans="7:13" ht="16.5">
       <c r="G857" s="27"/>
       <c r="M857" s="27"/>
     </row>
-    <row r="858" spans="7:13">
+    <row r="858" spans="7:13" ht="16.5">
       <c r="G858" s="27"/>
       <c r="M858" s="27"/>
     </row>
-    <row r="859" spans="7:13">
+    <row r="859" spans="7:13" ht="16.5">
       <c r="G859" s="27"/>
       <c r="M859" s="27"/>
     </row>
-    <row r="860" spans="7:13">
+    <row r="860" spans="7:13" ht="16.5">
       <c r="G860" s="27"/>
       <c r="M860" s="27"/>
     </row>
-    <row r="861" spans="7:13">
+    <row r="861" spans="7:13" ht="16.5">
       <c r="G861" s="27"/>
       <c r="M861" s="27"/>
     </row>
-    <row r="862" spans="7:13">
+    <row r="862" spans="7:13" ht="16.5">
       <c r="G862" s="27"/>
       <c r="M862" s="27"/>
     </row>
-    <row r="863" spans="7:13">
+    <row r="863" spans="7:13" ht="16.5">
       <c r="G863" s="27"/>
       <c r="M863" s="27"/>
     </row>
-    <row r="864" spans="7:13">
+    <row r="864" spans="7:13" ht="16.5">
       <c r="G864" s="27"/>
       <c r="M864" s="27"/>
     </row>
-    <row r="865" spans="7:13">
+    <row r="865" spans="7:13" ht="16.5">
       <c r="G865" s="27"/>
       <c r="M865" s="27"/>
     </row>
-    <row r="866" spans="7:13">
+    <row r="866" spans="7:13" ht="16.5">
       <c r="G866" s="27"/>
       <c r="M866" s="27"/>
     </row>
-    <row r="867" spans="7:13">
+    <row r="867" spans="7:13" ht="16.5">
       <c r="G867" s="27"/>
       <c r="M867" s="27"/>
     </row>
-    <row r="868" spans="7:13">
+    <row r="868" spans="7:13" ht="16.5">
       <c r="G868" s="27"/>
       <c r="M868" s="27"/>
     </row>
-    <row r="869" spans="7:13">
+    <row r="869" spans="7:13" ht="16.5">
       <c r="G869" s="27"/>
       <c r="M869" s="27"/>
     </row>
-    <row r="870" spans="7:13">
+    <row r="870" spans="7:13" ht="16.5">
       <c r="G870" s="27"/>
       <c r="M870" s="27"/>
     </row>
-    <row r="871" spans="7:13">
+    <row r="871" spans="7:13" ht="16.5">
       <c r="G871" s="27"/>
       <c r="M871" s="27"/>
     </row>
-    <row r="872" spans="7:13">
+    <row r="872" spans="7:13" ht="16.5">
       <c r="G872" s="27"/>
       <c r="M872" s="27"/>
     </row>
-    <row r="873" spans="7:13">
+    <row r="873" spans="7:13" ht="16.5">
       <c r="G873" s="27"/>
       <c r="M873" s="27"/>
     </row>
-    <row r="874" spans="7:13">
+    <row r="874" spans="7:13" ht="16.5">
       <c r="G874" s="27"/>
       <c r="M874" s="27"/>
     </row>
-    <row r="875" spans="7:13">
+    <row r="875" spans="7:13" ht="16.5">
       <c r="G875" s="27"/>
       <c r="M875" s="27"/>
     </row>
-    <row r="876" spans="7:13">
+    <row r="876" spans="7:13" ht="16.5">
       <c r="G876" s="27"/>
       <c r="M876" s="27"/>
     </row>
-    <row r="877" spans="7:13">
+    <row r="877" spans="7:13" ht="16.5">
       <c r="G877" s="27"/>
       <c r="M877" s="27"/>
     </row>
-    <row r="878" spans="7:13">
+    <row r="878" spans="7:13" ht="16.5">
       <c r="G878" s="27"/>
       <c r="M878" s="27"/>
     </row>
-    <row r="879" spans="7:13">
+    <row r="879" spans="7:13" ht="16.5">
       <c r="G879" s="27"/>
       <c r="M879" s="27"/>
     </row>
-    <row r="880" spans="7:13">
+    <row r="880" spans="7:13" ht="16.5">
       <c r="G880" s="27"/>
       <c r="M880" s="27"/>
     </row>
-    <row r="881" spans="7:13">
+    <row r="881" spans="7:13" ht="16.5">
       <c r="G881" s="27"/>
       <c r="M881" s="27"/>
     </row>
-    <row r="882" spans="7:13">
+    <row r="882" spans="7:13" ht="16.5">
       <c r="G882" s="27"/>
       <c r="M882" s="27"/>
     </row>
-    <row r="883" spans="7:13">
+    <row r="883" spans="7:13" ht="16.5">
       <c r="G883" s="27"/>
       <c r="M883" s="27"/>
     </row>
-    <row r="884" spans="7:13">
+    <row r="884" spans="7:13" ht="16.5">
       <c r="G884" s="27"/>
       <c r="M884" s="27"/>
     </row>
-    <row r="885" spans="7:13">
+    <row r="885" spans="7:13" ht="16.5">
       <c r="G885" s="27"/>
       <c r="M885" s="27"/>
     </row>
-    <row r="886" spans="7:13">
+    <row r="886" spans="7:13" ht="16.5">
       <c r="G886" s="27"/>
       <c r="M886" s="27"/>
     </row>
-    <row r="887" spans="7:13">
+    <row r="887" spans="7:13" ht="16.5">
       <c r="G887" s="27"/>
       <c r="M887" s="27"/>
     </row>
-    <row r="888" spans="7:13">
+    <row r="888" spans="7:13" ht="16.5">
       <c r="G888" s="27"/>
       <c r="M888" s="27"/>
     </row>
-    <row r="889" spans="7:13">
+    <row r="889" spans="7:13" ht="16.5">
       <c r="G889" s="27"/>
       <c r="M889" s="27"/>
     </row>
-    <row r="890" spans="7:13">
+    <row r="890" spans="7:13" ht="16.5">
       <c r="G890" s="27"/>
       <c r="M890" s="27"/>
     </row>
-    <row r="891" spans="7:13">
+    <row r="891" spans="7:13" ht="16.5">
       <c r="G891" s="27"/>
       <c r="M891" s="27"/>
     </row>
-    <row r="892" spans="7:13">
+    <row r="892" spans="7:13" ht="16.5">
       <c r="G892" s="27"/>
       <c r="M892" s="27"/>
     </row>
-    <row r="893" spans="7:13">
+    <row r="893" spans="7:13" ht="16.5">
       <c r="G893" s="27"/>
       <c r="M893" s="27"/>
     </row>
-    <row r="894" spans="7:13">
+    <row r="894" spans="7:13" ht="16.5">
       <c r="G894" s="27"/>
       <c r="M894" s="27"/>
     </row>
-    <row r="895" spans="7:13">
+    <row r="895" spans="7:13" ht="16.5">
       <c r="G895" s="27"/>
       <c r="M895" s="27"/>
     </row>
-    <row r="896" spans="7:13">
+    <row r="896" spans="7:13" ht="16.5">
       <c r="G896" s="27"/>
       <c r="M896" s="27"/>
     </row>
-    <row r="897" spans="7:13">
+    <row r="897" spans="7:13" ht="16.5">
       <c r="G897" s="27"/>
       <c r="M897" s="27"/>
     </row>
-    <row r="898" spans="7:13">
+    <row r="898" spans="7:13" ht="16.5">
       <c r="G898" s="27"/>
       <c r="M898" s="27"/>
     </row>
-    <row r="899" spans="7:13">
+    <row r="899" spans="7:13" ht="16.5">
       <c r="G899" s="27"/>
       <c r="M899" s="27"/>
     </row>
-    <row r="900" spans="7:13">
+    <row r="900" spans="7:13" ht="16.5">
       <c r="G900" s="27"/>
       <c r="M900" s="27"/>
     </row>
-    <row r="901" spans="7:13">
+    <row r="901" spans="7:13" ht="16.5">
       <c r="G901" s="27"/>
       <c r="M901" s="27"/>
     </row>
-    <row r="902" spans="7:13">
+    <row r="902" spans="7:13" ht="16.5">
       <c r="G902" s="27"/>
       <c r="M902" s="27"/>
     </row>
-    <row r="903" spans="7:13">
+    <row r="903" spans="7:13" ht="16.5">
       <c r="G903" s="27"/>
       <c r="M903" s="27"/>
     </row>
-    <row r="904" spans="7:13">
+    <row r="904" spans="7:13" ht="16.5">
       <c r="G904" s="27"/>
       <c r="M904" s="27"/>
     </row>
-    <row r="905" spans="7:13">
+    <row r="905" spans="7:13" ht="16.5">
       <c r="G905" s="27"/>
       <c r="M905" s="27"/>
     </row>
-    <row r="906" spans="7:13">
+    <row r="906" spans="7:13" ht="16.5">
       <c r="G906" s="27"/>
       <c r="M906" s="27"/>
     </row>
-    <row r="907" spans="7:13">
+    <row r="907" spans="7:13" ht="16.5">
       <c r="G907" s="27"/>
       <c r="M907" s="27"/>
     </row>
-    <row r="908" spans="7:13">
+    <row r="908" spans="7:13" ht="16.5">
       <c r="G908" s="27"/>
       <c r="M908" s="27"/>
     </row>
-    <row r="909" spans="7:13">
+    <row r="909" spans="7:13" ht="16.5">
       <c r="G909" s="27"/>
       <c r="M909" s="27"/>
     </row>
-    <row r="910" spans="7:13">
+    <row r="910" spans="7:13" ht="16.5">
       <c r="G910" s="27"/>
       <c r="M910" s="27"/>
     </row>
-    <row r="911" spans="7:13">
+    <row r="911" spans="7:13" ht="16.5">
       <c r="G911" s="27"/>
       <c r="M911" s="27"/>
     </row>
-    <row r="912" spans="7:13">
+    <row r="912" spans="7:13" ht="16.5">
       <c r="G912" s="27"/>
       <c r="M912" s="27"/>
     </row>
-    <row r="913" spans="7:13">
+    <row r="913" spans="7:13" ht="16.5">
       <c r="G913" s="27"/>
       <c r="M913" s="27"/>
     </row>
-    <row r="914" spans="7:13">
+    <row r="914" spans="7:13" ht="16.5">
       <c r="G914" s="27"/>
       <c r="M914" s="27"/>
     </row>
-    <row r="915" spans="7:13">
+    <row r="915" spans="7:13" ht="16.5">
       <c r="G915" s="27"/>
       <c r="M915" s="27"/>
     </row>
-    <row r="916" spans="7:13">
+    <row r="916" spans="7:13" ht="16.5">
       <c r="G916" s="27"/>
       <c r="M916" s="27"/>
     </row>
-    <row r="917" spans="7:13">
+    <row r="917" spans="7:13" ht="16.5">
       <c r="G917" s="27"/>
       <c r="M917" s="27"/>
     </row>
-    <row r="918" spans="7:13">
+    <row r="918" spans="7:13" ht="16.5">
       <c r="G918" s="27"/>
       <c r="M918" s="27"/>
     </row>
-    <row r="919" spans="7:13">
+    <row r="919" spans="7:13" ht="16.5">
       <c r="G919" s="27"/>
       <c r="M919" s="27"/>
     </row>
-    <row r="920" spans="7:13">
+    <row r="920" spans="7:13" ht="16.5">
       <c r="G920" s="27"/>
       <c r="M920" s="27"/>
     </row>
-    <row r="921" spans="7:13">
+    <row r="921" spans="7:13" ht="16.5">
       <c r="G921" s="27"/>
       <c r="M921" s="27"/>
     </row>
-    <row r="922" spans="7:13">
+    <row r="922" spans="7:13" ht="16.5">
       <c r="G922" s="27"/>
       <c r="M922" s="27"/>
     </row>
-    <row r="923" spans="7:13">
+    <row r="923" spans="7:13" ht="16.5">
       <c r="G923" s="27"/>
       <c r="M923" s="27"/>
     </row>
-    <row r="924" spans="7:13">
+    <row r="924" spans="7:13" ht="16.5">
       <c r="G924" s="27"/>
       <c r="M924" s="27"/>
     </row>
-    <row r="925" spans="7:13">
+    <row r="925" spans="7:13" ht="16.5">
       <c r="G925" s="27"/>
       <c r="M925" s="27"/>
     </row>
-    <row r="926" spans="7:13">
+    <row r="926" spans="7:13" ht="16.5">
       <c r="G926" s="27"/>
       <c r="M926" s="27"/>
     </row>
-    <row r="927" spans="7:13">
+    <row r="927" spans="7:13" ht="16.5">
       <c r="G927" s="27"/>
       <c r="M927" s="27"/>
     </row>
-    <row r="928" spans="7:13">
+    <row r="928" spans="7:13" ht="16.5">
       <c r="G928" s="27"/>
       <c r="M928" s="27"/>
     </row>
-    <row r="929" spans="7:13">
+    <row r="929" spans="7:13" ht="16.5">
       <c r="G929" s="27"/>
       <c r="M929" s="27"/>
     </row>
-    <row r="930" spans="7:13">
+    <row r="930" spans="7:13" ht="16.5">
       <c r="G930" s="27"/>
       <c r="M930" s="27"/>
     </row>
-    <row r="931" spans="7:13">
+    <row r="931" spans="7:13" ht="16.5">
       <c r="G931" s="27"/>
       <c r="M931" s="27"/>
     </row>
-    <row r="932" spans="7:13">
+    <row r="932" spans="7:13" ht="16.5">
       <c r="G932" s="27"/>
       <c r="M932" s="27"/>
     </row>
-    <row r="933" spans="7:13">
+    <row r="933" spans="7:13" ht="16.5">
       <c r="G933" s="27"/>
       <c r="M933" s="27"/>
     </row>
-    <row r="934" spans="7:13">
+    <row r="934" spans="7:13" ht="16.5">
       <c r="G934" s="27"/>
       <c r="M934" s="27"/>
     </row>
-    <row r="935" spans="7:13">
+    <row r="935" spans="7:13" ht="16.5">
       <c r="G935" s="27"/>
       <c r="M935" s="27"/>
     </row>
-    <row r="936" spans="7:13">
+    <row r="936" spans="7:13" ht="16.5">
       <c r="G936" s="27"/>
       <c r="M936" s="27"/>
     </row>
-    <row r="937" spans="7:13">
+    <row r="937" spans="7:13" ht="16.5">
       <c r="G937" s="27"/>
       <c r="M937" s="27"/>
     </row>
-    <row r="938" spans="7:13">
+    <row r="938" spans="7:13" ht="16.5">
       <c r="G938" s="27"/>
       <c r="M938" s="27"/>
     </row>
-    <row r="939" spans="7:13">
+    <row r="939" spans="7:13" ht="16.5">
       <c r="G939" s="27"/>
       <c r="M939" s="27"/>
     </row>
-    <row r="940" spans="7:13">
+    <row r="940" spans="7:13" ht="16.5">
       <c r="G940" s="27"/>
       <c r="M940" s="27"/>
     </row>
-    <row r="941" spans="7:13">
+    <row r="941" spans="7:13" ht="16.5">
       <c r="G941" s="27"/>
       <c r="M941" s="27"/>
     </row>
-    <row r="942" spans="7:13">
+    <row r="942" spans="7:13" ht="16.5">
       <c r="G942" s="27"/>
       <c r="M942" s="27"/>
     </row>
-    <row r="943" spans="7:13">
+    <row r="943" spans="7:13" ht="16.5">
       <c r="G943" s="27"/>
       <c r="M943" s="27"/>
     </row>
-    <row r="944" spans="7:13">
+    <row r="944" spans="7:13" ht="16.5">
       <c r="G944" s="27"/>
       <c r="M944" s="27"/>
     </row>
-    <row r="945" spans="7:13">
+    <row r="945" spans="7:13" ht="16.5">
       <c r="G945" s="27"/>
       <c r="M945" s="27"/>
     </row>
-    <row r="946" spans="7:13">
+    <row r="946" spans="7:13" ht="16.5">
       <c r="G946" s="27"/>
       <c r="M946" s="27"/>
     </row>
-    <row r="947" spans="7:13">
+    <row r="947" spans="7:13" ht="16.5">
       <c r="G947" s="27"/>
       <c r="M947" s="27"/>
     </row>
-    <row r="948" spans="7:13">
+    <row r="948" spans="7:13" ht="16.5">
       <c r="G948" s="27"/>
       <c r="M948" s="27"/>
     </row>
-    <row r="949" spans="7:13">
+    <row r="949" spans="7:13" ht="16.5">
       <c r="G949" s="27"/>
       <c r="M949" s="27"/>
     </row>
-    <row r="950" spans="7:13">
+    <row r="950" spans="7:13" ht="16.5">
       <c r="G950" s="27"/>
       <c r="M950" s="27"/>
     </row>
-    <row r="951" spans="7:13">
+    <row r="951" spans="7:13" ht="16.5">
       <c r="G951" s="27"/>
       <c r="M951" s="27"/>
     </row>
-    <row r="952" spans="7:13">
+    <row r="952" spans="7:13" ht="16.5">
       <c r="G952" s="27"/>
       <c r="M952" s="27"/>
     </row>
-    <row r="953" spans="7:13">
+    <row r="953" spans="7:13" ht="16.5">
       <c r="G953" s="27"/>
       <c r="M953" s="27"/>
     </row>
-    <row r="954" spans="7:13">
+    <row r="954" spans="7:13" ht="16.5">
       <c r="G954" s="27"/>
       <c r="M954" s="27"/>
     </row>
-    <row r="955" spans="7:13">
+    <row r="955" spans="7:13" ht="16.5">
       <c r="G955" s="27"/>
       <c r="M955" s="27"/>
     </row>
-    <row r="956" spans="7:13">
+    <row r="956" spans="7:13" ht="16.5">
       <c r="G956" s="27"/>
       <c r="M956" s="27"/>
     </row>
-    <row r="957" spans="7:13">
+    <row r="957" spans="7:13" ht="16.5">
       <c r="G957" s="27"/>
       <c r="M957" s="27"/>
     </row>
-    <row r="958" spans="7:13">
+    <row r="958" spans="7:13" ht="16.5">
       <c r="G958" s="27"/>
       <c r="M958" s="27"/>
     </row>
-    <row r="959" spans="7:13">
+    <row r="959" spans="7:13" ht="16.5">
       <c r="G959" s="27"/>
       <c r="M959" s="27"/>
     </row>
-    <row r="960" spans="7:13">
+    <row r="960" spans="7:13" ht="16.5">
       <c r="G960" s="27"/>
       <c r="M960" s="27"/>
     </row>
-    <row r="961" spans="7:13">
+    <row r="961" spans="7:13" ht="16.5">
       <c r="G961" s="27"/>
       <c r="M961" s="27"/>
     </row>
-    <row r="962" spans="7:13">
+    <row r="962" spans="7:13" ht="16.5">
       <c r="G962" s="27"/>
       <c r="M962" s="27"/>
     </row>
-    <row r="963" spans="7:13">
+    <row r="963" spans="7:13" ht="16.5">
       <c r="G963" s="27"/>
       <c r="M963" s="27"/>
     </row>
-    <row r="964" spans="7:13">
+    <row r="964" spans="7:13" ht="16.5">
       <c r="G964" s="27"/>
       <c r="M964" s="27"/>
     </row>
-    <row r="965" spans="7:13">
+    <row r="965" spans="7:13" ht="16.5">
       <c r="G965" s="27"/>
       <c r="M965" s="27"/>
     </row>
-    <row r="966" spans="7:13">
+    <row r="966" spans="7:13" ht="16.5">
       <c r="G966" s="27"/>
       <c r="M966" s="27"/>
     </row>
-    <row r="967" spans="7:13">
+    <row r="967" spans="7:13" ht="16.5">
       <c r="G967" s="27"/>
       <c r="M967" s="27"/>
     </row>
-    <row r="968" spans="7:13">
+    <row r="968" spans="7:13" ht="16.5">
       <c r="G968" s="27"/>
       <c r="M968" s="27"/>
     </row>
-    <row r="969" spans="7:13">
+    <row r="969" spans="7:13" ht="16.5">
       <c r="G969" s="27"/>
       <c r="M969" s="27"/>
     </row>
-    <row r="970" spans="7:13">
+    <row r="970" spans="7:13" ht="16.5">
       <c r="G970" s="27"/>
       <c r="M970" s="27"/>
     </row>
-    <row r="971" spans="7:13">
+    <row r="971" spans="7:13" ht="16.5">
       <c r="G971" s="27"/>
       <c r="M971" s="27"/>
     </row>
-    <row r="972" spans="7:13">
+    <row r="972" spans="7:13" ht="16.5">
       <c r="G972" s="27"/>
       <c r="M972" s="27"/>
     </row>
-    <row r="973" spans="7:13">
+    <row r="973" spans="7:13" ht="16.5">
       <c r="G973" s="27"/>
       <c r="M973" s="27"/>
     </row>
-    <row r="974" spans="7:13">
+    <row r="974" spans="7:13" ht="16.5">
       <c r="G974" s="27"/>
       <c r="M974" s="27"/>
     </row>
-    <row r="975" spans="7:13">
+    <row r="975" spans="7:13" ht="16.5">
       <c r="G975" s="27"/>
       <c r="M975" s="27"/>
     </row>
-    <row r="976" spans="7:13">
+    <row r="976" spans="7:13" ht="16.5">
       <c r="G976" s="27"/>
       <c r="M976" s="27"/>
     </row>
-    <row r="977" spans="7:13">
+    <row r="977" spans="7:13" ht="16.5">
       <c r="G977" s="27"/>
       <c r="M977" s="27"/>
     </row>
-    <row r="978" spans="7:13">
+    <row r="978" spans="7:13" ht="16.5">
       <c r="G978" s="27"/>
       <c r="M978" s="27"/>
     </row>
-    <row r="979" spans="7:13">
+    <row r="979" spans="7:13" ht="16.5">
       <c r="G979" s="27"/>
       <c r="M979" s="27"/>
     </row>
-    <row r="980" spans="7:13">
+    <row r="980" spans="7:13" ht="16.5">
       <c r="G980" s="27"/>
       <c r="M980" s="27"/>
     </row>
-    <row r="981" spans="7:13">
+    <row r="981" spans="7:13" ht="16.5">
       <c r="G981" s="27"/>
       <c r="M981" s="27"/>
     </row>
-    <row r="982" spans="7:13">
+    <row r="982" spans="7:13" ht="16.5">
       <c r="G982" s="27"/>
       <c r="M982" s="27"/>
     </row>
-    <row r="983" spans="7:13">
+    <row r="983" spans="7:13" ht="16.5">
       <c r="G983" s="27"/>
       <c r="M983" s="27"/>
     </row>
-    <row r="984" spans="7:13">
+    <row r="984" spans="7:13" ht="16.5">
       <c r="G984" s="27"/>
       <c r="M984" s="27"/>
     </row>
-    <row r="985" spans="7:13">
+    <row r="985" spans="7:13" ht="16.5">
       <c r="G985" s="27"/>
       <c r="M985" s="27"/>
     </row>
-    <row r="986" spans="7:13">
+    <row r="986" spans="7:13" ht="16.5">
       <c r="G986" s="27"/>
       <c r="M986" s="27"/>
     </row>
-    <row r="987" spans="7:13">
+    <row r="987" spans="7:13" ht="16.5">
       <c r="G987" s="27"/>
       <c r="M987" s="27"/>
     </row>
-    <row r="988" spans="7:13">
+    <row r="988" spans="7:13" ht="16.5">
       <c r="G988" s="27"/>
       <c r="M988" s="27"/>
     </row>
-    <row r="989" spans="7:13">
+    <row r="989" spans="7:13" ht="16.5">
       <c r="G989" s="27"/>
       <c r="M989" s="27"/>
     </row>
-    <row r="990" spans="7:13">
+    <row r="990" spans="7:13" ht="16.5">
       <c r="G990" s="27"/>
       <c r="M990" s="27"/>
     </row>
-    <row r="991" spans="7:13">
+    <row r="991" spans="7:13" ht="16.5">
       <c r="G991" s="27"/>
       <c r="M991" s="27"/>
     </row>
-    <row r="992" spans="7:13">
+    <row r="992" spans="7:13" ht="16.5">
       <c r="G992" s="27"/>
       <c r="M992" s="27"/>
     </row>
-    <row r="993" spans="7:13">
+    <row r="993" spans="7:13" ht="16.5">
       <c r="G993" s="27"/>
       <c r="M993" s="27"/>
     </row>
-    <row r="994" spans="7:13">
+    <row r="994" spans="7:13" ht="16.5">
       <c r="G994" s="27"/>
       <c r="M994" s="27"/>
     </row>
-    <row r="995" spans="7:13">
+    <row r="995" spans="7:13" ht="16.5">
       <c r="G995" s="27"/>
       <c r="M995" s="27"/>
     </row>
-    <row r="996" spans="7:13">
+    <row r="996" spans="7:13" ht="16.5">
       <c r="G996" s="27"/>
       <c r="M996" s="27"/>
     </row>
-    <row r="997" spans="7:13">
+    <row r="997" spans="7:13" ht="16.5">
       <c r="G997" s="27"/>
       <c r="M997" s="27"/>
     </row>
-    <row r="998" spans="7:13">
+    <row r="998" spans="7:13" ht="16.5">
       <c r="G998" s="27"/>
       <c r="M998" s="27"/>
     </row>
-    <row r="999" spans="7:13">
+    <row r="999" spans="7:13" ht="16.5">
       <c r="G999" s="27"/>
       <c r="M999" s="27"/>
     </row>
-    <row r="1000" spans="7:13">
+    <row r="1000" spans="7:13" ht="16.5">
       <c r="G1000" s="27"/>
       <c r="M1000" s="27"/>
     </row>
@@ -21313,130 +21342,6 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
-  <dimension ref="A1:K11"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
-  <cols>
-    <col min="1" max="1" width="22.625" customWidth="1"/>
-    <col min="2" max="2" width="17.25" customWidth="1"/>
-    <col min="3" max="3" width="18.75" customWidth="1"/>
-    <col min="4" max="4" width="25.25" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:11">
-      <c r="A1" t="s">
-        <v>21</v>
-      </c>
-      <c r="B1" t="s">
-        <v>15</v>
-      </c>
-      <c r="C1" t="s">
-        <v>1</v>
-      </c>
-      <c r="D1" t="s">
-        <v>568</v>
-      </c>
-    </row>
-    <row r="2" spans="1:11">
-      <c r="A2" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="3" spans="1:11">
-      <c r="A3" t="s">
-        <v>65</v>
-      </c>
-      <c r="C3" t="s">
-        <v>67</v>
-      </c>
-      <c r="D3" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="4" spans="1:11">
-      <c r="A4" t="s">
-        <v>569</v>
-      </c>
-      <c r="B4">
-        <v>1</v>
-      </c>
-      <c r="C4" t="s">
-        <v>570</v>
-      </c>
-      <c r="D4" s="33" t="s">
-        <v>1728</v>
-      </c>
-    </row>
-    <row r="5" spans="1:11">
-      <c r="A5" s="33" t="s">
-        <v>1715</v>
-      </c>
-      <c r="B5">
-        <v>2</v>
-      </c>
-      <c r="C5" t="s">
-        <v>570</v>
-      </c>
-      <c r="D5" s="33" t="s">
-        <v>1727</v>
-      </c>
-      <c r="J5" t="s">
-        <v>15</v>
-      </c>
-      <c r="K5" t="s">
-        <v>571</v>
-      </c>
-    </row>
-    <row r="6" spans="1:11">
-      <c r="A6" s="33" t="s">
-        <v>1716</v>
-      </c>
-      <c r="B6">
-        <v>3</v>
-      </c>
-      <c r="C6" t="s">
-        <v>570</v>
-      </c>
-      <c r="D6" s="33" t="s">
-        <v>1727</v>
-      </c>
-      <c r="K6" t="s">
-        <v>572</v>
-      </c>
-    </row>
-    <row r="7" spans="1:11">
-      <c r="K7" t="s">
-        <v>573</v>
-      </c>
-    </row>
-    <row r="8" spans="1:11">
-      <c r="K8" t="s">
-        <v>574</v>
-      </c>
-    </row>
-    <row r="9" spans="1:11">
-      <c r="K9" s="17" t="s">
-        <v>575</v>
-      </c>
-    </row>
-    <row r="10" spans="1:11">
-      <c r="K10" s="33" t="s">
-        <v>1679</v>
-      </c>
-    </row>
-    <row r="11" spans="1:11">
-      <c r="K11" s="33" t="s">
-        <v>1680</v>
-      </c>
-    </row>
-  </sheetData>
-  <phoneticPr fontId="27" type="noConversion"/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <dimension ref="A1:N716"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="15" customHeight="1"/>
@@ -21478,7 +21383,7 @@
       <c r="G1" s="31" t="s">
         <v>580</v>
       </c>
-      <c r="H1" s="60" t="s">
+      <c r="H1" s="59" t="s">
         <v>1469</v>
       </c>
       <c r="I1" s="31" t="s">
@@ -21580,7 +21485,7 @@
       <c r="G4">
         <v>170000</v>
       </c>
-      <c r="J4" s="58" t="s">
+      <c r="J4" s="57" t="s">
         <v>1450</v>
       </c>
     </row>
@@ -26451,7 +26356,7 @@
       </c>
     </row>
     <row r="208" spans="2:10" ht="15" customHeight="1">
-      <c r="B208" s="81">
+      <c r="B208" s="80">
         <v>38</v>
       </c>
       <c r="C208">
@@ -26474,7 +26379,7 @@
       </c>
     </row>
     <row r="209" spans="2:10" ht="15" customHeight="1">
-      <c r="B209" s="81">
+      <c r="B209" s="80">
         <v>38</v>
       </c>
       <c r="C209">
@@ -26497,7 +26402,7 @@
       </c>
     </row>
     <row r="210" spans="2:10" ht="15" customHeight="1">
-      <c r="B210" s="81">
+      <c r="B210" s="80">
         <v>38</v>
       </c>
       <c r="C210">
@@ -26520,7 +26425,7 @@
       </c>
     </row>
     <row r="211" spans="2:10" ht="15" customHeight="1">
-      <c r="B211" s="81">
+      <c r="B211" s="80">
         <v>38</v>
       </c>
       <c r="C211">
@@ -26543,7 +26448,7 @@
       </c>
     </row>
     <row r="212" spans="2:10" ht="15" customHeight="1">
-      <c r="B212" s="81">
+      <c r="B212" s="80">
         <v>38</v>
       </c>
       <c r="C212">
@@ -26566,7 +26471,7 @@
       </c>
     </row>
     <row r="213" spans="2:10" ht="15" customHeight="1">
-      <c r="B213" s="81">
+      <c r="B213" s="80">
         <v>38</v>
       </c>
       <c r="C213">
@@ -26589,7 +26494,7 @@
       </c>
     </row>
     <row r="214" spans="2:10" ht="15" customHeight="1">
-      <c r="B214" s="81">
+      <c r="B214" s="80">
         <v>38</v>
       </c>
       <c r="C214">
@@ -26612,7 +26517,7 @@
       </c>
     </row>
     <row r="215" spans="2:10" ht="15" customHeight="1">
-      <c r="B215" s="81">
+      <c r="B215" s="80">
         <v>38</v>
       </c>
       <c r="C215">
@@ -26635,7 +26540,7 @@
       </c>
     </row>
     <row r="216" spans="2:10" ht="15" customHeight="1">
-      <c r="B216" s="81">
+      <c r="B216" s="80">
         <v>38</v>
       </c>
       <c r="C216">
@@ -26658,7 +26563,7 @@
       </c>
     </row>
     <row r="217" spans="2:10" ht="15" customHeight="1">
-      <c r="B217" s="81">
+      <c r="B217" s="80">
         <v>38</v>
       </c>
       <c r="C217">
@@ -26681,7 +26586,7 @@
       </c>
     </row>
     <row r="218" spans="2:10" ht="15" customHeight="1">
-      <c r="B218" s="81">
+      <c r="B218" s="80">
         <v>38</v>
       </c>
       <c r="C218">
@@ -26704,7 +26609,7 @@
       </c>
     </row>
     <row r="219" spans="2:10" ht="15" customHeight="1">
-      <c r="B219" s="81">
+      <c r="B219" s="80">
         <v>38</v>
       </c>
       <c r="C219">
@@ -26727,7 +26632,7 @@
       </c>
     </row>
     <row r="220" spans="2:10" ht="15" customHeight="1">
-      <c r="B220" s="81">
+      <c r="B220" s="80">
         <v>38</v>
       </c>
       <c r="C220">
@@ -26750,7 +26655,7 @@
       </c>
     </row>
     <row r="221" spans="2:10" ht="15" customHeight="1">
-      <c r="B221" s="81">
+      <c r="B221" s="80">
         <v>38</v>
       </c>
       <c r="C221">
@@ -26773,7 +26678,7 @@
       </c>
     </row>
     <row r="222" spans="2:10" ht="15" customHeight="1">
-      <c r="B222" s="81">
+      <c r="B222" s="80">
         <v>38</v>
       </c>
       <c r="C222">
@@ -26796,7 +26701,7 @@
       </c>
     </row>
     <row r="223" spans="2:10" ht="15" customHeight="1">
-      <c r="B223" s="81">
+      <c r="B223" s="80">
         <v>38</v>
       </c>
       <c r="C223">
@@ -26819,7 +26724,7 @@
       </c>
     </row>
     <row r="224" spans="2:10" ht="15" customHeight="1">
-      <c r="B224" s="81">
+      <c r="B224" s="80">
         <v>38</v>
       </c>
       <c r="C224">
@@ -29634,7 +29539,7 @@
       <c r="D348">
         <v>1</v>
       </c>
-      <c r="E348" s="55" t="s">
+      <c r="E348" s="54" t="s">
         <v>1432</v>
       </c>
       <c r="F348" t="s">
@@ -33705,7 +33610,7 @@
       <c r="G530">
         <v>5500</v>
       </c>
-      <c r="J530" s="58" t="s">
+      <c r="J530" s="57" t="s">
         <v>1449</v>
       </c>
     </row>
@@ -34078,7 +33983,7 @@
       </c>
     </row>
     <row r="547" spans="1:10" s="31" customFormat="1" ht="15" customHeight="1">
-      <c r="A547" s="79" t="s">
+      <c r="A547" s="78" t="s">
         <v>1451</v>
       </c>
       <c r="B547" s="14">
@@ -34090,10 +33995,10 @@
       <c r="D547" s="14">
         <v>2</v>
       </c>
-      <c r="E547" s="79" t="s">
+      <c r="E547" s="78" t="s">
         <v>1452</v>
       </c>
-      <c r="F547" s="79" t="s">
+      <c r="F547" s="78" t="s">
         <v>1060</v>
       </c>
       <c r="G547" s="14">
@@ -34101,375 +34006,375 @@
       </c>
     </row>
     <row r="548" spans="1:10" s="31" customFormat="1" ht="15" customHeight="1">
-      <c r="A548" s="80" t="s">
+      <c r="A548" s="79" t="s">
         <v>1451</v>
       </c>
-      <c r="B548" s="66">
+      <c r="B548" s="65">
         <v>92</v>
       </c>
-      <c r="C548" s="66">
+      <c r="C548" s="65">
         <v>4001</v>
       </c>
-      <c r="D548" s="66">
-        <v>1</v>
-      </c>
-      <c r="E548" s="80" t="s">
+      <c r="D548" s="65">
+        <v>1</v>
+      </c>
+      <c r="E548" s="79" t="s">
         <v>1453</v>
       </c>
-      <c r="F548" s="80" t="s">
+      <c r="F548" s="79" t="s">
         <v>1060</v>
       </c>
-      <c r="G548" s="66">
+      <c r="G548" s="65">
         <v>9000</v>
       </c>
     </row>
     <row r="549" spans="1:10" s="31" customFormat="1" ht="15" customHeight="1">
-      <c r="A549" s="80" t="s">
+      <c r="A549" s="79" t="s">
         <v>1451</v>
       </c>
-      <c r="B549" s="66">
+      <c r="B549" s="65">
         <v>92</v>
       </c>
-      <c r="C549" s="66">
+      <c r="C549" s="65">
         <v>4002</v>
       </c>
-      <c r="D549" s="66">
-        <v>1</v>
-      </c>
-      <c r="E549" s="80" t="s">
+      <c r="D549" s="65">
+        <v>1</v>
+      </c>
+      <c r="E549" s="79" t="s">
         <v>1454</v>
       </c>
-      <c r="F549" s="80" t="s">
+      <c r="F549" s="79" t="s">
         <v>1060</v>
       </c>
-      <c r="G549" s="66">
+      <c r="G549" s="65">
         <v>45000</v>
       </c>
     </row>
     <row r="550" spans="1:10" s="31" customFormat="1" ht="15" customHeight="1">
-      <c r="A550" s="80" t="s">
+      <c r="A550" s="79" t="s">
         <v>1451</v>
       </c>
-      <c r="B550" s="66">
+      <c r="B550" s="65">
         <v>92</v>
       </c>
-      <c r="C550" s="66">
+      <c r="C550" s="65">
         <v>4003</v>
       </c>
-      <c r="D550" s="66">
-        <v>1</v>
-      </c>
-      <c r="E550" s="80" t="s">
+      <c r="D550" s="65">
+        <v>1</v>
+      </c>
+      <c r="E550" s="79" t="s">
         <v>1455</v>
       </c>
-      <c r="F550" s="80" t="s">
+      <c r="F550" s="79" t="s">
         <v>1060</v>
       </c>
-      <c r="G550" s="66">
+      <c r="G550" s="65">
         <v>85000</v>
       </c>
     </row>
     <row r="551" spans="1:10" s="31" customFormat="1" ht="15" customHeight="1">
-      <c r="A551" s="80" t="s">
+      <c r="A551" s="79" t="s">
         <v>1451</v>
       </c>
-      <c r="B551" s="66">
+      <c r="B551" s="65">
         <v>92</v>
       </c>
-      <c r="C551" s="66">
+      <c r="C551" s="65">
         <v>4004</v>
       </c>
-      <c r="D551" s="66">
-        <v>1</v>
-      </c>
-      <c r="E551" s="80" t="s">
+      <c r="D551" s="65">
+        <v>1</v>
+      </c>
+      <c r="E551" s="79" t="s">
         <v>1456</v>
       </c>
-      <c r="F551" s="80" t="s">
+      <c r="F551" s="79" t="s">
         <v>1060</v>
       </c>
-      <c r="G551" s="66">
+      <c r="G551" s="65">
         <v>152000</v>
       </c>
     </row>
     <row r="552" spans="1:10" s="31" customFormat="1" ht="15" customHeight="1">
-      <c r="A552" s="80" t="s">
+      <c r="A552" s="79" t="s">
         <v>1451</v>
       </c>
-      <c r="B552" s="66">
+      <c r="B552" s="65">
         <v>92</v>
       </c>
-      <c r="C552" s="66">
+      <c r="C552" s="65">
         <v>4005</v>
       </c>
-      <c r="D552" s="66">
-        <v>1</v>
-      </c>
-      <c r="E552" s="80" t="s">
+      <c r="D552" s="65">
+        <v>1</v>
+      </c>
+      <c r="E552" s="79" t="s">
         <v>1457</v>
       </c>
-      <c r="F552" s="80" t="s">
+      <c r="F552" s="79" t="s">
         <v>1060</v>
       </c>
-      <c r="G552" s="66">
+      <c r="G552" s="65">
         <v>265000</v>
       </c>
     </row>
     <row r="553" spans="1:10" s="31" customFormat="1" ht="15" customHeight="1">
-      <c r="A553" s="80" t="s">
+      <c r="A553" s="79" t="s">
         <v>1451</v>
       </c>
-      <c r="B553" s="66">
+      <c r="B553" s="65">
         <v>92</v>
       </c>
-      <c r="C553" s="66">
+      <c r="C553" s="65">
         <v>4006</v>
       </c>
-      <c r="D553" s="66">
-        <v>1</v>
-      </c>
-      <c r="E553" s="80" t="s">
+      <c r="D553" s="65">
+        <v>1</v>
+      </c>
+      <c r="E553" s="79" t="s">
         <v>1458</v>
       </c>
-      <c r="F553" s="80" t="s">
+      <c r="F553" s="79" t="s">
         <v>1060</v>
       </c>
-      <c r="G553" s="66">
+      <c r="G553" s="65">
         <v>352000</v>
       </c>
     </row>
     <row r="554" spans="1:10" s="31" customFormat="1" ht="15" customHeight="1">
-      <c r="A554" s="80" t="s">
+      <c r="A554" s="79" t="s">
         <v>1451</v>
       </c>
-      <c r="B554" s="66">
+      <c r="B554" s="65">
         <v>92</v>
       </c>
-      <c r="C554" s="66">
+      <c r="C554" s="65">
         <v>4007</v>
       </c>
-      <c r="D554" s="66">
-        <v>1</v>
-      </c>
-      <c r="E554" s="80" t="s">
+      <c r="D554" s="65">
+        <v>1</v>
+      </c>
+      <c r="E554" s="79" t="s">
         <v>1459</v>
       </c>
-      <c r="F554" s="80" t="s">
+      <c r="F554" s="79" t="s">
         <v>1060</v>
       </c>
-      <c r="G554" s="66">
+      <c r="G554" s="65">
         <v>456000</v>
       </c>
     </row>
     <row r="555" spans="1:10" s="31" customFormat="1" ht="15" customHeight="1">
-      <c r="A555" s="80" t="s">
+      <c r="A555" s="79" t="s">
         <v>1451</v>
       </c>
-      <c r="B555" s="66">
+      <c r="B555" s="65">
         <v>92</v>
       </c>
-      <c r="C555" s="66">
+      <c r="C555" s="65">
         <v>4008</v>
       </c>
-      <c r="D555" s="66">
-        <v>1</v>
-      </c>
-      <c r="E555" s="80" t="s">
+      <c r="D555" s="65">
+        <v>1</v>
+      </c>
+      <c r="E555" s="79" t="s">
         <v>1460</v>
       </c>
-      <c r="F555" s="80" t="s">
+      <c r="F555" s="79" t="s">
         <v>1060</v>
       </c>
-      <c r="G555" s="66">
+      <c r="G555" s="65">
         <v>800000</v>
       </c>
     </row>
     <row r="556" spans="1:10" s="31" customFormat="1" ht="15" customHeight="1">
-      <c r="A556" s="80" t="s">
+      <c r="A556" s="79" t="s">
         <v>1451</v>
       </c>
-      <c r="B556" s="66">
+      <c r="B556" s="65">
         <v>92</v>
       </c>
-      <c r="C556" s="66">
+      <c r="C556" s="65">
         <v>4101</v>
       </c>
-      <c r="D556" s="66">
-        <v>1</v>
-      </c>
-      <c r="E556" s="80" t="s">
+      <c r="D556" s="65">
+        <v>1</v>
+      </c>
+      <c r="E556" s="79" t="s">
         <v>1461</v>
       </c>
-      <c r="F556" s="80" t="s">
+      <c r="F556" s="79" t="s">
         <v>1060</v>
       </c>
-      <c r="G556" s="66">
+      <c r="G556" s="65">
         <v>9000</v>
       </c>
     </row>
     <row r="557" spans="1:10" s="31" customFormat="1" ht="15" customHeight="1">
-      <c r="A557" s="80" t="s">
+      <c r="A557" s="79" t="s">
         <v>1451</v>
       </c>
-      <c r="B557" s="66">
+      <c r="B557" s="65">
         <v>92</v>
       </c>
-      <c r="C557" s="66">
+      <c r="C557" s="65">
         <v>4102</v>
       </c>
-      <c r="D557" s="66">
-        <v>1</v>
-      </c>
-      <c r="E557" s="80" t="s">
+      <c r="D557" s="65">
+        <v>1</v>
+      </c>
+      <c r="E557" s="79" t="s">
         <v>1462</v>
       </c>
-      <c r="F557" s="80" t="s">
+      <c r="F557" s="79" t="s">
         <v>1060</v>
       </c>
-      <c r="G557" s="66">
+      <c r="G557" s="65">
         <v>45000</v>
       </c>
     </row>
     <row r="558" spans="1:10" s="31" customFormat="1" ht="15" customHeight="1">
-      <c r="A558" s="80" t="s">
+      <c r="A558" s="79" t="s">
         <v>1451</v>
       </c>
-      <c r="B558" s="66">
+      <c r="B558" s="65">
         <v>92</v>
       </c>
-      <c r="C558" s="66">
+      <c r="C558" s="65">
         <v>4103</v>
       </c>
-      <c r="D558" s="66">
-        <v>1</v>
-      </c>
-      <c r="E558" s="80" t="s">
+      <c r="D558" s="65">
+        <v>1</v>
+      </c>
+      <c r="E558" s="79" t="s">
         <v>1463</v>
       </c>
-      <c r="F558" s="80" t="s">
+      <c r="F558" s="79" t="s">
         <v>1060</v>
       </c>
-      <c r="G558" s="66">
+      <c r="G558" s="65">
         <v>85000</v>
       </c>
     </row>
     <row r="559" spans="1:10" s="31" customFormat="1" ht="15" customHeight="1">
-      <c r="A559" s="80" t="s">
+      <c r="A559" s="79" t="s">
         <v>1451</v>
       </c>
-      <c r="B559" s="66">
+      <c r="B559" s="65">
         <v>92</v>
       </c>
-      <c r="C559" s="66">
+      <c r="C559" s="65">
         <v>4104</v>
       </c>
-      <c r="D559" s="66">
-        <v>1</v>
-      </c>
-      <c r="E559" s="80" t="s">
+      <c r="D559" s="65">
+        <v>1</v>
+      </c>
+      <c r="E559" s="79" t="s">
         <v>1464</v>
       </c>
-      <c r="F559" s="80" t="s">
+      <c r="F559" s="79" t="s">
         <v>1060</v>
       </c>
-      <c r="G559" s="66">
+      <c r="G559" s="65">
         <v>152000</v>
       </c>
     </row>
     <row r="560" spans="1:10" s="31" customFormat="1" ht="15" customHeight="1">
-      <c r="A560" s="80" t="s">
+      <c r="A560" s="79" t="s">
         <v>1451</v>
       </c>
-      <c r="B560" s="66">
+      <c r="B560" s="65">
         <v>92</v>
       </c>
-      <c r="C560" s="66">
+      <c r="C560" s="65">
         <v>4105</v>
       </c>
-      <c r="D560" s="66">
-        <v>1</v>
-      </c>
-      <c r="E560" s="80" t="s">
+      <c r="D560" s="65">
+        <v>1</v>
+      </c>
+      <c r="E560" s="79" t="s">
         <v>1465</v>
       </c>
-      <c r="F560" s="80" t="s">
+      <c r="F560" s="79" t="s">
         <v>1060</v>
       </c>
-      <c r="G560" s="66">
+      <c r="G560" s="65">
         <v>265000</v>
       </c>
     </row>
     <row r="561" spans="1:7" s="31" customFormat="1" ht="15" customHeight="1">
-      <c r="A561" s="80" t="s">
+      <c r="A561" s="79" t="s">
         <v>1451</v>
       </c>
-      <c r="B561" s="66">
+      <c r="B561" s="65">
         <v>92</v>
       </c>
-      <c r="C561" s="66">
+      <c r="C561" s="65">
         <v>4106</v>
       </c>
-      <c r="D561" s="66">
-        <v>1</v>
-      </c>
-      <c r="E561" s="80" t="s">
+      <c r="D561" s="65">
+        <v>1</v>
+      </c>
+      <c r="E561" s="79" t="s">
         <v>1466</v>
       </c>
-      <c r="F561" s="80" t="s">
+      <c r="F561" s="79" t="s">
         <v>1060</v>
       </c>
-      <c r="G561" s="66">
+      <c r="G561" s="65">
         <v>352000</v>
       </c>
     </row>
     <row r="562" spans="1:7" s="31" customFormat="1" ht="15" customHeight="1">
-      <c r="A562" s="80" t="s">
+      <c r="A562" s="79" t="s">
         <v>1451</v>
       </c>
-      <c r="B562" s="66">
+      <c r="B562" s="65">
         <v>92</v>
       </c>
-      <c r="C562" s="66">
+      <c r="C562" s="65">
         <v>4107</v>
       </c>
-      <c r="D562" s="66">
-        <v>1</v>
-      </c>
-      <c r="E562" s="80" t="s">
+      <c r="D562" s="65">
+        <v>1</v>
+      </c>
+      <c r="E562" s="79" t="s">
         <v>1467</v>
       </c>
-      <c r="F562" s="80" t="s">
+      <c r="F562" s="79" t="s">
         <v>1060</v>
       </c>
-      <c r="G562" s="66">
+      <c r="G562" s="65">
         <v>456000</v>
       </c>
     </row>
     <row r="563" spans="1:7" s="31" customFormat="1" ht="15" customHeight="1">
-      <c r="A563" s="80" t="s">
+      <c r="A563" s="79" t="s">
         <v>1451</v>
       </c>
-      <c r="B563" s="66">
+      <c r="B563" s="65">
         <v>92</v>
       </c>
-      <c r="C563" s="66">
+      <c r="C563" s="65">
         <v>4108</v>
       </c>
-      <c r="D563" s="66">
-        <v>1</v>
-      </c>
-      <c r="E563" s="80" t="s">
+      <c r="D563" s="65">
+        <v>1</v>
+      </c>
+      <c r="E563" s="79" t="s">
         <v>1468</v>
       </c>
-      <c r="F563" s="80" t="s">
+      <c r="F563" s="79" t="s">
         <v>1060</v>
       </c>
-      <c r="G563" s="66">
+      <c r="G563" s="65">
         <v>800000</v>
       </c>
     </row>
     <row r="564" spans="1:7" s="31" customFormat="1" ht="15" customHeight="1">
-      <c r="A564" s="79" t="s">
+      <c r="A564" s="78" t="s">
         <v>1451</v>
       </c>
       <c r="B564" s="14">
@@ -34492,375 +34397,375 @@
       </c>
     </row>
     <row r="565" spans="1:7" s="31" customFormat="1" ht="15" customHeight="1">
-      <c r="A565" s="80" t="s">
+      <c r="A565" s="79" t="s">
         <v>1451</v>
       </c>
-      <c r="B565" s="66">
+      <c r="B565" s="65">
         <v>93</v>
       </c>
-      <c r="C565" s="66">
+      <c r="C565" s="65">
         <v>3001</v>
       </c>
-      <c r="D565" s="66">
-        <v>1</v>
-      </c>
-      <c r="E565" s="66" t="s">
+      <c r="D565" s="65">
+        <v>1</v>
+      </c>
+      <c r="E565" s="65" t="s">
         <v>957</v>
       </c>
-      <c r="F565" s="80" t="s">
+      <c r="F565" s="79" t="s">
         <v>838</v>
       </c>
-      <c r="G565" s="66">
+      <c r="G565" s="65">
         <v>990</v>
       </c>
     </row>
     <row r="566" spans="1:7" s="31" customFormat="1" ht="15" customHeight="1">
-      <c r="A566" s="80" t="s">
+      <c r="A566" s="79" t="s">
         <v>1451</v>
       </c>
-      <c r="B566" s="66">
+      <c r="B566" s="65">
         <v>93</v>
       </c>
-      <c r="C566" s="66">
+      <c r="C566" s="65">
         <v>3002</v>
       </c>
-      <c r="D566" s="66">
-        <v>1</v>
-      </c>
-      <c r="E566" s="66" t="s">
+      <c r="D566" s="65">
+        <v>1</v>
+      </c>
+      <c r="E566" s="65" t="s">
         <v>958</v>
       </c>
-      <c r="F566" s="66" t="s">
+      <c r="F566" s="65" t="s">
         <v>838</v>
       </c>
-      <c r="G566" s="66">
+      <c r="G566" s="65">
         <v>4990</v>
       </c>
     </row>
     <row r="567" spans="1:7" s="31" customFormat="1" ht="15" customHeight="1">
-      <c r="A567" s="80" t="s">
+      <c r="A567" s="79" t="s">
         <v>1451</v>
       </c>
-      <c r="B567" s="66">
+      <c r="B567" s="65">
         <v>93</v>
       </c>
-      <c r="C567" s="66">
+      <c r="C567" s="65">
         <v>3003</v>
       </c>
-      <c r="D567" s="66">
-        <v>1</v>
-      </c>
-      <c r="E567" s="66" t="s">
+      <c r="D567" s="65">
+        <v>1</v>
+      </c>
+      <c r="E567" s="65" t="s">
         <v>959</v>
       </c>
-      <c r="F567" s="66" t="s">
+      <c r="F567" s="65" t="s">
         <v>838</v>
       </c>
-      <c r="G567" s="66">
+      <c r="G567" s="65">
         <v>7990</v>
       </c>
     </row>
     <row r="568" spans="1:7" s="31" customFormat="1" ht="15" customHeight="1">
-      <c r="A568" s="80" t="s">
+      <c r="A568" s="79" t="s">
         <v>1451</v>
       </c>
-      <c r="B568" s="66">
+      <c r="B568" s="65">
         <v>93</v>
       </c>
-      <c r="C568" s="66">
+      <c r="C568" s="65">
         <v>3004</v>
       </c>
-      <c r="D568" s="66">
-        <v>1</v>
-      </c>
-      <c r="E568" s="66" t="s">
+      <c r="D568" s="65">
+        <v>1</v>
+      </c>
+      <c r="E568" s="65" t="s">
         <v>960</v>
       </c>
-      <c r="F568" s="66" t="s">
+      <c r="F568" s="65" t="s">
         <v>838</v>
       </c>
-      <c r="G568" s="66">
+      <c r="G568" s="65">
         <v>14990</v>
       </c>
     </row>
     <row r="569" spans="1:7" s="31" customFormat="1" ht="15" customHeight="1">
-      <c r="A569" s="80" t="s">
+      <c r="A569" s="79" t="s">
         <v>1451</v>
       </c>
-      <c r="B569" s="66">
+      <c r="B569" s="65">
         <v>93</v>
       </c>
-      <c r="C569" s="66">
+      <c r="C569" s="65">
         <v>3005</v>
       </c>
-      <c r="D569" s="66">
-        <v>1</v>
-      </c>
-      <c r="E569" s="66" t="s">
+      <c r="D569" s="65">
+        <v>1</v>
+      </c>
+      <c r="E569" s="65" t="s">
         <v>961</v>
       </c>
-      <c r="F569" s="66" t="s">
+      <c r="F569" s="65" t="s">
         <v>838</v>
       </c>
-      <c r="G569" s="66">
+      <c r="G569" s="65">
         <v>19990</v>
       </c>
     </row>
     <row r="570" spans="1:7" s="31" customFormat="1" ht="15" customHeight="1">
-      <c r="A570" s="80" t="s">
+      <c r="A570" s="79" t="s">
         <v>1451</v>
       </c>
-      <c r="B570" s="66">
+      <c r="B570" s="65">
         <v>93</v>
       </c>
-      <c r="C570" s="66">
+      <c r="C570" s="65">
         <v>3006</v>
       </c>
-      <c r="D570" s="66">
-        <v>1</v>
-      </c>
-      <c r="E570" s="66" t="s">
+      <c r="D570" s="65">
+        <v>1</v>
+      </c>
+      <c r="E570" s="65" t="s">
         <v>962</v>
       </c>
-      <c r="F570" s="66" t="s">
+      <c r="F570" s="65" t="s">
         <v>838</v>
       </c>
-      <c r="G570" s="66">
+      <c r="G570" s="65">
         <v>29990</v>
       </c>
     </row>
     <row r="571" spans="1:7" s="31" customFormat="1" ht="15" customHeight="1">
-      <c r="A571" s="80" t="s">
+      <c r="A571" s="79" t="s">
         <v>1451</v>
       </c>
-      <c r="B571" s="66">
+      <c r="B571" s="65">
         <v>93</v>
       </c>
-      <c r="C571" s="66">
+      <c r="C571" s="65">
         <v>3007</v>
       </c>
-      <c r="D571" s="66">
-        <v>1</v>
-      </c>
-      <c r="E571" s="66" t="s">
+      <c r="D571" s="65">
+        <v>1</v>
+      </c>
+      <c r="E571" s="65" t="s">
         <v>963</v>
       </c>
-      <c r="F571" s="66" t="s">
+      <c r="F571" s="65" t="s">
         <v>838</v>
       </c>
-      <c r="G571" s="66">
+      <c r="G571" s="65">
         <v>39990</v>
       </c>
     </row>
     <row r="572" spans="1:7" s="31" customFormat="1" ht="15" customHeight="1">
-      <c r="A572" s="80" t="s">
+      <c r="A572" s="79" t="s">
         <v>1451</v>
       </c>
-      <c r="B572" s="66">
+      <c r="B572" s="65">
         <v>93</v>
       </c>
-      <c r="C572" s="66">
+      <c r="C572" s="65">
         <v>3008</v>
       </c>
-      <c r="D572" s="66">
-        <v>1</v>
-      </c>
-      <c r="E572" s="66" t="s">
+      <c r="D572" s="65">
+        <v>1</v>
+      </c>
+      <c r="E572" s="65" t="s">
         <v>964</v>
       </c>
-      <c r="F572" s="66" t="s">
+      <c r="F572" s="65" t="s">
         <v>838</v>
       </c>
-      <c r="G572" s="66">
+      <c r="G572" s="65">
         <v>79990</v>
       </c>
     </row>
     <row r="573" spans="1:7" s="31" customFormat="1" ht="15" customHeight="1">
-      <c r="A573" s="80" t="s">
+      <c r="A573" s="79" t="s">
         <v>1451</v>
       </c>
-      <c r="B573" s="66">
+      <c r="B573" s="65">
         <v>93</v>
       </c>
-      <c r="C573" s="66">
+      <c r="C573" s="65">
         <v>3101</v>
       </c>
-      <c r="D573" s="66">
-        <v>1</v>
-      </c>
-      <c r="E573" s="66" t="s">
+      <c r="D573" s="65">
+        <v>1</v>
+      </c>
+      <c r="E573" s="65" t="s">
         <v>975</v>
       </c>
-      <c r="F573" s="66" t="s">
+      <c r="F573" s="65" t="s">
         <v>838</v>
       </c>
-      <c r="G573" s="66">
+      <c r="G573" s="65">
         <v>990</v>
       </c>
     </row>
     <row r="574" spans="1:7" s="31" customFormat="1" ht="15" customHeight="1">
-      <c r="A574" s="80" t="s">
+      <c r="A574" s="79" t="s">
         <v>1451</v>
       </c>
-      <c r="B574" s="66">
+      <c r="B574" s="65">
         <v>93</v>
       </c>
-      <c r="C574" s="66">
+      <c r="C574" s="65">
         <v>3102</v>
       </c>
-      <c r="D574" s="66">
-        <v>1</v>
-      </c>
-      <c r="E574" s="66" t="s">
+      <c r="D574" s="65">
+        <v>1</v>
+      </c>
+      <c r="E574" s="65" t="s">
         <v>976</v>
       </c>
-      <c r="F574" s="66" t="s">
+      <c r="F574" s="65" t="s">
         <v>838</v>
       </c>
-      <c r="G574" s="66">
+      <c r="G574" s="65">
         <v>4990</v>
       </c>
     </row>
     <row r="575" spans="1:7" s="31" customFormat="1" ht="15" customHeight="1">
-      <c r="A575" s="80" t="s">
+      <c r="A575" s="79" t="s">
         <v>1451</v>
       </c>
-      <c r="B575" s="66">
+      <c r="B575" s="65">
         <v>93</v>
       </c>
-      <c r="C575" s="66">
+      <c r="C575" s="65">
         <v>3103</v>
       </c>
-      <c r="D575" s="66">
-        <v>1</v>
-      </c>
-      <c r="E575" s="66" t="s">
+      <c r="D575" s="65">
+        <v>1</v>
+      </c>
+      <c r="E575" s="65" t="s">
         <v>977</v>
       </c>
-      <c r="F575" s="66" t="s">
+      <c r="F575" s="65" t="s">
         <v>838</v>
       </c>
-      <c r="G575" s="66">
+      <c r="G575" s="65">
         <v>7990</v>
       </c>
     </row>
     <row r="576" spans="1:7" s="31" customFormat="1" ht="15" customHeight="1">
-      <c r="A576" s="80" t="s">
+      <c r="A576" s="79" t="s">
         <v>1451</v>
       </c>
-      <c r="B576" s="66">
+      <c r="B576" s="65">
         <v>93</v>
       </c>
-      <c r="C576" s="66">
+      <c r="C576" s="65">
         <v>3104</v>
       </c>
-      <c r="D576" s="66">
-        <v>1</v>
-      </c>
-      <c r="E576" s="66" t="s">
+      <c r="D576" s="65">
+        <v>1</v>
+      </c>
+      <c r="E576" s="65" t="s">
         <v>978</v>
       </c>
-      <c r="F576" s="66" t="s">
+      <c r="F576" s="65" t="s">
         <v>838</v>
       </c>
-      <c r="G576" s="66">
+      <c r="G576" s="65">
         <v>14990</v>
       </c>
     </row>
     <row r="577" spans="1:7" s="31" customFormat="1" ht="15" customHeight="1">
-      <c r="A577" s="80" t="s">
+      <c r="A577" s="79" t="s">
         <v>1451</v>
       </c>
-      <c r="B577" s="66">
+      <c r="B577" s="65">
         <v>93</v>
       </c>
-      <c r="C577" s="66">
+      <c r="C577" s="65">
         <v>3105</v>
       </c>
-      <c r="D577" s="66">
-        <v>1</v>
-      </c>
-      <c r="E577" s="66" t="s">
+      <c r="D577" s="65">
+        <v>1</v>
+      </c>
+      <c r="E577" s="65" t="s">
         <v>979</v>
       </c>
-      <c r="F577" s="66" t="s">
+      <c r="F577" s="65" t="s">
         <v>838</v>
       </c>
-      <c r="G577" s="66">
+      <c r="G577" s="65">
         <v>19990</v>
       </c>
     </row>
     <row r="578" spans="1:7" s="31" customFormat="1" ht="15" customHeight="1">
-      <c r="A578" s="80" t="s">
+      <c r="A578" s="79" t="s">
         <v>1451</v>
       </c>
-      <c r="B578" s="66">
+      <c r="B578" s="65">
         <v>93</v>
       </c>
-      <c r="C578" s="66">
+      <c r="C578" s="65">
         <v>3106</v>
       </c>
-      <c r="D578" s="66">
-        <v>1</v>
-      </c>
-      <c r="E578" s="66" t="s">
+      <c r="D578" s="65">
+        <v>1</v>
+      </c>
+      <c r="E578" s="65" t="s">
         <v>980</v>
       </c>
-      <c r="F578" s="66" t="s">
+      <c r="F578" s="65" t="s">
         <v>838</v>
       </c>
-      <c r="G578" s="66">
+      <c r="G578" s="65">
         <v>29990</v>
       </c>
     </row>
     <row r="579" spans="1:7" s="31" customFormat="1" ht="15" customHeight="1">
-      <c r="A579" s="80" t="s">
+      <c r="A579" s="79" t="s">
         <v>1451</v>
       </c>
-      <c r="B579" s="66">
+      <c r="B579" s="65">
         <v>93</v>
       </c>
-      <c r="C579" s="66">
+      <c r="C579" s="65">
         <v>3107</v>
       </c>
-      <c r="D579" s="66">
-        <v>1</v>
-      </c>
-      <c r="E579" s="66" t="s">
+      <c r="D579" s="65">
+        <v>1</v>
+      </c>
+      <c r="E579" s="65" t="s">
         <v>981</v>
       </c>
-      <c r="F579" s="66" t="s">
+      <c r="F579" s="65" t="s">
         <v>838</v>
       </c>
-      <c r="G579" s="66">
+      <c r="G579" s="65">
         <v>39990</v>
       </c>
     </row>
     <row r="580" spans="1:7" s="31" customFormat="1" ht="15" customHeight="1">
-      <c r="A580" s="80" t="s">
+      <c r="A580" s="79" t="s">
         <v>1451</v>
       </c>
-      <c r="B580" s="66">
+      <c r="B580" s="65">
         <v>93</v>
       </c>
-      <c r="C580" s="66">
+      <c r="C580" s="65">
         <v>3108</v>
       </c>
-      <c r="D580" s="66">
-        <v>1</v>
-      </c>
-      <c r="E580" s="66" t="s">
+      <c r="D580" s="65">
+        <v>1</v>
+      </c>
+      <c r="E580" s="65" t="s">
         <v>982</v>
       </c>
-      <c r="F580" s="66" t="s">
+      <c r="F580" s="65" t="s">
         <v>838</v>
       </c>
-      <c r="G580" s="66">
+      <c r="G580" s="65">
         <v>79990</v>
       </c>
     </row>
     <row r="581" spans="1:7" ht="15" customHeight="1">
-      <c r="A581" s="79" t="s">
+      <c r="A581" s="78" t="s">
         <v>1451</v>
       </c>
       <c r="B581" s="14">
@@ -34872,381 +34777,381 @@
       <c r="D581" s="14">
         <v>2</v>
       </c>
-      <c r="E581" s="58" t="s">
+      <c r="E581" s="57" t="s">
         <v>1470</v>
       </c>
       <c r="F581" s="14" t="s">
         <v>717</v>
       </c>
-      <c r="G581" s="68">
+      <c r="G581" s="67">
         <v>650000</v>
       </c>
     </row>
     <row r="582" spans="1:7" ht="15" customHeight="1">
-      <c r="A582" s="80" t="s">
+      <c r="A582" s="79" t="s">
         <v>1451</v>
       </c>
-      <c r="B582" s="66">
+      <c r="B582" s="65">
         <v>93</v>
       </c>
-      <c r="C582" s="66">
+      <c r="C582" s="65">
         <v>2001</v>
       </c>
-      <c r="D582" s="66">
-        <v>1</v>
-      </c>
-      <c r="E582" s="66" t="s">
+      <c r="D582" s="65">
+        <v>1</v>
+      </c>
+      <c r="E582" s="65" t="s">
         <v>821</v>
       </c>
-      <c r="F582" s="66" t="s">
+      <c r="F582" s="65" t="s">
         <v>717</v>
       </c>
-      <c r="G582" s="67">
+      <c r="G582" s="66">
         <v>160000</v>
       </c>
     </row>
     <row r="583" spans="1:7" ht="15" customHeight="1">
-      <c r="A583" s="80" t="s">
+      <c r="A583" s="79" t="s">
         <v>1451</v>
       </c>
-      <c r="B583" s="66">
+      <c r="B583" s="65">
         <v>93</v>
       </c>
-      <c r="C583" s="66">
+      <c r="C583" s="65">
         <v>2002</v>
       </c>
-      <c r="D583" s="66">
-        <v>1</v>
-      </c>
-      <c r="E583" s="66" t="s">
+      <c r="D583" s="65">
+        <v>1</v>
+      </c>
+      <c r="E583" s="65" t="s">
         <v>822</v>
       </c>
-      <c r="F583" s="66" t="s">
+      <c r="F583" s="65" t="s">
         <v>717</v>
       </c>
-      <c r="G583" s="67">
+      <c r="G583" s="66">
         <v>650000</v>
       </c>
     </row>
     <row r="584" spans="1:7" ht="15" customHeight="1">
-      <c r="A584" s="80" t="s">
+      <c r="A584" s="79" t="s">
         <v>1451</v>
       </c>
-      <c r="B584" s="66">
+      <c r="B584" s="65">
         <v>93</v>
       </c>
-      <c r="C584" s="66">
+      <c r="C584" s="65">
         <v>2003</v>
       </c>
-      <c r="D584" s="66">
-        <v>1</v>
-      </c>
-      <c r="E584" s="66" t="s">
+      <c r="D584" s="65">
+        <v>1</v>
+      </c>
+      <c r="E584" s="65" t="s">
         <v>823</v>
       </c>
-      <c r="F584" s="66" t="s">
+      <c r="F584" s="65" t="s">
         <v>717</v>
       </c>
-      <c r="G584" s="67">
+      <c r="G584" s="66">
         <v>1000000</v>
       </c>
     </row>
     <row r="585" spans="1:7" ht="15" customHeight="1">
-      <c r="A585" s="80" t="s">
+      <c r="A585" s="79" t="s">
         <v>1451</v>
       </c>
-      <c r="B585" s="66">
+      <c r="B585" s="65">
         <v>93</v>
       </c>
-      <c r="C585" s="66">
+      <c r="C585" s="65">
         <v>2004</v>
       </c>
-      <c r="D585" s="66">
-        <v>1</v>
-      </c>
-      <c r="E585" s="66" t="s">
+      <c r="D585" s="65">
+        <v>1</v>
+      </c>
+      <c r="E585" s="65" t="s">
         <v>824</v>
       </c>
-      <c r="F585" s="66" t="s">
+      <c r="F585" s="65" t="s">
         <v>717</v>
       </c>
-      <c r="G585" s="67">
+      <c r="G585" s="66">
         <v>1800000</v>
       </c>
     </row>
     <row r="586" spans="1:7" ht="15" customHeight="1">
-      <c r="A586" s="80" t="s">
+      <c r="A586" s="79" t="s">
         <v>1451</v>
       </c>
-      <c r="B586" s="66">
+      <c r="B586" s="65">
         <v>93</v>
       </c>
-      <c r="C586" s="66">
+      <c r="C586" s="65">
         <v>2005</v>
       </c>
-      <c r="D586" s="66">
-        <v>1</v>
-      </c>
-      <c r="E586" s="66" t="s">
+      <c r="D586" s="65">
+        <v>1</v>
+      </c>
+      <c r="E586" s="65" t="s">
         <v>825</v>
       </c>
-      <c r="F586" s="66" t="s">
+      <c r="F586" s="65" t="s">
         <v>717</v>
       </c>
-      <c r="G586" s="67">
+      <c r="G586" s="66">
         <v>2400000</v>
       </c>
     </row>
     <row r="587" spans="1:7" ht="15" customHeight="1">
-      <c r="A587" s="80" t="s">
+      <c r="A587" s="79" t="s">
         <v>1451</v>
       </c>
-      <c r="B587" s="66">
+      <c r="B587" s="65">
         <v>93</v>
       </c>
-      <c r="C587" s="66">
+      <c r="C587" s="65">
         <v>2006</v>
       </c>
-      <c r="D587" s="66">
-        <v>1</v>
-      </c>
-      <c r="E587" s="66" t="s">
+      <c r="D587" s="65">
+        <v>1</v>
+      </c>
+      <c r="E587" s="65" t="s">
         <v>826</v>
       </c>
-      <c r="F587" s="66" t="s">
+      <c r="F587" s="65" t="s">
         <v>717</v>
       </c>
-      <c r="G587" s="67">
+      <c r="G587" s="66">
         <v>3800000</v>
       </c>
     </row>
     <row r="588" spans="1:7" ht="15" customHeight="1">
-      <c r="A588" s="80" t="s">
+      <c r="A588" s="79" t="s">
         <v>1451</v>
       </c>
-      <c r="B588" s="66">
+      <c r="B588" s="65">
         <v>93</v>
       </c>
-      <c r="C588" s="66">
+      <c r="C588" s="65">
         <v>2007</v>
       </c>
-      <c r="D588" s="66">
-        <v>1</v>
-      </c>
-      <c r="E588" s="66" t="s">
+      <c r="D588" s="65">
+        <v>1</v>
+      </c>
+      <c r="E588" s="65" t="s">
         <v>827</v>
       </c>
-      <c r="F588" s="66" t="s">
+      <c r="F588" s="65" t="s">
         <v>717</v>
       </c>
-      <c r="G588" s="67">
+      <c r="G588" s="66">
         <v>4900000</v>
       </c>
     </row>
     <row r="589" spans="1:7" ht="15" customHeight="1">
-      <c r="A589" s="80" t="s">
+      <c r="A589" s="79" t="s">
         <v>1451</v>
       </c>
-      <c r="B589" s="66">
+      <c r="B589" s="65">
         <v>93</v>
       </c>
-      <c r="C589" s="66">
+      <c r="C589" s="65">
         <v>2008</v>
       </c>
-      <c r="D589" s="66">
-        <v>1</v>
-      </c>
-      <c r="E589" s="66" t="s">
+      <c r="D589" s="65">
+        <v>1</v>
+      </c>
+      <c r="E589" s="65" t="s">
         <v>828</v>
       </c>
-      <c r="F589" s="66" t="s">
+      <c r="F589" s="65" t="s">
         <v>717</v>
       </c>
-      <c r="G589" s="67">
+      <c r="G589" s="66">
         <v>10000000</v>
       </c>
     </row>
     <row r="590" spans="1:7" ht="15" customHeight="1">
-      <c r="A590" s="80" t="s">
+      <c r="A590" s="79" t="s">
         <v>1451</v>
       </c>
-      <c r="B590" s="66">
+      <c r="B590" s="65">
         <v>93</v>
       </c>
-      <c r="C590" s="66">
+      <c r="C590" s="65">
         <v>2101</v>
       </c>
-      <c r="D590" s="66">
-        <v>1</v>
-      </c>
-      <c r="E590" s="66" t="s">
+      <c r="D590" s="65">
+        <v>1</v>
+      </c>
+      <c r="E590" s="65" t="s">
         <v>966</v>
       </c>
-      <c r="F590" s="66" t="s">
+      <c r="F590" s="65" t="s">
         <v>717</v>
       </c>
-      <c r="G590" s="67">
+      <c r="G590" s="66">
         <v>160000</v>
       </c>
     </row>
     <row r="591" spans="1:7" ht="15" customHeight="1">
-      <c r="A591" s="80" t="s">
+      <c r="A591" s="79" t="s">
         <v>1451</v>
       </c>
-      <c r="B591" s="66">
+      <c r="B591" s="65">
         <v>93</v>
       </c>
-      <c r="C591" s="66">
+      <c r="C591" s="65">
         <v>2102</v>
       </c>
-      <c r="D591" s="66">
-        <v>1</v>
-      </c>
-      <c r="E591" s="66" t="s">
+      <c r="D591" s="65">
+        <v>1</v>
+      </c>
+      <c r="E591" s="65" t="s">
         <v>967</v>
       </c>
-      <c r="F591" s="66" t="s">
+      <c r="F591" s="65" t="s">
         <v>717</v>
       </c>
-      <c r="G591" s="67">
+      <c r="G591" s="66">
         <v>650000</v>
       </c>
     </row>
     <row r="592" spans="1:7" ht="15" customHeight="1">
-      <c r="A592" s="80" t="s">
+      <c r="A592" s="79" t="s">
         <v>1451</v>
       </c>
-      <c r="B592" s="66">
+      <c r="B592" s="65">
         <v>93</v>
       </c>
-      <c r="C592" s="66">
+      <c r="C592" s="65">
         <v>2103</v>
       </c>
-      <c r="D592" s="66">
-        <v>1</v>
-      </c>
-      <c r="E592" s="66" t="s">
+      <c r="D592" s="65">
+        <v>1</v>
+      </c>
+      <c r="E592" s="65" t="s">
         <v>968</v>
       </c>
-      <c r="F592" s="66" t="s">
+      <c r="F592" s="65" t="s">
         <v>717</v>
       </c>
-      <c r="G592" s="67">
+      <c r="G592" s="66">
         <v>1000000</v>
       </c>
     </row>
     <row r="593" spans="1:10" ht="15" customHeight="1">
-      <c r="A593" s="80" t="s">
+      <c r="A593" s="79" t="s">
         <v>1451</v>
       </c>
-      <c r="B593" s="66">
+      <c r="B593" s="65">
         <v>93</v>
       </c>
-      <c r="C593" s="66">
+      <c r="C593" s="65">
         <v>2104</v>
       </c>
-      <c r="D593" s="66">
-        <v>1</v>
-      </c>
-      <c r="E593" s="66" t="s">
+      <c r="D593" s="65">
+        <v>1</v>
+      </c>
+      <c r="E593" s="65" t="s">
         <v>969</v>
       </c>
-      <c r="F593" s="66" t="s">
+      <c r="F593" s="65" t="s">
         <v>717</v>
       </c>
-      <c r="G593" s="67">
+      <c r="G593" s="66">
         <v>1800000</v>
       </c>
     </row>
     <row r="594" spans="1:10" ht="15" customHeight="1">
-      <c r="A594" s="80" t="s">
+      <c r="A594" s="79" t="s">
         <v>1451</v>
       </c>
-      <c r="B594" s="66">
+      <c r="B594" s="65">
         <v>93</v>
       </c>
-      <c r="C594" s="66">
+      <c r="C594" s="65">
         <v>2105</v>
       </c>
-      <c r="D594" s="66">
-        <v>1</v>
-      </c>
-      <c r="E594" s="66" t="s">
+      <c r="D594" s="65">
+        <v>1</v>
+      </c>
+      <c r="E594" s="65" t="s">
         <v>970</v>
       </c>
-      <c r="F594" s="66" t="s">
+      <c r="F594" s="65" t="s">
         <v>717</v>
       </c>
-      <c r="G594" s="67">
+      <c r="G594" s="66">
         <v>2400000</v>
       </c>
     </row>
     <row r="595" spans="1:10" ht="15" customHeight="1">
-      <c r="A595" s="80" t="s">
+      <c r="A595" s="79" t="s">
         <v>1451</v>
       </c>
-      <c r="B595" s="66">
+      <c r="B595" s="65">
         <v>93</v>
       </c>
-      <c r="C595" s="66">
+      <c r="C595" s="65">
         <v>2106</v>
       </c>
-      <c r="D595" s="66">
-        <v>1</v>
-      </c>
-      <c r="E595" s="66" t="s">
+      <c r="D595" s="65">
+        <v>1</v>
+      </c>
+      <c r="E595" s="65" t="s">
         <v>971</v>
       </c>
-      <c r="F595" s="66" t="s">
+      <c r="F595" s="65" t="s">
         <v>717</v>
       </c>
-      <c r="G595" s="67">
+      <c r="G595" s="66">
         <v>3800000</v>
       </c>
     </row>
     <row r="596" spans="1:10" ht="15" customHeight="1">
-      <c r="A596" s="80" t="s">
+      <c r="A596" s="79" t="s">
         <v>1451</v>
       </c>
-      <c r="B596" s="66">
+      <c r="B596" s="65">
         <v>93</v>
       </c>
-      <c r="C596" s="66">
+      <c r="C596" s="65">
         <v>2107</v>
       </c>
-      <c r="D596" s="66">
-        <v>1</v>
-      </c>
-      <c r="E596" s="66" t="s">
+      <c r="D596" s="65">
+        <v>1</v>
+      </c>
+      <c r="E596" s="65" t="s">
         <v>972</v>
       </c>
-      <c r="F596" s="66" t="s">
+      <c r="F596" s="65" t="s">
         <v>717</v>
       </c>
-      <c r="G596" s="67">
+      <c r="G596" s="66">
         <v>4900000</v>
       </c>
     </row>
     <row r="597" spans="1:10" ht="15" customHeight="1">
-      <c r="A597" s="80" t="s">
+      <c r="A597" s="79" t="s">
         <v>1451</v>
       </c>
-      <c r="B597" s="66">
+      <c r="B597" s="65">
         <v>93</v>
       </c>
-      <c r="C597" s="66">
+      <c r="C597" s="65">
         <v>2108</v>
       </c>
-      <c r="D597" s="66">
-        <v>1</v>
-      </c>
-      <c r="E597" s="66" t="s">
+      <c r="D597" s="65">
+        <v>1</v>
+      </c>
+      <c r="E597" s="65" t="s">
         <v>973</v>
       </c>
-      <c r="F597" s="66" t="s">
+      <c r="F597" s="65" t="s">
         <v>717</v>
       </c>
-      <c r="G597" s="67">
+      <c r="G597" s="66">
         <v>10000000</v>
       </c>
     </row>
@@ -35272,8 +35177,8 @@
       <c r="G598" s="31">
         <v>1500000</v>
       </c>
-      <c r="I598" s="76"/>
-      <c r="J598" s="60" t="s">
+      <c r="I598" s="75"/>
+      <c r="J598" s="59" t="s">
         <v>1647</v>
       </c>
     </row>
@@ -35299,8 +35204,8 @@
       <c r="G599" s="31">
         <v>7500000</v>
       </c>
-      <c r="I599" s="76"/>
-      <c r="J599" s="60" t="s">
+      <c r="I599" s="75"/>
+      <c r="J599" s="59" t="s">
         <v>1648</v>
       </c>
     </row>
@@ -35326,8 +35231,8 @@
       <c r="G600" s="31">
         <v>12000000</v>
       </c>
-      <c r="I600" s="76"/>
-      <c r="J600" s="60" t="s">
+      <c r="I600" s="75"/>
+      <c r="J600" s="59" t="s">
         <v>1649</v>
       </c>
     </row>
@@ -35353,8 +35258,8 @@
       <c r="G601" s="31">
         <v>23000000</v>
       </c>
-      <c r="I601" s="76"/>
-      <c r="J601" s="60" t="s">
+      <c r="I601" s="75"/>
+      <c r="J601" s="59" t="s">
         <v>1650</v>
       </c>
     </row>
@@ -35380,8 +35285,8 @@
       <c r="G602" s="31">
         <v>30000000</v>
       </c>
-      <c r="I602" s="76"/>
-      <c r="J602" s="60" t="s">
+      <c r="I602" s="75"/>
+      <c r="J602" s="59" t="s">
         <v>1651</v>
       </c>
     </row>
@@ -35407,8 +35312,8 @@
       <c r="G603" s="31">
         <v>45000000</v>
       </c>
-      <c r="I603" s="76"/>
-      <c r="J603" s="60" t="s">
+      <c r="I603" s="75"/>
+      <c r="J603" s="59" t="s">
         <v>1652</v>
       </c>
     </row>
@@ -35434,8 +35339,8 @@
       <c r="G604" s="31">
         <v>60000000</v>
       </c>
-      <c r="I604" s="76"/>
-      <c r="J604" s="60" t="s">
+      <c r="I604" s="75"/>
+      <c r="J604" s="59" t="s">
         <v>1653</v>
       </c>
     </row>
@@ -35461,8 +35366,8 @@
       <c r="G605" s="31">
         <v>119000000</v>
       </c>
-      <c r="I605" s="76"/>
-      <c r="J605" s="60" t="s">
+      <c r="I605" s="75"/>
+      <c r="J605" s="59" t="s">
         <v>1654</v>
       </c>
     </row>
@@ -35488,7 +35393,7 @@
       <c r="G606" s="31">
         <v>7500000</v>
       </c>
-      <c r="I606" s="76"/>
+      <c r="I606" s="75"/>
       <c r="J606" s="31" t="s">
         <v>1072</v>
       </c>
@@ -35515,8 +35420,8 @@
       <c r="G607" s="31">
         <v>1500000</v>
       </c>
-      <c r="I607" s="76"/>
-      <c r="J607" s="60" t="s">
+      <c r="I607" s="75"/>
+      <c r="J607" s="59" t="s">
         <v>1655</v>
       </c>
     </row>
@@ -35542,8 +35447,8 @@
       <c r="G608" s="31">
         <v>7500000</v>
       </c>
-      <c r="I608" s="76"/>
-      <c r="J608" s="60" t="s">
+      <c r="I608" s="75"/>
+      <c r="J608" s="59" t="s">
         <v>1656</v>
       </c>
     </row>
@@ -35569,8 +35474,8 @@
       <c r="G609" s="31">
         <v>12000000</v>
       </c>
-      <c r="I609" s="76"/>
-      <c r="J609" s="60" t="s">
+      <c r="I609" s="75"/>
+      <c r="J609" s="59" t="s">
         <v>1657</v>
       </c>
     </row>
@@ -35596,8 +35501,8 @@
       <c r="G610" s="31">
         <v>23000000</v>
       </c>
-      <c r="I610" s="76"/>
-      <c r="J610" s="60" t="s">
+      <c r="I610" s="75"/>
+      <c r="J610" s="59" t="s">
         <v>1658</v>
       </c>
     </row>
@@ -35623,8 +35528,8 @@
       <c r="G611" s="31">
         <v>30000000</v>
       </c>
-      <c r="I611" s="76"/>
-      <c r="J611" s="60" t="s">
+      <c r="I611" s="75"/>
+      <c r="J611" s="59" t="s">
         <v>1659</v>
       </c>
     </row>
@@ -35650,8 +35555,8 @@
       <c r="G612" s="31">
         <v>45000000</v>
       </c>
-      <c r="I612" s="76"/>
-      <c r="J612" s="60" t="s">
+      <c r="I612" s="75"/>
+      <c r="J612" s="59" t="s">
         <v>1660</v>
       </c>
     </row>
@@ -35677,8 +35582,8 @@
       <c r="G613" s="31">
         <v>60000000</v>
       </c>
-      <c r="I613" s="76"/>
-      <c r="J613" s="60" t="s">
+      <c r="I613" s="75"/>
+      <c r="J613" s="59" t="s">
         <v>1661</v>
       </c>
     </row>
@@ -35704,7 +35609,7 @@
       <c r="G614" s="31">
         <v>119000000</v>
       </c>
-      <c r="J614" s="60" t="s">
+      <c r="J614" s="59" t="s">
         <v>1662</v>
       </c>
     </row>
@@ -35730,7 +35635,7 @@
       <c r="G615" s="31">
         <v>1500000</v>
       </c>
-      <c r="J615" s="60" t="s">
+      <c r="J615" s="59" t="s">
         <v>1647</v>
       </c>
     </row>
@@ -35756,7 +35661,7 @@
       <c r="G616" s="31">
         <v>7500000</v>
       </c>
-      <c r="J616" s="60" t="s">
+      <c r="J616" s="59" t="s">
         <v>1648</v>
       </c>
     </row>
@@ -35782,7 +35687,7 @@
       <c r="G617" s="31">
         <v>12000000</v>
       </c>
-      <c r="J617" s="60" t="s">
+      <c r="J617" s="59" t="s">
         <v>1649</v>
       </c>
     </row>
@@ -35808,7 +35713,7 @@
       <c r="G618" s="31">
         <v>23000000</v>
       </c>
-      <c r="J618" s="60" t="s">
+      <c r="J618" s="59" t="s">
         <v>1650</v>
       </c>
     </row>
@@ -35834,7 +35739,7 @@
       <c r="G619" s="31">
         <v>30000000</v>
       </c>
-      <c r="J619" s="60" t="s">
+      <c r="J619" s="59" t="s">
         <v>1651</v>
       </c>
     </row>
@@ -35860,7 +35765,7 @@
       <c r="G620" s="31">
         <v>45000000</v>
       </c>
-      <c r="J620" s="60" t="s">
+      <c r="J620" s="59" t="s">
         <v>1652</v>
       </c>
     </row>
@@ -35886,7 +35791,7 @@
       <c r="G621" s="31">
         <v>60000000</v>
       </c>
-      <c r="J621" s="60" t="s">
+      <c r="J621" s="59" t="s">
         <v>1653</v>
       </c>
     </row>
@@ -35912,7 +35817,7 @@
       <c r="G622" s="31">
         <v>119000000</v>
       </c>
-      <c r="J622" s="60" t="s">
+      <c r="J622" s="59" t="s">
         <v>1654</v>
       </c>
     </row>
@@ -35964,7 +35869,7 @@
       <c r="G624" s="31">
         <v>1500000</v>
       </c>
-      <c r="J624" s="60" t="s">
+      <c r="J624" s="59" t="s">
         <v>1655</v>
       </c>
     </row>
@@ -35990,7 +35895,7 @@
       <c r="G625" s="31">
         <v>7500000</v>
       </c>
-      <c r="J625" s="60" t="s">
+      <c r="J625" s="59" t="s">
         <v>1656</v>
       </c>
     </row>
@@ -36016,7 +35921,7 @@
       <c r="G626" s="31">
         <v>12000000</v>
       </c>
-      <c r="J626" s="60" t="s">
+      <c r="J626" s="59" t="s">
         <v>1657</v>
       </c>
     </row>
@@ -36042,7 +35947,7 @@
       <c r="G627" s="31">
         <v>23000000</v>
       </c>
-      <c r="J627" s="60" t="s">
+      <c r="J627" s="59" t="s">
         <v>1658</v>
       </c>
     </row>
@@ -36068,7 +35973,7 @@
       <c r="G628" s="31">
         <v>30000000</v>
       </c>
-      <c r="J628" s="60" t="s">
+      <c r="J628" s="59" t="s">
         <v>1659</v>
       </c>
     </row>
@@ -36094,7 +35999,7 @@
       <c r="G629" s="31">
         <v>45000000</v>
       </c>
-      <c r="J629" s="60" t="s">
+      <c r="J629" s="59" t="s">
         <v>1660</v>
       </c>
     </row>
@@ -36120,7 +36025,7 @@
       <c r="G630" s="31">
         <v>60000000</v>
       </c>
-      <c r="J630" s="60" t="s">
+      <c r="J630" s="59" t="s">
         <v>1661</v>
       </c>
     </row>
@@ -36146,7 +36051,7 @@
       <c r="G631" s="31">
         <v>119000000</v>
       </c>
-      <c r="J631" s="60" t="s">
+      <c r="J631" s="59" t="s">
         <v>1662</v>
       </c>
     </row>
@@ -36169,7 +36074,7 @@
       <c r="G632" s="31">
         <v>1500000</v>
       </c>
-      <c r="J632" s="60" t="s">
+      <c r="J632" s="59" t="s">
         <v>1647</v>
       </c>
     </row>
@@ -36192,7 +36097,7 @@
       <c r="G633" s="31">
         <v>7500000</v>
       </c>
-      <c r="J633" s="60" t="s">
+      <c r="J633" s="59" t="s">
         <v>1648</v>
       </c>
     </row>
@@ -36215,7 +36120,7 @@
       <c r="G634" s="31">
         <v>12000000</v>
       </c>
-      <c r="J634" s="60" t="s">
+      <c r="J634" s="59" t="s">
         <v>1649</v>
       </c>
     </row>
@@ -36238,7 +36143,7 @@
       <c r="G635" s="31">
         <v>23000000</v>
       </c>
-      <c r="J635" s="60" t="s">
+      <c r="J635" s="59" t="s">
         <v>1650</v>
       </c>
     </row>
@@ -36261,7 +36166,7 @@
       <c r="G636" s="31">
         <v>30000000</v>
       </c>
-      <c r="J636" s="60" t="s">
+      <c r="J636" s="59" t="s">
         <v>1651</v>
       </c>
     </row>
@@ -36284,7 +36189,7 @@
       <c r="G637" s="31">
         <v>45000000</v>
       </c>
-      <c r="J637" s="60" t="s">
+      <c r="J637" s="59" t="s">
         <v>1652</v>
       </c>
     </row>
@@ -36307,7 +36212,7 @@
       <c r="G638" s="31">
         <v>60000000</v>
       </c>
-      <c r="J638" s="60" t="s">
+      <c r="J638" s="59" t="s">
         <v>1653</v>
       </c>
     </row>
@@ -36330,7 +36235,7 @@
       <c r="G639" s="31">
         <v>119000000</v>
       </c>
-      <c r="J639" s="60" t="s">
+      <c r="J639" s="59" t="s">
         <v>1654</v>
       </c>
     </row>
@@ -36376,7 +36281,7 @@
       <c r="G641" s="31">
         <v>1500000</v>
       </c>
-      <c r="J641" s="60" t="s">
+      <c r="J641" s="59" t="s">
         <v>1655</v>
       </c>
     </row>
@@ -36399,7 +36304,7 @@
       <c r="G642" s="31">
         <v>7500000</v>
       </c>
-      <c r="J642" s="60" t="s">
+      <c r="J642" s="59" t="s">
         <v>1656</v>
       </c>
     </row>
@@ -36422,7 +36327,7 @@
       <c r="G643" s="31">
         <v>12000000</v>
       </c>
-      <c r="J643" s="60" t="s">
+      <c r="J643" s="59" t="s">
         <v>1657</v>
       </c>
     </row>
@@ -36445,7 +36350,7 @@
       <c r="G644" s="31">
         <v>23000000</v>
       </c>
-      <c r="J644" s="60" t="s">
+      <c r="J644" s="59" t="s">
         <v>1658</v>
       </c>
     </row>
@@ -36468,7 +36373,7 @@
       <c r="G645" s="31">
         <v>30000000</v>
       </c>
-      <c r="J645" s="60" t="s">
+      <c r="J645" s="59" t="s">
         <v>1659</v>
       </c>
     </row>
@@ -36491,7 +36396,7 @@
       <c r="G646" s="31">
         <v>45000000</v>
       </c>
-      <c r="J646" s="60" t="s">
+      <c r="J646" s="59" t="s">
         <v>1660</v>
       </c>
     </row>
@@ -36514,7 +36419,7 @@
       <c r="G647" s="31">
         <v>60000000</v>
       </c>
-      <c r="J647" s="60" t="s">
+      <c r="J647" s="59" t="s">
         <v>1661</v>
       </c>
     </row>
@@ -36537,7 +36442,7 @@
       <c r="G648" s="31">
         <v>119000000</v>
       </c>
-      <c r="J648" s="60" t="s">
+      <c r="J648" s="59" t="s">
         <v>1662</v>
       </c>
     </row>
@@ -36563,10 +36468,10 @@
       <c r="H649" t="s">
         <v>838</v>
       </c>
-      <c r="I649" s="77">
+      <c r="I649" s="76">
         <v>990</v>
       </c>
-      <c r="J649" s="60" t="s">
+      <c r="J649" s="59" t="s">
         <v>1647</v>
       </c>
     </row>
@@ -36592,10 +36497,10 @@
       <c r="H650" t="s">
         <v>838</v>
       </c>
-      <c r="I650" s="77">
+      <c r="I650" s="76">
         <v>4990</v>
       </c>
-      <c r="J650" s="60" t="s">
+      <c r="J650" s="59" t="s">
         <v>1648</v>
       </c>
     </row>
@@ -36621,10 +36526,10 @@
       <c r="H651" t="s">
         <v>838</v>
       </c>
-      <c r="I651" s="77">
+      <c r="I651" s="76">
         <v>7990</v>
       </c>
-      <c r="J651" s="60" t="s">
+      <c r="J651" s="59" t="s">
         <v>1649</v>
       </c>
     </row>
@@ -36650,10 +36555,10 @@
       <c r="H652" t="s">
         <v>838</v>
       </c>
-      <c r="I652" s="77">
+      <c r="I652" s="76">
         <v>14990</v>
       </c>
-      <c r="J652" s="60" t="s">
+      <c r="J652" s="59" t="s">
         <v>1650</v>
       </c>
     </row>
@@ -36679,10 +36584,10 @@
       <c r="H653" t="s">
         <v>838</v>
       </c>
-      <c r="I653" s="77">
+      <c r="I653" s="76">
         <v>19990</v>
       </c>
-      <c r="J653" s="60" t="s">
+      <c r="J653" s="59" t="s">
         <v>1651</v>
       </c>
     </row>
@@ -36708,10 +36613,10 @@
       <c r="H654" t="s">
         <v>838</v>
       </c>
-      <c r="I654" s="77">
+      <c r="I654" s="76">
         <v>29990</v>
       </c>
-      <c r="J654" s="60" t="s">
+      <c r="J654" s="59" t="s">
         <v>1652</v>
       </c>
     </row>
@@ -36737,10 +36642,10 @@
       <c r="H655" t="s">
         <v>838</v>
       </c>
-      <c r="I655" s="77">
+      <c r="I655" s="76">
         <v>39990</v>
       </c>
-      <c r="J655" s="60" t="s">
+      <c r="J655" s="59" t="s">
         <v>1653</v>
       </c>
     </row>
@@ -36766,10 +36671,10 @@
       <c r="H656" t="s">
         <v>838</v>
       </c>
-      <c r="I656" s="77">
+      <c r="I656" s="76">
         <v>79990</v>
       </c>
-      <c r="J656" s="60" t="s">
+      <c r="J656" s="59" t="s">
         <v>1654</v>
       </c>
     </row>
@@ -36795,7 +36700,7 @@
       <c r="H657" t="s">
         <v>838</v>
       </c>
-      <c r="I657" s="77">
+      <c r="I657" s="76">
         <v>4990</v>
       </c>
       <c r="J657" s="31" t="s">
@@ -36824,10 +36729,10 @@
       <c r="H658" t="s">
         <v>838</v>
       </c>
-      <c r="I658" s="77">
+      <c r="I658" s="76">
         <v>990</v>
       </c>
-      <c r="J658" s="60" t="s">
+      <c r="J658" s="59" t="s">
         <v>1655</v>
       </c>
     </row>
@@ -36853,10 +36758,10 @@
       <c r="H659" t="s">
         <v>838</v>
       </c>
-      <c r="I659" s="77">
+      <c r="I659" s="76">
         <v>4990</v>
       </c>
-      <c r="J659" s="60" t="s">
+      <c r="J659" s="59" t="s">
         <v>1656</v>
       </c>
     </row>
@@ -36882,10 +36787,10 @@
       <c r="H660" t="s">
         <v>838</v>
       </c>
-      <c r="I660" s="77">
+      <c r="I660" s="76">
         <v>7990</v>
       </c>
-      <c r="J660" s="60" t="s">
+      <c r="J660" s="59" t="s">
         <v>1657</v>
       </c>
     </row>
@@ -36911,10 +36816,10 @@
       <c r="H661" t="s">
         <v>838</v>
       </c>
-      <c r="I661" s="77">
+      <c r="I661" s="76">
         <v>14990</v>
       </c>
-      <c r="J661" s="60" t="s">
+      <c r="J661" s="59" t="s">
         <v>1658</v>
       </c>
     </row>
@@ -36940,10 +36845,10 @@
       <c r="H662" t="s">
         <v>838</v>
       </c>
-      <c r="I662" s="77">
+      <c r="I662" s="76">
         <v>19990</v>
       </c>
-      <c r="J662" s="60" t="s">
+      <c r="J662" s="59" t="s">
         <v>1659</v>
       </c>
     </row>
@@ -36969,10 +36874,10 @@
       <c r="H663" t="s">
         <v>838</v>
       </c>
-      <c r="I663" s="77">
+      <c r="I663" s="76">
         <v>29990</v>
       </c>
-      <c r="J663" s="60" t="s">
+      <c r="J663" s="59" t="s">
         <v>1660</v>
       </c>
     </row>
@@ -36998,10 +36903,10 @@
       <c r="H664" t="s">
         <v>838</v>
       </c>
-      <c r="I664" s="77">
+      <c r="I664" s="76">
         <v>39990</v>
       </c>
-      <c r="J664" s="60" t="s">
+      <c r="J664" s="59" t="s">
         <v>1661</v>
       </c>
     </row>
@@ -37030,7 +36935,7 @@
       <c r="I665">
         <v>79990</v>
       </c>
-      <c r="J665" s="60" t="s">
+      <c r="J665" s="59" t="s">
         <v>1662</v>
       </c>
     </row>
@@ -37756,10 +37661,10 @@
       <c r="H700" t="s">
         <v>838</v>
       </c>
-      <c r="I700" s="77">
+      <c r="I700" s="76">
         <v>990</v>
       </c>
-      <c r="J700" s="60" t="s">
+      <c r="J700" s="59" t="s">
         <v>1647</v>
       </c>
     </row>
@@ -37785,10 +37690,10 @@
       <c r="H701" t="s">
         <v>838</v>
       </c>
-      <c r="I701" s="77">
+      <c r="I701" s="76">
         <v>4990</v>
       </c>
-      <c r="J701" s="60" t="s">
+      <c r="J701" s="59" t="s">
         <v>1648</v>
       </c>
     </row>
@@ -37814,10 +37719,10 @@
       <c r="H702" t="s">
         <v>838</v>
       </c>
-      <c r="I702" s="77">
+      <c r="I702" s="76">
         <v>7990</v>
       </c>
-      <c r="J702" s="60" t="s">
+      <c r="J702" s="59" t="s">
         <v>1649</v>
       </c>
     </row>
@@ -37843,10 +37748,10 @@
       <c r="H703" t="s">
         <v>838</v>
       </c>
-      <c r="I703" s="77">
+      <c r="I703" s="76">
         <v>14990</v>
       </c>
-      <c r="J703" s="60" t="s">
+      <c r="J703" s="59" t="s">
         <v>1650</v>
       </c>
     </row>
@@ -37872,10 +37777,10 @@
       <c r="H704" t="s">
         <v>838</v>
       </c>
-      <c r="I704" s="77">
+      <c r="I704" s="76">
         <v>19990</v>
       </c>
-      <c r="J704" s="60" t="s">
+      <c r="J704" s="59" t="s">
         <v>1651</v>
       </c>
     </row>
@@ -37901,10 +37806,10 @@
       <c r="H705" t="s">
         <v>838</v>
       </c>
-      <c r="I705" s="77">
+      <c r="I705" s="76">
         <v>29990</v>
       </c>
-      <c r="J705" s="60" t="s">
+      <c r="J705" s="59" t="s">
         <v>1652</v>
       </c>
     </row>
@@ -37930,10 +37835,10 @@
       <c r="H706" t="s">
         <v>838</v>
       </c>
-      <c r="I706" s="77">
+      <c r="I706" s="76">
         <v>39990</v>
       </c>
-      <c r="J706" s="60" t="s">
+      <c r="J706" s="59" t="s">
         <v>1653</v>
       </c>
     </row>
@@ -37959,10 +37864,10 @@
       <c r="H707" t="s">
         <v>838</v>
       </c>
-      <c r="I707" s="77">
+      <c r="I707" s="76">
         <v>79990</v>
       </c>
-      <c r="J707" s="60" t="s">
+      <c r="J707" s="59" t="s">
         <v>1654</v>
       </c>
     </row>
@@ -37988,7 +37893,7 @@
       <c r="H708" t="s">
         <v>838</v>
       </c>
-      <c r="I708" s="77">
+      <c r="I708" s="76">
         <v>4990</v>
       </c>
       <c r="J708" s="31" t="s">
@@ -38017,10 +37922,10 @@
       <c r="H709" t="s">
         <v>838</v>
       </c>
-      <c r="I709" s="77">
+      <c r="I709" s="76">
         <v>990</v>
       </c>
-      <c r="J709" s="60" t="s">
+      <c r="J709" s="59" t="s">
         <v>1655</v>
       </c>
     </row>
@@ -38046,10 +37951,10 @@
       <c r="H710" t="s">
         <v>838</v>
       </c>
-      <c r="I710" s="77">
+      <c r="I710" s="76">
         <v>4990</v>
       </c>
-      <c r="J710" s="60" t="s">
+      <c r="J710" s="59" t="s">
         <v>1656</v>
       </c>
     </row>
@@ -38075,10 +37980,10 @@
       <c r="H711" t="s">
         <v>838</v>
       </c>
-      <c r="I711" s="77">
+      <c r="I711" s="76">
         <v>7990</v>
       </c>
-      <c r="J711" s="60" t="s">
+      <c r="J711" s="59" t="s">
         <v>1657</v>
       </c>
     </row>
@@ -38104,10 +38009,10 @@
       <c r="H712" t="s">
         <v>838</v>
       </c>
-      <c r="I712" s="77">
+      <c r="I712" s="76">
         <v>14990</v>
       </c>
-      <c r="J712" s="60" t="s">
+      <c r="J712" s="59" t="s">
         <v>1658</v>
       </c>
     </row>
@@ -38133,10 +38038,10 @@
       <c r="H713" t="s">
         <v>838</v>
       </c>
-      <c r="I713" s="77">
+      <c r="I713" s="76">
         <v>19990</v>
       </c>
-      <c r="J713" s="60" t="s">
+      <c r="J713" s="59" t="s">
         <v>1659</v>
       </c>
     </row>
@@ -38162,10 +38067,10 @@
       <c r="H714" t="s">
         <v>838</v>
       </c>
-      <c r="I714" s="77">
+      <c r="I714" s="76">
         <v>29990</v>
       </c>
-      <c r="J714" s="60" t="s">
+      <c r="J714" s="59" t="s">
         <v>1660</v>
       </c>
     </row>
@@ -38191,10 +38096,10 @@
       <c r="H715" t="s">
         <v>838</v>
       </c>
-      <c r="I715" s="77">
+      <c r="I715" s="76">
         <v>39990</v>
       </c>
-      <c r="J715" s="60" t="s">
+      <c r="J715" s="59" t="s">
         <v>1661</v>
       </c>
     </row>
@@ -38223,7 +38128,7 @@
       <c r="I716">
         <v>79990</v>
       </c>
-      <c r="J716" s="60" t="s">
+      <c r="J716" s="59" t="s">
         <v>1662</v>
       </c>
     </row>
@@ -38232,6 +38137,130 @@
   <phoneticPr fontId="27" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
+  <dimension ref="A1:K11"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
+  <cols>
+    <col min="1" max="1" width="22.625" customWidth="1"/>
+    <col min="2" max="2" width="17.25" customWidth="1"/>
+    <col min="3" max="3" width="18.75" customWidth="1"/>
+    <col min="4" max="4" width="25.25" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:11">
+      <c r="A1" t="s">
+        <v>21</v>
+      </c>
+      <c r="B1" t="s">
+        <v>15</v>
+      </c>
+      <c r="C1" t="s">
+        <v>1</v>
+      </c>
+      <c r="D1" t="s">
+        <v>568</v>
+      </c>
+    </row>
+    <row r="2" spans="1:11">
+      <c r="A2" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="3" spans="1:11">
+      <c r="A3" t="s">
+        <v>65</v>
+      </c>
+      <c r="C3" t="s">
+        <v>67</v>
+      </c>
+      <c r="D3" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="4" spans="1:11">
+      <c r="A4" t="s">
+        <v>569</v>
+      </c>
+      <c r="B4">
+        <v>1</v>
+      </c>
+      <c r="C4" t="s">
+        <v>570</v>
+      </c>
+      <c r="D4" s="33" t="s">
+        <v>1728</v>
+      </c>
+    </row>
+    <row r="5" spans="1:11">
+      <c r="A5" s="33" t="s">
+        <v>1715</v>
+      </c>
+      <c r="B5">
+        <v>2</v>
+      </c>
+      <c r="C5" t="s">
+        <v>570</v>
+      </c>
+      <c r="D5" s="33" t="s">
+        <v>1727</v>
+      </c>
+      <c r="J5" t="s">
+        <v>15</v>
+      </c>
+      <c r="K5" t="s">
+        <v>571</v>
+      </c>
+    </row>
+    <row r="6" spans="1:11">
+      <c r="A6" s="33" t="s">
+        <v>1716</v>
+      </c>
+      <c r="B6">
+        <v>3</v>
+      </c>
+      <c r="C6" t="s">
+        <v>570</v>
+      </c>
+      <c r="D6" s="33" t="s">
+        <v>1727</v>
+      </c>
+      <c r="K6" t="s">
+        <v>572</v>
+      </c>
+    </row>
+    <row r="7" spans="1:11">
+      <c r="K7" t="s">
+        <v>573</v>
+      </c>
+    </row>
+    <row r="8" spans="1:11">
+      <c r="K8" t="s">
+        <v>574</v>
+      </c>
+    </row>
+    <row r="9" spans="1:11">
+      <c r="K9" s="17" t="s">
+        <v>575</v>
+      </c>
+    </row>
+    <row r="10" spans="1:11">
+      <c r="K10" s="33" t="s">
+        <v>1679</v>
+      </c>
+    </row>
+    <row r="11" spans="1:11">
+      <c r="K11" s="33" t="s">
+        <v>1680</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="27" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
 </worksheet>
 </file>
 
@@ -38668,7 +38697,7 @@
       <c r="E21" s="51">
         <v>650000</v>
       </c>
-      <c r="F21" s="56" t="s">
+      <c r="F21" s="55" t="s">
         <v>1347</v>
       </c>
       <c r="G21">
@@ -38688,7 +38717,7 @@
       <c r="E22" s="51">
         <v>160000</v>
       </c>
-      <c r="F22" s="56" t="s">
+      <c r="F22" s="55" t="s">
         <v>1348</v>
       </c>
       <c r="G22">
@@ -38709,7 +38738,7 @@
       <c r="E23" s="51">
         <v>650000</v>
       </c>
-      <c r="F23" s="56" t="s">
+      <c r="F23" s="55" t="s">
         <v>1347</v>
       </c>
       <c r="G23">
@@ -38730,7 +38759,7 @@
       <c r="E24" s="51">
         <v>1000000</v>
       </c>
-      <c r="F24" s="56" t="s">
+      <c r="F24" s="55" t="s">
         <v>1349</v>
       </c>
       <c r="G24">
@@ -38751,7 +38780,7 @@
       <c r="E25" s="51">
         <v>1800000</v>
       </c>
-      <c r="F25" s="56" t="s">
+      <c r="F25" s="55" t="s">
         <v>1350</v>
       </c>
       <c r="G25">
@@ -38772,7 +38801,7 @@
       <c r="E26" s="51">
         <v>2400000</v>
       </c>
-      <c r="F26" s="56" t="s">
+      <c r="F26" s="55" t="s">
         <v>1351</v>
       </c>
       <c r="G26">
@@ -38793,7 +38822,7 @@
       <c r="E27" s="51">
         <v>3800000</v>
       </c>
-      <c r="F27" s="56" t="s">
+      <c r="F27" s="55" t="s">
         <v>1352</v>
       </c>
       <c r="G27">
@@ -38814,7 +38843,7 @@
       <c r="E28" s="51">
         <v>4900000</v>
       </c>
-      <c r="F28" s="57" t="s">
+      <c r="F28" s="56" t="s">
         <v>1112</v>
       </c>
       <c r="G28">
@@ -38835,7 +38864,7 @@
       <c r="E29" s="51">
         <v>10000000</v>
       </c>
-      <c r="F29" s="57" t="s">
+      <c r="F29" s="56" t="s">
         <v>1113</v>
       </c>
       <c r="G29">
@@ -38856,7 +38885,7 @@
       <c r="E30" s="51">
         <v>160000</v>
       </c>
-      <c r="F30" s="56" t="s">
+      <c r="F30" s="55" t="s">
         <v>1348</v>
       </c>
       <c r="G30">
@@ -38876,7 +38905,7 @@
       <c r="E31" s="51">
         <v>650000</v>
       </c>
-      <c r="F31" s="56" t="s">
+      <c r="F31" s="55" t="s">
         <v>1347</v>
       </c>
       <c r="G31">
@@ -38896,7 +38925,7 @@
       <c r="E32" s="51">
         <v>1000000</v>
       </c>
-      <c r="F32" s="56" t="s">
+      <c r="F32" s="55" t="s">
         <v>1349</v>
       </c>
       <c r="G32">
@@ -38916,7 +38945,7 @@
       <c r="E33" s="51">
         <v>1800000</v>
       </c>
-      <c r="F33" s="56" t="s">
+      <c r="F33" s="55" t="s">
         <v>1350</v>
       </c>
       <c r="G33">
@@ -38936,7 +38965,7 @@
       <c r="E34" s="51">
         <v>2400000</v>
       </c>
-      <c r="F34" s="56" t="s">
+      <c r="F34" s="55" t="s">
         <v>1351</v>
       </c>
       <c r="G34">
@@ -38956,7 +38985,7 @@
       <c r="E35" s="51">
         <v>3800000</v>
       </c>
-      <c r="F35" s="56" t="s">
+      <c r="F35" s="55" t="s">
         <v>1352</v>
       </c>
       <c r="G35">
@@ -38976,7 +39005,7 @@
       <c r="E36" s="51">
         <v>4900000</v>
       </c>
-      <c r="F36" s="57" t="s">
+      <c r="F36" s="56" t="s">
         <v>1112</v>
       </c>
       <c r="G36">
@@ -38996,7 +39025,7 @@
       <c r="E37" s="51">
         <v>10000000</v>
       </c>
-      <c r="F37" s="57" t="s">
+      <c r="F37" s="56" t="s">
         <v>1113</v>
       </c>
       <c r="G37">
@@ -40396,8 +40425,8 @@
       <c r="E106" s="31">
         <v>7500000</v>
       </c>
-      <c r="F106" s="54">
-        <v>7500</v>
+      <c r="F106" s="92" t="s">
+        <v>1730</v>
       </c>
       <c r="G106">
         <v>1</v>
@@ -40419,8 +40448,8 @@
       <c r="E107" s="31">
         <v>1500000</v>
       </c>
-      <c r="F107" s="54">
-        <v>1500</v>
+      <c r="F107" s="92" t="s">
+        <v>1729</v>
       </c>
       <c r="G107" s="13">
         <v>0</v>
@@ -40442,8 +40471,8 @@
       <c r="E108" s="31">
         <v>7500000</v>
       </c>
-      <c r="F108" s="54">
-        <v>7500</v>
+      <c r="F108" s="92" t="s">
+        <v>1730</v>
       </c>
       <c r="G108" s="13">
         <v>0</v>
@@ -40465,8 +40494,8 @@
       <c r="E109" s="31">
         <v>12000000</v>
       </c>
-      <c r="F109" s="54">
-        <v>12000</v>
+      <c r="F109" s="92" t="s">
+        <v>1731</v>
       </c>
       <c r="G109" s="13">
         <v>0</v>
@@ -40488,8 +40517,8 @@
       <c r="E110" s="31">
         <v>23000000</v>
       </c>
-      <c r="F110" s="54">
-        <v>23000</v>
+      <c r="F110" s="92" t="s">
+        <v>1732</v>
       </c>
       <c r="G110" s="13">
         <v>0</v>
@@ -40511,8 +40540,8 @@
       <c r="E111" s="31">
         <v>30000000</v>
       </c>
-      <c r="F111" s="54">
-        <v>30000</v>
+      <c r="F111" s="92" t="s">
+        <v>1733</v>
       </c>
       <c r="G111" s="13">
         <v>0</v>
@@ -40534,8 +40563,8 @@
       <c r="E112" s="31">
         <v>45000000</v>
       </c>
-      <c r="F112" s="54">
-        <v>45000</v>
+      <c r="F112" s="92" t="s">
+        <v>1734</v>
       </c>
       <c r="G112" s="13">
         <v>0</v>
@@ -40557,8 +40586,8 @@
       <c r="E113" s="31">
         <v>60000000</v>
       </c>
-      <c r="F113" s="54">
-        <v>60000</v>
+      <c r="F113" s="92" t="s">
+        <v>1735</v>
       </c>
       <c r="G113" s="13">
         <v>0</v>
@@ -40580,8 +40609,8 @@
       <c r="E114" s="31">
         <v>119000000</v>
       </c>
-      <c r="F114" s="54">
-        <v>119000</v>
+      <c r="F114" s="92" t="s">
+        <v>1736</v>
       </c>
       <c r="G114" s="13">
         <v>0</v>
@@ -40603,8 +40632,8 @@
       <c r="E115" s="31">
         <v>1500000</v>
       </c>
-      <c r="F115" s="54">
-        <v>1500</v>
+      <c r="F115" s="92" t="s">
+        <v>1729</v>
       </c>
       <c r="G115" s="13">
         <v>0</v>
@@ -40626,8 +40655,8 @@
       <c r="E116" s="31">
         <v>7500000</v>
       </c>
-      <c r="F116" s="54">
-        <v>7500</v>
+      <c r="F116" s="92" t="s">
+        <v>1730</v>
       </c>
       <c r="G116" s="13">
         <v>0</v>
@@ -40649,8 +40678,8 @@
       <c r="E117" s="31">
         <v>12000000</v>
       </c>
-      <c r="F117" s="54">
-        <v>12000</v>
+      <c r="F117" s="92" t="s">
+        <v>1731</v>
       </c>
       <c r="G117" s="13">
         <v>0</v>
@@ -40672,8 +40701,8 @@
       <c r="E118" s="31">
         <v>23000000</v>
       </c>
-      <c r="F118" s="54">
-        <v>23000</v>
+      <c r="F118" s="92" t="s">
+        <v>1732</v>
       </c>
       <c r="G118" s="13">
         <v>0</v>
@@ -40695,8 +40724,8 @@
       <c r="E119" s="31">
         <v>30000000</v>
       </c>
-      <c r="F119" s="54">
-        <v>30000</v>
+      <c r="F119" s="92" t="s">
+        <v>1733</v>
       </c>
       <c r="G119" s="13">
         <v>0</v>
@@ -40718,8 +40747,8 @@
       <c r="E120" s="31">
         <v>45000000</v>
       </c>
-      <c r="F120" s="54">
-        <v>45000</v>
+      <c r="F120" s="92" t="s">
+        <v>1734</v>
       </c>
       <c r="G120" s="13">
         <v>0</v>
@@ -40741,8 +40770,8 @@
       <c r="E121" s="31">
         <v>60000000</v>
       </c>
-      <c r="F121" s="54">
-        <v>60000</v>
+      <c r="F121" s="92" t="s">
+        <v>1735</v>
       </c>
       <c r="G121" s="13">
         <v>0</v>
@@ -40764,8 +40793,8 @@
       <c r="E122" s="31">
         <v>119000000</v>
       </c>
-      <c r="F122" s="54">
-        <v>119000</v>
+      <c r="F122" s="92" t="s">
+        <v>1736</v>
       </c>
       <c r="G122" s="13">
         <v>0</v>
@@ -41237,19 +41266,19 @@
       <c r="B4" s="5">
         <v>100</v>
       </c>
-      <c r="C4" s="62" t="s">
+      <c r="C4" s="61" t="s">
         <v>1717</v>
       </c>
       <c r="D4" s="6" t="s">
         <v>1168</v>
       </c>
-      <c r="E4" s="62" t="s">
+      <c r="E4" s="61" t="s">
         <v>1718</v>
       </c>
       <c r="F4" s="6" t="s">
         <v>1492</v>
       </c>
-      <c r="G4" s="62" t="s">
+      <c r="G4" s="61" t="s">
         <v>1719</v>
       </c>
       <c r="H4" s="7">
@@ -41269,19 +41298,19 @@
       <c r="B5" s="6">
         <v>101</v>
       </c>
-      <c r="C5" s="62" t="s">
+      <c r="C5" s="61" t="s">
         <v>1717</v>
       </c>
       <c r="D5" s="6" t="s">
         <v>1493</v>
       </c>
-      <c r="E5" s="62" t="s">
+      <c r="E5" s="61" t="s">
         <v>1718</v>
       </c>
       <c r="F5" s="6" t="s">
         <v>1494</v>
       </c>
-      <c r="G5" s="62" t="s">
+      <c r="G5" s="61" t="s">
         <v>1719</v>
       </c>
       <c r="H5" s="6">
@@ -41301,19 +41330,19 @@
       <c r="B6" s="6">
         <v>200</v>
       </c>
-      <c r="C6" s="62" t="s">
+      <c r="C6" s="61" t="s">
         <v>1717</v>
       </c>
       <c r="D6" s="6" t="s">
         <v>1493</v>
       </c>
-      <c r="E6" s="62" t="s">
+      <c r="E6" s="61" t="s">
         <v>1718</v>
       </c>
       <c r="F6" s="6" t="s">
         <v>1494</v>
       </c>
-      <c r="G6" s="62" t="s">
+      <c r="G6" s="61" t="s">
         <v>1719</v>
       </c>
       <c r="H6" s="6">
@@ -41333,19 +41362,19 @@
       <c r="B7" s="6">
         <v>201</v>
       </c>
-      <c r="C7" s="62" t="s">
+      <c r="C7" s="61" t="s">
         <v>1717</v>
       </c>
       <c r="D7" s="6" t="s">
         <v>1493</v>
       </c>
-      <c r="E7" s="62" t="s">
+      <c r="E7" s="61" t="s">
         <v>1718</v>
       </c>
       <c r="F7" s="6" t="s">
         <v>1494</v>
       </c>
-      <c r="G7" s="62" t="s">
+      <c r="G7" s="61" t="s">
         <v>1719</v>
       </c>
       <c r="H7" s="6">
@@ -41365,19 +41394,19 @@
       <c r="B8" s="6">
         <v>202</v>
       </c>
-      <c r="C8" s="62" t="s">
+      <c r="C8" s="61" t="s">
         <v>1717</v>
       </c>
       <c r="D8" s="6" t="s">
         <v>1498</v>
       </c>
-      <c r="E8" s="62" t="s">
+      <c r="E8" s="61" t="s">
         <v>1718</v>
       </c>
       <c r="F8" s="6" t="s">
         <v>1494</v>
       </c>
-      <c r="G8" s="62" t="s">
+      <c r="G8" s="61" t="s">
         <v>1719</v>
       </c>
       <c r="H8" s="6">
@@ -41397,19 +41426,19 @@
       <c r="B9" s="6">
         <v>203</v>
       </c>
-      <c r="C9" s="62" t="s">
+      <c r="C9" s="61" t="s">
         <v>1717</v>
       </c>
       <c r="D9" s="6" t="s">
         <v>1498</v>
       </c>
-      <c r="E9" s="62" t="s">
+      <c r="E9" s="61" t="s">
         <v>1718</v>
       </c>
       <c r="F9" s="6" t="s">
         <v>1494</v>
       </c>
-      <c r="G9" s="62" t="s">
+      <c r="G9" s="61" t="s">
         <v>1719</v>
       </c>
       <c r="H9" s="6">
@@ -41429,19 +41458,19 @@
       <c r="B10" s="6">
         <v>204</v>
       </c>
-      <c r="C10" s="62" t="s">
+      <c r="C10" s="61" t="s">
         <v>1717</v>
       </c>
       <c r="D10" s="6" t="s">
         <v>1498</v>
       </c>
-      <c r="E10" s="62" t="s">
+      <c r="E10" s="61" t="s">
         <v>1718</v>
       </c>
       <c r="F10" s="6" t="s">
         <v>1494</v>
       </c>
-      <c r="G10" s="62" t="s">
+      <c r="G10" s="61" t="s">
         <v>1719</v>
       </c>
       <c r="H10" s="6"/>
@@ -41456,19 +41485,19 @@
       <c r="B11" s="6">
         <v>205</v>
       </c>
-      <c r="C11" s="62" t="s">
+      <c r="C11" s="61" t="s">
         <v>1717</v>
       </c>
       <c r="D11" s="6" t="s">
         <v>1498</v>
       </c>
-      <c r="E11" s="62" t="s">
+      <c r="E11" s="61" t="s">
         <v>1718</v>
       </c>
       <c r="F11" s="6" t="s">
         <v>1494</v>
       </c>
-      <c r="G11" s="62" t="s">
+      <c r="G11" s="61" t="s">
         <v>1719</v>
       </c>
       <c r="H11" s="6">
@@ -41481,35 +41510,35 @@
         <v>1495</v>
       </c>
     </row>
-    <row r="12" spans="1:10" s="59" customFormat="1">
-      <c r="A12" s="69" t="s">
+    <row r="12" spans="1:10" s="58" customFormat="1">
+      <c r="A12" s="68" t="s">
         <v>1471</v>
       </c>
-      <c r="B12" s="70">
+      <c r="B12" s="69">
         <v>206</v>
       </c>
-      <c r="C12" s="70" t="s">
+      <c r="C12" s="69" t="s">
         <v>1472</v>
       </c>
-      <c r="D12" s="70" t="s">
+      <c r="D12" s="69" t="s">
         <v>1175</v>
       </c>
-      <c r="E12" s="70" t="s">
+      <c r="E12" s="69" t="s">
         <v>1473</v>
       </c>
-      <c r="F12" s="70" t="s">
+      <c r="F12" s="69" t="s">
         <v>1171</v>
       </c>
-      <c r="G12" s="70" t="s">
+      <c r="G12" s="69" t="s">
         <v>1474</v>
       </c>
-      <c r="H12" s="70">
+      <c r="H12" s="69">
         <v>92</v>
       </c>
-      <c r="I12" s="75" t="s">
+      <c r="I12" s="74" t="s">
         <v>1480</v>
       </c>
-      <c r="J12" s="72" t="s">
+      <c r="J12" s="71" t="s">
         <v>1475</v>
       </c>
     </row>
@@ -41520,19 +41549,19 @@
       <c r="B13" s="6">
         <v>300</v>
       </c>
-      <c r="C13" s="89" t="s">
+      <c r="C13" s="88" t="s">
         <v>1720</v>
       </c>
       <c r="D13" s="6" t="s">
         <v>1501</v>
       </c>
-      <c r="E13" s="90" t="s">
+      <c r="E13" s="89" t="s">
         <v>1721</v>
       </c>
       <c r="F13" s="6" t="s">
         <v>1502</v>
       </c>
-      <c r="G13" s="90" t="s">
+      <c r="G13" s="89" t="s">
         <v>1722</v>
       </c>
       <c r="H13" s="6">
@@ -41552,19 +41581,19 @@
       <c r="B14" s="6">
         <v>301</v>
       </c>
-      <c r="C14" s="89" t="s">
+      <c r="C14" s="88" t="s">
         <v>1720</v>
       </c>
       <c r="D14" s="6" t="s">
         <v>1501</v>
       </c>
-      <c r="E14" s="90" t="s">
+      <c r="E14" s="89" t="s">
         <v>1721</v>
       </c>
       <c r="F14" s="6" t="s">
         <v>1502</v>
       </c>
-      <c r="G14" s="90" t="s">
+      <c r="G14" s="89" t="s">
         <v>1722</v>
       </c>
       <c r="H14" s="6">
@@ -41584,19 +41613,19 @@
       <c r="B15" s="6">
         <v>302</v>
       </c>
-      <c r="C15" s="89" t="s">
+      <c r="C15" s="88" t="s">
         <v>1720</v>
       </c>
       <c r="D15" s="6" t="s">
         <v>1501</v>
       </c>
-      <c r="E15" s="90" t="s">
+      <c r="E15" s="89" t="s">
         <v>1721</v>
       </c>
       <c r="F15" s="6" t="s">
         <v>1183</v>
       </c>
-      <c r="G15" s="90" t="s">
+      <c r="G15" s="89" t="s">
         <v>1722</v>
       </c>
       <c r="H15" s="6"/>
@@ -41604,64 +41633,64 @@
         <v>1114</v>
       </c>
     </row>
-    <row r="16" spans="1:10" s="59" customFormat="1">
-      <c r="A16" s="82" t="s">
+    <row r="16" spans="1:10" s="58" customFormat="1">
+      <c r="A16" s="81" t="s">
         <v>1710</v>
       </c>
-      <c r="B16" s="73">
+      <c r="B16" s="72">
         <v>303</v>
       </c>
-      <c r="C16" s="89" t="s">
+      <c r="C16" s="88" t="s">
         <v>1720</v>
       </c>
-      <c r="D16" s="91" t="s">
+      <c r="D16" s="90" t="s">
         <v>1476</v>
       </c>
-      <c r="E16" s="90" t="s">
+      <c r="E16" s="89" t="s">
         <v>1721</v>
       </c>
-      <c r="F16" s="91" t="s">
+      <c r="F16" s="90" t="s">
         <v>1183</v>
       </c>
-      <c r="G16" s="90" t="s">
+      <c r="G16" s="89" t="s">
         <v>1722</v>
       </c>
-      <c r="H16" s="74">
+      <c r="H16" s="73">
         <v>93</v>
       </c>
-      <c r="I16" s="71" t="s">
+      <c r="I16" s="70" t="s">
         <v>1114</v>
       </c>
-      <c r="J16" s="88" t="s">
+      <c r="J16" s="87" t="s">
         <v>1713</v>
       </c>
     </row>
     <row r="17" spans="1:10" s="49" customFormat="1">
-      <c r="A17" s="86" t="s">
+      <c r="A17" s="85" t="s">
         <v>1707</v>
       </c>
-      <c r="B17" s="83" t="s">
+      <c r="B17" s="82" t="s">
         <v>1706</v>
       </c>
-      <c r="C17" s="89" t="s">
+      <c r="C17" s="88" t="s">
         <v>1720</v>
       </c>
-      <c r="D17" s="84" t="s">
+      <c r="D17" s="83" t="s">
         <v>1501</v>
       </c>
-      <c r="E17" s="90" t="s">
+      <c r="E17" s="89" t="s">
         <v>1721</v>
       </c>
-      <c r="F17" s="84" t="s">
+      <c r="F17" s="83" t="s">
         <v>1502</v>
       </c>
-      <c r="G17" s="90" t="s">
+      <c r="G17" s="89" t="s">
         <v>1722</v>
       </c>
-      <c r="H17" s="83" t="s">
+      <c r="H17" s="82" t="s">
         <v>1708</v>
       </c>
-      <c r="I17" s="85" t="s">
+      <c r="I17" s="84" t="s">
         <v>1114</v>
       </c>
       <c r="J17" s="50" t="s">
@@ -41675,19 +41704,19 @@
       <c r="B18" s="7">
         <v>400</v>
       </c>
-      <c r="C18" s="89" t="s">
+      <c r="C18" s="88" t="s">
         <v>1723</v>
       </c>
       <c r="D18" s="7" t="s">
         <v>1501</v>
       </c>
-      <c r="E18" s="90" t="s">
+      <c r="E18" s="89" t="s">
         <v>1721</v>
       </c>
       <c r="F18" s="7" t="s">
         <v>1502</v>
       </c>
-      <c r="G18" s="90" t="s">
+      <c r="G18" s="89" t="s">
         <v>1722</v>
       </c>
       <c r="H18" s="7">
@@ -41707,19 +41736,19 @@
       <c r="B19" s="7">
         <v>401</v>
       </c>
-      <c r="C19" s="89" t="s">
+      <c r="C19" s="88" t="s">
         <v>1723</v>
       </c>
       <c r="D19" s="7" t="s">
         <v>1501</v>
       </c>
-      <c r="E19" s="90" t="s">
+      <c r="E19" s="89" t="s">
         <v>1721</v>
       </c>
       <c r="F19" s="7" t="s">
         <v>1502</v>
       </c>
-      <c r="G19" s="90" t="s">
+      <c r="G19" s="89" t="s">
         <v>1722</v>
       </c>
       <c r="H19" s="7">
@@ -41739,19 +41768,19 @@
       <c r="B20" s="7">
         <v>402</v>
       </c>
-      <c r="C20" s="89" t="s">
+      <c r="C20" s="88" t="s">
         <v>1723</v>
       </c>
       <c r="D20" s="7" t="s">
         <v>1501</v>
       </c>
-      <c r="E20" s="90" t="s">
+      <c r="E20" s="89" t="s">
         <v>1721</v>
       </c>
       <c r="F20" s="7" t="s">
         <v>1183</v>
       </c>
-      <c r="G20" s="90" t="s">
+      <c r="G20" s="89" t="s">
         <v>1722</v>
       </c>
       <c r="H20" s="7"/>
@@ -41766,19 +41795,19 @@
       <c r="B21" s="7">
         <v>403</v>
       </c>
-      <c r="C21" s="62" t="s">
+      <c r="C21" s="61" t="s">
         <v>1504</v>
       </c>
       <c r="D21" s="7" t="s">
         <v>1501</v>
       </c>
-      <c r="E21" s="64" t="s">
+      <c r="E21" s="63" t="s">
         <v>1711</v>
       </c>
       <c r="F21" s="7" t="s">
         <v>1183</v>
       </c>
-      <c r="G21" s="64" t="s">
+      <c r="G21" s="63" t="s">
         <v>1505</v>
       </c>
       <c r="H21" s="7"/>
@@ -41786,35 +41815,35 @@
         <v>1133</v>
       </c>
     </row>
-    <row r="22" spans="1:10" s="59" customFormat="1">
-      <c r="A22" s="92" t="s">
+    <row r="22" spans="1:10" s="58" customFormat="1">
+      <c r="A22" s="91" t="s">
         <v>1477</v>
       </c>
-      <c r="B22" s="73">
+      <c r="B22" s="72">
         <v>404</v>
       </c>
-      <c r="C22" s="89" t="s">
+      <c r="C22" s="88" t="s">
         <v>1723</v>
       </c>
-      <c r="D22" s="91" t="s">
+      <c r="D22" s="90" t="s">
         <v>1476</v>
       </c>
-      <c r="E22" s="90" t="s">
+      <c r="E22" s="89" t="s">
         <v>1721</v>
       </c>
-      <c r="F22" s="91" t="s">
+      <c r="F22" s="90" t="s">
         <v>1183</v>
       </c>
-      <c r="G22" s="90" t="s">
+      <c r="G22" s="89" t="s">
         <v>1722</v>
       </c>
-      <c r="H22" s="74">
+      <c r="H22" s="73">
         <v>93</v>
       </c>
-      <c r="I22" s="71" t="s">
+      <c r="I22" s="70" t="s">
         <v>1111</v>
       </c>
-      <c r="J22" s="69" t="s">
+      <c r="J22" s="68" t="s">
         <v>1180</v>
       </c>
     </row>
@@ -41822,28 +41851,28 @@
       <c r="A23" s="50" t="s">
         <v>1709</v>
       </c>
-      <c r="B23" s="85">
+      <c r="B23" s="84">
         <v>405</v>
       </c>
-      <c r="C23" s="89" t="s">
+      <c r="C23" s="88" t="s">
         <v>1723</v>
       </c>
-      <c r="D23" s="85" t="s">
+      <c r="D23" s="84" t="s">
         <v>1501</v>
       </c>
-      <c r="E23" s="90" t="s">
+      <c r="E23" s="89" t="s">
         <v>1721</v>
       </c>
-      <c r="F23" s="85" t="s">
+      <c r="F23" s="84" t="s">
         <v>1183</v>
       </c>
-      <c r="G23" s="90" t="s">
+      <c r="G23" s="89" t="s">
         <v>1722</v>
       </c>
-      <c r="H23" s="85">
+      <c r="H23" s="84">
         <v>73</v>
       </c>
-      <c r="I23" s="85" t="s">
+      <c r="I23" s="84" t="s">
         <v>1111</v>
       </c>
       <c r="J23" s="50" t="s">
@@ -41857,19 +41886,19 @@
       <c r="B24" s="5">
         <v>500</v>
       </c>
-      <c r="C24" s="89" t="s">
+      <c r="C24" s="88" t="s">
         <v>1724</v>
       </c>
       <c r="D24" s="6" t="s">
         <v>1501</v>
       </c>
-      <c r="E24" s="89" t="s">
+      <c r="E24" s="88" t="s">
         <v>1725</v>
       </c>
       <c r="F24" s="6" t="s">
         <v>1502</v>
       </c>
-      <c r="G24" s="89" t="s">
+      <c r="G24" s="88" t="s">
         <v>1726</v>
       </c>
       <c r="H24" s="7">
@@ -41889,19 +41918,19 @@
       <c r="B25" s="5">
         <v>501</v>
       </c>
-      <c r="C25" s="89" t="s">
+      <c r="C25" s="88" t="s">
         <v>1724</v>
       </c>
       <c r="D25" s="6" t="s">
         <v>1501</v>
       </c>
-      <c r="E25" s="89" t="s">
+      <c r="E25" s="88" t="s">
         <v>1725</v>
       </c>
       <c r="F25" s="6" t="s">
         <v>1502</v>
       </c>
-      <c r="G25" s="89" t="s">
+      <c r="G25" s="88" t="s">
         <v>1726</v>
       </c>
       <c r="H25" s="7">
@@ -41921,19 +41950,19 @@
       <c r="B26" s="5">
         <v>502</v>
       </c>
-      <c r="C26" s="89" t="s">
+      <c r="C26" s="88" t="s">
         <v>1724</v>
       </c>
       <c r="D26" s="6" t="s">
         <v>1501</v>
       </c>
-      <c r="E26" s="89" t="s">
+      <c r="E26" s="88" t="s">
         <v>1725</v>
       </c>
       <c r="F26" s="6" t="s">
         <v>1183</v>
       </c>
-      <c r="G26" s="89" t="s">
+      <c r="G26" s="88" t="s">
         <v>1726</v>
       </c>
       <c r="H26" s="7"/>
@@ -41945,28 +41974,28 @@
       <c r="A27" s="50" t="s">
         <v>1712</v>
       </c>
-      <c r="B27" s="87">
+      <c r="B27" s="86">
         <v>503</v>
       </c>
-      <c r="C27" s="89" t="s">
+      <c r="C27" s="88" t="s">
         <v>1724</v>
       </c>
-      <c r="D27" s="84" t="s">
+      <c r="D27" s="83" t="s">
         <v>1501</v>
       </c>
-      <c r="E27" s="89" t="s">
+      <c r="E27" s="88" t="s">
         <v>1725</v>
       </c>
-      <c r="F27" s="84" t="s">
+      <c r="F27" s="83" t="s">
         <v>1183</v>
       </c>
-      <c r="G27" s="89" t="s">
+      <c r="G27" s="88" t="s">
         <v>1726</v>
       </c>
-      <c r="H27" s="85">
+      <c r="H27" s="84">
         <v>73</v>
       </c>
-      <c r="I27" s="85" t="s">
+      <c r="I27" s="84" t="s">
         <v>1148</v>
       </c>
       <c r="J27" s="50" t="s">
@@ -41976,20 +42005,20 @@
     <row r="28" spans="1:10">
       <c r="A28" s="33"/>
       <c r="B28" s="7"/>
-      <c r="C28" s="63"/>
+      <c r="C28" s="62"/>
       <c r="D28" s="7"/>
-      <c r="E28" s="64"/>
+      <c r="E28" s="63"/>
       <c r="F28" s="7"/>
-      <c r="G28" s="65"/>
+      <c r="G28" s="64"/>
       <c r="H28" s="7"/>
       <c r="I28" s="7"/>
       <c r="J28" s="4"/>
     </row>
     <row r="29" spans="1:10">
       <c r="A29" s="33"/>
-      <c r="C29" s="61"/>
-      <c r="F29" s="61"/>
-      <c r="G29" s="61"/>
+      <c r="C29" s="60"/>
+      <c r="F29" s="60"/>
+      <c r="G29" s="60"/>
       <c r="H29" s="7"/>
       <c r="I29" s="7"/>
     </row>

--- a/source/bin/excel/mall.xlsx
+++ b/source/bin/excel/mall.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\liqi-excel\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F194500E-FF12-400C-857C-0C70220607E6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7839A858-1E25-479B-9652-07753EC4611B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" firstSheet="3" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" firstSheet="3" activeTab="8" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="export" sheetId="2" r:id="rId1"/>
@@ -44573,7 +44573,7 @@
         <v>553</v>
       </c>
       <c r="D5" s="33" t="s">
-        <v>1754</v>
+        <v>1758</v>
       </c>
       <c r="J5" t="s">
         <v>15</v>
@@ -44593,7 +44593,7 @@
         <v>553</v>
       </c>
       <c r="D6" s="33" t="s">
-        <v>1754</v>
+        <v>1758</v>
       </c>
       <c r="K6" t="s">
         <v>555</v>

--- a/source/bin/excel/mall.xlsx
+++ b/source/bin/excel/mall.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\liqi-excel\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7839A858-1E25-479B-9652-07753EC4611B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7126B13E-AC55-4DD6-A2CB-4BBA5F4495D8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" firstSheet="3" activeTab="8" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" firstSheet="3" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="export" sheetId="2" r:id="rId1"/>
@@ -9174,10 +9174,6 @@
     <phoneticPr fontId="25" type="noConversion"/>
   </si>
   <si>
-    <t>2026-04-13 08:00+08</t>
-    <phoneticPr fontId="25" type="noConversion"/>
-  </si>
-  <si>
     <t>2018-08-20 08:00+08</t>
   </si>
   <si>
@@ -9208,6 +9204,10 @@
   </si>
   <si>
     <t>中文服</t>
+    <phoneticPr fontId="25" type="noConversion"/>
+  </si>
+  <si>
+    <t>2026-04-22 08:00+08</t>
     <phoneticPr fontId="25" type="noConversion"/>
   </si>
 </sst>
@@ -10484,7 +10484,7 @@
     </row>
     <row r="9" spans="1:4">
       <c r="A9" s="33" t="s">
-        <v>1759</v>
+        <v>1758</v>
       </c>
       <c r="B9" t="s">
         <v>15</v>
@@ -10493,7 +10493,7 @@
         <v>10</v>
       </c>
       <c r="D9" s="33" t="s">
-        <v>1760</v>
+        <v>1759</v>
       </c>
     </row>
   </sheetData>
@@ -40541,7 +40541,7 @@
         <v>15</v>
       </c>
       <c r="C1" s="33" t="s">
-        <v>1762</v>
+        <v>1761</v>
       </c>
     </row>
     <row r="2" spans="1:3">
@@ -40562,13 +40562,13 @@
     </row>
     <row r="4" spans="1:3">
       <c r="A4" s="33" t="s">
-        <v>1763</v>
+        <v>1762</v>
       </c>
       <c r="B4">
         <v>1</v>
       </c>
       <c r="C4" s="33" t="s">
-        <v>1755</v>
+        <v>1754</v>
       </c>
     </row>
     <row r="5" spans="1:3">
@@ -40579,7 +40579,7 @@
         <v>2</v>
       </c>
       <c r="C5" s="33" t="s">
-        <v>1757</v>
+        <v>1756</v>
       </c>
     </row>
     <row r="6" spans="1:3">
@@ -40590,18 +40590,18 @@
         <v>3</v>
       </c>
       <c r="C6" s="33" t="s">
-        <v>1757</v>
+        <v>1756</v>
       </c>
     </row>
     <row r="7" spans="1:3">
       <c r="A7" s="33" t="s">
-        <v>1763</v>
+        <v>1762</v>
       </c>
       <c r="B7">
         <v>1</v>
       </c>
       <c r="C7" s="33" t="s">
-        <v>1756</v>
+        <v>1755</v>
       </c>
     </row>
     <row r="8" spans="1:3">
@@ -40612,7 +40612,7 @@
         <v>2</v>
       </c>
       <c r="C8" s="33" t="s">
-        <v>1758</v>
+        <v>1757</v>
       </c>
     </row>
     <row r="9" spans="1:3">
@@ -40623,7 +40623,7 @@
         <v>3</v>
       </c>
       <c r="C9" s="33" t="s">
-        <v>1758</v>
+        <v>1757</v>
       </c>
     </row>
     <row r="10" spans="1:3">
@@ -40634,7 +40634,7 @@
         <v>2</v>
       </c>
       <c r="C10" s="33" t="s">
-        <v>1754</v>
+        <v>1763</v>
       </c>
     </row>
     <row r="11" spans="1:3">
@@ -40645,7 +40645,7 @@
         <v>3</v>
       </c>
       <c r="C11" s="33" t="s">
-        <v>1754</v>
+        <v>1763</v>
       </c>
     </row>
   </sheetData>
@@ -44573,7 +44573,7 @@
         <v>553</v>
       </c>
       <c r="D5" s="33" t="s">
-        <v>1758</v>
+        <v>1757</v>
       </c>
       <c r="J5" t="s">
         <v>15</v>
@@ -44593,7 +44593,7 @@
         <v>553</v>
       </c>
       <c r="D6" s="33" t="s">
-        <v>1758</v>
+        <v>1757</v>
       </c>
       <c r="K6" t="s">
         <v>555</v>
@@ -44626,7 +44626,7 @@
     </row>
     <row r="13" spans="1:11">
       <c r="K13" s="33" t="s">
-        <v>1761</v>
+        <v>1760</v>
       </c>
     </row>
   </sheetData>

--- a/source/bin/excel/mall.xlsx
+++ b/source/bin/excel/mall.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29929"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\liqi-excel\data\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Work\Git\liqi-excel\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7126B13E-AC55-4DD6-A2CB-4BBA5F4495D8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{47F64069-8C3A-43BA-81F1-4E1924D7722C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" firstSheet="3" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="28110" windowHeight="16440" firstSheet="4" activeTab="8" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="export" sheetId="2" r:id="rId1"/>
@@ -72,7 +72,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4904" uniqueCount="1764">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4905" uniqueCount="1765">
   <si>
     <t>sheet</t>
   </si>
@@ -4408,95 +4408,95 @@
   </si>
   <si>
     <t>80辉玉</t>
-    <phoneticPr fontId="25" type="noConversion"/>
+    <phoneticPr fontId="21" type="noConversion"/>
   </si>
   <si>
     <t>325辉玉</t>
-    <phoneticPr fontId="25" type="noConversion"/>
+    <phoneticPr fontId="21" type="noConversion"/>
   </si>
   <si>
     <t>900辉玉</t>
-    <phoneticPr fontId="25" type="noConversion"/>
+    <phoneticPr fontId="21" type="noConversion"/>
   </si>
   <si>
     <t>500辉玉</t>
-    <phoneticPr fontId="25" type="noConversion"/>
+    <phoneticPr fontId="21" type="noConversion"/>
   </si>
   <si>
     <t>1900辉玉</t>
-    <phoneticPr fontId="25" type="noConversion"/>
+    <phoneticPr fontId="21" type="noConversion"/>
   </si>
   <si>
     <t>2450辉玉</t>
-    <phoneticPr fontId="25" type="noConversion"/>
+    <phoneticPr fontId="21" type="noConversion"/>
   </si>
   <si>
     <t>5000辉玉</t>
-    <phoneticPr fontId="25" type="noConversion"/>
+    <phoneticPr fontId="21" type="noConversion"/>
   </si>
   <si>
     <t>80輝玉</t>
-    <phoneticPr fontId="25" type="noConversion"/>
+    <phoneticPr fontId="21" type="noConversion"/>
   </si>
   <si>
     <t>325輝玉</t>
-    <phoneticPr fontId="25" type="noConversion"/>
+    <phoneticPr fontId="21" type="noConversion"/>
   </si>
   <si>
     <t>500輝玉</t>
-    <phoneticPr fontId="25" type="noConversion"/>
+    <phoneticPr fontId="21" type="noConversion"/>
   </si>
   <si>
     <t>900輝玉</t>
-    <phoneticPr fontId="25" type="noConversion"/>
+    <phoneticPr fontId="21" type="noConversion"/>
   </si>
   <si>
     <t>1200輝玉</t>
-    <phoneticPr fontId="25" type="noConversion"/>
+    <phoneticPr fontId="21" type="noConversion"/>
   </si>
   <si>
     <t>1900輝玉</t>
-    <phoneticPr fontId="25" type="noConversion"/>
+    <phoneticPr fontId="21" type="noConversion"/>
   </si>
   <si>
     <t>2450輝玉</t>
-    <phoneticPr fontId="25" type="noConversion"/>
+    <phoneticPr fontId="21" type="noConversion"/>
   </si>
   <si>
     <t>5000輝玉</t>
-    <phoneticPr fontId="25" type="noConversion"/>
+    <phoneticPr fontId="21" type="noConversion"/>
   </si>
   <si>
     <t>80Jade</t>
-    <phoneticPr fontId="25" type="noConversion"/>
+    <phoneticPr fontId="21" type="noConversion"/>
   </si>
   <si>
     <t>325Jade</t>
-    <phoneticPr fontId="25" type="noConversion"/>
+    <phoneticPr fontId="21" type="noConversion"/>
   </si>
   <si>
     <t>500Jade</t>
-    <phoneticPr fontId="25" type="noConversion"/>
+    <phoneticPr fontId="21" type="noConversion"/>
   </si>
   <si>
     <t>900Jade</t>
-    <phoneticPr fontId="25" type="noConversion"/>
+    <phoneticPr fontId="21" type="noConversion"/>
   </si>
   <si>
     <t>1200Jade</t>
-    <phoneticPr fontId="25" type="noConversion"/>
+    <phoneticPr fontId="21" type="noConversion"/>
   </si>
   <si>
     <t>1900Jade</t>
-    <phoneticPr fontId="25" type="noConversion"/>
+    <phoneticPr fontId="21" type="noConversion"/>
   </si>
   <si>
     <t>2450Jade</t>
-    <phoneticPr fontId="25" type="noConversion"/>
+    <phoneticPr fontId="21" type="noConversion"/>
   </si>
   <si>
     <t>5000Jade</t>
-    <phoneticPr fontId="25" type="noConversion"/>
+    <phoneticPr fontId="21" type="noConversion"/>
   </si>
   <si>
     <r>
@@ -4512,7 +4512,7 @@
       </rPr>
       <t>휘석</t>
     </r>
-    <phoneticPr fontId="25" type="noConversion"/>
+    <phoneticPr fontId="21" type="noConversion"/>
   </si>
   <si>
     <r>
@@ -4528,7 +4528,7 @@
       </rPr>
       <t>휘석</t>
     </r>
-    <phoneticPr fontId="25" type="noConversion"/>
+    <phoneticPr fontId="21" type="noConversion"/>
   </si>
   <si>
     <r>
@@ -4544,7 +4544,7 @@
       </rPr>
       <t>휘석</t>
     </r>
-    <phoneticPr fontId="25" type="noConversion"/>
+    <phoneticPr fontId="21" type="noConversion"/>
   </si>
   <si>
     <r>
@@ -4560,7 +4560,7 @@
       </rPr>
       <t>휘석</t>
     </r>
-    <phoneticPr fontId="25" type="noConversion"/>
+    <phoneticPr fontId="21" type="noConversion"/>
   </si>
   <si>
     <r>
@@ -4576,7 +4576,7 @@
       </rPr>
       <t>휘석</t>
     </r>
-    <phoneticPr fontId="25" type="noConversion"/>
+    <phoneticPr fontId="21" type="noConversion"/>
   </si>
   <si>
     <r>
@@ -4592,115 +4592,115 @@
       </rPr>
       <t>휘석</t>
     </r>
-    <phoneticPr fontId="25" type="noConversion"/>
+    <phoneticPr fontId="21" type="noConversion"/>
   </si>
   <si>
     <t>160円</t>
-    <phoneticPr fontId="25" type="noConversion"/>
+    <phoneticPr fontId="21" type="noConversion"/>
   </si>
   <si>
     <t>650円</t>
-    <phoneticPr fontId="25" type="noConversion"/>
+    <phoneticPr fontId="21" type="noConversion"/>
   </si>
   <si>
     <t>1,800円</t>
-    <phoneticPr fontId="25" type="noConversion"/>
+    <phoneticPr fontId="21" type="noConversion"/>
   </si>
   <si>
     <t>2,400円</t>
-    <phoneticPr fontId="25" type="noConversion"/>
+    <phoneticPr fontId="21" type="noConversion"/>
   </si>
   <si>
     <t>3,800円</t>
-    <phoneticPr fontId="25" type="noConversion"/>
+    <phoneticPr fontId="21" type="noConversion"/>
   </si>
   <si>
     <t>1,000円</t>
-    <phoneticPr fontId="25" type="noConversion"/>
+    <phoneticPr fontId="21" type="noConversion"/>
   </si>
   <si>
     <t>首充另赠80辉玉</t>
-    <phoneticPr fontId="25" type="noConversion"/>
+    <phoneticPr fontId="21" type="noConversion"/>
   </si>
   <si>
     <t>首充另赠325辉玉</t>
-    <phoneticPr fontId="25" type="noConversion"/>
+    <phoneticPr fontId="21" type="noConversion"/>
   </si>
   <si>
     <t>首充另赠500辉玉</t>
-    <phoneticPr fontId="25" type="noConversion"/>
+    <phoneticPr fontId="21" type="noConversion"/>
   </si>
   <si>
     <t>首充另赠1900辉玉</t>
-    <phoneticPr fontId="25" type="noConversion"/>
+    <phoneticPr fontId="21" type="noConversion"/>
   </si>
   <si>
     <t>首充另赠2450辉玉</t>
-    <phoneticPr fontId="25" type="noConversion"/>
+    <phoneticPr fontId="21" type="noConversion"/>
   </si>
   <si>
     <t>首充另赠5000辉玉</t>
-    <phoneticPr fontId="25" type="noConversion"/>
+    <phoneticPr fontId="21" type="noConversion"/>
   </si>
   <si>
     <t>首儲另贈80輝玉</t>
-    <phoneticPr fontId="25" type="noConversion"/>
+    <phoneticPr fontId="21" type="noConversion"/>
   </si>
   <si>
     <t>首儲另贈325輝玉</t>
-    <phoneticPr fontId="25" type="noConversion"/>
+    <phoneticPr fontId="21" type="noConversion"/>
   </si>
   <si>
     <t>首儲另贈500輝玉</t>
-    <phoneticPr fontId="25" type="noConversion"/>
+    <phoneticPr fontId="21" type="noConversion"/>
   </si>
   <si>
     <t>首儲另贈1200輝玉</t>
-    <phoneticPr fontId="25" type="noConversion"/>
+    <phoneticPr fontId="21" type="noConversion"/>
   </si>
   <si>
     <t>首儲另贈1900輝玉</t>
-    <phoneticPr fontId="25" type="noConversion"/>
+    <phoneticPr fontId="21" type="noConversion"/>
   </si>
   <si>
     <t>首儲另贈2450輝玉</t>
-    <phoneticPr fontId="25" type="noConversion"/>
+    <phoneticPr fontId="21" type="noConversion"/>
   </si>
   <si>
     <t>首儲另贈5000輝玉</t>
-    <phoneticPr fontId="25" type="noConversion"/>
+    <phoneticPr fontId="21" type="noConversion"/>
   </si>
   <si>
     <t>有償80+無償80</t>
-    <phoneticPr fontId="25" type="noConversion"/>
+    <phoneticPr fontId="21" type="noConversion"/>
   </si>
   <si>
     <t>有償325+無償325</t>
-    <phoneticPr fontId="25" type="noConversion"/>
+    <phoneticPr fontId="21" type="noConversion"/>
   </si>
   <si>
     <t>有償500+無償500</t>
-    <phoneticPr fontId="25" type="noConversion"/>
+    <phoneticPr fontId="21" type="noConversion"/>
   </si>
   <si>
     <t>有償1900+無償1900</t>
-    <phoneticPr fontId="25" type="noConversion"/>
+    <phoneticPr fontId="21" type="noConversion"/>
   </si>
   <si>
     <t>有償2450+無償2450</t>
-    <phoneticPr fontId="25" type="noConversion"/>
+    <phoneticPr fontId="21" type="noConversion"/>
   </si>
   <si>
     <t>有償5000+無償5000</t>
-    <phoneticPr fontId="25" type="noConversion"/>
+    <phoneticPr fontId="21" type="noConversion"/>
   </si>
   <si>
     <t>80+Bonus80</t>
-    <phoneticPr fontId="25" type="noConversion"/>
+    <phoneticPr fontId="21" type="noConversion"/>
   </si>
   <si>
     <t>80+80</t>
-    <phoneticPr fontId="25" type="noConversion"/>
+    <phoneticPr fontId="21" type="noConversion"/>
   </si>
   <si>
     <r>
@@ -4717,11 +4717,11 @@
       </rPr>
       <t>325</t>
     </r>
-    <phoneticPr fontId="25" type="noConversion"/>
+    <phoneticPr fontId="21" type="noConversion"/>
   </si>
   <si>
     <t>325+325</t>
-    <phoneticPr fontId="25" type="noConversion"/>
+    <phoneticPr fontId="21" type="noConversion"/>
   </si>
   <si>
     <r>
@@ -4738,19 +4738,19 @@
       </rPr>
       <t>500</t>
     </r>
-    <phoneticPr fontId="25" type="noConversion"/>
+    <phoneticPr fontId="21" type="noConversion"/>
   </si>
   <si>
     <t>500+500</t>
-    <phoneticPr fontId="25" type="noConversion"/>
+    <phoneticPr fontId="21" type="noConversion"/>
   </si>
   <si>
     <t>1900+Bonus1900</t>
-    <phoneticPr fontId="25" type="noConversion"/>
+    <phoneticPr fontId="21" type="noConversion"/>
   </si>
   <si>
     <t>1900+1900</t>
-    <phoneticPr fontId="25" type="noConversion"/>
+    <phoneticPr fontId="21" type="noConversion"/>
   </si>
   <si>
     <r>
@@ -4767,11 +4767,11 @@
       </rPr>
       <t>2450</t>
     </r>
-    <phoneticPr fontId="25" type="noConversion"/>
+    <phoneticPr fontId="21" type="noConversion"/>
   </si>
   <si>
     <t>2450+2450</t>
-    <phoneticPr fontId="25" type="noConversion"/>
+    <phoneticPr fontId="21" type="noConversion"/>
   </si>
   <si>
     <r>
@@ -4788,79 +4788,79 @@
       </rPr>
       <t>5000</t>
     </r>
-    <phoneticPr fontId="25" type="noConversion"/>
+    <phoneticPr fontId="21" type="noConversion"/>
   </si>
   <si>
     <t>5000+5000</t>
-    <phoneticPr fontId="25" type="noConversion"/>
+    <phoneticPr fontId="21" type="noConversion"/>
   </si>
   <si>
     <t>輝石パックA</t>
-    <phoneticPr fontId="25" type="noConversion"/>
+    <phoneticPr fontId="21" type="noConversion"/>
   </si>
   <si>
     <t>輝石パックB</t>
-    <phoneticPr fontId="25" type="noConversion"/>
+    <phoneticPr fontId="21" type="noConversion"/>
   </si>
   <si>
     <t>輝石パックC</t>
-    <phoneticPr fontId="25" type="noConversion"/>
+    <phoneticPr fontId="21" type="noConversion"/>
   </si>
   <si>
     <t>輝石パックD</t>
-    <phoneticPr fontId="25" type="noConversion"/>
+    <phoneticPr fontId="21" type="noConversion"/>
   </si>
   <si>
     <t>輝石パックE</t>
-    <phoneticPr fontId="25" type="noConversion"/>
+    <phoneticPr fontId="21" type="noConversion"/>
   </si>
   <si>
     <t>輝石パックF</t>
-    <phoneticPr fontId="25" type="noConversion"/>
+    <phoneticPr fontId="21" type="noConversion"/>
   </si>
   <si>
     <t>輝石パックG</t>
-    <phoneticPr fontId="25" type="noConversion"/>
+    <phoneticPr fontId="21" type="noConversion"/>
   </si>
   <si>
     <t>輝石パックH</t>
-    <phoneticPr fontId="25" type="noConversion"/>
+    <phoneticPr fontId="21" type="noConversion"/>
   </si>
   <si>
     <t>着せ替え券パックA</t>
-    <phoneticPr fontId="25" type="noConversion"/>
+    <phoneticPr fontId="21" type="noConversion"/>
   </si>
   <si>
     <t>着せ替え券パックB</t>
-    <phoneticPr fontId="25" type="noConversion"/>
+    <phoneticPr fontId="21" type="noConversion"/>
   </si>
   <si>
     <t>着せ替え券パックC</t>
-    <phoneticPr fontId="25" type="noConversion"/>
+    <phoneticPr fontId="21" type="noConversion"/>
   </si>
   <si>
     <t>着せ替え券パックD</t>
-    <phoneticPr fontId="25" type="noConversion"/>
+    <phoneticPr fontId="21" type="noConversion"/>
   </si>
   <si>
     <t>着せ替え券パックE</t>
-    <phoneticPr fontId="25" type="noConversion"/>
+    <phoneticPr fontId="21" type="noConversion"/>
   </si>
   <si>
     <t>着せ替え券パックF</t>
-    <phoneticPr fontId="25" type="noConversion"/>
+    <phoneticPr fontId="21" type="noConversion"/>
   </si>
   <si>
     <t>着せ替え券パックG</t>
-    <phoneticPr fontId="25" type="noConversion"/>
+    <phoneticPr fontId="21" type="noConversion"/>
   </si>
   <si>
     <t>着せ替え券パックH</t>
-    <phoneticPr fontId="25" type="noConversion"/>
+    <phoneticPr fontId="21" type="noConversion"/>
   </si>
   <si>
     <t>有償80</t>
-    <phoneticPr fontId="25" type="noConversion"/>
+    <phoneticPr fontId="21" type="noConversion"/>
   </si>
   <si>
     <r>
@@ -4888,7 +4888,7 @@
       </rPr>
       <t>着せ替え券</t>
     </r>
-    <phoneticPr fontId="25" type="noConversion"/>
+    <phoneticPr fontId="21" type="noConversion"/>
   </si>
   <si>
     <r>
@@ -4916,7 +4916,7 @@
       </rPr>
       <t>着せ替え券</t>
     </r>
-    <phoneticPr fontId="25" type="noConversion"/>
+    <phoneticPr fontId="21" type="noConversion"/>
   </si>
   <si>
     <r>
@@ -4944,63 +4944,63 @@
       </rPr>
       <t>着せ替え券</t>
     </r>
-    <phoneticPr fontId="25" type="noConversion"/>
+    <phoneticPr fontId="21" type="noConversion"/>
   </si>
   <si>
     <t>日服-WebMoney</t>
-    <phoneticPr fontId="25" type="noConversion"/>
+    <phoneticPr fontId="21" type="noConversion"/>
   </si>
   <si>
     <t>日服-PayPay</t>
-    <phoneticPr fontId="25" type="noConversion"/>
+    <phoneticPr fontId="21" type="noConversion"/>
   </si>
   <si>
     <t>JPY 650</t>
-    <phoneticPr fontId="25" type="noConversion"/>
+    <phoneticPr fontId="21" type="noConversion"/>
   </si>
   <si>
     <t>JPY 160</t>
-    <phoneticPr fontId="25" type="noConversion"/>
+    <phoneticPr fontId="21" type="noConversion"/>
   </si>
   <si>
     <t>JPY 1000</t>
-    <phoneticPr fontId="25" type="noConversion"/>
+    <phoneticPr fontId="21" type="noConversion"/>
   </si>
   <si>
     <t>JPY 1800</t>
-    <phoneticPr fontId="25" type="noConversion"/>
+    <phoneticPr fontId="21" type="noConversion"/>
   </si>
   <si>
     <t>JPY 2400</t>
-    <phoneticPr fontId="25" type="noConversion"/>
+    <phoneticPr fontId="21" type="noConversion"/>
   </si>
   <si>
     <t>JPY 3800</t>
-    <phoneticPr fontId="25" type="noConversion"/>
+    <phoneticPr fontId="21" type="noConversion"/>
   </si>
   <si>
     <t>650 ポイント</t>
-    <phoneticPr fontId="25" type="noConversion"/>
+    <phoneticPr fontId="21" type="noConversion"/>
   </si>
   <si>
     <t>160 ポイント</t>
-    <phoneticPr fontId="25" type="noConversion"/>
+    <phoneticPr fontId="21" type="noConversion"/>
   </si>
   <si>
     <t>1800 ポイント</t>
-    <phoneticPr fontId="25" type="noConversion"/>
+    <phoneticPr fontId="21" type="noConversion"/>
   </si>
   <si>
     <t>1000 ポイント</t>
-    <phoneticPr fontId="25" type="noConversion"/>
+    <phoneticPr fontId="21" type="noConversion"/>
   </si>
   <si>
     <t>2400 ポイント</t>
-    <phoneticPr fontId="25" type="noConversion"/>
+    <phoneticPr fontId="21" type="noConversion"/>
   </si>
   <si>
     <t>3800 ポイント</t>
-    <phoneticPr fontId="25" type="noConversion"/>
+    <phoneticPr fontId="21" type="noConversion"/>
   </si>
   <si>
     <r>
@@ -5023,263 +5023,263 @@
       </rPr>
       <t>jp</t>
     </r>
-    <phoneticPr fontId="25" type="noConversion"/>
+    <phoneticPr fontId="21" type="noConversion"/>
   </si>
   <si>
     <t>有償325+無償5</t>
-    <phoneticPr fontId="25" type="noConversion"/>
+    <phoneticPr fontId="21" type="noConversion"/>
   </si>
   <si>
     <t>另外赠送5辉玉</t>
-    <phoneticPr fontId="25" type="noConversion"/>
+    <phoneticPr fontId="21" type="noConversion"/>
   </si>
   <si>
     <t>另外赠送10辉玉</t>
-    <phoneticPr fontId="25" type="noConversion"/>
+    <phoneticPr fontId="21" type="noConversion"/>
   </si>
   <si>
     <t>另外赠送60辉玉</t>
-    <phoneticPr fontId="25" type="noConversion"/>
+    <phoneticPr fontId="21" type="noConversion"/>
   </si>
   <si>
     <t>另外赠送110辉玉</t>
-    <phoneticPr fontId="25" type="noConversion"/>
+    <phoneticPr fontId="21" type="noConversion"/>
   </si>
   <si>
     <t>另外赠送250辉玉</t>
-    <phoneticPr fontId="25" type="noConversion"/>
+    <phoneticPr fontId="21" type="noConversion"/>
   </si>
   <si>
     <t>另外赠送1300辉玉</t>
-    <phoneticPr fontId="25" type="noConversion"/>
+    <phoneticPr fontId="21" type="noConversion"/>
   </si>
   <si>
     <t>另外贈送5輝玉</t>
-    <phoneticPr fontId="25" type="noConversion"/>
+    <phoneticPr fontId="21" type="noConversion"/>
   </si>
   <si>
     <t>另外贈送10輝玉</t>
-    <phoneticPr fontId="25" type="noConversion"/>
+    <phoneticPr fontId="21" type="noConversion"/>
   </si>
   <si>
     <t>另外贈送60輝玉</t>
-    <phoneticPr fontId="25" type="noConversion"/>
+    <phoneticPr fontId="21" type="noConversion"/>
   </si>
   <si>
     <t>另外贈送110輝玉</t>
-    <phoneticPr fontId="25" type="noConversion"/>
+    <phoneticPr fontId="21" type="noConversion"/>
   </si>
   <si>
     <t>另外贈送250輝玉</t>
-    <phoneticPr fontId="25" type="noConversion"/>
+    <phoneticPr fontId="21" type="noConversion"/>
   </si>
   <si>
     <t>另外贈送1300輝玉</t>
-    <phoneticPr fontId="25" type="noConversion"/>
+    <phoneticPr fontId="21" type="noConversion"/>
   </si>
   <si>
     <t>另外赠送550辉玉</t>
-    <phoneticPr fontId="25" type="noConversion"/>
+    <phoneticPr fontId="21" type="noConversion"/>
   </si>
   <si>
     <t>另外贈送550輝玉</t>
-    <phoneticPr fontId="25" type="noConversion"/>
+    <phoneticPr fontId="21" type="noConversion"/>
   </si>
   <si>
     <t>有償500+無償10</t>
-    <phoneticPr fontId="25" type="noConversion"/>
+    <phoneticPr fontId="21" type="noConversion"/>
   </si>
   <si>
     <t>有償900+無償60</t>
-    <phoneticPr fontId="25" type="noConversion"/>
+    <phoneticPr fontId="21" type="noConversion"/>
   </si>
   <si>
     <t>有償1900+無償250</t>
-    <phoneticPr fontId="25" type="noConversion"/>
+    <phoneticPr fontId="21" type="noConversion"/>
   </si>
   <si>
     <t>有償1200+無償110</t>
-    <phoneticPr fontId="25" type="noConversion"/>
+    <phoneticPr fontId="21" type="noConversion"/>
   </si>
   <si>
     <t>有償2450+無償550</t>
-    <phoneticPr fontId="25" type="noConversion"/>
+    <phoneticPr fontId="21" type="noConversion"/>
   </si>
   <si>
     <t>有償5000+無償1300</t>
-    <phoneticPr fontId="25" type="noConversion"/>
+    <phoneticPr fontId="21" type="noConversion"/>
   </si>
   <si>
     <t>325+Bonus5</t>
-    <phoneticPr fontId="25" type="noConversion"/>
+    <phoneticPr fontId="21" type="noConversion"/>
   </si>
   <si>
     <t>500+Bonus10</t>
-    <phoneticPr fontId="25" type="noConversion"/>
+    <phoneticPr fontId="21" type="noConversion"/>
   </si>
   <si>
     <t>900+Bonus60</t>
-    <phoneticPr fontId="25" type="noConversion"/>
+    <phoneticPr fontId="21" type="noConversion"/>
   </si>
   <si>
     <t>1200+Bonus110</t>
-    <phoneticPr fontId="25" type="noConversion"/>
+    <phoneticPr fontId="21" type="noConversion"/>
   </si>
   <si>
     <t>1900+Bonus250</t>
-    <phoneticPr fontId="25" type="noConversion"/>
+    <phoneticPr fontId="21" type="noConversion"/>
   </si>
   <si>
     <t>2450+Bonus550</t>
-    <phoneticPr fontId="25" type="noConversion"/>
+    <phoneticPr fontId="21" type="noConversion"/>
   </si>
   <si>
     <t>5000+Bonus1300</t>
-    <phoneticPr fontId="25" type="noConversion"/>
+    <phoneticPr fontId="21" type="noConversion"/>
   </si>
   <si>
     <t>325+10</t>
-    <phoneticPr fontId="25" type="noConversion"/>
+    <phoneticPr fontId="21" type="noConversion"/>
   </si>
   <si>
     <t>500+10</t>
-    <phoneticPr fontId="25" type="noConversion"/>
+    <phoneticPr fontId="21" type="noConversion"/>
   </si>
   <si>
     <t>900+60</t>
-    <phoneticPr fontId="25" type="noConversion"/>
+    <phoneticPr fontId="21" type="noConversion"/>
   </si>
   <si>
     <t>1200+110</t>
-    <phoneticPr fontId="25" type="noConversion"/>
+    <phoneticPr fontId="21" type="noConversion"/>
   </si>
   <si>
     <t>1900+250</t>
-    <phoneticPr fontId="25" type="noConversion"/>
+    <phoneticPr fontId="21" type="noConversion"/>
   </si>
   <si>
     <t>2450+550</t>
-    <phoneticPr fontId="25" type="noConversion"/>
+    <phoneticPr fontId="21" type="noConversion"/>
   </si>
   <si>
     <t>5000+1300</t>
-    <phoneticPr fontId="25" type="noConversion"/>
+    <phoneticPr fontId="21" type="noConversion"/>
   </si>
   <si>
     <t>325着せ替え券</t>
-    <phoneticPr fontId="25" type="noConversion"/>
+    <phoneticPr fontId="21" type="noConversion"/>
   </si>
   <si>
     <t>500着せ替え券</t>
-    <phoneticPr fontId="25" type="noConversion"/>
+    <phoneticPr fontId="21" type="noConversion"/>
   </si>
   <si>
     <t>1900着せ替え券</t>
-    <phoneticPr fontId="25" type="noConversion"/>
+    <phoneticPr fontId="21" type="noConversion"/>
   </si>
   <si>
     <t>2450着せ替え券</t>
-    <phoneticPr fontId="25" type="noConversion"/>
+    <phoneticPr fontId="21" type="noConversion"/>
   </si>
   <si>
     <t>5000着せ替え券</t>
-    <phoneticPr fontId="25" type="noConversion"/>
+    <phoneticPr fontId="21" type="noConversion"/>
   </si>
   <si>
     <t>80服饰券</t>
-    <phoneticPr fontId="25" type="noConversion"/>
+    <phoneticPr fontId="21" type="noConversion"/>
   </si>
   <si>
     <t>325服饰券</t>
-    <phoneticPr fontId="25" type="noConversion"/>
+    <phoneticPr fontId="21" type="noConversion"/>
   </si>
   <si>
     <t>500服饰券</t>
-    <phoneticPr fontId="25" type="noConversion"/>
+    <phoneticPr fontId="21" type="noConversion"/>
   </si>
   <si>
     <t>5000服饰券</t>
-    <phoneticPr fontId="25" type="noConversion"/>
+    <phoneticPr fontId="21" type="noConversion"/>
   </si>
   <si>
     <t>900服饰券</t>
-    <phoneticPr fontId="25" type="noConversion"/>
+    <phoneticPr fontId="21" type="noConversion"/>
   </si>
   <si>
     <t>1200服饰券</t>
-    <phoneticPr fontId="25" type="noConversion"/>
+    <phoneticPr fontId="21" type="noConversion"/>
   </si>
   <si>
     <t>1900服饰券</t>
-    <phoneticPr fontId="25" type="noConversion"/>
+    <phoneticPr fontId="21" type="noConversion"/>
   </si>
   <si>
     <t>2450服饰券</t>
-    <phoneticPr fontId="25" type="noConversion"/>
+    <phoneticPr fontId="21" type="noConversion"/>
   </si>
   <si>
     <t>80服飾券</t>
-    <phoneticPr fontId="25" type="noConversion"/>
+    <phoneticPr fontId="21" type="noConversion"/>
   </si>
   <si>
     <t>325服飾券</t>
-    <phoneticPr fontId="25" type="noConversion"/>
+    <phoneticPr fontId="21" type="noConversion"/>
   </si>
   <si>
     <t>500服飾券</t>
-    <phoneticPr fontId="25" type="noConversion"/>
+    <phoneticPr fontId="21" type="noConversion"/>
   </si>
   <si>
     <t>900服飾券</t>
-    <phoneticPr fontId="25" type="noConversion"/>
+    <phoneticPr fontId="21" type="noConversion"/>
   </si>
   <si>
     <t>1200服飾券</t>
-    <phoneticPr fontId="25" type="noConversion"/>
+    <phoneticPr fontId="21" type="noConversion"/>
   </si>
   <si>
     <t>1900服飾券</t>
-    <phoneticPr fontId="25" type="noConversion"/>
+    <phoneticPr fontId="21" type="noConversion"/>
   </si>
   <si>
     <t>2450服飾券</t>
-    <phoneticPr fontId="25" type="noConversion"/>
+    <phoneticPr fontId="21" type="noConversion"/>
   </si>
   <si>
     <t>5000服飾券</t>
-    <phoneticPr fontId="25" type="noConversion"/>
+    <phoneticPr fontId="21" type="noConversion"/>
   </si>
   <si>
     <t>80 Outfit Voucher</t>
-    <phoneticPr fontId="25" type="noConversion"/>
+    <phoneticPr fontId="21" type="noConversion"/>
   </si>
   <si>
     <t>325 Outfit Voucher</t>
-    <phoneticPr fontId="25" type="noConversion"/>
+    <phoneticPr fontId="21" type="noConversion"/>
   </si>
   <si>
     <t>500 Outfit Voucher</t>
-    <phoneticPr fontId="25" type="noConversion"/>
+    <phoneticPr fontId="21" type="noConversion"/>
   </si>
   <si>
     <t>900 Outfit Voucher</t>
-    <phoneticPr fontId="25" type="noConversion"/>
+    <phoneticPr fontId="21" type="noConversion"/>
   </si>
   <si>
     <t>1200 Outfit Voucher</t>
-    <phoneticPr fontId="25" type="noConversion"/>
+    <phoneticPr fontId="21" type="noConversion"/>
   </si>
   <si>
     <t>1900 Outfit Voucher</t>
-    <phoneticPr fontId="25" type="noConversion"/>
+    <phoneticPr fontId="21" type="noConversion"/>
   </si>
   <si>
     <t>2450 Outfit Voucher</t>
-    <phoneticPr fontId="25" type="noConversion"/>
+    <phoneticPr fontId="21" type="noConversion"/>
   </si>
   <si>
     <t>5000 Outfit Voucher</t>
-    <phoneticPr fontId="25" type="noConversion"/>
+    <phoneticPr fontId="21" type="noConversion"/>
   </si>
   <si>
     <r>
@@ -5315,7 +5315,7 @@
       </rPr>
       <t>교환권</t>
     </r>
-    <phoneticPr fontId="25" type="noConversion"/>
+    <phoneticPr fontId="21" type="noConversion"/>
   </si>
   <si>
     <r>
@@ -5351,7 +5351,7 @@
       </rPr>
       <t>교환권</t>
     </r>
-    <phoneticPr fontId="25" type="noConversion"/>
+    <phoneticPr fontId="21" type="noConversion"/>
   </si>
   <si>
     <r>
@@ -5387,7 +5387,7 @@
       </rPr>
       <t>교환권</t>
     </r>
-    <phoneticPr fontId="25" type="noConversion"/>
+    <phoneticPr fontId="21" type="noConversion"/>
   </si>
   <si>
     <r>
@@ -5423,7 +5423,7 @@
       </rPr>
       <t>교환권</t>
     </r>
-    <phoneticPr fontId="25" type="noConversion"/>
+    <phoneticPr fontId="21" type="noConversion"/>
   </si>
   <si>
     <r>
@@ -5459,7 +5459,7 @@
       </rPr>
       <t>교환권</t>
     </r>
-    <phoneticPr fontId="25" type="noConversion"/>
+    <phoneticPr fontId="21" type="noConversion"/>
   </si>
   <si>
     <r>
@@ -5495,7 +5495,7 @@
       </rPr>
       <t>교환권</t>
     </r>
-    <phoneticPr fontId="25" type="noConversion"/>
+    <phoneticPr fontId="21" type="noConversion"/>
   </si>
   <si>
     <r>
@@ -5531,7 +5531,7 @@
       </rPr>
       <t>교환권</t>
     </r>
-    <phoneticPr fontId="25" type="noConversion"/>
+    <phoneticPr fontId="21" type="noConversion"/>
   </si>
   <si>
     <r>
@@ -5567,83 +5567,83 @@
       </rPr>
       <t>교환권</t>
     </r>
-    <phoneticPr fontId="25" type="noConversion"/>
+    <phoneticPr fontId="21" type="noConversion"/>
   </si>
   <si>
     <t>com.yostarjp.mahjongsoul.jade1200</t>
-    <phoneticPr fontId="25" type="noConversion"/>
+    <phoneticPr fontId="21" type="noConversion"/>
   </si>
   <si>
     <t>雀魂-65輝玉</t>
-    <phoneticPr fontId="25" type="noConversion"/>
+    <phoneticPr fontId="21" type="noConversion"/>
   </si>
   <si>
     <t>雀魂-340輝玉</t>
-    <phoneticPr fontId="25" type="noConversion"/>
+    <phoneticPr fontId="21" type="noConversion"/>
   </si>
   <si>
     <t>雀魂-660輝玉</t>
-    <phoneticPr fontId="25" type="noConversion"/>
+    <phoneticPr fontId="21" type="noConversion"/>
   </si>
   <si>
     <t>雀魂-1200輝玉</t>
-    <phoneticPr fontId="25" type="noConversion"/>
+    <phoneticPr fontId="21" type="noConversion"/>
   </si>
   <si>
     <t>雀魂-2100輝玉</t>
-    <phoneticPr fontId="25" type="noConversion"/>
+    <phoneticPr fontId="21" type="noConversion"/>
   </si>
   <si>
     <t>雀魂-2800輝玉</t>
-    <phoneticPr fontId="25" type="noConversion"/>
+    <phoneticPr fontId="21" type="noConversion"/>
   </si>
   <si>
     <t>雀魂-3660輝玉</t>
-    <phoneticPr fontId="25" type="noConversion"/>
+    <phoneticPr fontId="21" type="noConversion"/>
   </si>
   <si>
     <t>雀魂-6480輝玉</t>
-    <phoneticPr fontId="25" type="noConversion"/>
+    <phoneticPr fontId="21" type="noConversion"/>
   </si>
   <si>
     <t>雀魂-65服飾券</t>
-    <phoneticPr fontId="25" type="noConversion"/>
+    <phoneticPr fontId="21" type="noConversion"/>
   </si>
   <si>
     <t>雀魂-340服飾券</t>
-    <phoneticPr fontId="25" type="noConversion"/>
+    <phoneticPr fontId="21" type="noConversion"/>
   </si>
   <si>
     <t>雀魂-660服飾券</t>
-    <phoneticPr fontId="25" type="noConversion"/>
+    <phoneticPr fontId="21" type="noConversion"/>
   </si>
   <si>
     <t>雀魂-1200服飾券</t>
-    <phoneticPr fontId="25" type="noConversion"/>
+    <phoneticPr fontId="21" type="noConversion"/>
   </si>
   <si>
     <t>雀魂-2100服飾券</t>
-    <phoneticPr fontId="25" type="noConversion"/>
+    <phoneticPr fontId="21" type="noConversion"/>
   </si>
   <si>
     <t>雀魂-2800服飾券</t>
-    <phoneticPr fontId="25" type="noConversion"/>
+    <phoneticPr fontId="21" type="noConversion"/>
   </si>
   <si>
     <t>雀魂-3660服飾券</t>
-    <phoneticPr fontId="25" type="noConversion"/>
+    <phoneticPr fontId="21" type="noConversion"/>
   </si>
   <si>
     <t>雀魂-6480服飾券</t>
-    <phoneticPr fontId="25" type="noConversion"/>
+    <phoneticPr fontId="21" type="noConversion"/>
   </si>
   <si>
     <t>雀魂-月势御守</t>
-    <phoneticPr fontId="25" type="noConversion"/>
+    <phoneticPr fontId="21" type="noConversion"/>
   </si>
   <si>
     <t>雀魂-月勢御守</t>
-    <phoneticPr fontId="25" type="noConversion"/>
+    <phoneticPr fontId="21" type="noConversion"/>
   </si>
   <si>
     <r>
@@ -5720,11 +5720,11 @@
   </si>
   <si>
     <t>actual_code</t>
-    <phoneticPr fontId="25" type="noConversion"/>
+    <phoneticPr fontId="21" type="noConversion"/>
   </si>
   <si>
     <t>com.yostarjp.mahjongsoul.fortunecharm</t>
-    <phoneticPr fontId="25" type="noConversion"/>
+    <phoneticPr fontId="21" type="noConversion"/>
   </si>
   <si>
     <t>台服，switch</t>
@@ -5809,7 +5809,7 @@
   </si>
   <si>
     <t>shelves_008</t>
-    <phoneticPr fontId="25" type="noConversion"/>
+    <phoneticPr fontId="21" type="noConversion"/>
   </si>
   <si>
     <r>
@@ -5825,11 +5825,11 @@
       </rPr>
       <t>8</t>
     </r>
-    <phoneticPr fontId="25" type="noConversion"/>
+    <phoneticPr fontId="21" type="noConversion"/>
   </si>
   <si>
     <t>HKD</t>
-    <phoneticPr fontId="25" type="noConversion"/>
+    <phoneticPr fontId="21" type="noConversion"/>
   </si>
   <si>
     <r>
@@ -5846,7 +5846,7 @@
       </rPr>
       <t>8</t>
     </r>
-    <phoneticPr fontId="25" type="noConversion"/>
+    <phoneticPr fontId="21" type="noConversion"/>
   </si>
   <si>
     <r>
@@ -5890,7 +5890,7 @@
       </rPr>
       <t>43</t>
     </r>
-    <phoneticPr fontId="25" type="noConversion"/>
+    <phoneticPr fontId="21" type="noConversion"/>
   </si>
   <si>
     <r>
@@ -5918,7 +5918,7 @@
       </rPr>
       <t>82</t>
     </r>
-    <phoneticPr fontId="25" type="noConversion"/>
+    <phoneticPr fontId="21" type="noConversion"/>
   </si>
   <si>
     <r>
@@ -5946,7 +5946,7 @@
       </rPr>
       <t>150</t>
     </r>
-    <phoneticPr fontId="25" type="noConversion"/>
+    <phoneticPr fontId="21" type="noConversion"/>
   </si>
   <si>
     <r>
@@ -5974,7 +5974,7 @@
       </rPr>
       <t>260</t>
     </r>
-    <phoneticPr fontId="25" type="noConversion"/>
+    <phoneticPr fontId="21" type="noConversion"/>
   </si>
   <si>
     <r>
@@ -6002,7 +6002,7 @@
       </rPr>
       <t>340</t>
     </r>
-    <phoneticPr fontId="25" type="noConversion"/>
+    <phoneticPr fontId="21" type="noConversion"/>
   </si>
   <si>
     <r>
@@ -6030,7 +6030,7 @@
       </rPr>
       <t>450</t>
     </r>
-    <phoneticPr fontId="25" type="noConversion"/>
+    <phoneticPr fontId="21" type="noConversion"/>
   </si>
   <si>
     <r>
@@ -6058,7 +6058,7 @@
       </rPr>
       <t>780</t>
     </r>
-    <phoneticPr fontId="25" type="noConversion"/>
+    <phoneticPr fontId="21" type="noConversion"/>
   </si>
   <si>
     <r>
@@ -6086,7 +6086,7 @@
       </rPr>
       <t>8</t>
     </r>
-    <phoneticPr fontId="25" type="noConversion"/>
+    <phoneticPr fontId="21" type="noConversion"/>
   </si>
   <si>
     <r>
@@ -6402,7 +6402,7 @@
   </si>
   <si>
     <t>102002-102006-102008</t>
-    <phoneticPr fontId="25" type="noConversion"/>
+    <phoneticPr fontId="21" type="noConversion"/>
   </si>
   <si>
     <t>70辉玉</t>
@@ -8673,7 +8673,7 @@
       </rPr>
       <t>小于配置时间的，登录时会重置双倍状态</t>
     </r>
-    <phoneticPr fontId="25" type="noConversion"/>
+    <phoneticPr fontId="21" type="noConversion"/>
   </si>
   <si>
     <r>
@@ -8713,7 +8713,7 @@
       </rPr>
       <t>不重置双倍状态</t>
     </r>
-    <phoneticPr fontId="25" type="noConversion"/>
+    <phoneticPr fontId="21" type="noConversion"/>
   </si>
   <si>
     <t>liqi.gmo.1010</t>
@@ -8768,14 +8768,14 @@
   </si>
   <si>
     <t>各服月卡统一的发放内容</t>
-    <phoneticPr fontId="25" type="noConversion"/>
+    <phoneticPr fontId="21" type="noConversion"/>
   </si>
   <si>
     <t>month_ticket_info</t>
   </si>
   <si>
     <t>server</t>
-    <phoneticPr fontId="25" type="noConversion"/>
+    <phoneticPr fontId="21" type="noConversion"/>
   </si>
   <si>
     <t>#export</t>
@@ -8785,11 +8785,11 @@
   </si>
   <si>
     <t>每日交付资源种类</t>
-    <phoneticPr fontId="25" type="noConversion"/>
+    <phoneticPr fontId="21" type="noConversion"/>
   </si>
   <si>
     <t>悠星PC</t>
-    <phoneticPr fontId="25" type="noConversion"/>
+    <phoneticPr fontId="21" type="noConversion"/>
   </si>
   <si>
     <r>
@@ -8806,35 +8806,35 @@
       </rPr>
       <t>40201添加悠星PC</t>
     </r>
-    <phoneticPr fontId="25" type="noConversion"/>
+    <phoneticPr fontId="21" type="noConversion"/>
   </si>
   <si>
     <t>304</t>
-    <phoneticPr fontId="25" type="noConversion"/>
+    <phoneticPr fontId="21" type="noConversion"/>
   </si>
   <si>
     <t>美服，PC</t>
-    <phoneticPr fontId="25" type="noConversion"/>
+    <phoneticPr fontId="21" type="noConversion"/>
   </si>
   <si>
     <t>73</t>
-    <phoneticPr fontId="25" type="noConversion"/>
+    <phoneticPr fontId="21" type="noConversion"/>
   </si>
   <si>
     <t>日服，PC</t>
-    <phoneticPr fontId="25" type="noConversion"/>
+    <phoneticPr fontId="21" type="noConversion"/>
   </si>
   <si>
     <t>美服，Switch</t>
-    <phoneticPr fontId="25" type="noConversion"/>
+    <phoneticPr fontId="21" type="noConversion"/>
   </si>
   <si>
     <t>101002-101006-101008</t>
-    <phoneticPr fontId="25" type="noConversion"/>
+    <phoneticPr fontId="21" type="noConversion"/>
   </si>
   <si>
     <t>韩服，PC</t>
-    <phoneticPr fontId="25" type="noConversion"/>
+    <phoneticPr fontId="21" type="noConversion"/>
   </si>
   <si>
     <r>
@@ -8857,19 +8857,19 @@
       </rPr>
       <t>ostar</t>
     </r>
-    <phoneticPr fontId="25" type="noConversion"/>
+    <phoneticPr fontId="21" type="noConversion"/>
   </si>
   <si>
     <t>yostar</t>
-    <phoneticPr fontId="25" type="noConversion"/>
+    <phoneticPr fontId="21" type="noConversion"/>
   </si>
   <si>
     <t>日服</t>
-    <phoneticPr fontId="25" type="noConversion"/>
+    <phoneticPr fontId="21" type="noConversion"/>
   </si>
   <si>
     <t>美服/韩服</t>
-    <phoneticPr fontId="25" type="noConversion"/>
+    <phoneticPr fontId="21" type="noConversion"/>
   </si>
   <si>
     <r>
@@ -8908,11 +8908,11 @@
       </rPr>
       <t>-5-6-8-10-11</t>
     </r>
-    <phoneticPr fontId="25" type="noConversion"/>
+    <phoneticPr fontId="21" type="noConversion"/>
   </si>
   <si>
     <t>101001-101002-101003-101004-101007-101009-101010</t>
-    <phoneticPr fontId="25" type="noConversion"/>
+    <phoneticPr fontId="21" type="noConversion"/>
   </si>
   <si>
     <r>
@@ -8951,79 +8951,79 @@
       </rPr>
       <t>102004-102007-102009-102010</t>
     </r>
-    <phoneticPr fontId="25" type="noConversion"/>
+    <phoneticPr fontId="21" type="noConversion"/>
   </si>
   <si>
     <t>1-4-5-9-12</t>
-    <phoneticPr fontId="25" type="noConversion"/>
+    <phoneticPr fontId="21" type="noConversion"/>
   </si>
   <si>
     <t>101001-101002-101003-101008-101011</t>
-    <phoneticPr fontId="25" type="noConversion"/>
+    <phoneticPr fontId="21" type="noConversion"/>
   </si>
   <si>
     <t>102001-102002-102003-102008-102011</t>
-    <phoneticPr fontId="25" type="noConversion"/>
+    <phoneticPr fontId="21" type="noConversion"/>
   </si>
   <si>
     <t>1-3-5-9-12</t>
-    <phoneticPr fontId="25" type="noConversion"/>
+    <phoneticPr fontId="21" type="noConversion"/>
   </si>
   <si>
     <t>1-4-5-9</t>
-    <phoneticPr fontId="25" type="noConversion"/>
+    <phoneticPr fontId="21" type="noConversion"/>
   </si>
   <si>
     <t>101001-101002-101003-101008</t>
-    <phoneticPr fontId="25" type="noConversion"/>
+    <phoneticPr fontId="21" type="noConversion"/>
   </si>
   <si>
     <t>102001-102002-102003-102008</t>
-    <phoneticPr fontId="25" type="noConversion"/>
+    <phoneticPr fontId="21" type="noConversion"/>
   </si>
   <si>
     <t>2025-08-20 08:00+08</t>
-    <phoneticPr fontId="25" type="noConversion"/>
+    <phoneticPr fontId="21" type="noConversion"/>
   </si>
   <si>
     <t>₩1,500</t>
-    <phoneticPr fontId="25" type="noConversion"/>
+    <phoneticPr fontId="21" type="noConversion"/>
   </si>
   <si>
     <t>₩7,500</t>
-    <phoneticPr fontId="25" type="noConversion"/>
+    <phoneticPr fontId="21" type="noConversion"/>
   </si>
   <si>
     <t>₩12,000</t>
-    <phoneticPr fontId="25" type="noConversion"/>
+    <phoneticPr fontId="21" type="noConversion"/>
   </si>
   <si>
     <t>₩23,000</t>
-    <phoneticPr fontId="25" type="noConversion"/>
+    <phoneticPr fontId="21" type="noConversion"/>
   </si>
   <si>
     <t>₩30,000</t>
-    <phoneticPr fontId="25" type="noConversion"/>
+    <phoneticPr fontId="21" type="noConversion"/>
   </si>
   <si>
     <t>₩45,000</t>
-    <phoneticPr fontId="25" type="noConversion"/>
+    <phoneticPr fontId="21" type="noConversion"/>
   </si>
   <si>
     <t>₩60,000</t>
-    <phoneticPr fontId="25" type="noConversion"/>
+    <phoneticPr fontId="21" type="noConversion"/>
   </si>
   <si>
     <t>₩119,000</t>
-    <phoneticPr fontId="25" type="noConversion"/>
+    <phoneticPr fontId="21" type="noConversion"/>
   </si>
   <si>
     <t xml:space="preserve">YOSTAR_JP_WEB         </t>
-    <phoneticPr fontId="25" type="noConversion"/>
+    <phoneticPr fontId="21" type="noConversion"/>
   </si>
   <si>
     <t xml:space="preserve">YOSTAR_JP_WEB         </t>
-    <phoneticPr fontId="25" type="noConversion"/>
+    <phoneticPr fontId="21" type="noConversion"/>
   </si>
   <si>
     <r>
@@ -9051,63 +9051,63 @@
       </rPr>
       <t>mahjongsoul.outfitvoucher4900</t>
     </r>
-    <phoneticPr fontId="25" type="noConversion"/>
+    <phoneticPr fontId="21" type="noConversion"/>
   </si>
   <si>
     <t>日服steam</t>
-    <phoneticPr fontId="25" type="noConversion"/>
+    <phoneticPr fontId="21" type="noConversion"/>
   </si>
   <si>
     <t>美服steam</t>
-    <phoneticPr fontId="25" type="noConversion"/>
+    <phoneticPr fontId="21" type="noConversion"/>
   </si>
   <si>
     <t>韩服steam</t>
-    <phoneticPr fontId="25" type="noConversion"/>
+    <phoneticPr fontId="21" type="noConversion"/>
   </si>
   <si>
     <t>日ios</t>
-    <phoneticPr fontId="25" type="noConversion"/>
+    <phoneticPr fontId="21" type="noConversion"/>
   </si>
   <si>
     <t>美ios</t>
-    <phoneticPr fontId="25" type="noConversion"/>
+    <phoneticPr fontId="21" type="noConversion"/>
   </si>
   <si>
     <t>日gp</t>
-    <phoneticPr fontId="25" type="noConversion"/>
+    <phoneticPr fontId="21" type="noConversion"/>
   </si>
   <si>
     <t>美gp</t>
-    <phoneticPr fontId="25" type="noConversion"/>
+    <phoneticPr fontId="21" type="noConversion"/>
   </si>
   <si>
     <t>韩服android</t>
-    <phoneticPr fontId="25" type="noConversion"/>
+    <phoneticPr fontId="21" type="noConversion"/>
   </si>
   <si>
     <t>美web</t>
-    <phoneticPr fontId="25" type="noConversion"/>
+    <phoneticPr fontId="21" type="noConversion"/>
   </si>
   <si>
     <t>韩web</t>
-    <phoneticPr fontId="25" type="noConversion"/>
+    <phoneticPr fontId="21" type="noConversion"/>
   </si>
   <si>
     <t>支付平台</t>
-    <phoneticPr fontId="25" type="noConversion"/>
+    <phoneticPr fontId="21" type="noConversion"/>
   </si>
   <si>
     <t>商品ID</t>
-    <phoneticPr fontId="25" type="noConversion"/>
+    <phoneticPr fontId="21" type="noConversion"/>
   </si>
   <si>
     <t>上架平台商品ID</t>
-    <phoneticPr fontId="25" type="noConversion"/>
+    <phoneticPr fontId="21" type="noConversion"/>
   </si>
   <si>
     <t>extendRes/items/main/monthcard.jpg</t>
-    <phoneticPr fontId="25" type="noConversion"/>
+    <phoneticPr fontId="21" type="noConversion"/>
   </si>
   <si>
     <t>extendRes/items/main/jade0.jpg</t>
@@ -9159,19 +9159,19 @@
   </si>
   <si>
     <t>韩服，Steam</t>
-    <phoneticPr fontId="25" type="noConversion"/>
+    <phoneticPr fontId="21" type="noConversion"/>
   </si>
   <si>
     <t>日服，Steam</t>
-    <phoneticPr fontId="25" type="noConversion"/>
+    <phoneticPr fontId="21" type="noConversion"/>
   </si>
   <si>
     <t>美服，Steam</t>
-    <phoneticPr fontId="25" type="noConversion"/>
+    <phoneticPr fontId="21" type="noConversion"/>
   </si>
   <si>
     <t>305</t>
-    <phoneticPr fontId="25" type="noConversion"/>
+    <phoneticPr fontId="21" type="noConversion"/>
   </si>
   <si>
     <t>2018-08-20 08:00+08</t>
@@ -9184,31 +9184,35 @@
   </si>
   <si>
     <t>2025-04-23 07:00+08</t>
-    <phoneticPr fontId="25" type="noConversion"/>
+    <phoneticPr fontId="21" type="noConversion"/>
   </si>
   <si>
     <t>recharge_bonus</t>
-    <phoneticPr fontId="25" type="noConversion"/>
+    <phoneticPr fontId="21" type="noConversion"/>
   </si>
   <si>
     <t>首充双倍区间</t>
-    <phoneticPr fontId="25" type="noConversion"/>
+    <phoneticPr fontId="21" type="noConversion"/>
   </si>
   <si>
     <t>注：此表已废弃，改用recharge_bonus，不要修改也不再加新内容</t>
-    <phoneticPr fontId="25" type="noConversion"/>
+    <phoneticPr fontId="21" type="noConversion"/>
   </si>
   <si>
     <t>reset_time</t>
-    <phoneticPr fontId="25" type="noConversion"/>
+    <phoneticPr fontId="21" type="noConversion"/>
   </si>
   <si>
     <t>中文服</t>
-    <phoneticPr fontId="25" type="noConversion"/>
+    <phoneticPr fontId="21" type="noConversion"/>
+  </si>
+  <si>
+    <t>64</t>
+    <phoneticPr fontId="21" type="noConversion"/>
   </si>
   <si>
     <t>2026-04-22 08:00+08</t>
-    <phoneticPr fontId="25" type="noConversion"/>
+    <phoneticPr fontId="21" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -9220,40 +9224,12 @@
     <numFmt numFmtId="176" formatCode="0;[Red]0"/>
     <numFmt numFmtId="177" formatCode="\¥#,##0;[Red]\¥\-#,##0"/>
   </numFmts>
-  <fonts count="40">
+  <fonts count="36">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="等线"/>
       <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="等线"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="等线"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="等线"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="等线"/>
-      <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -9640,15 +9616,15 @@
   </borders>
   <cellStyleXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0"/>
-    <xf numFmtId="44" fontId="34" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
+    <xf numFmtId="44" fontId="30" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="98">
+  <cellXfs count="96">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
@@ -9680,15 +9656,15 @@
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="8" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="9" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="11" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="12" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="13" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -9697,17 +9673,17 @@
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="5" borderId="0" xfId="2" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="5" borderId="0" xfId="2" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyProtection="1">
@@ -9716,68 +9692,68 @@
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyProtection="1">
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="28" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="24" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="28" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="24" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="29" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="25" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="30" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="26" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="30" fillId="7" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="26" fillId="7" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="12" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="22" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="8" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="29" fillId="10" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="25" fillId="10" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="29" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="25" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="32" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="28" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="32" fillId="10" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="28" fillId="10" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="11" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="11" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="12" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="26" fillId="12" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="22" fillId="12" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="177" fontId="26" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="177" fontId="22" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="177" fontId="26" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="177" fontId="22" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="177" fontId="0" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="26" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="22" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="13" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="0" xfId="0" applyFont="1" applyProtection="1">
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" xfId="0" applyFont="1" applyProtection="1">
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="49" fontId="26" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="49" fontId="26" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="22" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="49" fontId="22" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="14" borderId="0" xfId="0" applyFill="1"/>
@@ -9791,31 +9767,24 @@
     <xf numFmtId="49" fontId="0" fillId="13" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="13" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="49" fontId="6" fillId="13" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="176" fontId="0" fillId="13" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="13" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="13" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="15" borderId="0" xfId="0" applyFill="1" applyProtection="1">
       <protection locked="0"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="15" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="37" fillId="5" borderId="0" xfId="2" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="33" fillId="5" borderId="0" xfId="2" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="4" fillId="14" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="2" fillId="14" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="16" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="26" fillId="13" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="49" fontId="26" fillId="12" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="22" fillId="13" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="49" fontId="22" fillId="12" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="12" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
@@ -9824,41 +9793,44 @@
     <xf numFmtId="0" fontId="0" fillId="12" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="49" fontId="26" fillId="12" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="49" fontId="22" fillId="12" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="176" fontId="0" fillId="12" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="49" fontId="3" fillId="13" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="49" fontId="26" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="22" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="22" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="49" fontId="2" fillId="13" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="31" fillId="3" borderId="3" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="34" fillId="12" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="13" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="49" fontId="35" fillId="3" borderId="3" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="38" fillId="12" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="34" fillId="12" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="49" fontId="34" fillId="12" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="49" fontId="38" fillId="12" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="49" fontId="38" fillId="12" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="34" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="49" fontId="38" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="34" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="38" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="34" fillId="12" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="176" fontId="34" fillId="12" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="38" fillId="12" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="176" fontId="38" fillId="12" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="13" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
+    <xf numFmtId="49" fontId="1" fillId="13" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="49" fontId="1" fillId="13" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="13" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="4">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -10497,7 +10469,7 @@
       </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="25" type="noConversion"/>
+  <phoneticPr fontId="21" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>
 </worksheet>
@@ -10672,7 +10644,7 @@
       </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="25" type="noConversion"/>
+  <phoneticPr fontId="21" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
   <drawing r:id="rId1"/>
@@ -10811,7 +10783,7 @@
       </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="25" type="noConversion"/>
+  <phoneticPr fontId="21" type="noConversion"/>
   <hyperlinks>
     <hyperlink ref="I6" r:id="rId1" xr:uid="{00000000-0004-0000-0800-000000000000}"/>
   </hyperlinks>
@@ -10900,7 +10872,7 @@
       </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="25" type="noConversion"/>
+  <phoneticPr fontId="21" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>
 </worksheet>
@@ -11349,7 +11321,7 @@
       <c r="Z6" s="28" t="s">
         <v>83</v>
       </c>
-      <c r="AA6" s="75" t="s">
+      <c r="AA6" s="72" t="s">
         <v>1653</v>
       </c>
     </row>
@@ -11403,7 +11375,7 @@
       <c r="U7" s="28" t="s">
         <v>1658</v>
       </c>
-      <c r="V7" s="75" t="s">
+      <c r="V7" s="72" t="s">
         <v>1659</v>
       </c>
       <c r="W7" t="s">
@@ -11418,7 +11390,7 @@
       <c r="Z7" s="28" t="s">
         <v>1658</v>
       </c>
-      <c r="AA7" s="75" t="s">
+      <c r="AA7" s="72" t="s">
         <v>1659</v>
       </c>
     </row>
@@ -11430,7 +11402,7 @@
       <c r="V8" s="28"/>
     </row>
   </sheetData>
-  <phoneticPr fontId="25" type="noConversion"/>
+  <phoneticPr fontId="21" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
 </worksheet>
@@ -11572,7 +11544,7 @@
       </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="25" type="noConversion"/>
+  <phoneticPr fontId="21" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -16788,7 +16760,7 @@
       <c r="R68">
         <v>12</v>
       </c>
-      <c r="S68" s="90" t="s">
+      <c r="S68" s="84" t="s">
         <v>1709</v>
       </c>
       <c r="T68" t="s">
@@ -16872,7 +16844,7 @@
       <c r="R69">
         <v>30</v>
       </c>
-      <c r="S69" s="90" t="s">
+      <c r="S69" s="84" t="s">
         <v>1710</v>
       </c>
       <c r="T69" t="s">
@@ -16970,7 +16942,7 @@
       <c r="R70">
         <v>60</v>
       </c>
-      <c r="S70" s="90" t="s">
+      <c r="S70" s="84" t="s">
         <v>1711</v>
       </c>
       <c r="T70" t="s">
@@ -17068,7 +17040,7 @@
       <c r="R71">
         <v>98</v>
       </c>
-      <c r="S71" s="90" t="s">
+      <c r="S71" s="84" t="s">
         <v>1712</v>
       </c>
       <c r="T71" t="s">
@@ -17166,7 +17138,7 @@
       <c r="R72">
         <v>128</v>
       </c>
-      <c r="S72" s="90" t="s">
+      <c r="S72" s="84" t="s">
         <v>1713</v>
       </c>
       <c r="T72" t="s">
@@ -17264,7 +17236,7 @@
       <c r="R73">
         <v>198</v>
       </c>
-      <c r="S73" s="90" t="s">
+      <c r="S73" s="84" t="s">
         <v>1714</v>
       </c>
       <c r="T73" t="s">
@@ -17362,7 +17334,7 @@
       <c r="R74">
         <v>328</v>
       </c>
-      <c r="S74" s="90" t="s">
+      <c r="S74" s="84" t="s">
         <v>1715</v>
       </c>
       <c r="T74" t="s">
@@ -17460,7 +17432,7 @@
       <c r="R75">
         <v>648</v>
       </c>
-      <c r="S75" s="90" t="s">
+      <c r="S75" s="84" t="s">
         <v>1716</v>
       </c>
       <c r="T75" t="s">
@@ -17555,7 +17527,7 @@
       <c r="Q76">
         <v>7</v>
       </c>
-      <c r="S76" s="90" t="s">
+      <c r="S76" s="84" t="s">
         <v>1709</v>
       </c>
       <c r="X76" s="23"/>
@@ -17616,7 +17588,7 @@
       <c r="Q77">
         <v>35</v>
       </c>
-      <c r="S77" s="90" t="s">
+      <c r="S77" s="84" t="s">
         <v>1710</v>
       </c>
       <c r="X77" s="23"/>
@@ -17677,7 +17649,7 @@
       <c r="Q78">
         <v>56</v>
       </c>
-      <c r="S78" s="90" t="s">
+      <c r="S78" s="84" t="s">
         <v>1711</v>
       </c>
       <c r="X78" s="23"/>
@@ -17738,7 +17710,7 @@
       <c r="Q79">
         <v>110</v>
       </c>
-      <c r="S79" s="90" t="s">
+      <c r="S79" s="84" t="s">
         <v>1712</v>
       </c>
       <c r="X79" s="23"/>
@@ -17799,7 +17771,7 @@
       <c r="Q80">
         <v>145</v>
       </c>
-      <c r="S80" s="90" t="s">
+      <c r="S80" s="84" t="s">
         <v>1713</v>
       </c>
       <c r="X80" s="23"/>
@@ -17860,7 +17832,7 @@
       <c r="Q81">
         <v>220</v>
       </c>
-      <c r="S81" s="90" t="s">
+      <c r="S81" s="84" t="s">
         <v>1714</v>
       </c>
       <c r="X81" s="23"/>
@@ -17921,7 +17893,7 @@
       <c r="Q82">
         <v>293</v>
       </c>
-      <c r="S82" s="90" t="s">
+      <c r="S82" s="84" t="s">
         <v>1715</v>
       </c>
       <c r="X82" s="23"/>
@@ -17982,7 +17954,7 @@
       <c r="Q83">
         <v>580</v>
       </c>
-      <c r="S83" s="90" t="s">
+      <c r="S83" s="84" t="s">
         <v>1716</v>
       </c>
       <c r="X83" s="23"/>
@@ -21665,7 +21637,7 @@
       <c r="M1000" s="27"/>
     </row>
   </sheetData>
-  <phoneticPr fontId="25" type="noConversion"/>
+  <phoneticPr fontId="21" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>
   <legacyDrawing r:id="rId1"/>
@@ -26687,7 +26659,7 @@
       </c>
     </row>
     <row r="208" spans="2:10" ht="15" customHeight="1">
-      <c r="B208" s="78">
+      <c r="B208" s="75">
         <v>38</v>
       </c>
       <c r="C208">
@@ -26710,7 +26682,7 @@
       </c>
     </row>
     <row r="209" spans="2:10" ht="15" customHeight="1">
-      <c r="B209" s="78">
+      <c r="B209" s="75">
         <v>38</v>
       </c>
       <c r="C209">
@@ -26733,7 +26705,7 @@
       </c>
     </row>
     <row r="210" spans="2:10" ht="15" customHeight="1">
-      <c r="B210" s="78">
+      <c r="B210" s="75">
         <v>38</v>
       </c>
       <c r="C210">
@@ -26756,7 +26728,7 @@
       </c>
     </row>
     <row r="211" spans="2:10" ht="15" customHeight="1">
-      <c r="B211" s="78">
+      <c r="B211" s="75">
         <v>38</v>
       </c>
       <c r="C211">
@@ -26779,7 +26751,7 @@
       </c>
     </row>
     <row r="212" spans="2:10" ht="15" customHeight="1">
-      <c r="B212" s="78">
+      <c r="B212" s="75">
         <v>38</v>
       </c>
       <c r="C212">
@@ -26802,7 +26774,7 @@
       </c>
     </row>
     <row r="213" spans="2:10" ht="15" customHeight="1">
-      <c r="B213" s="78">
+      <c r="B213" s="75">
         <v>38</v>
       </c>
       <c r="C213">
@@ -26825,7 +26797,7 @@
       </c>
     </row>
     <row r="214" spans="2:10" ht="15" customHeight="1">
-      <c r="B214" s="78">
+      <c r="B214" s="75">
         <v>38</v>
       </c>
       <c r="C214">
@@ -26848,7 +26820,7 @@
       </c>
     </row>
     <row r="215" spans="2:10" ht="15" customHeight="1">
-      <c r="B215" s="78">
+      <c r="B215" s="75">
         <v>38</v>
       </c>
       <c r="C215">
@@ -26871,7 +26843,7 @@
       </c>
     </row>
     <row r="216" spans="2:10" ht="15" customHeight="1">
-      <c r="B216" s="78">
+      <c r="B216" s="75">
         <v>38</v>
       </c>
       <c r="C216">
@@ -26894,7 +26866,7 @@
       </c>
     </row>
     <row r="217" spans="2:10" ht="15" customHeight="1">
-      <c r="B217" s="78">
+      <c r="B217" s="75">
         <v>38</v>
       </c>
       <c r="C217">
@@ -26917,7 +26889,7 @@
       </c>
     </row>
     <row r="218" spans="2:10" ht="15" customHeight="1">
-      <c r="B218" s="78">
+      <c r="B218" s="75">
         <v>38</v>
       </c>
       <c r="C218">
@@ -26940,7 +26912,7 @@
       </c>
     </row>
     <row r="219" spans="2:10" ht="15" customHeight="1">
-      <c r="B219" s="78">
+      <c r="B219" s="75">
         <v>38</v>
       </c>
       <c r="C219">
@@ -26963,7 +26935,7 @@
       </c>
     </row>
     <row r="220" spans="2:10" ht="15" customHeight="1">
-      <c r="B220" s="78">
+      <c r="B220" s="75">
         <v>38</v>
       </c>
       <c r="C220">
@@ -26986,7 +26958,7 @@
       </c>
     </row>
     <row r="221" spans="2:10" ht="15" customHeight="1">
-      <c r="B221" s="78">
+      <c r="B221" s="75">
         <v>38</v>
       </c>
       <c r="C221">
@@ -27009,7 +26981,7 @@
       </c>
     </row>
     <row r="222" spans="2:10" ht="15" customHeight="1">
-      <c r="B222" s="78">
+      <c r="B222" s="75">
         <v>38</v>
       </c>
       <c r="C222">
@@ -27032,7 +27004,7 @@
       </c>
     </row>
     <row r="223" spans="2:10" ht="15" customHeight="1">
-      <c r="B223" s="78">
+      <c r="B223" s="75">
         <v>38</v>
       </c>
       <c r="C223">
@@ -27055,7 +27027,7 @@
       </c>
     </row>
     <row r="224" spans="2:10" ht="15" customHeight="1">
-      <c r="B224" s="78">
+      <c r="B224" s="75">
         <v>38</v>
       </c>
       <c r="C224">
@@ -34329,7 +34301,7 @@
       </c>
     </row>
     <row r="547" spans="1:10" s="31" customFormat="1" ht="15" customHeight="1">
-      <c r="A547" s="76" t="s">
+      <c r="A547" s="73" t="s">
         <v>1432</v>
       </c>
       <c r="B547" s="14">
@@ -34341,10 +34313,10 @@
       <c r="D547" s="14">
         <v>2</v>
       </c>
-      <c r="E547" s="76" t="s">
+      <c r="E547" s="73" t="s">
         <v>1433</v>
       </c>
-      <c r="F547" s="76" t="s">
+      <c r="F547" s="73" t="s">
         <v>1041</v>
       </c>
       <c r="G547" s="14">
@@ -34352,7 +34324,7 @@
       </c>
     </row>
     <row r="548" spans="1:10" s="31" customFormat="1" ht="15" customHeight="1">
-      <c r="A548" s="77" t="s">
+      <c r="A548" s="74" t="s">
         <v>1432</v>
       </c>
       <c r="B548" s="63">
@@ -34364,10 +34336,10 @@
       <c r="D548" s="63">
         <v>1</v>
       </c>
-      <c r="E548" s="77" t="s">
+      <c r="E548" s="74" t="s">
         <v>1434</v>
       </c>
-      <c r="F548" s="77" t="s">
+      <c r="F548" s="74" t="s">
         <v>1041</v>
       </c>
       <c r="G548" s="63">
@@ -34375,7 +34347,7 @@
       </c>
     </row>
     <row r="549" spans="1:10" s="31" customFormat="1" ht="15" customHeight="1">
-      <c r="A549" s="77" t="s">
+      <c r="A549" s="74" t="s">
         <v>1432</v>
       </c>
       <c r="B549" s="63">
@@ -34387,10 +34359,10 @@
       <c r="D549" s="63">
         <v>1</v>
       </c>
-      <c r="E549" s="77" t="s">
+      <c r="E549" s="74" t="s">
         <v>1435</v>
       </c>
-      <c r="F549" s="77" t="s">
+      <c r="F549" s="74" t="s">
         <v>1041</v>
       </c>
       <c r="G549" s="63">
@@ -34398,7 +34370,7 @@
       </c>
     </row>
     <row r="550" spans="1:10" s="31" customFormat="1" ht="15" customHeight="1">
-      <c r="A550" s="77" t="s">
+      <c r="A550" s="74" t="s">
         <v>1432</v>
       </c>
       <c r="B550" s="63">
@@ -34410,10 +34382,10 @@
       <c r="D550" s="63">
         <v>1</v>
       </c>
-      <c r="E550" s="77" t="s">
+      <c r="E550" s="74" t="s">
         <v>1436</v>
       </c>
-      <c r="F550" s="77" t="s">
+      <c r="F550" s="74" t="s">
         <v>1041</v>
       </c>
       <c r="G550" s="63">
@@ -34421,7 +34393,7 @@
       </c>
     </row>
     <row r="551" spans="1:10" s="31" customFormat="1" ht="15" customHeight="1">
-      <c r="A551" s="77" t="s">
+      <c r="A551" s="74" t="s">
         <v>1432</v>
       </c>
       <c r="B551" s="63">
@@ -34433,10 +34405,10 @@
       <c r="D551" s="63">
         <v>1</v>
       </c>
-      <c r="E551" s="77" t="s">
+      <c r="E551" s="74" t="s">
         <v>1437</v>
       </c>
-      <c r="F551" s="77" t="s">
+      <c r="F551" s="74" t="s">
         <v>1041</v>
       </c>
       <c r="G551" s="63">
@@ -34444,7 +34416,7 @@
       </c>
     </row>
     <row r="552" spans="1:10" s="31" customFormat="1" ht="15" customHeight="1">
-      <c r="A552" s="77" t="s">
+      <c r="A552" s="74" t="s">
         <v>1432</v>
       </c>
       <c r="B552" s="63">
@@ -34456,10 +34428,10 @@
       <c r="D552" s="63">
         <v>1</v>
       </c>
-      <c r="E552" s="77" t="s">
+      <c r="E552" s="74" t="s">
         <v>1438</v>
       </c>
-      <c r="F552" s="77" t="s">
+      <c r="F552" s="74" t="s">
         <v>1041</v>
       </c>
       <c r="G552" s="63">
@@ -34467,7 +34439,7 @@
       </c>
     </row>
     <row r="553" spans="1:10" s="31" customFormat="1" ht="15" customHeight="1">
-      <c r="A553" s="77" t="s">
+      <c r="A553" s="74" t="s">
         <v>1432</v>
       </c>
       <c r="B553" s="63">
@@ -34479,10 +34451,10 @@
       <c r="D553" s="63">
         <v>1</v>
       </c>
-      <c r="E553" s="77" t="s">
+      <c r="E553" s="74" t="s">
         <v>1439</v>
       </c>
-      <c r="F553" s="77" t="s">
+      <c r="F553" s="74" t="s">
         <v>1041</v>
       </c>
       <c r="G553" s="63">
@@ -34490,7 +34462,7 @@
       </c>
     </row>
     <row r="554" spans="1:10" s="31" customFormat="1" ht="15" customHeight="1">
-      <c r="A554" s="77" t="s">
+      <c r="A554" s="74" t="s">
         <v>1432</v>
       </c>
       <c r="B554" s="63">
@@ -34502,10 +34474,10 @@
       <c r="D554" s="63">
         <v>1</v>
       </c>
-      <c r="E554" s="77" t="s">
+      <c r="E554" s="74" t="s">
         <v>1440</v>
       </c>
-      <c r="F554" s="77" t="s">
+      <c r="F554" s="74" t="s">
         <v>1041</v>
       </c>
       <c r="G554" s="63">
@@ -34513,7 +34485,7 @@
       </c>
     </row>
     <row r="555" spans="1:10" s="31" customFormat="1" ht="15" customHeight="1">
-      <c r="A555" s="77" t="s">
+      <c r="A555" s="74" t="s">
         <v>1432</v>
       </c>
       <c r="B555" s="63">
@@ -34525,10 +34497,10 @@
       <c r="D555" s="63">
         <v>1</v>
       </c>
-      <c r="E555" s="77" t="s">
+      <c r="E555" s="74" t="s">
         <v>1441</v>
       </c>
-      <c r="F555" s="77" t="s">
+      <c r="F555" s="74" t="s">
         <v>1041</v>
       </c>
       <c r="G555" s="63">
@@ -34536,7 +34508,7 @@
       </c>
     </row>
     <row r="556" spans="1:10" s="31" customFormat="1" ht="15" customHeight="1">
-      <c r="A556" s="77" t="s">
+      <c r="A556" s="74" t="s">
         <v>1432</v>
       </c>
       <c r="B556" s="63">
@@ -34548,10 +34520,10 @@
       <c r="D556" s="63">
         <v>1</v>
       </c>
-      <c r="E556" s="77" t="s">
+      <c r="E556" s="74" t="s">
         <v>1442</v>
       </c>
-      <c r="F556" s="77" t="s">
+      <c r="F556" s="74" t="s">
         <v>1041</v>
       </c>
       <c r="G556" s="63">
@@ -34559,7 +34531,7 @@
       </c>
     </row>
     <row r="557" spans="1:10" s="31" customFormat="1" ht="15" customHeight="1">
-      <c r="A557" s="77" t="s">
+      <c r="A557" s="74" t="s">
         <v>1432</v>
       </c>
       <c r="B557" s="63">
@@ -34571,10 +34543,10 @@
       <c r="D557" s="63">
         <v>1</v>
       </c>
-      <c r="E557" s="77" t="s">
+      <c r="E557" s="74" t="s">
         <v>1443</v>
       </c>
-      <c r="F557" s="77" t="s">
+      <c r="F557" s="74" t="s">
         <v>1041</v>
       </c>
       <c r="G557" s="63">
@@ -34582,7 +34554,7 @@
       </c>
     </row>
     <row r="558" spans="1:10" s="31" customFormat="1" ht="15" customHeight="1">
-      <c r="A558" s="77" t="s">
+      <c r="A558" s="74" t="s">
         <v>1432</v>
       </c>
       <c r="B558" s="63">
@@ -34594,10 +34566,10 @@
       <c r="D558" s="63">
         <v>1</v>
       </c>
-      <c r="E558" s="77" t="s">
+      <c r="E558" s="74" t="s">
         <v>1444</v>
       </c>
-      <c r="F558" s="77" t="s">
+      <c r="F558" s="74" t="s">
         <v>1041</v>
       </c>
       <c r="G558" s="63">
@@ -34605,7 +34577,7 @@
       </c>
     </row>
     <row r="559" spans="1:10" s="31" customFormat="1" ht="15" customHeight="1">
-      <c r="A559" s="77" t="s">
+      <c r="A559" s="74" t="s">
         <v>1432</v>
       </c>
       <c r="B559" s="63">
@@ -34617,10 +34589,10 @@
       <c r="D559" s="63">
         <v>1</v>
       </c>
-      <c r="E559" s="77" t="s">
+      <c r="E559" s="74" t="s">
         <v>1445</v>
       </c>
-      <c r="F559" s="77" t="s">
+      <c r="F559" s="74" t="s">
         <v>1041</v>
       </c>
       <c r="G559" s="63">
@@ -34628,7 +34600,7 @@
       </c>
     </row>
     <row r="560" spans="1:10" s="31" customFormat="1" ht="15" customHeight="1">
-      <c r="A560" s="77" t="s">
+      <c r="A560" s="74" t="s">
         <v>1432</v>
       </c>
       <c r="B560" s="63">
@@ -34640,10 +34612,10 @@
       <c r="D560" s="63">
         <v>1</v>
       </c>
-      <c r="E560" s="77" t="s">
+      <c r="E560" s="74" t="s">
         <v>1446</v>
       </c>
-      <c r="F560" s="77" t="s">
+      <c r="F560" s="74" t="s">
         <v>1041</v>
       </c>
       <c r="G560" s="63">
@@ -34651,7 +34623,7 @@
       </c>
     </row>
     <row r="561" spans="1:7" s="31" customFormat="1" ht="15" customHeight="1">
-      <c r="A561" s="77" t="s">
+      <c r="A561" s="74" t="s">
         <v>1432</v>
       </c>
       <c r="B561" s="63">
@@ -34663,10 +34635,10 @@
       <c r="D561" s="63">
         <v>1</v>
       </c>
-      <c r="E561" s="77" t="s">
+      <c r="E561" s="74" t="s">
         <v>1447</v>
       </c>
-      <c r="F561" s="77" t="s">
+      <c r="F561" s="74" t="s">
         <v>1041</v>
       </c>
       <c r="G561" s="63">
@@ -34674,7 +34646,7 @@
       </c>
     </row>
     <row r="562" spans="1:7" s="31" customFormat="1" ht="15" customHeight="1">
-      <c r="A562" s="77" t="s">
+      <c r="A562" s="74" t="s">
         <v>1432</v>
       </c>
       <c r="B562" s="63">
@@ -34686,10 +34658,10 @@
       <c r="D562" s="63">
         <v>1</v>
       </c>
-      <c r="E562" s="77" t="s">
+      <c r="E562" s="74" t="s">
         <v>1448</v>
       </c>
-      <c r="F562" s="77" t="s">
+      <c r="F562" s="74" t="s">
         <v>1041</v>
       </c>
       <c r="G562" s="63">
@@ -34697,7 +34669,7 @@
       </c>
     </row>
     <row r="563" spans="1:7" s="31" customFormat="1" ht="15" customHeight="1">
-      <c r="A563" s="77" t="s">
+      <c r="A563" s="74" t="s">
         <v>1432</v>
       </c>
       <c r="B563" s="63">
@@ -34709,10 +34681,10 @@
       <c r="D563" s="63">
         <v>1</v>
       </c>
-      <c r="E563" s="77" t="s">
+      <c r="E563" s="74" t="s">
         <v>1449</v>
       </c>
-      <c r="F563" s="77" t="s">
+      <c r="F563" s="74" t="s">
         <v>1041</v>
       </c>
       <c r="G563" s="63">
@@ -34720,7 +34692,7 @@
       </c>
     </row>
     <row r="564" spans="1:7" s="31" customFormat="1" ht="15" customHeight="1">
-      <c r="A564" s="76" t="s">
+      <c r="A564" s="73" t="s">
         <v>1432</v>
       </c>
       <c r="B564" s="14">
@@ -34743,7 +34715,7 @@
       </c>
     </row>
     <row r="565" spans="1:7" s="31" customFormat="1" ht="15" customHeight="1">
-      <c r="A565" s="77" t="s">
+      <c r="A565" s="74" t="s">
         <v>1432</v>
       </c>
       <c r="B565" s="63">
@@ -34758,7 +34730,7 @@
       <c r="E565" s="63" t="s">
         <v>938</v>
       </c>
-      <c r="F565" s="77" t="s">
+      <c r="F565" s="74" t="s">
         <v>819</v>
       </c>
       <c r="G565" s="63">
@@ -34766,7 +34738,7 @@
       </c>
     </row>
     <row r="566" spans="1:7" s="31" customFormat="1" ht="15" customHeight="1">
-      <c r="A566" s="77" t="s">
+      <c r="A566" s="74" t="s">
         <v>1432</v>
       </c>
       <c r="B566" s="63">
@@ -34789,7 +34761,7 @@
       </c>
     </row>
     <row r="567" spans="1:7" s="31" customFormat="1" ht="15" customHeight="1">
-      <c r="A567" s="77" t="s">
+      <c r="A567" s="74" t="s">
         <v>1432</v>
       </c>
       <c r="B567" s="63">
@@ -34812,7 +34784,7 @@
       </c>
     </row>
     <row r="568" spans="1:7" s="31" customFormat="1" ht="15" customHeight="1">
-      <c r="A568" s="77" t="s">
+      <c r="A568" s="74" t="s">
         <v>1432</v>
       </c>
       <c r="B568" s="63">
@@ -34835,7 +34807,7 @@
       </c>
     </row>
     <row r="569" spans="1:7" s="31" customFormat="1" ht="15" customHeight="1">
-      <c r="A569" s="77" t="s">
+      <c r="A569" s="74" t="s">
         <v>1432</v>
       </c>
       <c r="B569" s="63">
@@ -34858,7 +34830,7 @@
       </c>
     </row>
     <row r="570" spans="1:7" s="31" customFormat="1" ht="15" customHeight="1">
-      <c r="A570" s="77" t="s">
+      <c r="A570" s="74" t="s">
         <v>1432</v>
       </c>
       <c r="B570" s="63">
@@ -34881,7 +34853,7 @@
       </c>
     </row>
     <row r="571" spans="1:7" s="31" customFormat="1" ht="15" customHeight="1">
-      <c r="A571" s="77" t="s">
+      <c r="A571" s="74" t="s">
         <v>1432</v>
       </c>
       <c r="B571" s="63">
@@ -34904,7 +34876,7 @@
       </c>
     </row>
     <row r="572" spans="1:7" s="31" customFormat="1" ht="15" customHeight="1">
-      <c r="A572" s="77" t="s">
+      <c r="A572" s="74" t="s">
         <v>1432</v>
       </c>
       <c r="B572" s="63">
@@ -34927,7 +34899,7 @@
       </c>
     </row>
     <row r="573" spans="1:7" s="31" customFormat="1" ht="15" customHeight="1">
-      <c r="A573" s="77" t="s">
+      <c r="A573" s="74" t="s">
         <v>1432</v>
       </c>
       <c r="B573" s="63">
@@ -34950,7 +34922,7 @@
       </c>
     </row>
     <row r="574" spans="1:7" s="31" customFormat="1" ht="15" customHeight="1">
-      <c r="A574" s="77" t="s">
+      <c r="A574" s="74" t="s">
         <v>1432</v>
       </c>
       <c r="B574" s="63">
@@ -34973,7 +34945,7 @@
       </c>
     </row>
     <row r="575" spans="1:7" s="31" customFormat="1" ht="15" customHeight="1">
-      <c r="A575" s="77" t="s">
+      <c r="A575" s="74" t="s">
         <v>1432</v>
       </c>
       <c r="B575" s="63">
@@ -34996,7 +34968,7 @@
       </c>
     </row>
     <row r="576" spans="1:7" s="31" customFormat="1" ht="15" customHeight="1">
-      <c r="A576" s="77" t="s">
+      <c r="A576" s="74" t="s">
         <v>1432</v>
       </c>
       <c r="B576" s="63">
@@ -35019,7 +34991,7 @@
       </c>
     </row>
     <row r="577" spans="1:7" s="31" customFormat="1" ht="15" customHeight="1">
-      <c r="A577" s="77" t="s">
+      <c r="A577" s="74" t="s">
         <v>1432</v>
       </c>
       <c r="B577" s="63">
@@ -35042,7 +35014,7 @@
       </c>
     </row>
     <row r="578" spans="1:7" s="31" customFormat="1" ht="15" customHeight="1">
-      <c r="A578" s="77" t="s">
+      <c r="A578" s="74" t="s">
         <v>1432</v>
       </c>
       <c r="B578" s="63">
@@ -35065,7 +35037,7 @@
       </c>
     </row>
     <row r="579" spans="1:7" s="31" customFormat="1" ht="15" customHeight="1">
-      <c r="A579" s="77" t="s">
+      <c r="A579" s="74" t="s">
         <v>1432</v>
       </c>
       <c r="B579" s="63">
@@ -35088,7 +35060,7 @@
       </c>
     </row>
     <row r="580" spans="1:7" s="31" customFormat="1" ht="15" customHeight="1">
-      <c r="A580" s="77" t="s">
+      <c r="A580" s="74" t="s">
         <v>1432</v>
       </c>
       <c r="B580" s="63">
@@ -35111,7 +35083,7 @@
       </c>
     </row>
     <row r="581" spans="1:7" ht="15" customHeight="1">
-      <c r="A581" s="76" t="s">
+      <c r="A581" s="73" t="s">
         <v>1432</v>
       </c>
       <c r="B581" s="14">
@@ -35134,7 +35106,7 @@
       </c>
     </row>
     <row r="582" spans="1:7" ht="15" customHeight="1">
-      <c r="A582" s="77" t="s">
+      <c r="A582" s="74" t="s">
         <v>1432</v>
       </c>
       <c r="B582" s="63">
@@ -35157,7 +35129,7 @@
       </c>
     </row>
     <row r="583" spans="1:7" ht="15" customHeight="1">
-      <c r="A583" s="77" t="s">
+      <c r="A583" s="74" t="s">
         <v>1432</v>
       </c>
       <c r="B583" s="63">
@@ -35180,7 +35152,7 @@
       </c>
     </row>
     <row r="584" spans="1:7" ht="15" customHeight="1">
-      <c r="A584" s="77" t="s">
+      <c r="A584" s="74" t="s">
         <v>1432</v>
       </c>
       <c r="B584" s="63">
@@ -35203,7 +35175,7 @@
       </c>
     </row>
     <row r="585" spans="1:7" ht="15" customHeight="1">
-      <c r="A585" s="77" t="s">
+      <c r="A585" s="74" t="s">
         <v>1432</v>
       </c>
       <c r="B585" s="63">
@@ -35226,7 +35198,7 @@
       </c>
     </row>
     <row r="586" spans="1:7" ht="15" customHeight="1">
-      <c r="A586" s="77" t="s">
+      <c r="A586" s="74" t="s">
         <v>1432</v>
       </c>
       <c r="B586" s="63">
@@ -35249,7 +35221,7 @@
       </c>
     </row>
     <row r="587" spans="1:7" ht="15" customHeight="1">
-      <c r="A587" s="77" t="s">
+      <c r="A587" s="74" t="s">
         <v>1432</v>
       </c>
       <c r="B587" s="63">
@@ -35272,7 +35244,7 @@
       </c>
     </row>
     <row r="588" spans="1:7" ht="15" customHeight="1">
-      <c r="A588" s="77" t="s">
+      <c r="A588" s="74" t="s">
         <v>1432</v>
       </c>
       <c r="B588" s="63">
@@ -35295,7 +35267,7 @@
       </c>
     </row>
     <row r="589" spans="1:7" ht="15" customHeight="1">
-      <c r="A589" s="77" t="s">
+      <c r="A589" s="74" t="s">
         <v>1432</v>
       </c>
       <c r="B589" s="63">
@@ -35318,7 +35290,7 @@
       </c>
     </row>
     <row r="590" spans="1:7" ht="15" customHeight="1">
-      <c r="A590" s="77" t="s">
+      <c r="A590" s="74" t="s">
         <v>1432</v>
       </c>
       <c r="B590" s="63">
@@ -35341,7 +35313,7 @@
       </c>
     </row>
     <row r="591" spans="1:7" ht="15" customHeight="1">
-      <c r="A591" s="77" t="s">
+      <c r="A591" s="74" t="s">
         <v>1432</v>
       </c>
       <c r="B591" s="63">
@@ -35364,7 +35336,7 @@
       </c>
     </row>
     <row r="592" spans="1:7" ht="15" customHeight="1">
-      <c r="A592" s="77" t="s">
+      <c r="A592" s="74" t="s">
         <v>1432</v>
       </c>
       <c r="B592" s="63">
@@ -35387,7 +35359,7 @@
       </c>
     </row>
     <row r="593" spans="1:10" ht="15" customHeight="1">
-      <c r="A593" s="77" t="s">
+      <c r="A593" s="74" t="s">
         <v>1432</v>
       </c>
       <c r="B593" s="63">
@@ -35410,7 +35382,7 @@
       </c>
     </row>
     <row r="594" spans="1:10" ht="15" customHeight="1">
-      <c r="A594" s="77" t="s">
+      <c r="A594" s="74" t="s">
         <v>1432</v>
       </c>
       <c r="B594" s="63">
@@ -35433,7 +35405,7 @@
       </c>
     </row>
     <row r="595" spans="1:10" ht="15" customHeight="1">
-      <c r="A595" s="77" t="s">
+      <c r="A595" s="74" t="s">
         <v>1432</v>
       </c>
       <c r="B595" s="63">
@@ -35456,7 +35428,7 @@
       </c>
     </row>
     <row r="596" spans="1:10" ht="15" customHeight="1">
-      <c r="A596" s="77" t="s">
+      <c r="A596" s="74" t="s">
         <v>1432</v>
       </c>
       <c r="B596" s="63">
@@ -35479,7 +35451,7 @@
       </c>
     </row>
     <row r="597" spans="1:10" ht="15" customHeight="1">
-      <c r="A597" s="77" t="s">
+      <c r="A597" s="74" t="s">
         <v>1432</v>
       </c>
       <c r="B597" s="63">
@@ -35523,7 +35495,7 @@
       <c r="G598" s="31">
         <v>1500000</v>
       </c>
-      <c r="I598" s="73"/>
+      <c r="I598" s="70"/>
       <c r="J598" s="59" t="s">
         <v>1628</v>
       </c>
@@ -35550,7 +35522,7 @@
       <c r="G599" s="31">
         <v>7500000</v>
       </c>
-      <c r="I599" s="73"/>
+      <c r="I599" s="70"/>
       <c r="J599" s="59" t="s">
         <v>1629</v>
       </c>
@@ -35577,7 +35549,7 @@
       <c r="G600" s="31">
         <v>12000000</v>
       </c>
-      <c r="I600" s="73"/>
+      <c r="I600" s="70"/>
       <c r="J600" s="59" t="s">
         <v>1630</v>
       </c>
@@ -35604,7 +35576,7 @@
       <c r="G601" s="31">
         <v>23000000</v>
       </c>
-      <c r="I601" s="73"/>
+      <c r="I601" s="70"/>
       <c r="J601" s="59" t="s">
         <v>1631</v>
       </c>
@@ -35631,7 +35603,7 @@
       <c r="G602" s="31">
         <v>30000000</v>
       </c>
-      <c r="I602" s="73"/>
+      <c r="I602" s="70"/>
       <c r="J602" s="59" t="s">
         <v>1632</v>
       </c>
@@ -35658,7 +35630,7 @@
       <c r="G603" s="31">
         <v>45000000</v>
       </c>
-      <c r="I603" s="73"/>
+      <c r="I603" s="70"/>
       <c r="J603" s="59" t="s">
         <v>1633</v>
       </c>
@@ -35685,7 +35657,7 @@
       <c r="G604" s="31">
         <v>60000000</v>
       </c>
-      <c r="I604" s="73"/>
+      <c r="I604" s="70"/>
       <c r="J604" s="59" t="s">
         <v>1634</v>
       </c>
@@ -35712,7 +35684,7 @@
       <c r="G605" s="31">
         <v>119000000</v>
       </c>
-      <c r="I605" s="73"/>
+      <c r="I605" s="70"/>
       <c r="J605" s="59" t="s">
         <v>1635</v>
       </c>
@@ -35739,7 +35711,7 @@
       <c r="G606" s="31">
         <v>7500000</v>
       </c>
-      <c r="I606" s="73"/>
+      <c r="I606" s="70"/>
       <c r="J606" s="31" t="s">
         <v>1053</v>
       </c>
@@ -35766,7 +35738,7 @@
       <c r="G607" s="31">
         <v>1500000</v>
       </c>
-      <c r="I607" s="73"/>
+      <c r="I607" s="70"/>
       <c r="J607" s="59" t="s">
         <v>1636</v>
       </c>
@@ -35793,7 +35765,7 @@
       <c r="G608" s="31">
         <v>7500000</v>
       </c>
-      <c r="I608" s="73"/>
+      <c r="I608" s="70"/>
       <c r="J608" s="59" t="s">
         <v>1637</v>
       </c>
@@ -35820,7 +35792,7 @@
       <c r="G609" s="31">
         <v>12000000</v>
       </c>
-      <c r="I609" s="73"/>
+      <c r="I609" s="70"/>
       <c r="J609" s="59" t="s">
         <v>1638</v>
       </c>
@@ -35847,7 +35819,7 @@
       <c r="G610" s="31">
         <v>23000000</v>
       </c>
-      <c r="I610" s="73"/>
+      <c r="I610" s="70"/>
       <c r="J610" s="59" t="s">
         <v>1639</v>
       </c>
@@ -35874,7 +35846,7 @@
       <c r="G611" s="31">
         <v>30000000</v>
       </c>
-      <c r="I611" s="73"/>
+      <c r="I611" s="70"/>
       <c r="J611" s="59" t="s">
         <v>1640</v>
       </c>
@@ -35901,7 +35873,7 @@
       <c r="G612" s="31">
         <v>45000000</v>
       </c>
-      <c r="I612" s="73"/>
+      <c r="I612" s="70"/>
       <c r="J612" s="59" t="s">
         <v>1641</v>
       </c>
@@ -35928,7 +35900,7 @@
       <c r="G613" s="31">
         <v>60000000</v>
       </c>
-      <c r="I613" s="73"/>
+      <c r="I613" s="70"/>
       <c r="J613" s="59" t="s">
         <v>1642</v>
       </c>
@@ -36817,7 +36789,7 @@
       <c r="H649" t="s">
         <v>819</v>
       </c>
-      <c r="I649" s="74">
+      <c r="I649" s="71">
         <v>990</v>
       </c>
       <c r="J649" s="59" t="s">
@@ -36846,7 +36818,7 @@
       <c r="H650" t="s">
         <v>819</v>
       </c>
-      <c r="I650" s="74">
+      <c r="I650" s="71">
         <v>4990</v>
       </c>
       <c r="J650" s="59" t="s">
@@ -36875,7 +36847,7 @@
       <c r="H651" t="s">
         <v>819</v>
       </c>
-      <c r="I651" s="74">
+      <c r="I651" s="71">
         <v>7990</v>
       </c>
       <c r="J651" s="59" t="s">
@@ -36904,7 +36876,7 @@
       <c r="H652" t="s">
         <v>819</v>
       </c>
-      <c r="I652" s="74">
+      <c r="I652" s="71">
         <v>14990</v>
       </c>
       <c r="J652" s="59" t="s">
@@ -36933,7 +36905,7 @@
       <c r="H653" t="s">
         <v>819</v>
       </c>
-      <c r="I653" s="74">
+      <c r="I653" s="71">
         <v>19990</v>
       </c>
       <c r="J653" s="59" t="s">
@@ -36962,7 +36934,7 @@
       <c r="H654" t="s">
         <v>819</v>
       </c>
-      <c r="I654" s="74">
+      <c r="I654" s="71">
         <v>29990</v>
       </c>
       <c r="J654" s="59" t="s">
@@ -36991,7 +36963,7 @@
       <c r="H655" t="s">
         <v>819</v>
       </c>
-      <c r="I655" s="74">
+      <c r="I655" s="71">
         <v>39990</v>
       </c>
       <c r="J655" s="59" t="s">
@@ -37020,7 +36992,7 @@
       <c r="H656" t="s">
         <v>819</v>
       </c>
-      <c r="I656" s="74">
+      <c r="I656" s="71">
         <v>79990</v>
       </c>
       <c r="J656" s="59" t="s">
@@ -37049,7 +37021,7 @@
       <c r="H657" t="s">
         <v>819</v>
       </c>
-      <c r="I657" s="74">
+      <c r="I657" s="71">
         <v>4990</v>
       </c>
       <c r="J657" s="31" t="s">
@@ -37078,7 +37050,7 @@
       <c r="H658" t="s">
         <v>819</v>
       </c>
-      <c r="I658" s="74">
+      <c r="I658" s="71">
         <v>990</v>
       </c>
       <c r="J658" s="59" t="s">
@@ -37107,7 +37079,7 @@
       <c r="H659" t="s">
         <v>819</v>
       </c>
-      <c r="I659" s="74">
+      <c r="I659" s="71">
         <v>4990</v>
       </c>
       <c r="J659" s="59" t="s">
@@ -37136,7 +37108,7 @@
       <c r="H660" t="s">
         <v>819</v>
       </c>
-      <c r="I660" s="74">
+      <c r="I660" s="71">
         <v>7990</v>
       </c>
       <c r="J660" s="59" t="s">
@@ -37165,7 +37137,7 @@
       <c r="H661" t="s">
         <v>819</v>
       </c>
-      <c r="I661" s="74">
+      <c r="I661" s="71">
         <v>14990</v>
       </c>
       <c r="J661" s="59" t="s">
@@ -37194,7 +37166,7 @@
       <c r="H662" t="s">
         <v>819</v>
       </c>
-      <c r="I662" s="74">
+      <c r="I662" s="71">
         <v>19990</v>
       </c>
       <c r="J662" s="59" t="s">
@@ -37223,7 +37195,7 @@
       <c r="H663" t="s">
         <v>819</v>
       </c>
-      <c r="I663" s="74">
+      <c r="I663" s="71">
         <v>29990</v>
       </c>
       <c r="J663" s="59" t="s">
@@ -37252,7 +37224,7 @@
       <c r="H664" t="s">
         <v>819</v>
       </c>
-      <c r="I664" s="74">
+      <c r="I664" s="71">
         <v>39990</v>
       </c>
       <c r="J664" s="59" t="s">
@@ -38010,7 +37982,7 @@
       <c r="H700" t="s">
         <v>819</v>
       </c>
-      <c r="I700" s="74">
+      <c r="I700" s="71">
         <v>990</v>
       </c>
       <c r="J700" s="59" t="s">
@@ -38039,7 +38011,7 @@
       <c r="H701" t="s">
         <v>819</v>
       </c>
-      <c r="I701" s="74">
+      <c r="I701" s="71">
         <v>4990</v>
       </c>
       <c r="J701" s="59" t="s">
@@ -38068,7 +38040,7 @@
       <c r="H702" t="s">
         <v>819</v>
       </c>
-      <c r="I702" s="74">
+      <c r="I702" s="71">
         <v>7990</v>
       </c>
       <c r="J702" s="59" t="s">
@@ -38097,7 +38069,7 @@
       <c r="H703" t="s">
         <v>819</v>
       </c>
-      <c r="I703" s="74">
+      <c r="I703" s="71">
         <v>14990</v>
       </c>
       <c r="J703" s="59" t="s">
@@ -38126,7 +38098,7 @@
       <c r="H704" t="s">
         <v>819</v>
       </c>
-      <c r="I704" s="74">
+      <c r="I704" s="71">
         <v>19990</v>
       </c>
       <c r="J704" s="59" t="s">
@@ -38155,7 +38127,7 @@
       <c r="H705" t="s">
         <v>819</v>
       </c>
-      <c r="I705" s="74">
+      <c r="I705" s="71">
         <v>29990</v>
       </c>
       <c r="J705" s="59" t="s">
@@ -38184,7 +38156,7 @@
       <c r="H706" t="s">
         <v>819</v>
       </c>
-      <c r="I706" s="74">
+      <c r="I706" s="71">
         <v>39990</v>
       </c>
       <c r="J706" s="59" t="s">
@@ -38213,7 +38185,7 @@
       <c r="H707" t="s">
         <v>819</v>
       </c>
-      <c r="I707" s="74">
+      <c r="I707" s="71">
         <v>79990</v>
       </c>
       <c r="J707" s="59" t="s">
@@ -38242,7 +38214,7 @@
       <c r="H708" t="s">
         <v>819</v>
       </c>
-      <c r="I708" s="74">
+      <c r="I708" s="71">
         <v>4990</v>
       </c>
       <c r="J708" s="31" t="s">
@@ -38271,7 +38243,7 @@
       <c r="H709" t="s">
         <v>819</v>
       </c>
-      <c r="I709" s="74">
+      <c r="I709" s="71">
         <v>990</v>
       </c>
       <c r="J709" s="59" t="s">
@@ -38300,7 +38272,7 @@
       <c r="H710" t="s">
         <v>819</v>
       </c>
-      <c r="I710" s="74">
+      <c r="I710" s="71">
         <v>4990</v>
       </c>
       <c r="J710" s="59" t="s">
@@ -38329,7 +38301,7 @@
       <c r="H711" t="s">
         <v>819</v>
       </c>
-      <c r="I711" s="74">
+      <c r="I711" s="71">
         <v>7990</v>
       </c>
       <c r="J711" s="59" t="s">
@@ -38358,7 +38330,7 @@
       <c r="H712" t="s">
         <v>819</v>
       </c>
-      <c r="I712" s="74">
+      <c r="I712" s="71">
         <v>14990</v>
       </c>
       <c r="J712" s="59" t="s">
@@ -38387,7 +38359,7 @@
       <c r="H713" t="s">
         <v>819</v>
       </c>
-      <c r="I713" s="74">
+      <c r="I713" s="71">
         <v>19990</v>
       </c>
       <c r="J713" s="59" t="s">
@@ -38416,7 +38388,7 @@
       <c r="H714" t="s">
         <v>819</v>
       </c>
-      <c r="I714" s="74">
+      <c r="I714" s="71">
         <v>29990</v>
       </c>
       <c r="J714" s="59" t="s">
@@ -38445,7 +38417,7 @@
       <c r="H715" t="s">
         <v>819</v>
       </c>
-      <c r="I715" s="74">
+      <c r="I715" s="71">
         <v>39990</v>
       </c>
       <c r="J715" s="59" t="s">
@@ -38863,7 +38835,7 @@
       <c r="H734" t="s">
         <v>819</v>
       </c>
-      <c r="I734" s="74">
+      <c r="I734" s="71">
         <v>990</v>
       </c>
       <c r="J734" s="59" t="s">
@@ -38892,7 +38864,7 @@
       <c r="H735" t="s">
         <v>819</v>
       </c>
-      <c r="I735" s="74">
+      <c r="I735" s="71">
         <v>4990</v>
       </c>
       <c r="J735" s="59" t="s">
@@ -38921,7 +38893,7 @@
       <c r="H736" t="s">
         <v>819</v>
       </c>
-      <c r="I736" s="74">
+      <c r="I736" s="71">
         <v>7990</v>
       </c>
       <c r="J736" s="59" t="s">
@@ -38950,7 +38922,7 @@
       <c r="H737" t="s">
         <v>819</v>
       </c>
-      <c r="I737" s="74">
+      <c r="I737" s="71">
         <v>14990</v>
       </c>
       <c r="J737" s="59" t="s">
@@ -38979,7 +38951,7 @@
       <c r="H738" t="s">
         <v>819</v>
       </c>
-      <c r="I738" s="74">
+      <c r="I738" s="71">
         <v>19990</v>
       </c>
       <c r="J738" s="59" t="s">
@@ -39008,7 +38980,7 @@
       <c r="H739" t="s">
         <v>819</v>
       </c>
-      <c r="I739" s="74">
+      <c r="I739" s="71">
         <v>29990</v>
       </c>
       <c r="J739" s="59" t="s">
@@ -39037,7 +39009,7 @@
       <c r="H740" t="s">
         <v>819</v>
       </c>
-      <c r="I740" s="74">
+      <c r="I740" s="71">
         <v>39990</v>
       </c>
       <c r="J740" s="59" t="s">
@@ -39066,7 +39038,7 @@
       <c r="H741" t="s">
         <v>819</v>
       </c>
-      <c r="I741" s="74">
+      <c r="I741" s="71">
         <v>79990</v>
       </c>
       <c r="J741" s="59" t="s">
@@ -39095,7 +39067,7 @@
       <c r="H742" t="s">
         <v>819</v>
       </c>
-      <c r="I742" s="74">
+      <c r="I742" s="71">
         <v>4990</v>
       </c>
       <c r="J742" s="31" t="s">
@@ -39124,7 +39096,7 @@
       <c r="H743" t="s">
         <v>819</v>
       </c>
-      <c r="I743" s="74">
+      <c r="I743" s="71">
         <v>990</v>
       </c>
       <c r="J743" s="59" t="s">
@@ -39153,7 +39125,7 @@
       <c r="H744" t="s">
         <v>819</v>
       </c>
-      <c r="I744" s="74">
+      <c r="I744" s="71">
         <v>4990</v>
       </c>
       <c r="J744" s="59" t="s">
@@ -39182,7 +39154,7 @@
       <c r="H745" t="s">
         <v>819</v>
       </c>
-      <c r="I745" s="74">
+      <c r="I745" s="71">
         <v>7990</v>
       </c>
       <c r="J745" s="59" t="s">
@@ -39211,7 +39183,7 @@
       <c r="H746" t="s">
         <v>819</v>
       </c>
-      <c r="I746" s="74">
+      <c r="I746" s="71">
         <v>14990</v>
       </c>
       <c r="J746" s="59" t="s">
@@ -39240,7 +39212,7 @@
       <c r="H747" t="s">
         <v>819</v>
       </c>
-      <c r="I747" s="74">
+      <c r="I747" s="71">
         <v>19990</v>
       </c>
       <c r="J747" s="59" t="s">
@@ -39269,7 +39241,7 @@
       <c r="H748" t="s">
         <v>819</v>
       </c>
-      <c r="I748" s="74">
+      <c r="I748" s="71">
         <v>29990</v>
       </c>
       <c r="J748" s="59" t="s">
@@ -39298,7 +39270,7 @@
       <c r="H749" t="s">
         <v>819</v>
       </c>
-      <c r="I749" s="74">
+      <c r="I749" s="71">
         <v>39990</v>
       </c>
       <c r="J749" s="59" t="s">
@@ -40045,7 +40017,7 @@
       <c r="H785" t="s">
         <v>819</v>
       </c>
-      <c r="I785" s="74">
+      <c r="I785" s="71">
         <v>990</v>
       </c>
       <c r="J785" s="59" t="s">
@@ -40074,7 +40046,7 @@
       <c r="H786" t="s">
         <v>819</v>
       </c>
-      <c r="I786" s="74">
+      <c r="I786" s="71">
         <v>4990</v>
       </c>
       <c r="J786" s="59" t="s">
@@ -40103,7 +40075,7 @@
       <c r="H787" t="s">
         <v>819</v>
       </c>
-      <c r="I787" s="74">
+      <c r="I787" s="71">
         <v>7990</v>
       </c>
       <c r="J787" s="59" t="s">
@@ -40132,7 +40104,7 @@
       <c r="H788" t="s">
         <v>819</v>
       </c>
-      <c r="I788" s="74">
+      <c r="I788" s="71">
         <v>14990</v>
       </c>
       <c r="J788" s="59" t="s">
@@ -40161,7 +40133,7 @@
       <c r="H789" t="s">
         <v>819</v>
       </c>
-      <c r="I789" s="74">
+      <c r="I789" s="71">
         <v>19990</v>
       </c>
       <c r="J789" s="59" t="s">
@@ -40190,7 +40162,7 @@
       <c r="H790" t="s">
         <v>819</v>
       </c>
-      <c r="I790" s="74">
+      <c r="I790" s="71">
         <v>29990</v>
       </c>
       <c r="J790" s="59" t="s">
@@ -40219,7 +40191,7 @@
       <c r="H791" t="s">
         <v>819</v>
       </c>
-      <c r="I791" s="74">
+      <c r="I791" s="71">
         <v>39990</v>
       </c>
       <c r="J791" s="59" t="s">
@@ -40248,7 +40220,7 @@
       <c r="H792" t="s">
         <v>819</v>
       </c>
-      <c r="I792" s="74">
+      <c r="I792" s="71">
         <v>79990</v>
       </c>
       <c r="J792" s="59" t="s">
@@ -40277,7 +40249,7 @@
       <c r="H793" t="s">
         <v>819</v>
       </c>
-      <c r="I793" s="74">
+      <c r="I793" s="71">
         <v>4990</v>
       </c>
       <c r="J793" s="31" t="s">
@@ -40306,7 +40278,7 @@
       <c r="H794" t="s">
         <v>819</v>
       </c>
-      <c r="I794" s="74">
+      <c r="I794" s="71">
         <v>990</v>
       </c>
       <c r="J794" s="59" t="s">
@@ -40335,7 +40307,7 @@
       <c r="H795" t="s">
         <v>819</v>
       </c>
-      <c r="I795" s="74">
+      <c r="I795" s="71">
         <v>4990</v>
       </c>
       <c r="J795" s="59" t="s">
@@ -40364,7 +40336,7 @@
       <c r="H796" t="s">
         <v>819</v>
       </c>
-      <c r="I796" s="74">
+      <c r="I796" s="71">
         <v>7990</v>
       </c>
       <c r="J796" s="59" t="s">
@@ -40393,7 +40365,7 @@
       <c r="H797" t="s">
         <v>819</v>
       </c>
-      <c r="I797" s="74">
+      <c r="I797" s="71">
         <v>14990</v>
       </c>
       <c r="J797" s="59" t="s">
@@ -40422,7 +40394,7 @@
       <c r="H798" t="s">
         <v>819</v>
       </c>
-      <c r="I798" s="74">
+      <c r="I798" s="71">
         <v>19990</v>
       </c>
       <c r="J798" s="59" t="s">
@@ -40451,7 +40423,7 @@
       <c r="H799" t="s">
         <v>819</v>
       </c>
-      <c r="I799" s="74">
+      <c r="I799" s="71">
         <v>29990</v>
       </c>
       <c r="J799" s="59" t="s">
@@ -40480,7 +40452,7 @@
       <c r="H800" t="s">
         <v>819</v>
       </c>
-      <c r="I800" s="74">
+      <c r="I800" s="71">
         <v>39990</v>
       </c>
       <c r="J800" s="59" t="s">
@@ -40518,7 +40490,7 @@
     </row>
   </sheetData>
   <autoFilter ref="B1:B751" xr:uid="{00000000-0001-0000-0400-000000000000}"/>
-  <phoneticPr fontId="25" type="noConversion"/>
+  <phoneticPr fontId="21" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
@@ -40634,7 +40606,7 @@
         <v>2</v>
       </c>
       <c r="C10" s="33" t="s">
-        <v>1763</v>
+        <v>1764</v>
       </c>
     </row>
     <row r="11" spans="1:3">
@@ -40645,11 +40617,11 @@
         <v>3</v>
       </c>
       <c r="C11" s="33" t="s">
-        <v>1763</v>
+        <v>1764</v>
       </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="25" type="noConversion"/>
+  <phoneticPr fontId="21" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -42815,7 +42787,7 @@
       <c r="E106" s="31">
         <v>7500000</v>
       </c>
-      <c r="F106" s="90" t="s">
+      <c r="F106" s="84" t="s">
         <v>1710</v>
       </c>
       <c r="G106">
@@ -42838,7 +42810,7 @@
       <c r="E107" s="31">
         <v>1500000</v>
       </c>
-      <c r="F107" s="90" t="s">
+      <c r="F107" s="84" t="s">
         <v>1709</v>
       </c>
       <c r="G107" s="13">
@@ -42861,7 +42833,7 @@
       <c r="E108" s="31">
         <v>7500000</v>
       </c>
-      <c r="F108" s="90" t="s">
+      <c r="F108" s="84" t="s">
         <v>1710</v>
       </c>
       <c r="G108" s="13">
@@ -42884,7 +42856,7 @@
       <c r="E109" s="31">
         <v>12000000</v>
       </c>
-      <c r="F109" s="90" t="s">
+      <c r="F109" s="84" t="s">
         <v>1711</v>
       </c>
       <c r="G109" s="13">
@@ -42907,7 +42879,7 @@
       <c r="E110" s="31">
         <v>23000000</v>
       </c>
-      <c r="F110" s="90" t="s">
+      <c r="F110" s="84" t="s">
         <v>1712</v>
       </c>
       <c r="G110" s="13">
@@ -42930,7 +42902,7 @@
       <c r="E111" s="31">
         <v>30000000</v>
       </c>
-      <c r="F111" s="90" t="s">
+      <c r="F111" s="84" t="s">
         <v>1713</v>
       </c>
       <c r="G111" s="13">
@@ -42953,7 +42925,7 @@
       <c r="E112" s="31">
         <v>45000000</v>
       </c>
-      <c r="F112" s="90" t="s">
+      <c r="F112" s="84" t="s">
         <v>1714</v>
       </c>
       <c r="G112" s="13">
@@ -42976,7 +42948,7 @@
       <c r="E113" s="31">
         <v>60000000</v>
       </c>
-      <c r="F113" s="90" t="s">
+      <c r="F113" s="84" t="s">
         <v>1715</v>
       </c>
       <c r="G113" s="13">
@@ -42999,7 +42971,7 @@
       <c r="E114" s="31">
         <v>119000000</v>
       </c>
-      <c r="F114" s="90" t="s">
+      <c r="F114" s="84" t="s">
         <v>1716</v>
       </c>
       <c r="G114" s="13">
@@ -43022,7 +42994,7 @@
       <c r="E115" s="31">
         <v>1500000</v>
       </c>
-      <c r="F115" s="90" t="s">
+      <c r="F115" s="84" t="s">
         <v>1709</v>
       </c>
       <c r="G115" s="13">
@@ -43045,7 +43017,7 @@
       <c r="E116" s="31">
         <v>7500000</v>
       </c>
-      <c r="F116" s="90" t="s">
+      <c r="F116" s="84" t="s">
         <v>1710</v>
       </c>
       <c r="G116" s="13">
@@ -43068,7 +43040,7 @@
       <c r="E117" s="31">
         <v>12000000</v>
       </c>
-      <c r="F117" s="90" t="s">
+      <c r="F117" s="84" t="s">
         <v>1711</v>
       </c>
       <c r="G117" s="13">
@@ -43091,7 +43063,7 @@
       <c r="E118" s="31">
         <v>23000000</v>
       </c>
-      <c r="F118" s="90" t="s">
+      <c r="F118" s="84" t="s">
         <v>1712</v>
       </c>
       <c r="G118" s="13">
@@ -43114,7 +43086,7 @@
       <c r="E119" s="31">
         <v>30000000</v>
       </c>
-      <c r="F119" s="90" t="s">
+      <c r="F119" s="84" t="s">
         <v>1713</v>
       </c>
       <c r="G119" s="13">
@@ -43137,7 +43109,7 @@
       <c r="E120" s="31">
         <v>45000000</v>
       </c>
-      <c r="F120" s="90" t="s">
+      <c r="F120" s="84" t="s">
         <v>1714</v>
       </c>
       <c r="G120" s="13">
@@ -43160,7 +43132,7 @@
       <c r="E121" s="31">
         <v>60000000</v>
       </c>
-      <c r="F121" s="90" t="s">
+      <c r="F121" s="84" t="s">
         <v>1715</v>
       </c>
       <c r="G121" s="13">
@@ -43183,7 +43155,7 @@
       <c r="E122" s="31">
         <v>119000000</v>
       </c>
-      <c r="F122" s="90" t="s">
+      <c r="F122" s="84" t="s">
         <v>1716</v>
       </c>
       <c r="G122" s="13">
@@ -43531,7 +43503,7 @@
       </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="25" type="noConversion"/>
+  <phoneticPr fontId="21" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
@@ -43925,10 +43897,10 @@
       <c r="H12" s="67">
         <v>92</v>
       </c>
-      <c r="I12" s="72" t="s">
+      <c r="I12" s="92" t="s">
         <v>1461</v>
       </c>
-      <c r="J12" s="69" t="s">
+      <c r="J12" s="93" t="s">
         <v>1456</v>
       </c>
     </row>
@@ -43939,19 +43911,19 @@
       <c r="B13" s="6">
         <v>300</v>
       </c>
-      <c r="C13" s="86" t="s">
+      <c r="C13" s="82" t="s">
         <v>1701</v>
       </c>
       <c r="D13" s="6" t="s">
         <v>1482</v>
       </c>
-      <c r="E13" s="87" t="s">
+      <c r="E13" s="83" t="s">
         <v>1702</v>
       </c>
       <c r="F13" s="6" t="s">
         <v>1483</v>
       </c>
-      <c r="G13" s="87" t="s">
+      <c r="G13" s="83" t="s">
         <v>1703</v>
       </c>
       <c r="H13" s="6">
@@ -43971,19 +43943,19 @@
       <c r="B14" s="6">
         <v>301</v>
       </c>
-      <c r="C14" s="86" t="s">
+      <c r="C14" s="82" t="s">
         <v>1701</v>
       </c>
       <c r="D14" s="6" t="s">
         <v>1482</v>
       </c>
-      <c r="E14" s="87" t="s">
+      <c r="E14" s="83" t="s">
         <v>1702</v>
       </c>
       <c r="F14" s="6" t="s">
         <v>1483</v>
       </c>
-      <c r="G14" s="87" t="s">
+      <c r="G14" s="83" t="s">
         <v>1703</v>
       </c>
       <c r="H14" s="6">
@@ -44003,119 +43975,121 @@
       <c r="B15" s="6">
         <v>302</v>
       </c>
-      <c r="C15" s="86" t="s">
+      <c r="C15" s="82" t="s">
         <v>1701</v>
       </c>
       <c r="D15" s="6" t="s">
         <v>1482</v>
       </c>
-      <c r="E15" s="87" t="s">
+      <c r="E15" s="83" t="s">
         <v>1702</v>
       </c>
       <c r="F15" s="6" t="s">
         <v>1164</v>
       </c>
-      <c r="G15" s="87" t="s">
+      <c r="G15" s="83" t="s">
         <v>1703</v>
       </c>
-      <c r="H15" s="6"/>
+      <c r="H15" s="61" t="s">
+        <v>1763</v>
+      </c>
       <c r="I15" s="10" t="s">
         <v>1095</v>
       </c>
     </row>
     <row r="16" spans="1:10" s="58" customFormat="1">
-      <c r="A16" s="79" t="s">
+      <c r="A16" s="76" t="s">
         <v>1691</v>
       </c>
-      <c r="B16" s="70">
+      <c r="B16" s="68">
         <v>303</v>
       </c>
-      <c r="C16" s="86" t="s">
+      <c r="C16" s="82" t="s">
         <v>1701</v>
       </c>
-      <c r="D16" s="88" t="s">
+      <c r="D16" s="94" t="s">
         <v>1457</v>
       </c>
-      <c r="E16" s="87" t="s">
+      <c r="E16" s="83" t="s">
         <v>1702</v>
       </c>
-      <c r="F16" s="88" t="s">
+      <c r="F16" s="94" t="s">
         <v>1164</v>
       </c>
-      <c r="G16" s="87" t="s">
+      <c r="G16" s="83" t="s">
         <v>1703</v>
       </c>
-      <c r="H16" s="71">
+      <c r="H16" s="69">
         <v>93</v>
       </c>
-      <c r="I16" s="68" t="s">
+      <c r="I16" s="92" t="s">
         <v>1095</v>
       </c>
-      <c r="J16" s="85" t="s">
+      <c r="J16" s="93" t="s">
         <v>1694</v>
       </c>
     </row>
     <row r="17" spans="1:10" s="49" customFormat="1">
-      <c r="A17" s="83" t="s">
+      <c r="A17" s="80" t="s">
         <v>1688</v>
       </c>
-      <c r="B17" s="80" t="s">
+      <c r="B17" s="77" t="s">
         <v>1687</v>
       </c>
-      <c r="C17" s="86" t="s">
+      <c r="C17" s="82" t="s">
         <v>1701</v>
       </c>
-      <c r="D17" s="81" t="s">
+      <c r="D17" s="78" t="s">
         <v>1482</v>
       </c>
-      <c r="E17" s="87" t="s">
+      <c r="E17" s="83" t="s">
         <v>1702</v>
       </c>
-      <c r="F17" s="81" t="s">
+      <c r="F17" s="78" t="s">
         <v>1483</v>
       </c>
-      <c r="G17" s="87" t="s">
+      <c r="G17" s="83" t="s">
         <v>1703</v>
       </c>
-      <c r="H17" s="80" t="s">
+      <c r="H17" s="77" t="s">
         <v>1689</v>
       </c>
-      <c r="I17" s="82" t="s">
+      <c r="I17" s="79" t="s">
         <v>1095</v>
       </c>
       <c r="J17" s="50" t="s">
         <v>1695</v>
       </c>
     </row>
-    <row r="18" spans="1:10" s="96" customFormat="1">
-      <c r="A18" s="92" t="s">
+    <row r="18" spans="1:10" s="90" customFormat="1">
+      <c r="A18" s="86" t="s">
         <v>1752</v>
       </c>
-      <c r="B18" s="93" t="s">
+      <c r="B18" s="87" t="s">
         <v>1753</v>
       </c>
-      <c r="C18" s="94" t="s">
+      <c r="C18" s="88" t="s">
         <v>1701</v>
       </c>
-      <c r="D18" s="93" t="s">
+      <c r="D18" s="87" t="s">
         <v>1457</v>
       </c>
-      <c r="E18" s="95" t="s">
+      <c r="E18" s="89" t="s">
         <v>1702</v>
       </c>
-      <c r="F18" s="93" t="s">
+      <c r="F18" s="87" t="s">
         <v>1164</v>
       </c>
-      <c r="G18" s="95" t="s">
+      <c r="G18" s="89" t="s">
         <v>1703</v>
       </c>
-      <c r="H18" s="91">
+      <c r="H18" s="85">
         <v>96</v>
       </c>
-      <c r="I18" s="91" t="s">
+      <c r="I18" s="85" t="s">
         <v>1095</v>
       </c>
-      <c r="J18" s="96" t="s">
+      <c r="J18" s="90" t="s">
         <v>1695</v>
       </c>
     </row>
@@ -44126,19 +44100,19 @@
       <c r="B19" s="7">
         <v>400</v>
       </c>
-      <c r="C19" s="86" t="s">
+      <c r="C19" s="82" t="s">
         <v>1704</v>
       </c>
       <c r="D19" s="7" t="s">
         <v>1482</v>
       </c>
-      <c r="E19" s="87" t="s">
+      <c r="E19" s="83" t="s">
         <v>1702</v>
       </c>
       <c r="F19" s="7" t="s">
         <v>1483</v>
       </c>
-      <c r="G19" s="87" t="s">
+      <c r="G19" s="83" t="s">
         <v>1703</v>
       </c>
       <c r="H19" s="7">
@@ -44158,19 +44132,19 @@
       <c r="B20" s="7">
         <v>401</v>
       </c>
-      <c r="C20" s="86" t="s">
+      <c r="C20" s="82" t="s">
         <v>1704</v>
       </c>
       <c r="D20" s="7" t="s">
         <v>1482</v>
       </c>
-      <c r="E20" s="87" t="s">
+      <c r="E20" s="83" t="s">
         <v>1702</v>
       </c>
       <c r="F20" s="7" t="s">
         <v>1483</v>
       </c>
-      <c r="G20" s="87" t="s">
+      <c r="G20" s="83" t="s">
         <v>1703</v>
       </c>
       <c r="H20" s="7">
@@ -44190,22 +44164,24 @@
       <c r="B21" s="7">
         <v>402</v>
       </c>
-      <c r="C21" s="86" t="s">
+      <c r="C21" s="82" t="s">
         <v>1704</v>
       </c>
       <c r="D21" s="7" t="s">
         <v>1482</v>
       </c>
-      <c r="E21" s="87" t="s">
+      <c r="E21" s="83" t="s">
         <v>1702</v>
       </c>
       <c r="F21" s="7" t="s">
         <v>1164</v>
       </c>
-      <c r="G21" s="87" t="s">
+      <c r="G21" s="83" t="s">
         <v>1703</v>
       </c>
-      <c r="H21" s="7"/>
+      <c r="H21" s="7">
+        <v>94</v>
+      </c>
       <c r="I21" s="10" t="s">
         <v>1092</v>
       </c>
@@ -44238,31 +44214,31 @@
       </c>
     </row>
     <row r="23" spans="1:10" s="58" customFormat="1">
-      <c r="A23" s="89" t="s">
+      <c r="A23" s="95" t="s">
         <v>1458</v>
       </c>
-      <c r="B23" s="70">
+      <c r="B23" s="68">
         <v>404</v>
       </c>
-      <c r="C23" s="86" t="s">
+      <c r="C23" s="82" t="s">
         <v>1704</v>
       </c>
-      <c r="D23" s="88" t="s">
+      <c r="D23" s="94" t="s">
         <v>1457</v>
       </c>
-      <c r="E23" s="87" t="s">
+      <c r="E23" s="83" t="s">
         <v>1702</v>
       </c>
-      <c r="F23" s="88" t="s">
+      <c r="F23" s="94" t="s">
         <v>1164</v>
       </c>
-      <c r="G23" s="87" t="s">
+      <c r="G23" s="83" t="s">
         <v>1703</v>
       </c>
-      <c r="H23" s="71">
+      <c r="H23" s="69">
         <v>93</v>
       </c>
-      <c r="I23" s="68" t="s">
+      <c r="I23" s="92" t="s">
         <v>1092</v>
       </c>
       <c r="J23" s="66" t="s">
@@ -44273,63 +44249,63 @@
       <c r="A24" s="50" t="s">
         <v>1690</v>
       </c>
-      <c r="B24" s="82">
+      <c r="B24" s="79">
         <v>405</v>
       </c>
-      <c r="C24" s="86" t="s">
+      <c r="C24" s="82" t="s">
         <v>1704</v>
       </c>
-      <c r="D24" s="82" t="s">
+      <c r="D24" s="79" t="s">
         <v>1482</v>
       </c>
-      <c r="E24" s="87" t="s">
+      <c r="E24" s="83" t="s">
         <v>1702</v>
       </c>
-      <c r="F24" s="82" t="s">
+      <c r="F24" s="79" t="s">
         <v>1164</v>
       </c>
-      <c r="G24" s="87" t="s">
+      <c r="G24" s="83" t="s">
         <v>1703</v>
       </c>
-      <c r="H24" s="82">
+      <c r="H24" s="79">
         <v>73</v>
       </c>
-      <c r="I24" s="82" t="s">
+      <c r="I24" s="79" t="s">
         <v>1092</v>
       </c>
       <c r="J24" s="50" t="s">
         <v>1695</v>
       </c>
     </row>
-    <row r="25" spans="1:10" s="96" customFormat="1">
-      <c r="A25" s="96" t="s">
+    <row r="25" spans="1:10" s="90" customFormat="1">
+      <c r="A25" s="90" t="s">
         <v>1751</v>
       </c>
-      <c r="B25" s="91">
+      <c r="B25" s="85">
         <v>406</v>
       </c>
-      <c r="C25" s="94" t="s">
+      <c r="C25" s="88" t="s">
         <v>1704</v>
       </c>
-      <c r="D25" s="91" t="s">
+      <c r="D25" s="85" t="s">
         <v>1457</v>
       </c>
-      <c r="E25" s="95" t="s">
+      <c r="E25" s="89" t="s">
         <v>1702</v>
       </c>
-      <c r="F25" s="91" t="s">
+      <c r="F25" s="85" t="s">
         <v>1164</v>
       </c>
-      <c r="G25" s="95" t="s">
+      <c r="G25" s="89" t="s">
         <v>1703</v>
       </c>
-      <c r="H25" s="91">
+      <c r="H25" s="85">
         <v>96</v>
       </c>
-      <c r="I25" s="91" t="s">
+      <c r="I25" s="85" t="s">
         <v>1092</v>
       </c>
-      <c r="J25" s="96" t="s">
+      <c r="J25" s="90" t="s">
         <v>1695</v>
       </c>
     </row>
@@ -44340,19 +44316,19 @@
       <c r="B26" s="5">
         <v>500</v>
       </c>
-      <c r="C26" s="86" t="s">
+      <c r="C26" s="82" t="s">
         <v>1705</v>
       </c>
       <c r="D26" s="6" t="s">
         <v>1482</v>
       </c>
-      <c r="E26" s="86" t="s">
+      <c r="E26" s="82" t="s">
         <v>1706</v>
       </c>
       <c r="F26" s="6" t="s">
         <v>1483</v>
       </c>
-      <c r="G26" s="86" t="s">
+      <c r="G26" s="82" t="s">
         <v>1707</v>
       </c>
       <c r="H26" s="7">
@@ -44372,19 +44348,19 @@
       <c r="B27" s="5">
         <v>501</v>
       </c>
-      <c r="C27" s="86" t="s">
+      <c r="C27" s="82" t="s">
         <v>1705</v>
       </c>
       <c r="D27" s="6" t="s">
         <v>1482</v>
       </c>
-      <c r="E27" s="86" t="s">
+      <c r="E27" s="82" t="s">
         <v>1706</v>
       </c>
       <c r="F27" s="6" t="s">
         <v>1483</v>
       </c>
-      <c r="G27" s="86" t="s">
+      <c r="G27" s="82" t="s">
         <v>1707</v>
       </c>
       <c r="H27" s="7">
@@ -44404,22 +44380,24 @@
       <c r="B28" s="5">
         <v>502</v>
       </c>
-      <c r="C28" s="86" t="s">
+      <c r="C28" s="82" t="s">
         <v>1705</v>
       </c>
       <c r="D28" s="6" t="s">
         <v>1482</v>
       </c>
-      <c r="E28" s="86" t="s">
+      <c r="E28" s="82" t="s">
         <v>1706</v>
       </c>
       <c r="F28" s="6" t="s">
         <v>1164</v>
       </c>
-      <c r="G28" s="86" t="s">
+      <c r="G28" s="82" t="s">
         <v>1707</v>
       </c>
-      <c r="H28" s="7"/>
+      <c r="H28" s="7">
+        <v>67</v>
+      </c>
       <c r="I28" s="7" t="s">
         <v>1129</v>
       </c>
@@ -44428,63 +44406,63 @@
       <c r="A29" s="50" t="s">
         <v>1693</v>
       </c>
-      <c r="B29" s="84">
+      <c r="B29" s="81">
         <v>503</v>
       </c>
-      <c r="C29" s="86" t="s">
+      <c r="C29" s="82" t="s">
         <v>1705</v>
       </c>
-      <c r="D29" s="81" t="s">
+      <c r="D29" s="78" t="s">
         <v>1482</v>
       </c>
-      <c r="E29" s="86" t="s">
+      <c r="E29" s="82" t="s">
         <v>1706</v>
       </c>
-      <c r="F29" s="81" t="s">
+      <c r="F29" s="78" t="s">
         <v>1164</v>
       </c>
-      <c r="G29" s="86" t="s">
+      <c r="G29" s="82" t="s">
         <v>1707</v>
       </c>
-      <c r="H29" s="91">
+      <c r="H29" s="85">
         <v>95</v>
       </c>
-      <c r="I29" s="82" t="s">
+      <c r="I29" s="79" t="s">
         <v>1129</v>
       </c>
       <c r="J29" s="50" t="s">
         <v>1695</v>
       </c>
     </row>
-    <row r="30" spans="1:10" s="96" customFormat="1">
-      <c r="A30" s="96" t="s">
+    <row r="30" spans="1:10" s="90" customFormat="1">
+      <c r="A30" s="90" t="s">
         <v>1750</v>
       </c>
-      <c r="B30" s="97">
+      <c r="B30" s="91">
         <v>504</v>
       </c>
-      <c r="C30" s="94" t="s">
+      <c r="C30" s="88" t="s">
         <v>1705</v>
       </c>
-      <c r="D30" s="93" t="s">
+      <c r="D30" s="87" t="s">
         <v>1457</v>
       </c>
-      <c r="E30" s="94" t="s">
+      <c r="E30" s="88" t="s">
         <v>1706</v>
       </c>
-      <c r="F30" s="93" t="s">
+      <c r="F30" s="87" t="s">
         <v>1164</v>
       </c>
-      <c r="G30" s="94" t="s">
+      <c r="G30" s="88" t="s">
         <v>1707</v>
       </c>
-      <c r="H30" s="91">
+      <c r="H30" s="85">
         <v>97</v>
       </c>
-      <c r="I30" s="91" t="s">
+      <c r="I30" s="85" t="s">
         <v>1129</v>
       </c>
-      <c r="J30" s="96" t="s">
+      <c r="J30" s="90" t="s">
         <v>1695</v>
       </c>
     </row>
@@ -44497,7 +44475,7 @@
       <c r="I31" s="7"/>
     </row>
   </sheetData>
-  <phoneticPr fontId="25" type="noConversion"/>
+  <phoneticPr fontId="21" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
   <drawing r:id="rId2"/>
@@ -44630,7 +44608,7 @@
       </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="25" type="noConversion"/>
+  <phoneticPr fontId="21" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
 </worksheet>

--- a/source/bin/excel/mall.xlsx
+++ b/source/bin/excel/mall.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="30026"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Work\Git\liqi-excel\data\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="H:\quehun-cehua\liqi-excel\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{47F64069-8C3A-43BA-81F1-4E1924D7722C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8D3882E6-F76C-4914-B29F-D8D6D7C7DC7F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="28110" windowHeight="16440" firstSheet="4" activeTab="8" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="export" sheetId="2" r:id="rId1"/>
@@ -72,7 +72,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4905" uniqueCount="1765">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4907" uniqueCount="1766">
   <si>
     <t>sheet</t>
   </si>
@@ -9212,6 +9212,10 @@
   </si>
   <si>
     <t>2026-04-22 08:00+08</t>
+    <phoneticPr fontId="21" type="noConversion"/>
+  </si>
+  <si>
+    <t>2026-08-19 11:00+08</t>
     <phoneticPr fontId="21" type="noConversion"/>
   </si>
 </sst>
@@ -40498,7 +40502,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{09055340-E681-4275-AA7E-F0060348C4B1}">
-  <dimension ref="A1:C11"/>
+  <dimension ref="A1:C12"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="12.25" customWidth="1"/>
@@ -40618,6 +40622,17 @@
       </c>
       <c r="C11" s="33" t="s">
         <v>1764</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3">
+      <c r="A12" s="33" t="s">
+        <v>1762</v>
+      </c>
+      <c r="B12">
+        <v>1</v>
+      </c>
+      <c r="C12" s="33" t="s">
+        <v>1765</v>
       </c>
     </row>
   </sheetData>
